--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -50,7 +50,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'PLANILLA GENERAL DE METRADOS'!$A$1:$L$322</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">RESUMEN!$A$1:$D$75</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">01.04.04.06.01</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA DE DILATACION E=1" CON TECNOPOR Y SELLADOR ELASTOMERICO</t>
+    <t xml:space="preserve">JUNTA DE DILATACION E=1" CON TECNOPOR Y SELLADOR ASFALTICO EN COLECTOR</t>
   </si>
   <si>
     <t xml:space="preserve">01.04.04.06.02</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA E=1" CON TECNOPOR ENTRE COLECTOR Y PISO ADYACENTE</t>
+    <t xml:space="preserve">JUNTA E=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">ITEM</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">COLECTOR PLUVIAL FRONTAL - JUNTAS Y EMPALMES DE CUNETAS</t>
   </si>
   <si>
-    <t xml:space="preserve">Lamina DP-01 (nota 5), DP-03 y DP-06C. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor + sellador elastomerico). Junta de tecnopor de 1" entre el colector y el cimiento del cerco, y entre el borde de la losa y el piso adyacente. Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
+    <t xml:space="preserve">Lamina DP-01 (nota 5), DP-03 y DP-06C. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor de 1" en todo el perimetro + sellador asfaltico RC-250 con arena de 1" x 2" en la cara expuesta, EG-2013 secc. 510.02 c y 438.02 e 3). Junta de tecnopor de 1" entre el colector y el cimiento del cerco, y entre el borde de la losa y el piso adyacente. Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
   </si>
   <si>
     <t xml:space="preserve">PROGRESIVA / DETALLE</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">PARCIAL (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA DE DILATACION e=1" CON TECNOPOR Y SELLADOR ELASTOMERICO (perimetro = 2 x ancho exterior + 2 x (e fondo + h max + e losa))</t>
+    <t xml:space="preserve">JUNTA DE DILATACION e=1" CON TECNOPOR Y SELLADOR ASFALTICO EN COLECTOR (perimetro = 2 x ancho exterior + 2 x (e fondo + h max + e losa))</t>
   </si>
   <si>
     <t xml:space="preserve">Juntas de dilatacion cada 4.00 m entre 0+004.00 y 0+068.00</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">TOTAL JUNTA DE DILATACION (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA DE TECNOPOR e=1" ENTRE COLECTOR, CERCO Y PISO ADYACENTE</t>
+    <t xml:space="preserve">JUNTA e=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">Contra el cimiento del cerco (tramo pegado al cerco, 0+000 a primer quiebre)</t>
@@ -3479,16 +3479,16 @@
     <t xml:space="preserve">glb</t>
   </si>
   <si>
-    <t xml:space="preserve">01.04.04.06.01 JUNTA DE DILATACION e=1" CON SELLADOR</t>
+    <t xml:space="preserve">01.04.04.06.01 JUNTA DE DILATACION e=1" CON TECNOPOR Y SELLADOR ASFALTICO</t>
   </si>
   <si>
     <t xml:space="preserve">Tecnopor 1"</t>
   </si>
   <si>
-    <t xml:space="preserve">Sello elastomerico de poliuretano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01.04.04.06.02 JUNTA DE TECNOPOR e=1"</t>
+    <t xml:space="preserve">Sellador asfaltico: asfalto liquido RC-250 + arena gruesa (sello de 1" x 2")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.02 JUNTA e=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - TAPA DE REGISTRO 0.68 x 0.68 C/MARCO Y CONTRAMARCO</t>
@@ -26828,15 +26828,17 @@
       <c r="E69" s="295" t="s">
         <v>987</v>
       </c>
-      <c r="F69" s="285" t="s">
-        <v>50</v>
+      <c r="F69" s="285" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
       </c>
       <c r="G69" s="284" t="n">
-        <v>0.35</v>
+        <v>0.0013</v>
       </c>
       <c r="H69" s="296" t="n">
         <f aca="false">G69*$D$68</f>
-        <v>35.224</v>
+        <v>0.130832</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -929,7 +929,7 @@
     <t xml:space="preserve">01.04.04.06.02</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA E=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
+    <t xml:space="preserve">JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">ITEM</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">TOTAL JUNTA DE DILATACION (m)</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNTA e=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
+    <t xml:space="preserve">JUNTA e=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">Contra el cimiento del cerco (tramo pegado al cerco, 0+000 a primer quiebre)</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">Sellador asfaltico: asfalto liquido RC-250 + arena gruesa (sello de 1" x 2")</t>
   </si>
   <si>
-    <t xml:space="preserve">01.04.04.06.02 JUNTA e=1" CON TECNOPOR ENTRE COLECTOR Y CERCO PERIMETRICO</t>
+    <t xml:space="preserve">01.04.04.06.02 JUNTA e=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO</t>
   </si>
   <si>
     <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - TAPA DE REGISTRO 0.68 x 0.68 C/MARCO Y CONTRAMARCO</t>
@@ -25469,7 +25469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -26924,6 +26924,46 @@
       <c r="H73" s="296" t="n">
         <f aca="false">G73*$D$72</f>
         <v>21.0979</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="21"/>
+      <c r="B74" s="304"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="295" t="s">
+        <v>987</v>
+      </c>
+      <c r="F74" s="285" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="G74" s="284" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H74" s="296" t="n">
+        <f aca="false">G74*$D$72</f>
+        <v>0.2742727</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="21"/>
+      <c r="B75" s="304"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="F75" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="G75" s="284" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H75" s="296" t="n">
+        <f aca="false">G75*$D$72</f>
+        <v>10.548950000000001</v>
       </c>
     </row>
   </sheetData>

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -510,7 +510,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1222">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4074,6 +4074,120 @@
   </si>
   <si>
     <t xml:space="preserve">Pintura en angulos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perimetro del contramarco L 1 1/2"x1 1/2"x1/8" (4 x 0.70)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso del angulo L 1 1/2"x1 1/2"x1/8" (contramarco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peso del angulo L 1 1/2"x1 1/2"x1/8" (marco de tapa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo pintado del angulo 1 1/2"x1 1/2" del contramarco (4 caras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo pintado del angulo 1 1/2"x1 1/2" del marco de tapa (4 caras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (ubicacion) y DP-06B (detalle): contramarco L 1 1/2"x1 1/2"x1/8" anclado a la losa, marco L 1 1/2"x1 1/2"x1/8" soldado a la tapa, tapa de concreto armado 0.68 x 0.68 x 0.08 con parrilla 3/8" @0.10 y asas; borde engrosado 0.15 x 0.10 alrededor de la abertura de 0.70 x 0.70.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRAMARCO METALICO L 1 1/2"x1 1/2"x1/8" CON ANCLAJES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registros x (2.80 x 1.83 + 2.72 x 1.83)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registros x (2.80 x 0.152 + 2.72 x 0.152)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contramarco: angulo L 1 1/2"x1 1/2"x1/8", 4 x 0.70 = 2.80 m x 1.83 kg/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anticorrosivo y esmalte en angulos: 2.80 x 0.152 + 2.72 x 0.152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada tapa incluye: contramarco L 1 1/2"x1 1/2"x1/8" con 8 anclajes, marco L 1 1/2"x1 1/2"x1/8", tapa de concreto armado 0.68 x 0.68 x 0.08 con parrilla y asas, refuerzo de borde y pintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angulo L 1 1/2"x1 1/2"x1/8" (incluye corte y soldadura)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lija para fierro N° 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thinner acrilico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contramarco metalico L 1 1/2"x1 1/2"x1/8" con anclajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80 x 1.83 + 2.72 x 1.83 = 10.10 kg por tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80 x 0.152 + 2.72 x 0.152 = 0.84 m2 por tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contramarco 4 x 0.70 = 2.80 m x 1.83 kg/m; 5 % de desperdicio (COLECTOR INSUMOS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS: 1 pliego cada 4 m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS: 15 % del volumen de pintura (dilucion y limpieza)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: barra de 6 m (10.98 kg) S/ 39.90 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: caja de 5 kg S/ 109.90 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento Pacasmayo tipo I 42.5 kg: S/ 36.50 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregados Tarapoto (Morales): S/ 48.00 el m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por cotizar en Tarapoto: no hay precio publicado de la piedra de 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMAPA San Martin: tarifa comercial de 30 m3 a mas, agua 6.80 + alcantarillado 1.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maderas del Norte: S/ 5.20 el p2 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru, Aceros Arequipa: 1/2" x 9 m S/ 36.50 y 3/8" x 9 m S/ 20.35 con IGV (ponderado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: rollo de 10 kg S/ 59.90 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promart: anticorrosivo Vencedor 1 gl S/ 53.00 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promart: esmalte sintetico CPP 1 gl S/ 57.00 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: lija para fierro 3M grano 80 S/ 2.50 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: thinner acrilico TOPEX 3.5 L S/ 38.90 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konstrutecnia: S/ 15.00 la hora-maquina con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konstrutecnia: S/ 13.00 la hora-maquina con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por cotizar en Tarapoto: no hay tarifa publicada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisis de la partida de Delphin 01.04.04.06.05.01 TAPA DE REGISTRO 0.68x0.68 C/MARCO Y CONTRAMARCO, partida 01.04.04.05.01 del metrado; componentes desagregados en la hoja DESAGREGADO TAPA REGISTRO. Cantidad por tapa = metrado del componente / numero de tapas. Ratios de insumos tomados de la hoja COLECTOR INSUMOS. Celda amarilla = dato (ratio o precio); verde = formula. Precios sin IGV obtenidos de precios publicados (octubre 2026), con su fuente en la columna H; los marcados "por cotizar" deben confirmarse en Tarapoto.</t>
   </si>
 </sst>
 </file>
@@ -11168,7 +11282,7 @@
         <v>27</v>
       </c>
       <c r="B36" s="149" t="s">
-        <v>596</v>
+        <v>1184</v>
       </c>
       <c r="C36" s="284" t="n">
         <v>2.8</v>
@@ -11202,10 +11316,10 @@
         <v>29</v>
       </c>
       <c r="B38" s="149" t="s">
-        <v>598</v>
+        <v>1185</v>
       </c>
       <c r="C38" s="284" t="n">
-        <v>3.63</v>
+        <v>1.83</v>
       </c>
       <c r="D38" s="285" t="s">
         <v>515</v>
@@ -11219,7 +11333,7 @@
         <v>30</v>
       </c>
       <c r="B39" s="149" t="s">
-        <v>600</v>
+        <v>1186</v>
       </c>
       <c r="C39" s="284" t="n">
         <v>1.83</v>
@@ -11236,16 +11350,16 @@
         <v>31</v>
       </c>
       <c r="B40" s="149" t="s">
-        <v>601</v>
+        <v>1187</v>
       </c>
       <c r="C40" s="284" t="n">
-        <v>0.203</v>
+        <v>0.152</v>
       </c>
       <c r="D40" s="285" t="s">
         <v>602</v>
       </c>
       <c r="E40" s="286" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11253,7 +11367,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="149" t="s">
-        <v>604</v>
+        <v>1188</v>
       </c>
       <c r="C41" s="284" t="n">
         <v>0.152</v>
@@ -18655,7 +18769,7 @@
       <c r="J133" s="36"/>
       <c r="K133" s="42" t="n">
         <f aca="false">+'PLANILLA TAPAS REGISTRO INTERNO'!J9</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="L133" s="43" t="s">
         <v>60</v>
@@ -18701,7 +18815,7 @@
       <c r="J135" s="36"/>
       <c r="K135" s="28" t="n">
         <f aca="false">+'METRADO LLORADEROS'!G20</f>
-        <v>157</v>
+        <v>157.0</v>
       </c>
       <c r="L135" s="43" t="s">
         <v>60</v>
@@ -19042,7 +19156,7 @@
       <c r="J150" s="24"/>
       <c r="K150" s="28" t="n">
         <f aca="false">+'METRADO CANALETAS'!G41</f>
-        <v>884</v>
+        <v>884.0</v>
       </c>
       <c r="L150" s="24" t="s">
         <v>60</v>
@@ -19065,7 +19179,7 @@
       <c r="J151" s="24"/>
       <c r="K151" s="28" t="n">
         <f aca="false">+'METRADO CANALETAS'!I41</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="L151" s="24" t="s">
         <v>60</v>
@@ -19088,7 +19202,7 @@
       <c r="J152" s="24"/>
       <c r="K152" s="28" t="n">
         <f aca="false">+'METRADO CANALETAS'!K41</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
       <c r="L152" s="24" t="s">
         <v>60</v>
@@ -19166,7 +19280,7 @@
       <c r="J156" s="37"/>
       <c r="K156" s="25" t="n">
         <f aca="false">+'METRADO  EN PISO (SUMIDERO)'!C12</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="L156" s="36" t="s">
         <v>60</v>
@@ -19189,7 +19303,7 @@
       <c r="J157" s="37"/>
       <c r="K157" s="25" t="n">
         <f aca="false">+'METRADO  EN PISO (SUMIDERO)'!D12</f>
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="L157" s="36" t="s">
         <v>60</v>
@@ -19212,7 +19326,7 @@
       <c r="J158" s="37"/>
       <c r="K158" s="25" t="n">
         <f aca="false">+'METRADO  EN PISO (SUMIDERO)'!F12</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L158" s="36" t="s">
         <v>60</v>
@@ -19267,7 +19381,7 @@
       <c r="J161" s="25"/>
       <c r="K161" s="25" t="n">
         <f aca="false">+'METRADO MONTANTES'!I43</f>
-        <v>162</v>
+        <v>162.0</v>
       </c>
       <c r="L161" s="24" t="s">
         <v>60</v>
@@ -19290,7 +19404,7 @@
       <c r="J162" s="25"/>
       <c r="K162" s="25" t="n">
         <f aca="false">+'METRADO MONTANTES'!O43</f>
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="L162" s="24" t="s">
         <v>60</v>
@@ -19313,7 +19427,7 @@
       <c r="J163" s="24"/>
       <c r="K163" s="25" t="n">
         <f aca="false">+'METRADO MONTANTES'!L43</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="L163" s="24" t="s">
         <v>60</v>
@@ -20575,7 +20689,7 @@
       <c r="I224" s="27"/>
       <c r="J224" s="27" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!P22</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="K224" s="27"/>
       <c r="L224" s="26"/>
@@ -22440,7 +22554,7 @@
       <c r="J313" s="25"/>
       <c r="K313" s="25" t="n">
         <f aca="false">SUM(J314:J316)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="L313" s="24" t="s">
         <v>60</v>
@@ -22462,7 +22576,7 @@
       <c r="I314" s="27"/>
       <c r="J314" s="27" t="n">
         <f aca="false">SUM('COLECTOR REGISTROS Y TAPAS'!E11:E17)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="K314" s="27"/>
       <c r="L314" s="26"/>
@@ -22483,7 +22597,7 @@
       <c r="I315" s="27"/>
       <c r="J315" s="27" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E10</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K315" s="27"/>
       <c r="L315" s="26"/>
@@ -22504,7 +22618,7 @@
       <c r="I316" s="27"/>
       <c r="J316" s="27" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K316" s="27"/>
       <c r="L316" s="26"/>
@@ -22512,7 +22626,7 @@
     <row r="317" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="26"/>
       <c r="B317" s="26" t="s">
-        <v>219</v>
+        <v>1195</v>
       </c>
       <c r="C317" s="27"/>
       <c r="D317" s="27"/>
@@ -22529,7 +22643,7 @@
       <c r="A318" s="26"/>
       <c r="B318" s="26" t="str">
         <f aca="false">"Totales para "&amp;K313&amp;" tapas: angulos "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E25,"0.00")&amp;" kg; concreto "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E27,"0.00")&amp;" m3; acero "&amp;TEXT('COLECTOR ACERO'!I41,"0.00")&amp;" kg; pintura "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E28,"0.00")&amp;" m2"</f>
-        <v>Totales para 10 tapas: angulos 151.42 kg; concreto 0.37 m3; acero 173.38 kg; pintura 9.82 m2</v>
+        <v>Totales para 10 tapas: angulos 101.02 kg; concreto 0.37 m3; acero 173.38 kg; pintura 8.39 m2</v>
       </c>
       <c r="C318" s="27"/>
       <c r="D318" s="27"/>
@@ -24566,7 +24680,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>864</v>
+        <v>1189</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -24783,7 +24897,7 @@
       <c r="D19" s="292"/>
       <c r="E19" s="300" t="n">
         <f aca="false">SUM(E10:E18)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="292"/>
     </row>
@@ -24822,7 +24936,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="149" t="s">
-        <v>893</v>
+        <v>1190</v>
       </c>
       <c r="C23" s="285" t="s">
         <v>60</v>
@@ -24832,7 +24946,7 @@
       </c>
       <c r="E23" s="296" t="n">
         <f aca="false">E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="286" t="s">
         <v>770</v>
@@ -24853,7 +24967,7 @@
       </c>
       <c r="E24" s="296" t="n">
         <f aca="false">E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F24" s="286" t="s">
         <v>770</v>
@@ -24870,11 +24984,11 @@
         <v>50</v>
       </c>
       <c r="D25" s="283" t="s">
-        <v>898</v>
+        <v>1191</v>
       </c>
       <c r="E25" s="296" t="n">
         <f aca="false">E19*('COLECTOR PARAMETROS'!$C$36*'COLECTOR PARAMETROS'!$C$38+'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$39)</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="F25" s="286" t="s">
         <v>899</v>
@@ -24895,7 +25009,7 @@
       </c>
       <c r="E26" s="296" t="n">
         <f aca="false">E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="286" t="s">
         <v>770</v>
@@ -24933,11 +25047,11 @@
         <v>168</v>
       </c>
       <c r="D28" s="283" t="s">
-        <v>904</v>
+        <v>1192</v>
       </c>
       <c r="E28" s="296" t="n">
         <f aca="false">E19*('COLECTOR PARAMETROS'!$C$36*'COLECTOR PARAMETROS'!$C$40+'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$41)</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="F28" s="286" t="s">
         <v>905</v>
@@ -25469,7 +25583,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -26634,10 +26748,10 @@
       </c>
       <c r="D60" s="290" t="n">
         <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="E60" s="295" t="s">
-        <v>977</v>
+        <v>1196</v>
       </c>
       <c r="F60" s="285" t="s">
         <v>50</v>
@@ -26647,7 +26761,7 @@
       </c>
       <c r="H60" s="296" t="n">
         <f aca="false">G60*$D$60</f>
-        <v>158.9868</v>
+        <v>106.0668</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26666,7 +26780,7 @@
       </c>
       <c r="H61" s="296" t="n">
         <f aca="false">G61*$D$60</f>
-        <v>4.54248</v>
+        <v>3.03048</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26685,7 +26799,7 @@
       </c>
       <c r="H62" s="296" t="n">
         <f aca="false">G62*$D$60</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26704,7 +26818,7 @@
       </c>
       <c r="H63" s="296" t="n">
         <f aca="false">G63*$D$60</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26719,7 +26833,7 @@
       </c>
       <c r="D64" s="290" t="n">
         <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="E64" s="295" t="s">
         <v>980</v>
@@ -26732,7 +26846,7 @@
       </c>
       <c r="H64" s="296" t="n">
         <f aca="false">G64*$D$64</f>
-        <v>0.785472</v>
+        <v>0.671232</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26751,7 +26865,7 @@
       </c>
       <c r="H65" s="296" t="n">
         <f aca="false">G65*$D$64</f>
-        <v>0.785472</v>
+        <v>0.671232</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26760,17 +26874,17 @@
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
       <c r="E66" s="295" t="s">
-        <v>983</v>
+        <v>1197</v>
       </c>
       <c r="F66" s="285" t="s">
-        <v>984</v>
+        <v>60</v>
       </c>
       <c r="G66" s="284" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="H66" s="296" t="n">
         <f aca="false">G66*$D$64</f>
-        <v>0.49092</v>
+        <v>2.0976</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26779,66 +26893,64 @@
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
       <c r="E67" s="295" t="s">
-        <v>952</v>
+        <v>1198</v>
       </c>
       <c r="F67" s="285" t="s">
-        <v>953</v>
+        <v>981</v>
       </c>
       <c r="G67" s="284" t="n">
-        <v>0.4</v>
+        <v>0.024</v>
       </c>
       <c r="H67" s="296" t="n">
         <f aca="false">G67*$D$64</f>
-        <v>3.92736</v>
+        <v>0.2013696</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="283" t="n">
+      <c r="A68" s="21"/>
+      <c r="B68" s="304"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="F68" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="G68" s="284" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H68" s="296" t="n">
+        <f aca="false">G68*$D$64</f>
+        <v>3.35616</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="283" t="n">
         <v>12</v>
       </c>
-      <c r="B68" s="295" t="s">
+      <c r="B69" s="295" t="s">
         <v>985</v>
       </c>
-      <c r="C68" s="285" t="s">
+      <c r="C69" s="285" t="s">
         <v>57</v>
       </c>
-      <c r="D68" s="290" t="n">
+      <c r="D69" s="290" t="n">
         <f aca="false">'PLANILLA GENERAL DE METRADOS'!K321</f>
         <v>100.64</v>
       </c>
-      <c r="E68" s="295" t="s">
+      <c r="E69" s="295" t="s">
         <v>986</v>
       </c>
-      <c r="F68" s="285" t="s">
+      <c r="F69" s="285" t="s">
         <v>168</v>
       </c>
-      <c r="G68" s="284" t="n">
+      <c r="G69" s="284" t="n">
         <v>0.25</v>
       </c>
-      <c r="H68" s="296" t="n">
-        <f aca="false">G68*$D$68</f>
+      <c r="H69" s="296" t="n">
+        <f aca="false">G69*$D$69</f>
         <v>25.16</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21"/>
-      <c r="B69" s="304"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="295" t="s">
-        <v>987</v>
-      </c>
-      <c r="F69" s="285" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="G69" s="284" t="n">
-        <v>0.0013</v>
-      </c>
-      <c r="H69" s="296" t="n">
-        <f aca="false">G69*$D$68</f>
-        <v>0.130832</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26847,17 +26959,19 @@
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
       <c r="E70" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="F70" s="285" t="s">
-        <v>953</v>
+        <v>987</v>
+      </c>
+      <c r="F70" s="285" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
       </c>
       <c r="G70" s="284" t="n">
-        <v>0.2</v>
+        <v>0.0013</v>
       </c>
       <c r="H70" s="296" t="n">
-        <f aca="false">G70*$D$68</f>
-        <v>20.128</v>
+        <f aca="false">G70*$D$69</f>
+        <v>0.130832</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26866,7 +26980,7 @@
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
       <c r="E71" s="295" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="F71" s="285" t="s">
         <v>953</v>
@@ -26875,55 +26989,55 @@
         <v>0.2</v>
       </c>
       <c r="H71" s="296" t="n">
-        <f aca="false">G71*$D$68</f>
+        <f aca="false">G71*$D$69</f>
         <v>20.128</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="283" t="n">
+      <c r="A72" s="21"/>
+      <c r="B72" s="304"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="F72" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="G72" s="284" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H72" s="296" t="n">
+        <f aca="false">G72*$D$69</f>
+        <v>20.128</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="283" t="n">
         <v>13</v>
       </c>
-      <c r="B72" s="295" t="s">
+      <c r="B73" s="295" t="s">
         <v>988</v>
       </c>
-      <c r="C72" s="285" t="s">
+      <c r="C73" s="285" t="s">
         <v>57</v>
       </c>
-      <c r="D72" s="290" t="n">
+      <c r="D73" s="290" t="n">
         <f aca="false">'PLANILLA GENERAL DE METRADOS'!K322</f>
         <v>210.979</v>
       </c>
-      <c r="E72" s="295" t="s">
+      <c r="E73" s="295" t="s">
         <v>986</v>
       </c>
-      <c r="F72" s="285" t="s">
+      <c r="F73" s="285" t="s">
         <v>168</v>
       </c>
-      <c r="G72" s="284" t="n">
+      <c r="G73" s="284" t="n">
         <v>0.15</v>
       </c>
-      <c r="H72" s="296" t="n">
-        <f aca="false">G72*$D$72</f>
+      <c r="H73" s="296" t="n">
+        <f aca="false">G73*$D$73</f>
         <v>31.64685</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
-      <c r="B73" s="304"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="295" t="s">
-        <v>955</v>
-      </c>
-      <c r="F73" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="G73" s="284" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H73" s="296" t="n">
-        <f aca="false">G73*$D$72</f>
-        <v>21.0979</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26932,19 +27046,17 @@
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
       <c r="E74" s="295" t="s">
-        <v>987</v>
-      </c>
-      <c r="F74" s="285" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
+        <v>955</v>
+      </c>
+      <c r="F74" s="285" t="s">
+        <v>953</v>
       </c>
       <c r="G74" s="284" t="n">
-        <v>0.0013</v>
+        <v>0.1</v>
       </c>
       <c r="H74" s="296" t="n">
-        <f aca="false">G74*$D$72</f>
-        <v>0.2742727</v>
+        <f aca="false">G74*$D$73</f>
+        <v>21.0979</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26953,17 +27065,38 @@
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="295" t="s">
+        <v>987</v>
+      </c>
+      <c r="F75" s="285" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="G75" s="284" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H75" s="296" t="n">
+        <f aca="false">G75*$D$73</f>
+        <v>0.2742727</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="21"/>
+      <c r="B76" s="304"/>
+      <c r="C76" s="21"/>
+      <c r="D76" s="21"/>
+      <c r="E76" s="295" t="s">
         <v>952</v>
       </c>
-      <c r="F75" s="285" t="s">
+      <c r="F76" s="285" t="s">
         <v>953</v>
       </c>
-      <c r="G75" s="284" t="n">
+      <c r="G76" s="284" t="n">
         <v>0.05</v>
       </c>
-      <c r="H75" s="296" t="n">
-        <f aca="false">G75*$D$72</f>
-        <v>10.548950000000001</v>
+      <c r="H76" s="296" t="n">
+        <f aca="false">G76*$D$73</f>
+        <v>10.54895</v>
       </c>
     </row>
   </sheetData>
@@ -27078,7 +27211,7 @@
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>990</v>
+        <v>1221</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -27131,22 +27264,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="149" t="s">
-        <v>996</v>
+        <v>1199</v>
       </c>
       <c r="C11" s="285" t="s">
         <v>60</v>
       </c>
       <c r="D11" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E23</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E11" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F11" s="306" t="n">
         <f aca="false">D11/E11</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G11" s="283" t="s">
         <v>997</v>
@@ -27167,15 +27300,15 @@
       </c>
       <c r="D12" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E24</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E12" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F12" s="306" t="n">
         <f aca="false">D12/E12</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="283" t="s">
         <v>1000</v>
@@ -27196,21 +27329,21 @@
       </c>
       <c r="D13" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="E13" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F13" s="306" t="n">
         <f aca="false">D13/E13</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="G13" s="283" t="s">
         <v>1003</v>
       </c>
       <c r="H13" s="149" t="s">
-        <v>1004</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27225,15 +27358,15 @@
       </c>
       <c r="D14" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E26</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E14" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F14" s="306" t="n">
         <f aca="false">D14/E14</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="283" t="s">
         <v>1006</v>
@@ -27258,7 +27391,7 @@
       </c>
       <c r="E15" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="306" t="n">
         <f aca="false">D15/E15</f>
@@ -27287,7 +27420,7 @@
       </c>
       <c r="E16" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="306" t="n">
         <f aca="false">D16/E16</f>
@@ -27312,21 +27445,21 @@
       </c>
       <c r="D17" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="E17" s="305" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="306" t="n">
         <f aca="false">D17/E17</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="G17" s="283" t="s">
         <v>1014</v>
       </c>
       <c r="H17" s="149" t="s">
-        <v>1015</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27384,14 +27517,14 @@
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21"/>
       <c r="B22" s="295" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C22" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="306" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C38</f>
-        <v>10.164</v>
+        <v>5.124</v>
       </c>
       <c r="E22" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G60</f>
@@ -27399,14 +27532,14 @@
       </c>
       <c r="F22" s="306" t="n">
         <f aca="false">D22*E22</f>
-        <v>10.6722</v>
+        <v>5.3802</v>
       </c>
       <c r="G22" s="290" t="n">
         <f aca="false">F22*SUMIF($B$68:$B$93,B22,$F$68:$F$93)</f>
-        <v>49.732452</v>
+        <v>16.571016</v>
       </c>
       <c r="H22" s="149" t="s">
-        <v>1025</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27431,7 +27564,7 @@
       </c>
       <c r="G23" s="290" t="n">
         <f aca="false">F23*SUMIF($B$68:$B$93,B23,$F$68:$F$93)</f>
-        <v>24.3553968</v>
+        <v>16.0975584</v>
       </c>
       <c r="H23" s="149" t="s">
         <v>1027</v>
@@ -27447,7 +27580,7 @@
       </c>
       <c r="D24" s="306" t="n">
         <f aca="false">F13</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="E24" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G61</f>
@@ -27455,11 +27588,11 @@
       </c>
       <c r="F24" s="306" t="n">
         <f aca="false">D24*E24</f>
-        <v>0.454248</v>
+        <v>0.303048</v>
       </c>
       <c r="G24" s="290" t="n">
         <f aca="false">F24*SUMIF($B$68:$B$93,B24,$F$68:$F$93)</f>
-        <v>6.15960288</v>
+        <v>5.64578424</v>
       </c>
       <c r="H24" s="149" t="s">
         <v>1029</v>
@@ -27475,7 +27608,7 @@
       </c>
       <c r="D25" s="306" t="n">
         <f aca="false">F13</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="E25" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G62</f>
@@ -27483,11 +27616,11 @@
       </c>
       <c r="F25" s="306" t="n">
         <f aca="false">D25*E25</f>
-        <v>1.51416</v>
+        <v>1.01016</v>
       </c>
       <c r="G25" s="290" t="n">
         <f aca="false">F25*SUMIF($B$68:$B$93,B25,$F$68:$F$93)</f>
-        <v>46.0607472</v>
+        <v>30.7290672</v>
       </c>
       <c r="H25" s="149" t="s">
         <v>1029</v>
@@ -27503,7 +27636,7 @@
       </c>
       <c r="D26" s="306" t="n">
         <f aca="false">F13</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="E26" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G63</f>
@@ -27511,11 +27644,11 @@
       </c>
       <c r="F26" s="306" t="n">
         <f aca="false">D26*E26</f>
-        <v>1.51416</v>
+        <v>1.01016</v>
       </c>
       <c r="G26" s="290" t="n">
         <f aca="false">F26*SUMIF($B$68:$B$93,B26,$F$68:$F$93)</f>
-        <v>34.749972</v>
+        <v>23.183172</v>
       </c>
       <c r="H26" s="149" t="s">
         <v>1029</v>
@@ -27531,7 +27664,7 @@
       </c>
       <c r="D27" s="306" t="n">
         <f aca="false">F13</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="E27" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G62</f>
@@ -27539,11 +27672,11 @@
       </c>
       <c r="F27" s="306" t="n">
         <f aca="false">D27*E27</f>
-        <v>1.51416</v>
+        <v>1.01016</v>
       </c>
       <c r="G27" s="290" t="n">
         <f aca="false">F27*SUMIF($B$68:$B$93,B27,$F$68:$F$93)</f>
-        <v>12.11328</v>
+        <v>8.08128</v>
       </c>
       <c r="H27" s="149" t="s">
         <v>1031</v>
@@ -27560,7 +27693,7 @@
       <c r="F28" s="295"/>
       <c r="G28" s="296" t="n">
         <f aca="false">SUM(G22:G27)</f>
-        <v>173.17145088</v>
+        <v>100.30787784</v>
       </c>
       <c r="H28" s="295"/>
     </row>
@@ -27600,7 +27733,7 @@
       </c>
       <c r="G30" s="290" t="n">
         <f aca="false">F30*SUMIF($B$68:$B$93,B30,$F$68:$F$93)</f>
-        <v>10.9815302016</v>
+        <v>11.1327017088</v>
       </c>
       <c r="H30" s="149" t="s">
         <v>1035</v>
@@ -27628,7 +27761,7 @@
       </c>
       <c r="G31" s="290" t="n">
         <f aca="false">F31*SUMIF($B$68:$B$93,B31,$F$68:$F$93)</f>
-        <v>0.978142464</v>
+        <v>0.7825139712</v>
       </c>
       <c r="H31" s="149" t="s">
         <v>1036</v>
@@ -27684,7 +27817,7 @@
       </c>
       <c r="G33" s="290" t="n">
         <f aca="false">F33*SUMIF($B$68:$B$93,B33,$F$68:$F$93)</f>
-        <v>0.03440256</v>
+        <v>0.05731466496</v>
       </c>
       <c r="H33" s="149" t="s">
         <v>1036</v>
@@ -27712,7 +27845,7 @@
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">F34*SUMIF($B$68:$B$93,B34,$F$68:$F$93)</f>
-        <v>0.443904</v>
+        <v>0.376134656</v>
       </c>
       <c r="H34" s="149" t="s">
         <v>1036</v>
@@ -27740,7 +27873,7 @@
       </c>
       <c r="G35" s="290" t="n">
         <f aca="false">F35*SUMIF($B$68:$B$93,B35,$F$68:$F$93)</f>
-        <v>0.295936</v>
+        <v>0.326121472</v>
       </c>
       <c r="H35" s="149" t="s">
         <v>1036</v>
@@ -27841,7 +27974,7 @@
       <c r="F39" s="295"/>
       <c r="G39" s="296" t="n">
         <f aca="false">SUM(G30:G38)</f>
-        <v>21.229042944</v>
+        <v>21.16991419136</v>
       </c>
       <c r="H39" s="295"/>
     </row>
@@ -27869,7 +28002,7 @@
       </c>
       <c r="D41" s="306" t="n">
         <f aca="false">F14</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E41" s="307" t="n">
         <v>1.15</v>
@@ -27880,7 +28013,7 @@
       </c>
       <c r="G41" s="290" t="n">
         <f aca="false">F41*SUMIF($B$68:$B$93,B41,$F$68:$F$93)</f>
-        <v>5.842</v>
+        <v>5.0715</v>
       </c>
       <c r="H41" s="149" t="s">
         <v>1040</v>
@@ -27897,7 +28030,7 @@
       <c r="F42" s="295"/>
       <c r="G42" s="296" t="n">
         <f aca="false">SUM(G41:G41)</f>
-        <v>5.842</v>
+        <v>5.0715</v>
       </c>
       <c r="H42" s="295"/>
     </row>
@@ -27937,7 +28070,7 @@
       </c>
       <c r="G44" s="290" t="n">
         <f aca="false">F44*SUMIF($B$68:$B$93,B44,$F$68:$F$93)</f>
-        <v>69.3590688</v>
+        <v>62.6234112</v>
       </c>
       <c r="H44" s="149" t="s">
         <v>1045</v>
@@ -28038,7 +28171,7 @@
       <c r="F48" s="295"/>
       <c r="G48" s="296" t="n">
         <f aca="false">SUM(G44:G47)</f>
-        <v>104.253416064</v>
+        <v>97.517758464</v>
       </c>
       <c r="H48" s="295"/>
     </row>
@@ -28066,7 +28199,7 @@
       </c>
       <c r="D50" s="306" t="n">
         <f aca="false">F17</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E50" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G64</f>
@@ -28074,11 +28207,11 @@
       </c>
       <c r="F50" s="306" t="n">
         <f aca="false">D50*E50</f>
-        <v>0.0785472</v>
+        <v>0.0671232</v>
       </c>
       <c r="G50" s="290" t="n">
         <f aca="false">F50*SUMIF($B$68:$B$93,B50,$F$68:$F$93)</f>
-        <v>4.659419904</v>
+        <v>3.015174144</v>
       </c>
       <c r="H50" s="149" t="s">
         <v>1036</v>
@@ -28094,7 +28227,7 @@
       </c>
       <c r="D51" s="306" t="n">
         <f aca="false">F17</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E51" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G65</f>
@@ -28102,11 +28235,11 @@
       </c>
       <c r="F51" s="306" t="n">
         <f aca="false">D51*E51</f>
-        <v>0.0785472</v>
+        <v>0.0671232</v>
       </c>
       <c r="G51" s="290" t="n">
         <f aca="false">F51*SUMIF($B$68:$B$93,B51,$F$68:$F$93)</f>
-        <v>4.326379776</v>
+        <v>3.242721792</v>
       </c>
       <c r="H51" s="149" t="s">
         <v>1036</v>
@@ -28115,137 +28248,138 @@
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="21"/>
       <c r="B52" s="295" t="s">
-        <v>983</v>
+        <v>1197</v>
       </c>
       <c r="C52" s="285" t="s">
-        <v>984</v>
+        <v>60</v>
       </c>
       <c r="D52" s="306" t="n">
         <f aca="false">F17</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E52" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G66</f>
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="F52" s="306" t="n">
         <f aca="false">D52*E52</f>
-        <v>0.049092</v>
+        <v>0.20976</v>
       </c>
       <c r="G52" s="290" t="n">
         <f aca="false">F52*SUMIF($B$68:$B$93,B52,$F$68:$F$93)</f>
-        <v>1.24791864</v>
+        <v>0.4446912</v>
       </c>
       <c r="H52" s="149" t="s">
-        <v>1036</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="21"/>
       <c r="B53" s="295" t="s">
-        <v>952</v>
+        <v>1198</v>
       </c>
       <c r="C53" s="285" t="s">
-        <v>953</v>
+        <v>981</v>
       </c>
       <c r="D53" s="306" t="n">
         <f aca="false">F17</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E53" s="306" t="n">
         <f aca="false">+'COLECTOR INSUMOS'!G67</f>
-        <v>0.4</v>
+        <v>0.024</v>
       </c>
       <c r="F53" s="306" t="n">
         <f aca="false">D53*E53</f>
-        <v>0.392736</v>
+        <v>0.02013696</v>
       </c>
       <c r="G53" s="290" t="n">
         <f aca="false">F53*SUMIF($B$68:$B$93,B53,$F$68:$F$93)</f>
-        <v>11.94702912</v>
+        <v>0.717882624</v>
       </c>
       <c r="H53" s="149" t="s">
-        <v>1036</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="21"/>
-      <c r="B54" s="294" t="s">
+      <c r="B54" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="C54" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D54" s="306" t="n">
+        <f aca="false">F17</f>
+        <v>0.83904</v>
+      </c>
+      <c r="E54" s="306" t="n">
+        <f aca="false">+'COLECTOR INSUMOS'!G68</f>
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="306" t="n">
+        <f aca="false">D54*E54</f>
+        <v>0.335616</v>
+      </c>
+      <c r="G54" s="290" t="n">
+        <f aca="false">F54*SUMIF($B$68:$B$93,B54,$F$68:$F$93)</f>
+        <v>10.20943872</v>
+      </c>
+      <c r="H54" s="149" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21"/>
+      <c r="B55" s="294" t="s">
         <v>1049</v>
       </c>
-      <c r="C54" s="295"/>
-      <c r="D54" s="295"/>
-      <c r="E54" s="295"/>
-      <c r="F54" s="295"/>
-      <c r="G54" s="296" t="n">
-        <f aca="false">SUM(G50:G53)</f>
-        <v>22.18074744</v>
-      </c>
-      <c r="H54" s="295"/>
-    </row>
-    <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="283" t="s">
+      <c r="C55" s="295"/>
+      <c r="D55" s="295"/>
+      <c r="E55" s="295"/>
+      <c r="F55" s="295"/>
+      <c r="G55" s="296" t="n">
+        <f aca="false">SUM(G50:G54)</f>
+        <v>17.62990848</v>
+      </c>
+      <c r="H55" s="295"/>
+    </row>
+    <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="283" t="s">
         <v>1050</v>
       </c>
-      <c r="B55" s="294" t="s">
+      <c r="B56" s="294" t="s">
         <v>1051</v>
       </c>
-      <c r="C55" s="294"/>
-      <c r="D55" s="294"/>
-      <c r="E55" s="294"/>
-      <c r="F55" s="294"/>
-      <c r="G55" s="294"/>
-      <c r="H55" s="294"/>
-    </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21"/>
-      <c r="B56" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="C56" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D56" s="306" t="n">
-        <f aca="false">F14</f>
-        <v>1</v>
-      </c>
-      <c r="E56" s="307" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="306" t="n">
-        <f aca="false">D56*E56</f>
-        <v>1</v>
-      </c>
-      <c r="G56" s="290" t="n">
-        <f aca="false">F56*SUMIF($B$68:$B$93,B56,$F$68:$F$93)</f>
-        <v>30.42</v>
-      </c>
-      <c r="H56" s="149" t="s">
-        <v>1052</v>
-      </c>
+      <c r="C56" s="294"/>
+      <c r="D56" s="294"/>
+      <c r="E56" s="294"/>
+      <c r="F56" s="294"/>
+      <c r="G56" s="294"/>
+      <c r="H56" s="294"/>
     </row>
     <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="21"/>
       <c r="B57" s="295" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C57" s="285" t="s">
         <v>953</v>
       </c>
       <c r="D57" s="306" t="n">
         <f aca="false">F14</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E57" s="307" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="306" t="n">
         <f aca="false">D57*E57</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G57" s="290" t="n">
         <f aca="false">F57*SUMIF($B$68:$B$93,B57,$F$68:$F$93)</f>
-        <v>20.79</v>
+        <v>30.42</v>
       </c>
       <c r="H57" s="149" t="s">
         <v>1052</v>
@@ -28253,33 +28387,60 @@
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21"/>
-      <c r="B58" s="294" t="s">
+      <c r="B58" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="C58" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D58" s="306" t="n">
+        <f aca="false">F14</f>
+        <v>1.0</v>
+      </c>
+      <c r="E58" s="307" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="306" t="n">
+        <f aca="false">D58*E58</f>
+        <v>1.0</v>
+      </c>
+      <c r="G58" s="290" t="n">
+        <f aca="false">F58*SUMIF($B$68:$B$93,B58,$F$68:$F$93)</f>
+        <v>20.79</v>
+      </c>
+      <c r="H58" s="149" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21"/>
+      <c r="B59" s="294" t="s">
         <v>1053</v>
-      </c>
-      <c r="C58" s="295"/>
-      <c r="D58" s="295"/>
-      <c r="E58" s="295"/>
-      <c r="F58" s="295"/>
-      <c r="G58" s="296" t="n">
-        <f aca="false">SUM(G56:G57)</f>
-        <v>51.21</v>
-      </c>
-      <c r="H58" s="295"/>
-    </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="295"/>
-      <c r="B59" s="294" t="s">
-        <v>1054</v>
       </c>
       <c r="C59" s="295"/>
       <c r="D59" s="295"/>
       <c r="E59" s="295"/>
       <c r="F59" s="295"/>
       <c r="G59" s="296" t="n">
-        <f aca="false">+G28+G39+G42+G48+G54+G58</f>
-        <v>377.886657328</v>
+        <f aca="false">SUM(G57:G58)</f>
+        <v>51.21</v>
       </c>
       <c r="H59" s="295"/>
+    </row>
+    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="295"/>
+      <c r="B60" s="294" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C60" s="295"/>
+      <c r="D60" s="295"/>
+      <c r="E60" s="295"/>
+      <c r="F60" s="295"/>
+      <c r="G60" s="296" t="n">
+        <f aca="false">+G28+G39+G42+G48+G55+G59</f>
+        <v>292.90695897536</v>
+      </c>
+      <c r="H60" s="295"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="294" t="s">
@@ -28342,7 +28503,7 @@
       <c r="B65" s="294"/>
       <c r="C65" s="290" t="n">
         <f aca="false">+E11</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="D65" s="290"/>
       <c r="E65" s="290"/>
@@ -28357,7 +28518,7 @@
       <c r="B66" s="294"/>
       <c r="C66" s="290" t="n">
         <f aca="false">8/E69</f>
-        <v>2.29141480198968</v>
+        <v>2.73021440919798</v>
       </c>
       <c r="D66" s="290"/>
       <c r="E66" s="290"/>
@@ -28415,18 +28576,18 @@
       </c>
       <c r="D69" s="306" t="n">
         <f aca="false">E69*$C$66/8</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E69" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B69,$F$21:$F$58)</f>
-        <v>3.4912928</v>
+        <f aca="false">SUMIF($B$21:$B$59,B69,$F$21:$F$59)</f>
+        <v>2.9301728</v>
       </c>
       <c r="F69" s="289" t="n">
         <v>30.42</v>
       </c>
       <c r="G69" s="290" t="n">
         <f aca="false">E69*F69</f>
-        <v>106.205126976</v>
+        <v>89.135856576</v>
       </c>
       <c r="H69" s="149" t="s">
         <v>1067</v>
@@ -28444,18 +28605,18 @@
       </c>
       <c r="D70" s="306" t="n">
         <f aca="false">E70*$C$66/8</f>
-        <v>0.601083014292013</v>
+        <v>0.544185243955578</v>
       </c>
       <c r="E70" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B70,$F$21:$F$58)</f>
-        <v>2.0985568</v>
+        <f aca="false">SUMIF($B$21:$B$59,B70,$F$21:$F$59)</f>
+        <v>1.5945568</v>
       </c>
       <c r="F70" s="289" t="n">
         <v>22.95</v>
       </c>
       <c r="G70" s="290" t="n">
         <f aca="false">E70*F70</f>
-        <v>48.16187856</v>
+        <v>36.59507856</v>
       </c>
       <c r="H70" s="149" t="s">
         <v>1067</v>
@@ -28473,10 +28634,10 @@
       </c>
       <c r="D71" s="306" t="n">
         <f aca="false">E71*$C$66/8</f>
-        <v>0.354238063332872</v>
+        <v>0.422073674289789</v>
       </c>
       <c r="E71" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B71,$F$21:$F$58)</f>
+        <f aca="false">SUMIF($B$21:$B$59,B71,$F$21:$F$59)</f>
         <v>1.2367488</v>
       </c>
       <c r="F71" s="289" t="n">
@@ -28501,7 +28662,7 @@
       <c r="F72" s="295"/>
       <c r="G72" s="296" t="n">
         <f aca="false">SUM(G69:G71)</f>
-        <v>180.079013088</v>
+        <v>151.442942688</v>
       </c>
       <c r="H72" s="295"/>
     </row>
@@ -28522,25 +28683,25 @@
         <v>4</v>
       </c>
       <c r="B74" s="295" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="C74" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D74" s="295"/>
       <c r="E74" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B74,$F$21:$F$58)</f>
-        <v>10.6722</v>
+        <f aca="false">SUMIF($B$21:$B$59,B74,$F$21:$F$59)</f>
+        <v>10.60668</v>
       </c>
       <c r="F74" s="289" t="n">
-        <v>4.66</v>
+        <v>3.08</v>
       </c>
       <c r="G74" s="290" t="n">
         <f aca="false">E74*F74</f>
-        <v>49.732452</v>
+        <v>32.6685744</v>
       </c>
       <c r="H74" s="149" t="s">
-        <v>1070</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28548,25 +28709,25 @@
         <v>5</v>
       </c>
       <c r="B75" s="295" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C75" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D75" s="295"/>
       <c r="E75" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B75,$F$21:$F$58)</f>
-        <v>5.22648</v>
+        <f aca="false">SUMIF($B$21:$B$59,B75,$F$21:$F$59)</f>
+        <v>0.303048</v>
       </c>
       <c r="F75" s="289" t="n">
-        <v>4.66</v>
+        <v>18.63</v>
       </c>
       <c r="G75" s="290" t="n">
         <f aca="false">E75*F75</f>
-        <v>24.3553968</v>
+        <v>5.64578424</v>
       </c>
       <c r="H75" s="149" t="s">
-        <v>1070</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28574,25 +28735,25 @@
         <v>6</v>
       </c>
       <c r="B76" s="295" t="s">
-        <v>1028</v>
+        <v>944</v>
       </c>
       <c r="C76" s="285" t="s">
-        <v>50</v>
+        <v>945</v>
       </c>
       <c r="D76" s="295"/>
       <c r="E76" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B76,$F$21:$F$58)</f>
-        <v>0.454248</v>
+        <f aca="false">SUMIF($B$21:$B$59,B76,$F$21:$F$59)</f>
+        <v>0.35993216</v>
       </c>
       <c r="F76" s="289" t="n">
-        <v>13.56</v>
+        <v>30.93</v>
       </c>
       <c r="G76" s="290" t="n">
         <f aca="false">E76*F76</f>
-        <v>6.15960288</v>
+        <v>11.1327017088</v>
       </c>
       <c r="H76" s="149" t="s">
-        <v>1070</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28600,25 +28761,25 @@
         <v>7</v>
       </c>
       <c r="B77" s="295" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="C77" s="285" t="s">
-        <v>945</v>
+        <v>167</v>
       </c>
       <c r="D77" s="295"/>
       <c r="E77" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B77,$F$21:$F$58)</f>
-        <v>0.35993216</v>
+        <f aca="false">SUMIF($B$21:$B$59,B77,$F$21:$F$59)</f>
+        <v>0.01923584</v>
       </c>
       <c r="F77" s="289" t="n">
-        <v>30.51</v>
+        <v>40.68</v>
       </c>
       <c r="G77" s="290" t="n">
         <f aca="false">E77*F77</f>
-        <v>10.9815302016</v>
+        <v>0.7825139712</v>
       </c>
       <c r="H77" s="149" t="s">
-        <v>1070</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28626,25 +28787,25 @@
         <v>8</v>
       </c>
       <c r="B78" s="295" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C78" s="285" t="s">
         <v>167</v>
       </c>
       <c r="D78" s="295"/>
       <c r="E78" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B78,$F$21:$F$58)</f>
-        <v>0.01923584</v>
+        <f aca="false">SUMIF($B$21:$B$59,B78,$F$21:$F$59)</f>
+        <v>0.01960576</v>
       </c>
       <c r="F78" s="289" t="n">
-        <v>50.85</v>
+        <v>101.69</v>
       </c>
       <c r="G78" s="290" t="n">
         <f aca="false">E78*F78</f>
-        <v>0.978142464</v>
+        <v>1.9937097344</v>
       </c>
       <c r="H78" s="149" t="s">
-        <v>1070</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28652,25 +28813,25 @@
         <v>9</v>
       </c>
       <c r="B79" s="295" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C79" s="285" t="s">
         <v>167</v>
       </c>
       <c r="D79" s="295"/>
       <c r="E79" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B79,$F$21:$F$58)</f>
-        <v>0.01960576</v>
+        <f aca="false">SUMIF($B$21:$B$59,B79,$F$21:$F$59)</f>
+        <v>0.006880512</v>
       </c>
       <c r="F79" s="289" t="n">
-        <v>101.69</v>
+        <v>8.33</v>
       </c>
       <c r="G79" s="290" t="n">
         <f aca="false">E79*F79</f>
-        <v>1.9937097344</v>
+        <v>0.05731466496</v>
       </c>
       <c r="H79" s="149" t="s">
-        <v>1070</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28678,25 +28839,25 @@
         <v>10</v>
       </c>
       <c r="B80" s="295" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="C80" s="285" t="s">
-        <v>167</v>
+        <v>960</v>
       </c>
       <c r="D80" s="295"/>
       <c r="E80" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B80,$F$21:$F$58)</f>
-        <v>0.006880512</v>
+        <f aca="false">SUMIF($B$21:$B$59,B80,$F$21:$F$59)</f>
+        <v>1.15</v>
       </c>
       <c r="F80" s="289" t="n">
-        <v>5</v>
+        <v>4.41</v>
       </c>
       <c r="G80" s="290" t="n">
         <f aca="false">E80*F80</f>
-        <v>0.03440256</v>
+        <v>5.0715</v>
       </c>
       <c r="H80" s="149" t="s">
-        <v>1070</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28704,25 +28865,25 @@
         <v>11</v>
       </c>
       <c r="B81" s="295" t="s">
-        <v>959</v>
+        <v>1044</v>
       </c>
       <c r="C81" s="285" t="s">
-        <v>960</v>
+        <v>50</v>
       </c>
       <c r="D81" s="295"/>
       <c r="E81" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B81,$F$21:$F$58)</f>
-        <v>1.15</v>
+        <f aca="false">SUMIF($B$21:$B$59,B81,$F$21:$F$59)</f>
+        <v>18.20448</v>
       </c>
       <c r="F81" s="289" t="n">
-        <v>5.08</v>
+        <v>3.44</v>
       </c>
       <c r="G81" s="290" t="n">
         <f aca="false">E81*F81</f>
-        <v>5.842</v>
+        <v>62.6234112</v>
       </c>
       <c r="H81" s="149" t="s">
-        <v>1070</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28730,25 +28891,25 @@
         <v>12</v>
       </c>
       <c r="B82" s="295" t="s">
-        <v>1044</v>
+        <v>965</v>
       </c>
       <c r="C82" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D82" s="295"/>
       <c r="E82" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B82,$F$21:$F$58)</f>
-        <v>18.20448</v>
+        <f aca="false">SUMIF($B$21:$B$59,B82,$F$21:$F$59)</f>
+        <v>1.040256</v>
       </c>
       <c r="F82" s="289" t="n">
-        <v>3.81</v>
+        <v>5.08</v>
       </c>
       <c r="G82" s="290" t="n">
         <f aca="false">E82*F82</f>
-        <v>69.3590688</v>
+        <v>5.28450048</v>
       </c>
       <c r="H82" s="149" t="s">
-        <v>1070</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28756,25 +28917,25 @@
         <v>13</v>
       </c>
       <c r="B83" s="295" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C83" s="285" t="s">
-        <v>50</v>
+        <v>981</v>
       </c>
       <c r="D83" s="295"/>
       <c r="E83" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B83,$F$21:$F$58)</f>
-        <v>1.040256</v>
+        <f aca="false">SUMIF($B$21:$B$59,B83,$F$21:$F$59)</f>
+        <v>0.0671232</v>
       </c>
       <c r="F83" s="289" t="n">
-        <v>5.08</v>
+        <v>44.92</v>
       </c>
       <c r="G83" s="290" t="n">
         <f aca="false">E83*F83</f>
-        <v>5.28450048</v>
+        <v>3.015174144</v>
       </c>
       <c r="H83" s="149" t="s">
-        <v>1070</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28782,25 +28943,25 @@
         <v>14</v>
       </c>
       <c r="B84" s="295" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C84" s="285" t="s">
         <v>981</v>
       </c>
       <c r="D84" s="295"/>
       <c r="E84" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B84,$F$21:$F$58)</f>
-        <v>0.0785472</v>
+        <f aca="false">SUMIF($B$21:$B$59,B84,$F$21:$F$59)</f>
+        <v>0.0671232</v>
       </c>
       <c r="F84" s="289" t="n">
-        <v>59.32</v>
+        <v>48.31</v>
       </c>
       <c r="G84" s="290" t="n">
         <f aca="false">E84*F84</f>
-        <v>4.659419904</v>
+        <v>3.242721792</v>
       </c>
       <c r="H84" s="149" t="s">
-        <v>1070</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28808,25 +28969,25 @@
         <v>15</v>
       </c>
       <c r="B85" s="295" t="s">
-        <v>982</v>
+        <v>1197</v>
       </c>
       <c r="C85" s="285" t="s">
-        <v>981</v>
+        <v>60</v>
       </c>
       <c r="D85" s="295"/>
       <c r="E85" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B85,$F$21:$F$58)</f>
-        <v>0.0785472</v>
+        <f aca="false">SUMIF($B$21:$B$59,B85,$F$21:$F$59)</f>
+        <v>0.20976</v>
       </c>
       <c r="F85" s="289" t="n">
-        <v>55.08</v>
+        <v>2.12</v>
       </c>
       <c r="G85" s="290" t="n">
         <f aca="false">E85*F85</f>
-        <v>4.326379776</v>
+        <v>0.4446912</v>
       </c>
       <c r="H85" s="149" t="s">
-        <v>1070</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28834,25 +28995,25 @@
         <v>16</v>
       </c>
       <c r="B86" s="295" t="s">
-        <v>983</v>
+        <v>1198</v>
       </c>
       <c r="C86" s="285" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="D86" s="295"/>
       <c r="E86" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B86,$F$21:$F$58)</f>
-        <v>0.049092</v>
+        <f aca="false">SUMIF($B$21:$B$59,B86,$F$21:$F$59)</f>
+        <v>0.02013696</v>
       </c>
       <c r="F86" s="289" t="n">
-        <v>25.42</v>
+        <v>35.65</v>
       </c>
       <c r="G86" s="290" t="n">
         <f aca="false">E86*F86</f>
-        <v>1.24791864</v>
+        <v>0.717882624</v>
       </c>
       <c r="H86" s="149" t="s">
-        <v>1070</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28866,7 +29027,7 @@
       <c r="F87" s="295"/>
       <c r="G87" s="296" t="n">
         <f aca="false">SUM(G74:G86)</f>
-        <v>184.95452424</v>
+        <v>132.68048015936</v>
       </c>
       <c r="H87" s="295"/>
     </row>
@@ -28898,11 +29059,11 @@
       </c>
       <c r="F89" s="290" t="n">
         <f aca="false">+G72</f>
-        <v>180.079013088</v>
+        <v>151.442942688</v>
       </c>
       <c r="G89" s="290" t="n">
         <f aca="false">E89*F89</f>
-        <v>5.40237039264</v>
+        <v>4.54328828064</v>
       </c>
       <c r="H89" s="149" t="s">
         <v>1073</v>
@@ -28920,21 +29081,21 @@
       </c>
       <c r="D90" s="306" t="n">
         <f aca="false">E90*$C$66/8</f>
-        <v>0.00847640163552023</v>
+        <v>0.0100996091425052</v>
       </c>
       <c r="E90" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B90,$F$21:$F$58)</f>
+        <f aca="false">SUMIF($B$21:$B$59,B90,$F$21:$F$59)</f>
         <v>0.0295936</v>
       </c>
       <c r="F90" s="289" t="n">
-        <v>15</v>
+        <v>12.71</v>
       </c>
       <c r="G90" s="290" t="n">
         <f aca="false">E90*F90</f>
-        <v>0.443904</v>
+        <v>0.376134656</v>
       </c>
       <c r="H90" s="149" t="s">
-        <v>1074</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28949,21 +29110,21 @@
       </c>
       <c r="D91" s="306" t="n">
         <f aca="false">E91*$C$66/8</f>
-        <v>0.00847640163552023</v>
+        <v>0.0100996091425052</v>
       </c>
       <c r="E91" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B91,$F$21:$F$58)</f>
+        <f aca="false">SUMIF($B$21:$B$59,B91,$F$21:$F$59)</f>
         <v>0.0295936</v>
       </c>
       <c r="F91" s="289" t="n">
-        <v>10</v>
+        <v>11.02</v>
       </c>
       <c r="G91" s="290" t="n">
         <f aca="false">E91*F91</f>
-        <v>0.295936</v>
+        <v>0.326121472</v>
       </c>
       <c r="H91" s="149" t="s">
-        <v>1074</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28978,21 +29139,21 @@
       </c>
       <c r="D92" s="306" t="n">
         <f aca="false">E92*$C$66/8</f>
-        <v>0.433696079572587</v>
+        <v>0.344744173449429</v>
       </c>
       <c r="E92" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$58,B92,$F$21:$F$58)</f>
-        <v>1.51416</v>
+        <f aca="false">SUMIF($B$21:$B$59,B92,$F$21:$F$59)</f>
+        <v>1.01016</v>
       </c>
       <c r="F92" s="289" t="n">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G92" s="290" t="n">
         <f aca="false">E92*F92</f>
-        <v>12.11328</v>
+        <v>8.08128</v>
       </c>
       <c r="H92" s="149" t="s">
-        <v>1074</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29006,7 +29167,7 @@
       <c r="F93" s="295"/>
       <c r="G93" s="296" t="n">
         <f aca="false">SUM(G89:G92)</f>
-        <v>18.25549039264</v>
+        <v>13.32682440864</v>
       </c>
       <c r="H93" s="295"/>
     </row>
@@ -29021,7 +29182,7 @@
       <c r="F94" s="294"/>
       <c r="G94" s="296" t="n">
         <f aca="false">+G72+G87+G93</f>
-        <v>383.28902772064</v>
+        <v>297.450247256</v>
       </c>
       <c r="H94" s="295"/>
     </row>
@@ -29036,7 +29197,7 @@
       <c r="F95" s="294"/>
       <c r="G95" s="296" t="n">
         <f aca="false">G94*C65</f>
-        <v>3832.8902772064</v>
+        <v>2974.50247256</v>
       </c>
       <c r="H95" s="295"/>
     </row>
@@ -29050,7 +29211,7 @@
       <c r="E96" s="295"/>
       <c r="F96" s="295"/>
       <c r="G96" s="283" t="str">
-        <f aca="false">IF(ABS(G59+G89-G94)&lt;0.005,"CONFORME","REVISAR")</f>
+        <f aca="false">IF(ABS(G60+G89-G94)&lt;0.005,"CONFORME","REVISAR")</f>
         <v>CONFORME</v>
       </c>
       <c r="H96" s="295"/>
@@ -29074,7 +29235,7 @@
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B56:H56"/>
     <mergeCell ref="A61:H61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="C62:H62"/>
@@ -31250,7 +31411,7 @@
       <c r="E11" s="149"/>
       <c r="F11" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E10</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G11" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F10</f>
@@ -31276,7 +31437,7 @@
       <c r="E12" s="149"/>
       <c r="F12" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E11</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G12" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F11</f>
@@ -31302,7 +31463,7 @@
       <c r="E13" s="149"/>
       <c r="F13" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E12</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G13" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F12</f>
@@ -31328,7 +31489,7 @@
       <c r="E14" s="149"/>
       <c r="F14" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E13</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F13</f>
@@ -31354,7 +31515,7 @@
       <c r="E15" s="149"/>
       <c r="F15" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E14</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F14</f>
@@ -31380,7 +31541,7 @@
       <c r="E16" s="149"/>
       <c r="F16" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E15</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F15</f>
@@ -31406,7 +31567,7 @@
       <c r="E17" s="149"/>
       <c r="F17" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E16</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F16</f>
@@ -31432,7 +31593,7 @@
       <c r="E18" s="149"/>
       <c r="F18" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E17</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F17</f>
@@ -31458,7 +31619,7 @@
       <c r="E19" s="149"/>
       <c r="F19" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="G19" s="283" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F18</f>
@@ -31475,7 +31636,7 @@
       <c r="E20" s="295"/>
       <c r="F20" s="296" t="n">
         <f aca="false">SUM(F11:F19)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G20" s="295"/>
     </row>
@@ -31529,22 +31690,22 @@
         <v>1</v>
       </c>
       <c r="B25" s="149" t="s">
-        <v>1154</v>
+        <v>1193</v>
       </c>
       <c r="C25" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="306" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C38</f>
-        <v>10.164</v>
+        <v>5.124</v>
       </c>
       <c r="E25" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="306" t="n">
         <f aca="false">D25*E25</f>
-        <v>101.64</v>
+        <v>51.24</v>
       </c>
       <c r="G25" s="149" t="s">
         <v>1155</v>
@@ -31566,7 +31727,7 @@
       </c>
       <c r="E26" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="306" t="n">
         <f aca="false">D26*E26</f>
@@ -31586,12 +31747,12 @@
       </c>
       <c r="D27" s="308" t="n">
         <f aca="false">SUM(D25:D26)</f>
-        <v>15.1416</v>
+        <v>10.1016</v>
       </c>
       <c r="E27" s="295"/>
       <c r="F27" s="296" t="n">
         <f aca="false">SUM(F25:F26)</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="G27" s="295"/>
     </row>
@@ -31622,7 +31783,7 @@
       </c>
       <c r="E29" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F29" s="306" t="n">
         <f aca="false">D29*E29</f>
@@ -31678,7 +31839,7 @@
       </c>
       <c r="E32" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F32" s="306" t="n">
         <f aca="false">D32*E32</f>
@@ -31704,7 +31865,7 @@
       </c>
       <c r="E33" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F33" s="306" t="n">
         <f aca="false">D33*E33</f>
@@ -31730,7 +31891,7 @@
       </c>
       <c r="E34" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="306" t="n">
         <f aca="false">D34*E34</f>
@@ -31756,7 +31917,7 @@
       </c>
       <c r="E35" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F35" s="306" t="n">
         <f aca="false">D35*E35</f>
@@ -31801,22 +31962,22 @@
         <v>8</v>
       </c>
       <c r="B38" s="149" t="s">
-        <v>1174</v>
+        <v>1194</v>
       </c>
       <c r="C38" s="285" t="s">
         <v>168</v>
       </c>
       <c r="D38" s="306" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C40+'COLECTOR PARAMETROS'!C37*'COLECTOR PARAMETROS'!C41</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E38" s="301" t="n">
         <f aca="false">+$F$20</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="306" t="n">
         <f aca="false">D38*E38</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="G38" s="149" t="s">
         <v>905</v>
@@ -31832,12 +31993,12 @@
       </c>
       <c r="D39" s="308" t="n">
         <f aca="false">SUM(D38:D38)</f>
-        <v>0.98184</v>
+        <v>0.83904</v>
       </c>
       <c r="E39" s="295"/>
       <c r="F39" s="296" t="n">
         <f aca="false">SUM(F38:F38)</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="G39" s="295"/>
     </row>
@@ -31882,11 +32043,11 @@
       <c r="D43" s="295"/>
       <c r="E43" s="306" t="n">
         <f aca="false">+F27</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="F43" s="306" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>151.416</v>
+        <v>101.016</v>
       </c>
       <c r="G43" s="283" t="str">
         <f aca="false">IF(ABS(E43-F43)&lt;0.001,"CONFORME","REVISAR")</f>
@@ -31948,11 +32109,11 @@
       <c r="D46" s="295"/>
       <c r="E46" s="306" t="n">
         <f aca="false">+F39</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="F46" s="306" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>9.8184</v>
+        <v>8.3904</v>
       </c>
       <c r="G46" s="283" t="str">
         <f aca="false">IF(ABS(E46-F46)&lt;0.001,"CONFORME","REVISAR")</f>

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -34,6 +34,8 @@
     <sheet name="ACU TAPA REGISTRO" sheetId="24" state="visible" r:id="rId26"/>
     <sheet name="ACU CANALETAS" sheetId="25" state="visible" r:id="rId27"/>
     <sheet name="DESAGREGADO TAPA REGISTRO" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="ACU JUNTA DILATACION" sheetId="27" state="visible" r:id="rId30"/>
+    <sheet name="ACU JUNTA CERCO" sheetId="28" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="24" name="_xlnm.Print_Area" vbProcedure="false">'ACU CANALETAS'!$A$1:$H$111</definedName>
@@ -510,7 +512,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1294">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4188,6 +4190,222 @@
   </si>
   <si>
     <t xml:space="preserve">Analisis de la partida de Delphin 01.04.04.06.05.01 TAPA DE REGISTRO 0.68x0.68 C/MARCO Y CONTRAMARCO, partida 01.04.04.05.01 del metrado; componentes desagregados en la hoja DESAGREGADO TAPA REGISTRO. Cantidad por tapa = metrado del componente / numero de tapas. Ratios de insumos tomados de la hoja COLECTOR INSUMOS. Celda amarilla = dato (ratio o precio); verde = formula. Precios sin IGV obtenidos de precios publicados (octubre 2026), con su fuente en la columna H; los marcados "por cotizar" deben confirmarse en Tarapoto.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - JUNTA DE DILATACION E=1" CON TECNOPOR Y SELLADOR ASFALTICO EN COLECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.01 JUNTA DE DILATACION E=1" CON TECNOPOR Y SELLADOR ASFALTICO EN COLECTOR (metrado 01.04.04.06.01, hoja COLECTOR JUNTAS Y EMPALMES). Se mide por metro de junta a lo largo del perimetro de la seccion. Cantidades de la lamina DD-03: plancha de tecnopor de 1" en toda la seccion y sellador asfaltico 1" x 2" (asfalto liquido RC-250 + arena gruesa) en las caras interiores y en la cara superior (EG-2013 MTC, 510). Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. CANTIDADES POR METRO DE JUNTA (lamina DD-03 y hoja COLECTOR JUNTAS Y EMPALMES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONCEPTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perimetro de la seccion en cada junta: 2 x 1.10 + 2 x (0.15 + 1.61 + 0.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES fila 11; DD-03 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de juntas de dilatacion (cada 4.00 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES fila 11; DD-03 E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area de tecnopor por junta: seccion 1.10 x 1.86 menos el hueco 0.80 x 1.61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03, cuadro de componentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor por metro de junta (area neta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio por el corte del anillo en planchas de 1.20 x 2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio: recortes del hueco interior y de las esquinas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area de una plancha de tecnopor 1" (1.20 x 2.40 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medida comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planchas de tecnopor por metro de junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pln/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitud sellada por junta: caras interiores 2 x 1.61 + 0.80 y cara superior 1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seccion del sellador 1" x 2" (0.0254 x 0.0508)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 B; EG-2013 510.02 c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla de sellador por metro de junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m3/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asfalto liquido RC-250 por m3 de mezcla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gal/m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio: mezcla de ~2,000 kg/m3 con ~9 % de asfalto = 180 kg / 3.6 kg/gal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa por m3 de mezcla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m3/m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio: arena suelta con 5 % de desperdicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operario por metro de junta (colocacion del tecnopor y sellado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS fila 71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peon por metro de junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS fila 72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. ANALISIS DE COSTO UNITARIO (formato Delphin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.01 JUNTA DE DILATACION E=1" CON TECNOPOR Y SELLADOR ASFALTICO EN COLECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.01 (hoja COLECTOR JUNTAS Y EMPALMES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento (m/dia, cuadrilla de 1 operario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANTIDAD POR M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">costo hora-hombre de la ACU TAPA REGISTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plancha de tecnopor 1" x 1.20 x 2.40 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pln</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru: plancha de poliestireno expandido 1" x 1.20 x 2.40 m (Dipropor) S/ 13.90 con IGV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asfalto liquido RC-250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conselva: asfalto liquido RC-250 por galon S/ 17.70 con IGV (Petroperu publica su lista ex planta; confirmar en Tarapoto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio de la ACU TAPA REGISTRO (Agregados Tarapoto, Morales)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 % del costo de mano de obra (incluye recipiente para calentar el asfalto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO DIRECTO DE LA PARTIDA (metrado x costo unitario, S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.02 JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO (metrado 01.04.04.06.02, hoja COLECTOR JUNTAS Y EMPALMES). Cantidades de la lamina DD-03: plancha de tecnopor de 1" de 0.90 m de altura contra el cimiento del cerco y de 0.10 m en el borde de la losa con el piso adyacente, con sellador asfaltico 1" x 2" (RC-250 + arena) en la cara superior. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junta contra el cimiento del cerco (0+000.00 a 0+058.81)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES fila 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altura de la plancha contra el cerco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junta en el borde de la losa con el piso adyacente (colector y cajas CL y CC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES filas 16 a 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altura de la plancha en el borde de la losa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitud total de la partida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES fila 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tecnopor por metro de junta (promedio ponderado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio por el corte en tiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezcla de sellador por metro de junta: 1" x 2" en la cara superior (0.0254 x 0.0508)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 C y D; EG-2013 510.02 c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peon por metro de junta (corte y colocacion de las tiras)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS fila 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operario por metro de junta (sellado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS fila 76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.02 JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.02 (hoja COLECTOR JUNTAS Y EMPALMES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento (m/dia, operario de sellado)</t>
   </si>
 </sst>
 </file>
@@ -4981,7 +5199,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="310">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6218,6 +6436,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -26945,12 +27167,13 @@
       <c r="F69" s="285" t="s">
         <v>168</v>
       </c>
-      <c r="G69" s="284" t="n">
-        <v>0.25</v>
+      <c r="G69" s="306" t="n">
+        <f aca="false">'ACU JUNTA DILATACION'!$D$14*(1+'ACU JUNTA DILATACION'!$D$15)</f>
+        <v>0.140844594594595</v>
       </c>
       <c r="H69" s="296" t="n">
         <f aca="false">G69*$D$69</f>
-        <v>25.16</v>
+        <v>14.1746</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26966,12 +27189,13 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="G70" s="284" t="n">
-        <v>0.0013</v>
+      <c r="G70" s="306" t="n">
+        <f aca="false">'ACU JUNTA DILATACION'!$D$20</f>
+        <v>0.00111595243243243</v>
       </c>
       <c r="H70" s="296" t="n">
         <f aca="false">G70*$D$69</f>
-        <v>0.130832</v>
+        <v>0.1123094528</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27032,12 +27256,13 @@
       <c r="F73" s="285" t="s">
         <v>168</v>
       </c>
-      <c r="G73" s="284" t="n">
-        <v>0.15</v>
+      <c r="G73" s="306" t="n">
+        <f aca="false">'ACU JUNTA CERCO'!$D$16*(1+'ACU JUNTA CERCO'!$D$17)</f>
+        <v>0.339128515160277</v>
       </c>
       <c r="H73" s="296" t="n">
         <f aca="false">G73*$D$73</f>
-        <v>31.64685</v>
+        <v>71.548995</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27072,12 +27297,13 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="G75" s="284" t="n">
-        <v>0.0013</v>
+      <c r="G75" s="306" t="n">
+        <f aca="false">'ACU JUNTA CERCO'!$D$20</f>
+        <v>0.00129032</v>
       </c>
       <c r="H75" s="296" t="n">
         <f aca="false">G75*$D$73</f>
-        <v>0.2742727</v>
+        <v>0.27223042328</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32149,6 +32375,1702 @@
     <mergeCell ref="B31:G31"/>
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="A41:G41"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="278"/>
+      <c r="C2" s="279" t="str">
+        <f aca="false">+RESUMEN!B4</f>
+        <v>GERENCIA TERRITORIAL BAJO MAYO - TARAPOTO</v>
+      </c>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+    </row>
+    <row r="3" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="278"/>
+      <c r="C3" s="279" t="str">
+        <f aca="false">+RESUMEN!B5</f>
+        <v>“CREACIÓN DEL SERVICIO DE PROTECCIÓN A MUJERES VÍCTIMAS DE VIOLENCIA EN SITUACIÓN DE RIESGO DE FEMINICIDIO O PELIGRE SU INTEGRIDAD Y/O SALUD FÍSICA Y/O MENTAL EN HOGAR DE REFUGIO TEMPORAL DISTRITO DE MORALES DE LA PROVINCIA DE SAN MARTÍN DEL DEPARTAMENTO DE SAN MARTÍN”, con CUI N.° 2675514</v>
+      </c>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="278"/>
+      <c r="C4" s="279" t="str">
+        <f aca="false">+RESUMEN!B6</f>
+        <v>SAN MARTIN - SAN MARTIN - MORALES</v>
+      </c>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="278"/>
+      <c r="C5" s="280" t="n">
+        <f aca="false">+RESUMEN!B7</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="294" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C11" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="306" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!E11</f>
+        <v>5.92</v>
+      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="149" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C12" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="306" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!D11</f>
+        <v>17.0</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="149" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D13" s="306" t="n">
+        <f aca="false">1.10*(0.15+1.61+0.10)-0.80*1.61</f>
+        <v>0.758</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="149" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="149" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C14" s="285" t="s">
+        <v>602</v>
+      </c>
+      <c r="D14" s="306" t="n">
+        <f aca="false">D13/D11</f>
+        <v>0.128040540540541</v>
+      </c>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="149" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="149" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C15" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D15" s="309" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
+      <c r="H15" s="149" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C16" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="309" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="149" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D17" s="306" t="n">
+        <f aca="false">D14*(1+D15)/D16</f>
+        <v>0.0489043731231231</v>
+      </c>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="306" t="n">
+        <f aca="false">2*1.61+0.80+1.10</f>
+        <v>5.12</v>
+      </c>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="306" t="n">
+        <f aca="false">0.0254*0.0508</f>
+        <v>0.00129032</v>
+      </c>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D20" s="306" t="n">
+        <f aca="false">D19*D18/D11</f>
+        <v>0.00111595243243243</v>
+      </c>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D21" s="309" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D22" s="309" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C23" s="285" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D23" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G71</f>
+        <v>0.2</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="149" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="283" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C24" s="285" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D24" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G72</f>
+        <v>0.2</v>
+      </c>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="149" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="294" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B26" s="294"/>
+      <c r="C26" s="294"/>
+      <c r="D26" s="294"/>
+      <c r="E26" s="294"/>
+      <c r="F26" s="294"/>
+      <c r="G26" s="294"/>
+      <c r="H26" s="294"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B27" s="294"/>
+      <c r="C27" s="295" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D27" s="295"/>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="295"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="294" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B28" s="294"/>
+      <c r="C28" s="295" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D28" s="295"/>
+      <c r="E28" s="295"/>
+      <c r="F28" s="295"/>
+      <c r="G28" s="295"/>
+      <c r="H28" s="295"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="294" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="294"/>
+      <c r="C29" s="295" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="295"/>
+      <c r="E29" s="295"/>
+      <c r="F29" s="295"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="294" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B30" s="294"/>
+      <c r="C30" s="290" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F12</f>
+        <v>100.64</v>
+      </c>
+      <c r="D30" s="290"/>
+      <c r="E30" s="290"/>
+      <c r="F30" s="290"/>
+      <c r="G30" s="290"/>
+      <c r="H30" s="290"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="294" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B31" s="294"/>
+      <c r="C31" s="290" t="n">
+        <f aca="false">8/E34</f>
+        <v>40.0</v>
+      </c>
+      <c r="D31" s="290"/>
+      <c r="E31" s="290"/>
+      <c r="F31" s="290"/>
+      <c r="G31" s="290"/>
+      <c r="H31" s="290"/>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B32" s="282" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C32" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="282" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E32" s="282" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F32" s="282" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G32" s="282" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H32" s="282" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21"/>
+      <c r="B33" s="294" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C33" s="294"/>
+      <c r="D33" s="294"/>
+      <c r="E33" s="294"/>
+      <c r="F33" s="294"/>
+      <c r="G33" s="294"/>
+      <c r="H33" s="294"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B34" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="C34" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D34" s="306" t="n">
+        <f aca="false">E34*$C$31/8</f>
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="306" t="n">
+        <f aca="false">$D$23</f>
+        <v>0.2</v>
+      </c>
+      <c r="F34" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F69</f>
+        <v>30.42</v>
+      </c>
+      <c r="G34" s="290" t="n">
+        <f aca="false">E34*F34</f>
+        <v>6.084</v>
+      </c>
+      <c r="H34" s="149" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B35" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="C35" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D35" s="306" t="n">
+        <f aca="false">E35*$C$31/8</f>
+        <v>1.0</v>
+      </c>
+      <c r="E35" s="306" t="n">
+        <f aca="false">$D$24</f>
+        <v>0.2</v>
+      </c>
+      <c r="F35" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F71</f>
+        <v>20.79</v>
+      </c>
+      <c r="G35" s="290" t="n">
+        <f aca="false">E35*F35</f>
+        <v>4.158</v>
+      </c>
+      <c r="H35" s="149" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21"/>
+      <c r="B36" s="294" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C36" s="295"/>
+      <c r="D36" s="295"/>
+      <c r="E36" s="295"/>
+      <c r="F36" s="295"/>
+      <c r="G36" s="296" t="n">
+        <f aca="false">SUM(G34:G35)</f>
+        <v>10.242</v>
+      </c>
+      <c r="H36" s="295"/>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21"/>
+      <c r="B37" s="294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C37" s="294"/>
+      <c r="D37" s="294"/>
+      <c r="E37" s="294"/>
+      <c r="F37" s="294"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B38" s="295" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C38" s="285" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D38" s="295"/>
+      <c r="E38" s="306" t="n">
+        <f aca="false">$D$17</f>
+        <v>0.0489043731231231</v>
+      </c>
+      <c r="F38" s="290" t="n">
+        <f aca="false">13.9/1.18</f>
+        <v>11.7796610169492</v>
+      </c>
+      <c r="G38" s="290" t="n">
+        <f aca="false">E38*F38</f>
+        <v>0.57607693763679</v>
+      </c>
+      <c r="H38" s="149" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B39" s="295" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C39" s="285" t="s">
+        <v>981</v>
+      </c>
+      <c r="D39" s="295"/>
+      <c r="E39" s="306" t="n">
+        <f aca="false">$D$20*$D$21</f>
+        <v>0.0557976216216216</v>
+      </c>
+      <c r="F39" s="290" t="n">
+        <f aca="false">17.7/1.18</f>
+        <v>15.0</v>
+      </c>
+      <c r="G39" s="290" t="n">
+        <f aca="false">E39*F39</f>
+        <v>0.836964324324325</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B40" s="295" t="s">
+        <v>946</v>
+      </c>
+      <c r="C40" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="295"/>
+      <c r="E40" s="306" t="n">
+        <f aca="false">$D$20*$D$22</f>
+        <v>0.00117175005405405</v>
+      </c>
+      <c r="F40" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <v>40.68</v>
+      </c>
+      <c r="G40" s="290" t="n">
+        <f aca="false">E40*F40</f>
+        <v>0.0476667921989189</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21"/>
+      <c r="B41" s="294" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C41" s="295"/>
+      <c r="D41" s="295"/>
+      <c r="E41" s="295"/>
+      <c r="F41" s="295"/>
+      <c r="G41" s="296" t="n">
+        <f aca="false">SUM(G38:G40)</f>
+        <v>1.46070805416003</v>
+      </c>
+      <c r="H41" s="295"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21"/>
+      <c r="B42" s="294" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C42" s="294"/>
+      <c r="D42" s="294"/>
+      <c r="E42" s="294"/>
+      <c r="F42" s="294"/>
+      <c r="G42" s="294"/>
+      <c r="H42" s="294"/>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B43" s="295" t="s">
+        <v>969</v>
+      </c>
+      <c r="C43" s="285" t="s">
+        <v>970</v>
+      </c>
+      <c r="D43" s="295"/>
+      <c r="E43" s="284" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="290" t="n">
+        <f aca="false">+G36</f>
+        <v>10.242</v>
+      </c>
+      <c r="G43" s="290" t="n">
+        <f aca="false">E43*F43</f>
+        <v>0.30726</v>
+      </c>
+      <c r="H43" s="149" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21"/>
+      <c r="B44" s="294" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C44" s="295"/>
+      <c r="D44" s="295"/>
+      <c r="E44" s="295"/>
+      <c r="F44" s="295"/>
+      <c r="G44" s="296" t="n">
+        <f aca="false">SUM(G43:G43)</f>
+        <v>0.30726</v>
+      </c>
+      <c r="H44" s="295"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="294" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B45" s="294"/>
+      <c r="C45" s="294"/>
+      <c r="D45" s="294"/>
+      <c r="E45" s="294"/>
+      <c r="F45" s="294"/>
+      <c r="G45" s="296" t="n">
+        <f aca="false">+G36+G41+G44</f>
+        <v>12.00996805416</v>
+      </c>
+      <c r="H45" s="295"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="294" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
+      <c r="D46" s="294"/>
+      <c r="E46" s="294"/>
+      <c r="F46" s="294"/>
+      <c r="G46" s="296" t="n">
+        <f aca="false">G45*C30</f>
+        <v>1208.68318497067</v>
+      </c>
+      <c r="H46" s="295"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="278"/>
+      <c r="C2" s="279" t="str">
+        <f aca="false">+RESUMEN!B4</f>
+        <v>GERENCIA TERRITORIAL BAJO MAYO - TARAPOTO</v>
+      </c>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+    </row>
+    <row r="3" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="278"/>
+      <c r="C3" s="279" t="str">
+        <f aca="false">+RESUMEN!B5</f>
+        <v>“CREACIÓN DEL SERVICIO DE PROTECCIÓN A MUJERES VÍCTIMAS DE VIOLENCIA EN SITUACIÓN DE RIESGO DE FEMINICIDIO O PELIGRE SU INTEGRIDAD Y/O SALUD FÍSICA Y/O MENTAL EN HOGAR DE REFUGIO TEMPORAL DISTRITO DE MORALES DE LA PROVINCIA DE SAN MARTÍN DEL DEPARTAMENTO DE SAN MARTÍN”, con CUI N.° 2675514</v>
+      </c>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="278"/>
+      <c r="C4" s="279" t="str">
+        <f aca="false">+RESUMEN!B6</f>
+        <v>SAN MARTIN - SAN MARTIN - MORALES</v>
+      </c>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="278"/>
+      <c r="C5" s="280" t="n">
+        <f aca="false">+RESUMEN!B7</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="294" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C11" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="306" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F15</f>
+        <v>58.805</v>
+      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="149" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C12" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="309" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="149" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="306" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F16+'COLECTOR JUNTAS Y EMPALMES'!F17+'COLECTOR JUNTAS Y EMPALMES'!F18</f>
+        <v>152.174</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="149" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="149" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C14" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="309" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="149" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="149" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C15" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="306" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
+        <v>210.979</v>
+      </c>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
+      <c r="H15" s="149" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C16" s="285" t="s">
+        <v>602</v>
+      </c>
+      <c r="D16" s="306" t="n">
+        <f aca="false">(D11*D12+D13*D14)/D15</f>
+        <v>0.322979538247883</v>
+      </c>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="149" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D17" s="309" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D18" s="309" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D19" s="306" t="n">
+        <f aca="false">D16*(1+D17)/D18</f>
+        <v>0.117752956652874</v>
+      </c>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D20" s="306" t="n">
+        <f aca="false">0.0254*0.0508</f>
+        <v>0.00129032</v>
+      </c>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D21" s="309" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D22" s="309" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C23" s="285" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D23" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G74</f>
+        <v>0.1</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="149" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="283" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C24" s="285" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D24" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G76</f>
+        <v>0.05</v>
+      </c>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
+      <c r="H24" s="149" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="294" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B26" s="294"/>
+      <c r="C26" s="294"/>
+      <c r="D26" s="294"/>
+      <c r="E26" s="294"/>
+      <c r="F26" s="294"/>
+      <c r="G26" s="294"/>
+      <c r="H26" s="294"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B27" s="294"/>
+      <c r="C27" s="295" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D27" s="295"/>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="295"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="294" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B28" s="294"/>
+      <c r="C28" s="295" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D28" s="295"/>
+      <c r="E28" s="295"/>
+      <c r="F28" s="295"/>
+      <c r="G28" s="295"/>
+      <c r="H28" s="295"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="294" t="s">
+        <v>502</v>
+      </c>
+      <c r="B29" s="294"/>
+      <c r="C29" s="295" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="295"/>
+      <c r="E29" s="295"/>
+      <c r="F29" s="295"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="294" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B30" s="294"/>
+      <c r="C30" s="290" t="n">
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
+        <v>210.979</v>
+      </c>
+      <c r="D30" s="290"/>
+      <c r="E30" s="290"/>
+      <c r="F30" s="290"/>
+      <c r="G30" s="290"/>
+      <c r="H30" s="290"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="294" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B31" s="294"/>
+      <c r="C31" s="290" t="n">
+        <f aca="false">8/E34</f>
+        <v>160.0</v>
+      </c>
+      <c r="D31" s="290"/>
+      <c r="E31" s="290"/>
+      <c r="F31" s="290"/>
+      <c r="G31" s="290"/>
+      <c r="H31" s="290"/>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B32" s="282" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C32" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="282" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E32" s="282" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F32" s="282" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G32" s="282" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H32" s="282" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21"/>
+      <c r="B33" s="294" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C33" s="294"/>
+      <c r="D33" s="294"/>
+      <c r="E33" s="294"/>
+      <c r="F33" s="294"/>
+      <c r="G33" s="294"/>
+      <c r="H33" s="294"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B34" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="C34" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D34" s="306" t="n">
+        <f aca="false">E34*$C$31/8</f>
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="306" t="n">
+        <f aca="false">$D$24</f>
+        <v>0.05</v>
+      </c>
+      <c r="F34" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F69</f>
+        <v>30.42</v>
+      </c>
+      <c r="G34" s="290" t="n">
+        <f aca="false">E34*F34</f>
+        <v>1.521</v>
+      </c>
+      <c r="H34" s="149" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B35" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="C35" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D35" s="306" t="n">
+        <f aca="false">E35*$C$31/8</f>
+        <v>2.0</v>
+      </c>
+      <c r="E35" s="306" t="n">
+        <f aca="false">$D$23</f>
+        <v>0.1</v>
+      </c>
+      <c r="F35" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F71</f>
+        <v>20.79</v>
+      </c>
+      <c r="G35" s="290" t="n">
+        <f aca="false">E35*F35</f>
+        <v>2.079</v>
+      </c>
+      <c r="H35" s="149" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21"/>
+      <c r="B36" s="294" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C36" s="295"/>
+      <c r="D36" s="295"/>
+      <c r="E36" s="295"/>
+      <c r="F36" s="295"/>
+      <c r="G36" s="296" t="n">
+        <f aca="false">SUM(G34:G35)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H36" s="295"/>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21"/>
+      <c r="B37" s="294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C37" s="294"/>
+      <c r="D37" s="294"/>
+      <c r="E37" s="294"/>
+      <c r="F37" s="294"/>
+      <c r="G37" s="294"/>
+      <c r="H37" s="294"/>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B38" s="295" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C38" s="285" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D38" s="295"/>
+      <c r="E38" s="306" t="n">
+        <f aca="false">$D$19</f>
+        <v>0.117752956652874</v>
+      </c>
+      <c r="F38" s="290" t="n">
+        <f aca="false">13.9/1.18</f>
+        <v>11.7796610169492</v>
+      </c>
+      <c r="G38" s="290" t="n">
+        <f aca="false">E38*F38</f>
+        <v>1.38708991311436</v>
+      </c>
+      <c r="H38" s="149" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B39" s="295" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C39" s="285" t="s">
+        <v>981</v>
+      </c>
+      <c r="D39" s="295"/>
+      <c r="E39" s="306" t="n">
+        <f aca="false">$D$20*$D$21</f>
+        <v>0.064516</v>
+      </c>
+      <c r="F39" s="290" t="n">
+        <f aca="false">17.7/1.18</f>
+        <v>15.0</v>
+      </c>
+      <c r="G39" s="290" t="n">
+        <f aca="false">E39*F39</f>
+        <v>0.96774</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B40" s="295" t="s">
+        <v>946</v>
+      </c>
+      <c r="C40" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="295"/>
+      <c r="E40" s="306" t="n">
+        <f aca="false">$D$20*$D$22</f>
+        <v>0.001354836</v>
+      </c>
+      <c r="F40" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <v>40.68</v>
+      </c>
+      <c r="G40" s="290" t="n">
+        <f aca="false">E40*F40</f>
+        <v>0.05511472848</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21"/>
+      <c r="B41" s="294" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C41" s="295"/>
+      <c r="D41" s="295"/>
+      <c r="E41" s="295"/>
+      <c r="F41" s="295"/>
+      <c r="G41" s="296" t="n">
+        <f aca="false">SUM(G38:G40)</f>
+        <v>2.40994464159436</v>
+      </c>
+      <c r="H41" s="295"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21"/>
+      <c r="B42" s="294" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C42" s="294"/>
+      <c r="D42" s="294"/>
+      <c r="E42" s="294"/>
+      <c r="F42" s="294"/>
+      <c r="G42" s="294"/>
+      <c r="H42" s="294"/>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B43" s="295" t="s">
+        <v>969</v>
+      </c>
+      <c r="C43" s="285" t="s">
+        <v>970</v>
+      </c>
+      <c r="D43" s="295"/>
+      <c r="E43" s="284" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F43" s="290" t="n">
+        <f aca="false">+G36</f>
+        <v>3.6</v>
+      </c>
+      <c r="G43" s="290" t="n">
+        <f aca="false">E43*F43</f>
+        <v>0.108</v>
+      </c>
+      <c r="H43" s="149" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21"/>
+      <c r="B44" s="294" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C44" s="295"/>
+      <c r="D44" s="295"/>
+      <c r="E44" s="295"/>
+      <c r="F44" s="295"/>
+      <c r="G44" s="296" t="n">
+        <f aca="false">SUM(G43:G43)</f>
+        <v>0.108</v>
+      </c>
+      <c r="H44" s="295"/>
+    </row>
+    <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="294" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B45" s="294"/>
+      <c r="C45" s="294"/>
+      <c r="D45" s="294"/>
+      <c r="E45" s="294"/>
+      <c r="F45" s="294"/>
+      <c r="G45" s="296" t="n">
+        <f aca="false">+G36+G41+G44</f>
+        <v>6.11794464159436</v>
+      </c>
+      <c r="H45" s="295"/>
+    </row>
+    <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="294" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B46" s="294"/>
+      <c r="C46" s="294"/>
+      <c r="D46" s="294"/>
+      <c r="E46" s="294"/>
+      <c r="F46" s="294"/>
+      <c r="G46" s="296" t="n">
+        <f aca="false">G45*C30</f>
+        <v>1290.75784253894</v>
+      </c>
+      <c r="H46" s="295"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -36,6 +36,7 @@
     <sheet name="DESAGREGADO TAPA REGISTRO" sheetId="26" state="visible" r:id="rId28"/>
     <sheet name="ACU JUNTA DILATACION" sheetId="27" state="visible" r:id="rId30"/>
     <sheet name="ACU JUNTA CERCO" sheetId="28" state="visible" r:id="rId31"/>
+    <sheet name="DESAGREGADO LLORADEROS" sheetId="29" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="24" name="_xlnm.Print_Area" vbProcedure="false">'ACU CANALETAS'!$A$1:$H$111</definedName>
@@ -512,7 +513,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1334">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4406,6 +4407,126 @@
   </si>
   <si>
     <t xml:space="preserve">Rendimiento (m/dia, operario de sellado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO DE LA PARTIDA 01.04.03.04.03.04 - LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La partida se mide por unidad de lloradero. A: ubicacion y numero, de la hoja METRADO LLORADEROS (muros de cuneta colindantes con area verde, medidos en la planta general de drenaje; un lloradero cada 1.50 m). B: componentes de un lloradero segun las laminas DL-01 y DL-02 (tubo PVC-U Ø 3" de 0.30 m con 8 perforaciones Ø 3/8", filtro de grava de 0.30 x 0.30 x 0.30 m forrado con geotextil no tejido) por el numero de lloraderos. Celda amarilla = dato; verde = formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. UBICACION Y NUMERO DE LLORADEROS (hoja METRADO LLORADEROS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EJE Y TRAMO (progresivas de la cuneta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONGITUD JUNTO A AREA VERDE (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPACIAM. (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planta general de drenaje; N° = REDONDEAR.MAS(L / 1.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL (und de la partida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. DATOS DEL DETALLE (laminas DL-01 y DL-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado del filtro localizado (cubo de grava forrado con geotextil)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 A: filtro 0.30 x 0.30 x 0.30 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitud del tubo PVC-U Ø 3" por lloradero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 B: 0.10 en el muro + 0.20 perforado dentro del filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perforaciones Ø 3/8" por fila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 B: 4 perforaciones @0.05 por fila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filas de perforaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 B: 2 filas a 120 grados, simetricas respecto al fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio de grava (acomodo y perdidas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio de obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traslapes del geotextil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-01 etapa 3: traslape de 0.10 m al cerrar el filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortero 1:3 de sellado alrededor del tubo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anillo de 0.02 m en las dos caras del muro (DL-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. COMPONENTES DE UN LLORADERO Y TOTAL DE LA PARTIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POR LLORADERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° LLORADEROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubo PVC-U Ø 3" para desague (NTP 399.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 B; sale de tubos de 3 m (10 lloraderos por tubo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perforaciones Ø 3/8" en el tramo dentro del filtro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02 B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavacion local del hueco del filtro (lado^3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-01 etapa 1; incluida en la mano de obra del ACU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grava filtrante (ripio) 20 a 40 mm: lado^3 + desperdicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-01 etapa 2; DL-02 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geotextil no tejido clase 2: 6 caras del cubo + traslapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-01 etapa 3; DL-02 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. CONTROL CON EL RESUMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESUMEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.03.04.03.04 LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m</t>
   </si>
 </sst>
 </file>
@@ -34082,6 +34203,959 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H46"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="278"/>
+      <c r="C2" s="279" t="str">
+        <f aca="false">+RESUMEN!B4</f>
+        <v>GERENCIA TERRITORIAL BAJO MAYO - TARAPOTO</v>
+      </c>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+    </row>
+    <row r="3" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="278"/>
+      <c r="C3" s="279" t="str">
+        <f aca="false">+RESUMEN!B5</f>
+        <v>“CREACIÓN DEL SERVICIO DE PROTECCIÓN A MUJERES VÍCTIMAS DE VIOLENCIA EN SITUACIÓN DE RIESGO DE FEMINICIDIO O PELIGRE SU INTEGRIDAD Y/O SALUD FÍSICA Y/O MENTAL EN HOGAR DE REFUGIO TEMPORAL DISTRITO DE MORALES DE LA PROVINCIA DE SAN MARTÍN DEL DEPARTAMENTO DE SAN MARTÍN”, con CUI N.° 2675514</v>
+      </c>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="278"/>
+      <c r="C4" s="279" t="str">
+        <f aca="false">+RESUMEN!B6</f>
+        <v>SAN MARTIN - SAN MARTIN - MORALES</v>
+      </c>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="278"/>
+      <c r="C5" s="280" t="n">
+        <f aca="false">+RESUMEN!B7</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="294" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>460</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E10" s="282" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F10" s="282" t="s">
+        <v>463</v>
+      </c>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B7&amp;": "&amp;'METRADO LLORADEROS'!C7</f>
+        <v>EJE 01: 0+000.00 a 0+037.00</v>
+      </c>
+      <c r="C11" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D7</f>
+        <v>LADO ESTE</v>
+      </c>
+      <c r="D11" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E7</f>
+        <v>37.0</v>
+      </c>
+      <c r="E11" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F7</f>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G7</f>
+        <v>25.0</v>
+      </c>
+      <c r="G11" s="295"/>
+      <c r="H11" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B8&amp;": "&amp;'METRADO LLORADEROS'!C8</f>
+        <v>EJE 01: 0+032.25 a 0+037.00</v>
+      </c>
+      <c r="C12" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D8</f>
+        <v>LADO OESTE</v>
+      </c>
+      <c r="D12" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E8</f>
+        <v>4.75</v>
+      </c>
+      <c r="E12" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F8</f>
+        <v>1.5</v>
+      </c>
+      <c r="F12" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G8</f>
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="295"/>
+      <c r="H12" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B9&amp;": "&amp;'METRADO LLORADEROS'!C9</f>
+        <v>EJE 02: 0+040.62 a 0+045.37</v>
+      </c>
+      <c r="C13" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D9</f>
+        <v>LADO SUR</v>
+      </c>
+      <c r="D13" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E9</f>
+        <v>4.75</v>
+      </c>
+      <c r="E13" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F9</f>
+        <v>1.5</v>
+      </c>
+      <c r="F13" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G9</f>
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="295"/>
+      <c r="H13" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B10&amp;": "&amp;'METRADO LLORADEROS'!C10</f>
+        <v>EJE 07: 0+040.62 a 0+042.87</v>
+      </c>
+      <c r="C14" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D10</f>
+        <v>LADO SUR</v>
+      </c>
+      <c r="D14" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E10</f>
+        <v>2.25</v>
+      </c>
+      <c r="E14" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F10</f>
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G10</f>
+        <v>2.0</v>
+      </c>
+      <c r="G14" s="295"/>
+      <c r="H14" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B11&amp;": "&amp;'METRADO LLORADEROS'!C11</f>
+        <v>EJE 07: 0+123.97 a 0+125.70</v>
+      </c>
+      <c r="C15" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D11</f>
+        <v>LADO ESTE</v>
+      </c>
+      <c r="D15" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E11</f>
+        <v>1.73</v>
+      </c>
+      <c r="E15" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F11</f>
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G11</f>
+        <v>2.0</v>
+      </c>
+      <c r="G15" s="295"/>
+      <c r="H15" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B12&amp;": "&amp;'METRADO LLORADEROS'!C12</f>
+        <v>EJE 07: 0+123.97 a 0+125.70</v>
+      </c>
+      <c r="C16" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D12</f>
+        <v>LADO OESTE</v>
+      </c>
+      <c r="D16" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E12</f>
+        <v>1.73</v>
+      </c>
+      <c r="E16" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F12</f>
+        <v>1.5</v>
+      </c>
+      <c r="F16" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G12</f>
+        <v>2.0</v>
+      </c>
+      <c r="G16" s="295"/>
+      <c r="H16" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B13&amp;": "&amp;'METRADO LLORADEROS'!C13</f>
+        <v>EJE 09: 0+000.50 a 0+005.00</v>
+      </c>
+      <c r="C17" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D13</f>
+        <v>LADO SUR</v>
+      </c>
+      <c r="D17" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E13</f>
+        <v>4.5</v>
+      </c>
+      <c r="E17" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F13</f>
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G13</f>
+        <v>3.0</v>
+      </c>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B14&amp;": "&amp;'METRADO LLORADEROS'!C14</f>
+        <v>EJE 11: 0+069.05 a 0+071.30</v>
+      </c>
+      <c r="C18" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D14</f>
+        <v>LADO ESTE</v>
+      </c>
+      <c r="D18" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E14</f>
+        <v>2.25</v>
+      </c>
+      <c r="E18" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F14</f>
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G14</f>
+        <v>2.0</v>
+      </c>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B15&amp;": "&amp;'METRADO LLORADEROS'!C15</f>
+        <v>EJE 11: 0+039.50 a 0+062.75</v>
+      </c>
+      <c r="C19" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D15</f>
+        <v>LADO OESTE</v>
+      </c>
+      <c r="D19" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E15</f>
+        <v>23.25</v>
+      </c>
+      <c r="E19" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F15</f>
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G15</f>
+        <v>16.0</v>
+      </c>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B16&amp;": "&amp;'METRADO LLORADEROS'!C16</f>
+        <v>EJE 11: 0+066.80 a 0+071.30</v>
+      </c>
+      <c r="C20" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D16</f>
+        <v>LADO OESTE</v>
+      </c>
+      <c r="D20" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E16</f>
+        <v>4.5</v>
+      </c>
+      <c r="E20" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F16</f>
+        <v>1.5</v>
+      </c>
+      <c r="F20" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G16</f>
+        <v>3.0</v>
+      </c>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B17&amp;": "&amp;'METRADO LLORADEROS'!C17</f>
+        <v>EJE 12: 0+078.50 a 0+109.00</v>
+      </c>
+      <c r="C21" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D17</f>
+        <v>LADO ESTE</v>
+      </c>
+      <c r="D21" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E17</f>
+        <v>30.5</v>
+      </c>
+      <c r="E21" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F17</f>
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G17</f>
+        <v>21.0</v>
+      </c>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="str">
+        <f aca="false">'METRADO LLORADEROS'!B18&amp;": "&amp;'METRADO LLORADEROS'!C18</f>
+        <v>EJE 12: 0+000.00 a 0+109.00</v>
+      </c>
+      <c r="C22" s="285" t="str">
+        <f aca="false">'METRADO LLORADEROS'!D18</f>
+        <v>LADO OESTE</v>
+      </c>
+      <c r="D22" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!E18</f>
+        <v>109.0</v>
+      </c>
+      <c r="E22" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!F18</f>
+        <v>1.5</v>
+      </c>
+      <c r="F22" s="290" t="n">
+        <f aca="false">'METRADO LLORADEROS'!G18</f>
+        <v>73.0</v>
+      </c>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21"/>
+      <c r="B23" s="294" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C23" s="295"/>
+      <c r="D23" s="296" t="n">
+        <f aca="false">SUM(D11:D22)</f>
+        <v>226.21</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="296" t="n">
+        <f aca="false">SUM(F11:F22)</f>
+        <v>157.0</v>
+      </c>
+      <c r="G23" s="295"/>
+      <c r="H23" s="295"/>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="294" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B25" s="294"/>
+      <c r="C25" s="294"/>
+      <c r="D25" s="294"/>
+      <c r="E25" s="294"/>
+      <c r="F25" s="294"/>
+      <c r="G25" s="294"/>
+      <c r="H25" s="294"/>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B26" s="282" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C26" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="282" t="s">
+        <v>292</v>
+      </c>
+      <c r="E26" s="282"/>
+      <c r="F26" s="282"/>
+      <c r="G26" s="282"/>
+      <c r="H26" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C27" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="307" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="149" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C28" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="307" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E28" s="295"/>
+      <c r="F28" s="295"/>
+      <c r="G28" s="295"/>
+      <c r="H28" s="149" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B29" s="149" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C29" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="307" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="E29" s="295"/>
+      <c r="F29" s="295"/>
+      <c r="G29" s="295"/>
+      <c r="H29" s="149" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B30" s="149" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C30" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="307" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="149" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B31" s="149" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C31" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D31" s="307" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E31" s="295"/>
+      <c r="F31" s="295"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="149" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B32" s="149" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C32" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D32" s="307" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="295"/>
+      <c r="F32" s="295"/>
+      <c r="G32" s="295"/>
+      <c r="H32" s="149" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B33" s="149" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C33" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="307" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="E33" s="295"/>
+      <c r="F33" s="295"/>
+      <c r="G33" s="295"/>
+      <c r="H33" s="149" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="294" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B35" s="294"/>
+      <c r="C35" s="294"/>
+      <c r="D35" s="294"/>
+      <c r="E35" s="294"/>
+      <c r="F35" s="294"/>
+      <c r="G35" s="294"/>
+      <c r="H35" s="294"/>
+    </row>
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="282" t="s">
+        <v>992</v>
+      </c>
+      <c r="C36" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="282" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E36" s="282" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F36" s="282" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" s="282"/>
+      <c r="H36" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B37" s="149" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C37" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="306" t="n">
+        <f aca="false">$D$28</f>
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F37" s="306" t="n">
+        <f aca="false">D37*E37</f>
+        <v>47.1</v>
+      </c>
+      <c r="G37" s="295"/>
+      <c r="H37" s="149" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B38" s="149" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C38" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D38" s="306" t="n">
+        <f aca="false">$D$29*$D$30</f>
+        <v>8.0</v>
+      </c>
+      <c r="E38" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F38" s="306" t="n">
+        <f aca="false">D38*E38</f>
+        <v>1256.0</v>
+      </c>
+      <c r="G38" s="295"/>
+      <c r="H38" s="149" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B39" s="149" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C39" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" s="306" t="n">
+        <f aca="false">$D$27^3</f>
+        <v>0.027</v>
+      </c>
+      <c r="E39" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F39" s="306" t="n">
+        <f aca="false">D39*E39</f>
+        <v>4.239</v>
+      </c>
+      <c r="G39" s="295"/>
+      <c r="H39" s="149" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B40" s="149" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C40" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="306" t="n">
+        <f aca="false">$D$27^3*(1+$D$31)</f>
+        <v>0.0297</v>
+      </c>
+      <c r="E40" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F40" s="306" t="n">
+        <f aca="false">D40*E40</f>
+        <v>4.6629</v>
+      </c>
+      <c r="G40" s="295"/>
+      <c r="H40" s="149" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B41" s="149" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C41" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="306" t="n">
+        <f aca="false">6*$D$27^2*(1+$D$32)</f>
+        <v>0.594</v>
+      </c>
+      <c r="E41" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F41" s="306" t="n">
+        <f aca="false">D41*E41</f>
+        <v>93.258</v>
+      </c>
+      <c r="G41" s="295"/>
+      <c r="H41" s="149" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B42" s="149" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C42" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="306" t="n">
+        <f aca="false">$D$33</f>
+        <v>0.0005</v>
+      </c>
+      <c r="E42" s="290" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F42" s="306" t="n">
+        <f aca="false">D42*E42</f>
+        <v>0.0785</v>
+      </c>
+      <c r="G42" s="295"/>
+      <c r="H42" s="149" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="294" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B44" s="294"/>
+      <c r="C44" s="294"/>
+      <c r="D44" s="294"/>
+      <c r="E44" s="294"/>
+      <c r="F44" s="294"/>
+      <c r="G44" s="294"/>
+      <c r="H44" s="294"/>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="282"/>
+      <c r="B45" s="282" t="s">
+        <v>891</v>
+      </c>
+      <c r="C45" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D45" s="282"/>
+      <c r="E45" s="282" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F45" s="282" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G45" s="282" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H45" s="282"/>
+    </row>
+    <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21"/>
+      <c r="B46" s="149" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C46" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="295"/>
+      <c r="E46" s="306" t="n">
+        <f aca="false">+$F$23</f>
+        <v>157.0</v>
+      </c>
+      <c r="F46" s="306" t="n">
+        <f aca="false">+RESUMEN!D32</f>
+        <v>157.0</v>
+      </c>
+      <c r="G46" s="283" t="str">
+        <f aca="false">IF(ABS(E46-F46)&lt;0.001,"CONFORME","REVISAR")</f>
+        <v>CONFORME</v>
+      </c>
+      <c r="H46" s="295"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A44:H44"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -37,6 +37,8 @@
     <sheet name="ACU JUNTA DILATACION" sheetId="27" state="visible" r:id="rId30"/>
     <sheet name="ACU JUNTA CERCO" sheetId="28" state="visible" r:id="rId31"/>
     <sheet name="DESAGREGADO LLORADEROS" sheetId="29" state="visible" r:id="rId32"/>
+    <sheet name="COSTO HORA HOMBRE 2026" sheetId="30" state="visible" r:id="rId33"/>
+    <sheet name="ACU LLORADEROS" sheetId="31" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="24" name="_xlnm.Print_Area" vbProcedure="false">'ACU CANALETAS'!$A$1:$H$111</definedName>
@@ -513,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1411">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4527,6 +4529,239 @@
   </si>
   <si>
     <t xml:space="preserve">01.04.03.04.03.04 LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borde de la losa con el piso adyacente: colector (un lado, lado via; al lado predio esta el cerco)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-04 y DD-03 D: junta de tecnopor en el borde de la losa superior, lado via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borde de la losa con el piso adyacente: caja CL (un lado, lado via)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 x (largo exterior + 0.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borde de la losa con el piso adyacente: caja CC (un lado, lado via)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (nota 5), DP-03 y DP-06C. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor de 1" en todo el perimetro + sellador asfaltico RC-250 con arena de 1" x 2" en la cara expuesta, EG-2013 secc. 510.02 c y 438.02 e 3). Junta de tecnopor de 1" entre el colector y el cimiento del cerco, y entre el borde de la losa y el piso adyacente (un solo lado, lado via). Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.02 JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO (metrado 01.04.04.06.02, hoja COLECTOR JUNTAS Y EMPALMES). Cantidades de la lamina DD-03: plancha de tecnopor de 1" de 0.90 m de altura contra el cimiento del cerco y de 0.10 m en el borde de la losa con el piso adyacente (un solo lado, lado via), con sellador asfaltico 1" x 2" (RC-250 + arena) en la cara superior. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junta en el borde de la losa con el piso adyacente, un lado (colector y cajas CL y CC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLANILLA DE METRADOS - JUNTA DE DILATACIÓN E=1" (0.0254 m) CON SELLADOR ASFÁLTICO EN CUNETAS: TODA LA SECCIÓN (2 MUROS + LOSA DE FONDO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancho interior del fondo de la cuneta (m): la junta cruza también la losa de fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG. POR
+JUNTA (m)
+2 muros + fondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTAS:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. EG-2013 MTC, Seccion 510 (cunetas revestidas de concreto): la junta corta toda la seccion en U, es decir los dos muros y la losa de fondo, para que cada pano de 3.00 m trabaje independiente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Longitud por junta = 2 x altura del muro (area del muro / longitud del eje, hoja CONCRETO EN CUNETAS) + ancho interior del fondo 0.40 m.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Junta e = 1" (0.0254 m): tecnopor de 1" en todo el espesor y sellador asfaltico (RC-250 + arena) en la cara interior; se mide en metros lineales de junta sellada. Detalle en la lamina DJ-01.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO DE LA HORA-HOMBRE 2026 - REGIMEN DE CONSTRUCCION CIVIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo de la hora-hombre que usan todas las ACU de la planilla. Jornal basico 2026: R.M. 197-2025-TR (convenio CAPECO - FTCCP). El costo hora-hombre de CAPECO (jornal + leyes y beneficios sociales + BUC + movilidad + ropa de trabajo) se lleva al jornal 2026 con la misma estructura: costo 2026 = costo 2024-2025 x jornal 2026 / jornal 2024-2025. Celda amarilla = dato; verde = formula. Cuando CAPECO publique la tabla 2026 se cambian solo las celdas amarillas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. COSTO HORA-HOMBRE POR CATEGORIA (S/ por hora)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATEGORIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORNAL BASICO 2024-2025 (S/ dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO HH CAPECO 2024-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACTOR HH / JORNAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORNAL BASICO 2026 (S/ dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO HH 2026 (S/ hh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUENTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jornal: R.M. 197-2025-TR (El Peruano, 19/12/2025) y tabla salarial 2026 FTCCP: jornal basico desde el 01/01/2026. Costo HH: CAPECO: tabla de costo hora-hombre pliego 2024-2025 (jornales 86.80 / 68.10 / 61.30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. COMPONENTES QUE INCLUYE EL COSTO HORA-HOMBRE (estructura CAPECO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jornal basico por 8 horas de labor (operario, oficial y peon).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leyes y beneficios sociales sobre el jornal basico (descanso dominical, feriados, vacaciones, gratificaciones, CTS, ESSALUD y otros), segun la tabla CAPECO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonificacion unificada de construccion (BUC): 32 % del jornal del operario y 30 % del oficial y del peon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonificacion por movilidad acumulada (S/ 8.60 por dia en la tabla FTCCP 2026) y ropa de trabajo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No incluye horas extras, trabajo en altura ni bonificacion por alta especializacion (no se usan en estas partidas).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoja COSTO HORA HOMBRE 2026 (CAPECO, jornal R.M. 197-2025-TR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.03.04.03.04 LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m (CUNETA COLINDANTE CON AREA VERDE) (metrado: hojas METRADO LLORADEROS y DESAGREGADO LLORADEROS). Cantidades por lloradero de las laminas DL-01 y DL-02: tubo PVC-U Ø 3" de 0.30 m con 8 perforaciones Ø 3/8", filtro de grava de 0.30 x 0.30 x 0.30 m forrado con geotextil no tejido y mortero 1:3 de sellado. Mano de obra de la hoja COSTO HORA HOMBRE 2026. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. CANTIDADES POR LLORADERO (hoja DESAGREGADO LLORADEROS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de lloraderos de la partida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO LLORADEROS fila 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubo PVC-U Ø 3" por lloradero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO LLORADEROS fila 37 (DL-02 B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio del tubo (corte de 10 piezas por tubo de 3 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grava filtrante por lloradero (incluye 10 % de desperdicio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO LLORADEROS fila 40 (DL-02 A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geotextil por lloradero (6 caras + 10 % de traslapes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO LLORADEROS fila 41 (DL-01 etapa 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio del geotextil (corte del rollo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO LLORADEROS fila 42 (DL-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento por m3 de mortero 1:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bol/m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dosificacion usual del mortero 1:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa por m3 de mortero 1:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arena suelta con 5 % de desperdicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua por m3 de mortero 1:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento de la cuadrilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">und/dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excavacion local de 0.027 m3, forrado, grava y cierre; el tubo se deja al vaciar el muro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operarios en la cuadrilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colocacion del tubo, sellado y control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peones en la cuadrilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excavacion, grava y relleno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.03.04.03.04 LLORADERO DE TUBERIA PVC Ø3" C/FILTRO DE GRAVA Y GEOTEXTIL @1.50 m (CUNETA COLINDANTE CON AREA VERDE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.03.04.03.04 (hojas METRADO LLORADEROS y DESAGREGADO LLORADEROS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendimiento (und/dia, cuadrilla 0.5 operario + 1 peon)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANTIDAD POR UND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubo PVC-U Ø 3" desague (NTP 399.003)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodimac Peru y Promart: tubo desague PVC 3" x 3 m liviano Pavco S/ 39.90 con IGV (S/ 11.27 el m sin IGV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grava filtrante 20 a 40 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregados Tarapoto (Morales): piedra chancada 3/4" S/ 70.00 el m3 puesto en obra (precio publicado mas cercano a la grava 20 a 40 mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geotextil no tejido 200 g/m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ferropolis Peru: geotextil no tejido 200 g/m2, rollo de 4 x 100 m S/ 2,300.00 (S/ 5.75 el m2 con IGV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio de la ACU TAPA REGISTRO (Cemento Pacasmayo tipo I S/ 36.50 con IGV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">precio de la ACU TAPA REGISTRO (EMAPA San Martin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 % del costo de mano de obra (pala, pico, barreta, sierra para PVC y taladro para las perforaciones)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. EG-2013 MTC, Seccion 510 (cunetas revestidas de concreto): la junta corta toda la seccion en U, es decir los dos muros y la losa de fondo, para que cada paño de 3.00 m trabaje independiente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancho interior del fondo (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORNAL 2024-2025 (S/ dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jornal 2026: R.M. 197-2025-TR (FTCCP). Costo HH: tabla CAPECO 2024-2025</t>
   </si>
 </sst>
 </file>
@@ -7333,7 +7568,7 @@
       </c>
       <c r="D30" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K133</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7348,7 +7583,7 @@
       </c>
       <c r="D31" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K134</f>
-        <v>241.959543966302</v>
+        <v>335.159543966302</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7363,7 +7598,7 @@
       </c>
       <c r="D32" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K135</f>
-        <v>157</v>
+        <v>157.0</v>
       </c>
       <c r="G32" s="0"/>
     </row>
@@ -7414,7 +7649,7 @@
       </c>
       <c r="D36" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K140</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7489,7 +7724,7 @@
       </c>
       <c r="D41" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K150</f>
-        <v>884</v>
+        <v>884.0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7504,7 +7739,7 @@
       </c>
       <c r="D42" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K151</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7519,7 +7754,7 @@
       </c>
       <c r="D43" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K152</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7559,7 +7794,7 @@
       </c>
       <c r="D46" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K156</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7574,7 +7809,7 @@
       </c>
       <c r="D47" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K157</f>
-        <v>24</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7589,7 +7824,7 @@
       </c>
       <c r="D48" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K158</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7614,7 +7849,7 @@
       </c>
       <c r="D50" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K161</f>
-        <v>162</v>
+        <v>162.0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7629,7 +7864,7 @@
       </c>
       <c r="D51" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K162</f>
-        <v>90</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7644,7 +7879,7 @@
       </c>
       <c r="D52" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K163</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7899,7 +8134,7 @@
       </c>
       <c r="D72" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K313</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7939,7 +8174,7 @@
       </c>
       <c r="D75" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K322</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
     </row>
   </sheetData>
@@ -8088,7 +8323,7 @@
       </c>
       <c r="G7" s="224" t="n">
         <f aca="false">IF(B7="","",IF(D7="ABIERTA",IF(E7-F7&lt;0,0,E7-F7),0))</f>
-        <v>32</v>
+        <v>32.0</v>
       </c>
       <c r="H7" s="225" t="s">
         <v>57</v>
@@ -8115,7 +8350,7 @@
       </c>
       <c r="G8" s="224" t="n">
         <f aca="false">IF(B8="","",IF(D8="ABIERTA",IF(E8-F8&lt;0,0,E8-F8),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H8" s="225" t="s">
         <v>57</v>
@@ -8169,7 +8404,7 @@
       </c>
       <c r="G10" s="224" t="n">
         <f aca="false">IF(B10="","",IF(D10="ABIERTA",IF(E10-F10&lt;0,0,E10-F10),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H10" s="225" t="s">
         <v>57</v>
@@ -8223,7 +8458,7 @@
       </c>
       <c r="G12" s="224" t="n">
         <f aca="false">IF(B12="","",IF(D12="ABIERTA",IF(E12-F12&lt;0,0,E12-F12),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H12" s="225" t="s">
         <v>57</v>
@@ -8277,7 +8512,7 @@
       </c>
       <c r="G14" s="224" t="n">
         <f aca="false">IF(B14="","",IF(D14="ABIERTA",IF(E14-F14&lt;0,0,E14-F14),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H14" s="225" t="s">
         <v>57</v>
@@ -8304,7 +8539,7 @@
       </c>
       <c r="G15" s="224" t="n">
         <f aca="false">IF(B15="","",IF(D15="ABIERTA",IF(E15-F15&lt;0,0,E15-F15),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H15" s="225" t="s">
         <v>57</v>
@@ -8412,7 +8647,7 @@
       </c>
       <c r="G19" s="224" t="n">
         <f aca="false">IF(B19="","",IF(D19="ABIERTA",IF(E19-F19&lt;0,0,E19-F19),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H19" s="225" t="s">
         <v>57</v>
@@ -8466,7 +8701,7 @@
       </c>
       <c r="G21" s="224" t="n">
         <f aca="false">IF(B21="","",IF(D21="ABIERTA",IF(E21-F21&lt;0,0,E21-F21),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H21" s="225" t="s">
         <v>57</v>
@@ -8520,7 +8755,7 @@
       </c>
       <c r="G23" s="224" t="n">
         <f aca="false">IF(B23="","",IF(D23="ABIERTA",IF(E23-F23&lt;0,0,E23-F23),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" s="225" t="s">
         <v>57</v>
@@ -8574,7 +8809,7 @@
       </c>
       <c r="G25" s="224" t="n">
         <f aca="false">IF(B25="","",IF(D25="ABIERTA",IF(E25-F25&lt;0,0,E25-F25),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H25" s="225" t="s">
         <v>57</v>
@@ -8628,7 +8863,7 @@
       </c>
       <c r="G27" s="224" t="n">
         <f aca="false">IF(B27="","",IF(D27="ABIERTA",IF(E27-F27&lt;0,0,E27-F27),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" s="225" t="s">
         <v>57</v>
@@ -8655,7 +8890,7 @@
       </c>
       <c r="G28" s="224" t="n">
         <f aca="false">IF(B28="","",IF(D28="ABIERTA",IF(E28-F28&lt;0,0,E28-F28),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H28" s="225" t="s">
         <v>57</v>
@@ -8682,7 +8917,7 @@
       </c>
       <c r="G29" s="224" t="n">
         <f aca="false">IF(B29="","",IF(D29="ABIERTA",IF(E29-F29&lt;0,0,E29-F29),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="225" t="s">
         <v>57</v>
@@ -8709,7 +8944,7 @@
       </c>
       <c r="G30" s="224" t="n">
         <f aca="false">IF(B30="","",IF(D30="ABIERTA",IF(E30-F30&lt;0,0,E30-F30),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" s="225" t="s">
         <v>57</v>
@@ -8736,7 +8971,7 @@
       </c>
       <c r="G31" s="224" t="n">
         <f aca="false">IF(B31="","",IF(D31="ABIERTA",IF(E31-F31&lt;0,0,E31-F31),0))</f>
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H31" s="225" t="s">
         <v>57</v>
@@ -8790,7 +9025,7 @@
       </c>
       <c r="G33" s="224" t="n">
         <f aca="false">IF(B33="","",IF(D33="ABIERTA",IF(E33-F33&lt;0,0,E33-F33),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" s="225" t="s">
         <v>57</v>
@@ -8817,7 +9052,7 @@
       </c>
       <c r="G34" s="224" t="n">
         <f aca="false">IF(B34="","",IF(D34="ABIERTA",IF(E34-F34&lt;0,0,E34-F34),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H34" s="225" t="s">
         <v>57</v>
@@ -8871,7 +9106,7 @@
       </c>
       <c r="G36" s="224" t="n">
         <f aca="false">IF(B36="","",IF(D36="ABIERTA",IF(E36-F36&lt;0,0,E36-F36),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H36" s="225" t="s">
         <v>57</v>
@@ -8934,7 +9169,7 @@
     <tabColor rgb="FF92D050"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="8.63671875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="228" width="24.91"/>
@@ -8946,7 +9181,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="229" t="s">
-        <v>442</v>
+        <v>1342</v>
       </c>
       <c r="B1" s="229"/>
       <c r="C1" s="229"/>
@@ -9049,10 +9284,10 @@
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="237" t="s">
-        <v>446</v>
-      </c>
-      <c r="B10" s="237" t="s">
-        <v>447</v>
+        <v>1408</v>
+      </c>
+      <c r="B10" s="236" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9081,7 +9316,7 @@
         <v>453</v>
       </c>
       <c r="I11" s="238" t="s">
-        <v>454</v>
+        <v>1344</v>
       </c>
       <c r="J11" s="238" t="s">
         <v>455</v>
@@ -9105,7 +9340,7 @@
       <c r="I12" s="240"/>
       <c r="J12" s="240" t="n">
         <f aca="false">SUM(J13:J24)</f>
-        <v>241.959543966302</v>
+        <v>335.159543966302</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9129,19 +9364,19 @@
       </c>
       <c r="G13" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H13" s="242" t="n">
         <f aca="false">ROUNDUP(D13/G13,0)</f>
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="I13" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F13+$B$10</f>
+        <v>1.15767366720517</v>
       </c>
       <c r="J13" s="242" t="n">
-        <f aca="false">H13*I13*F13</f>
-        <v>9.8497576736672</v>
+        <f aca="false">H13*I13</f>
+        <v>15.0497576736672</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9165,19 +9400,19 @@
       </c>
       <c r="G14" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H14" s="242" t="n">
         <f aca="false">ROUNDUP(D14/G14,0)</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="I14" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F14+$B$10</f>
+        <v>1.59709591134887</v>
       </c>
       <c r="J14" s="242" t="n">
-        <f aca="false">H14*I14*F14</f>
-        <v>52.6722200993504</v>
+        <f aca="false">H14*I14</f>
+        <v>70.2722200993504</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9201,19 +9436,19 @@
       </c>
       <c r="G15" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H15" s="242" t="n">
         <f aca="false">ROUNDUP(D15/G15,0)</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F15+$B$10</f>
+        <v>1.02886597938144</v>
       </c>
       <c r="J15" s="242" t="n">
-        <f aca="false">H15*I15*F15</f>
-        <v>1.25773195876289</v>
+        <f aca="false">H15*I15</f>
+        <v>2.05773195876289</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9237,19 +9472,19 @@
       </c>
       <c r="G16" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H16" s="242" t="n">
         <f aca="false">ROUNDUP(D16/G16,0)</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I16" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F16+$B$10</f>
+        <v>1.04186046511628</v>
       </c>
       <c r="J16" s="242" t="n">
-        <f aca="false">H16*I16*F16</f>
-        <v>1.92558139534884</v>
+        <f aca="false">H16*I16</f>
+        <v>3.12558139534884</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9273,19 +9508,19 @@
       </c>
       <c r="G17" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H17" s="242" t="n">
         <f aca="false">ROUNDUP(D17/G17,0)</f>
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="I17" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F17+$B$10</f>
+        <v>1.21887578070784</v>
       </c>
       <c r="J17" s="242" t="n">
-        <f aca="false">H17*I17*F17</f>
-        <v>12.2831367106176</v>
+        <f aca="false">H17*I17</f>
+        <v>18.2831367106176</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9309,19 +9544,19 @@
       </c>
       <c r="G18" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H18" s="242" t="n">
         <f aca="false">ROUNDUP(D18/G18,0)</f>
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="I18" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F18+$B$10</f>
+        <v>1.55852442671984</v>
       </c>
       <c r="J18" s="242" t="n">
-        <f aca="false">H18*I18*F18</f>
-        <v>47.4995014955135</v>
+        <f aca="false">H18*I18</f>
+        <v>63.8995014955135</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9345,19 +9580,19 @@
       </c>
       <c r="G19" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H19" s="242" t="n">
         <f aca="false">ROUNDUP(D19/G19,0)</f>
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="I19" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F19+$B$10</f>
+        <v>1.58536197295147</v>
       </c>
       <c r="J19" s="242" t="n">
-        <f aca="false">H19*I19*F19</f>
-        <v>49.7852028639618</v>
+        <f aca="false">H19*I19</f>
+        <v>66.5852028639618</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9381,19 +9616,19 @@
       </c>
       <c r="G20" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H20" s="242" t="n">
         <f aca="false">ROUNDUP(D20/G20,0)</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I20" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F20+$B$10</f>
+        <v>1.0390243902439</v>
       </c>
       <c r="J20" s="242" t="n">
-        <f aca="false">H20*I20*F20</f>
-        <v>1.91707317073171</v>
+        <f aca="false">H20*I20</f>
+        <v>3.11707317073171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9417,19 +9652,19 @@
       </c>
       <c r="G21" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H21" s="242" t="n">
         <f aca="false">ROUNDUP(D21/G21,0)</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I21" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F21+$B$10</f>
+        <v>1.03428571428571</v>
       </c>
       <c r="J21" s="242" t="n">
-        <f aca="false">H21*I21*F21</f>
-        <v>1.90285714285714</v>
+        <f aca="false">H21*I21</f>
+        <v>3.10285714285714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9453,19 +9688,19 @@
       </c>
       <c r="G22" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H22" s="242" t="n">
         <f aca="false">ROUNDUP(D22/G22,0)</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="I22" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F22+$B$10</f>
+        <v>1.08</v>
       </c>
       <c r="J22" s="242" t="n">
-        <f aca="false">H22*I22*F22</f>
-        <v>4.08</v>
+        <f aca="false">H22*I22</f>
+        <v>6.48</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9481,7 +9716,7 @@
       </c>
       <c r="E23" s="242" t="n">
         <f aca="false">+'CONCRETO EN CUNETAS'!M58</f>
-        <v>33</v>
+        <v>33.0</v>
       </c>
       <c r="F23" s="242" t="n">
         <f aca="false">E23/D23</f>
@@ -9489,19 +9724,19 @@
       </c>
       <c r="G23" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H23" s="242" t="n">
         <f aca="false">ROUNDUP(D23/G23,0)</f>
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="I23" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F23+$B$10</f>
+        <v>1.32359361880772</v>
       </c>
       <c r="J23" s="242" t="n">
-        <f aca="false">H23*I23*F23</f>
-        <v>22.1662468513854</v>
+        <f aca="false">H23*I23</f>
+        <v>31.7662468513854</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9517,7 +9752,7 @@
       </c>
       <c r="E24" s="242" t="n">
         <f aca="false">+'CONCRETO EN CUNETAS'!M70</f>
-        <v>54</v>
+        <v>54.0</v>
       </c>
       <c r="F24" s="242" t="n">
         <f aca="false">E24/D24</f>
@@ -9525,28 +9760,52 @@
       </c>
       <c r="G24" s="242" t="n">
         <f aca="false">B8</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H24" s="242" t="n">
         <f aca="false">ROUNDUP(D24/G24,0)</f>
-        <v>37</v>
+        <v>37.0</v>
       </c>
       <c r="I24" s="242" t="n">
-        <f aca="false">B9</f>
-        <v>2</v>
+        <f aca="false">$B$9*F24+$B$10</f>
+        <v>1.38973607038123</v>
       </c>
       <c r="J24" s="242" t="n">
-        <f aca="false">H24*I24*F24</f>
-        <v>36.6202346041056</v>
+        <f aca="false">H24*I24</f>
+        <v>51.4202346041056</v>
+      </c>
+    </row>
+    <row r="26" customHeight="true" ht="15">
+      <c r="A26" s="237" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="27" customHeight="true" ht="27">
+      <c r="A27" s="237" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="28" customHeight="true" ht="27">
+      <c r="A28" s="237" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="29" customHeight="true" ht="27">
+      <c r="A29" s="237" t="s">
+        <v>1348</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B5:J5"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A29:J29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9687,7 +9946,7 @@
       </c>
       <c r="G7" s="224" t="n">
         <f aca="false">IF(B7="","",ROUNDUP(E7/F7,0))</f>
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H7" s="225" t="s">
         <v>60</v>
@@ -9714,7 +9973,7 @@
       </c>
       <c r="G8" s="224" t="n">
         <f aca="false">IF(B8="","",ROUNDUP(E8/F8,0))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="H8" s="225" t="s">
         <v>60</v>
@@ -9741,7 +10000,7 @@
       </c>
       <c r="G9" s="224" t="n">
         <f aca="false">IF(B9="","",ROUNDUP(E9/F9,0))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="H9" s="225" t="s">
         <v>60</v>
@@ -9768,7 +10027,7 @@
       </c>
       <c r="G10" s="224" t="n">
         <f aca="false">IF(B10="","",ROUNDUP(E10/F10,0))</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H10" s="225" t="s">
         <v>60</v>
@@ -9795,7 +10054,7 @@
       </c>
       <c r="G11" s="224" t="n">
         <f aca="false">IF(B11="","",ROUNDUP(E11/F11,0))</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H11" s="225" t="s">
         <v>60</v>
@@ -9822,7 +10081,7 @@
       </c>
       <c r="G12" s="224" t="n">
         <f aca="false">IF(B12="","",ROUNDUP(E12/F12,0))</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H12" s="225" t="s">
         <v>60</v>
@@ -9849,7 +10108,7 @@
       </c>
       <c r="G13" s="224" t="n">
         <f aca="false">IF(B13="","",ROUNDUP(E13/F13,0))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H13" s="225" t="s">
         <v>60</v>
@@ -9876,7 +10135,7 @@
       </c>
       <c r="G14" s="224" t="n">
         <f aca="false">IF(B14="","",ROUNDUP(E14/F14,0))</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="H14" s="225" t="s">
         <v>60</v>
@@ -9903,7 +10162,7 @@
       </c>
       <c r="G15" s="224" t="n">
         <f aca="false">IF(B15="","",ROUNDUP(E15/F15,0))</f>
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="H15" s="225" t="s">
         <v>60</v>
@@ -9930,7 +10189,7 @@
       </c>
       <c r="G16" s="224" t="n">
         <f aca="false">IF(B16="","",ROUNDUP(E16/F16,0))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="H16" s="225" t="s">
         <v>60</v>
@@ -9957,7 +10216,7 @@
       </c>
       <c r="G17" s="224" t="n">
         <f aca="false">IF(B17="","",ROUNDUP(E17/F17,0))</f>
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="H17" s="225" t="s">
         <v>60</v>
@@ -9984,7 +10243,7 @@
       </c>
       <c r="G18" s="224" t="n">
         <f aca="false">IF(B18="","",ROUNDUP(E18/F18,0))</f>
-        <v>73</v>
+        <v>73.0</v>
       </c>
       <c r="H18" s="225" t="s">
         <v>60</v>
@@ -10004,7 +10263,7 @@
       <c r="F20" s="244"/>
       <c r="G20" s="227" t="n">
         <f aca="false">SUM(G7:G18)</f>
-        <v>157</v>
+        <v>157.0</v>
       </c>
       <c r="H20" s="227" t="s">
         <v>60</v>
@@ -10332,7 +10591,7 @@
       <c r="I9" s="208"/>
       <c r="J9" s="252" t="n">
         <f aca="false">+PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="K9" s="253" t="s">
         <v>60</v>
@@ -10375,7 +10634,7 @@
       </c>
       <c r="C12" s="256" t="n">
         <f aca="false">PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D12" s="256" t="n">
         <f aca="false">PARAMETROS!B5</f>
@@ -10440,7 +10699,7 @@
       </c>
       <c r="C15" s="256" t="n">
         <f aca="false">PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D15" s="256" t="n">
         <f aca="false">2*(PARAMETROS!B5+PARAMETROS!B6)</f>
@@ -10475,7 +10734,7 @@
       </c>
       <c r="C16" s="256" t="n">
         <f aca="false">PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D16" s="256" t="n">
         <f aca="false">PARAMETROS!B5</f>
@@ -10564,7 +10823,7 @@
       </c>
       <c r="C20" s="256" t="n">
         <f aca="false">PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D20" s="256" t="n">
         <f aca="false">PARAMETROS!B5-2*PARAMETROS!B8</f>
@@ -10572,7 +10831,7 @@
       </c>
       <c r="E20" s="256" t="n">
         <f aca="false">ROUND((PARAMETROS!B6-2*PARAMETROS!B8)/PARAMETROS!B9,0)+1</f>
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="256"/>
       <c r="G20" s="256" t="n">
@@ -10599,7 +10858,7 @@
       </c>
       <c r="C21" s="256" t="n">
         <f aca="false">PARAMETROS!B4</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D21" s="256" t="n">
         <f aca="false">PARAMETROS!B6-2*PARAMETROS!B8</f>
@@ -10607,7 +10866,7 @@
       </c>
       <c r="E21" s="256" t="n">
         <f aca="false">ROUND((PARAMETROS!B5-2*PARAMETROS!B8)/PARAMETROS!B9,0)+1</f>
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="F21" s="256"/>
       <c r="G21" s="256" t="n">
@@ -12947,7 +13206,7 @@
       </c>
       <c r="E21" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$45</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F21" s="287" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$50-'COLECTOR PARAMETROS'!$C$13-G21</f>
@@ -13058,7 +13317,7 @@
       </c>
       <c r="P22" s="290" t="n">
         <f aca="false">MAX(0,N22-L22)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="Q22" s="290" t="n">
         <v>0</v>
@@ -13100,7 +13359,7 @@
       </c>
       <c r="Q23" s="293" t="n">
         <f aca="false">SUM(Q21:Q22)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="R23" s="292"/>
     </row>
@@ -13663,7 +13922,7 @@
       </c>
       <c r="D13" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F13</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E13" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G13</f>
@@ -13825,7 +14084,7 @@
       </c>
       <c r="D16" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F16</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E16" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G16</f>
@@ -14085,7 +14344,7 @@
       </c>
       <c r="D24" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!E21</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E24" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$11</f>
@@ -14229,7 +14488,7 @@
       </c>
       <c r="D28" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!E21</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E28" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$11</f>
@@ -14372,7 +14631,7 @@
       </c>
       <c r="D32" s="290" t="n">
         <f aca="false">2*('COLECTOR MOV. TIERRAS'!D21+'COLECTOR MOV. TIERRAS'!E21)</f>
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E32" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F21</f>
@@ -14765,7 +15024,7 @@
       </c>
       <c r="D43" s="290" t="n">
         <f aca="false">2*('COLECTOR MOV. TIERRAS'!D22+'COLECTOR MOV. TIERRAS'!E22)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E43" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F22</f>
@@ -14818,7 +15077,7 @@
       </c>
       <c r="D45" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$42</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E45" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$43</f>
@@ -14829,7 +15088,7 @@
       </c>
       <c r="G45" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="H45" s="21"/>
       <c r="I45" s="21"/>
@@ -14866,7 +15125,7 @@
       </c>
       <c r="G46" s="299" t="n">
         <f aca="false">-('COLECTOR PARAMETROS'!$C$32-3)</f>
-        <v>-7</v>
+        <v>-7.0</v>
       </c>
       <c r="H46" s="21"/>
       <c r="I46" s="21"/>
@@ -15438,7 +15697,7 @@
       </c>
       <c r="D13" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F13</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E13" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G13</f>
@@ -15576,7 +15835,7 @@
       </c>
       <c r="D16" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F16</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E16" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G16</f>
@@ -15697,7 +15956,7 @@
       </c>
       <c r="D21" s="290" t="n">
         <f aca="false">2*('COLECTOR MOV. TIERRAS'!D21+'COLECTOR MOV. TIERRAS'!E21)</f>
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E21" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F21</f>
@@ -15732,7 +15991,7 @@
       </c>
       <c r="E22" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!E21</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="F22" s="298" t="n">
         <v>1</v>
@@ -15759,7 +16018,7 @@
       </c>
       <c r="D23" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!E21</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E23" s="287" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$46</f>
@@ -15790,7 +16049,7 @@
       </c>
       <c r="D24" s="290" t="n">
         <f aca="false">2*('COLECTOR MOV. TIERRAS'!D22+'COLECTOR MOV. TIERRAS'!E22)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="E24" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F22</f>
@@ -19135,7 +19394,7 @@
       <c r="J134" s="36"/>
       <c r="K134" s="28" t="n">
         <f aca="false">+'METRADO JUNTA DE DILATACION'!J12</f>
-        <v>241.959543966302</v>
+        <v>335.159543966302</v>
       </c>
       <c r="L134" s="43" t="s">
         <v>57</v>
@@ -23073,7 +23332,7 @@
       <c r="J322" s="25"/>
       <c r="K322" s="25" t="n">
         <f aca="false">+'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
       <c r="L322" s="24" t="s">
         <v>57</v>
@@ -23397,7 +23656,7 @@
       </c>
       <c r="K10" s="299" t="n">
         <f aca="false">ROUNDUP(D10/H10,0)</f>
-        <v>132</v>
+        <v>132.0</v>
       </c>
       <c r="L10" s="287" t="n">
         <f aca="false">IF(I10=2,2*(G10-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E10+F10-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G10-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E10+F10/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23405,7 +23664,7 @@
       </c>
       <c r="M10" s="287" t="n">
         <f aca="false">IF(I10=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N10" s="290" t="n">
         <f aca="false">K10*(L10+M10)</f>
@@ -23425,7 +23684,7 @@
       </c>
       <c r="R10" s="299" t="n">
         <f aca="false">ROUND(L10/Q10,0)+IF(M10&gt;0,ROUND(M10/Q10,0),0)</f>
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="S10" s="290" t="n">
         <f aca="false">R10*D10*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23481,7 +23740,7 @@
       </c>
       <c r="K11" s="299" t="n">
         <f aca="false">ROUNDUP(D11/H11,0)</f>
-        <v>34</v>
+        <v>34.0</v>
       </c>
       <c r="L11" s="287" t="n">
         <f aca="false">IF(I11=2,2*(G11-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E11+F11-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G11-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E11+F11/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23509,7 +23768,7 @@
       </c>
       <c r="R11" s="299" t="n">
         <f aca="false">ROUND(L11/Q11,0)+IF(M11&gt;0,ROUND(M11/Q11,0),0)</f>
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="S11" s="290" t="n">
         <f aca="false">R11*D11*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23565,7 +23824,7 @@
       </c>
       <c r="K12" s="299" t="n">
         <f aca="false">ROUNDUP(D12/H12,0)</f>
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="L12" s="287" t="n">
         <f aca="false">IF(I12=2,2*(G12-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E12+F12-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G12-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E12+F12/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23573,7 +23832,7 @@
       </c>
       <c r="M12" s="287" t="n">
         <f aca="false">IF(I12=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E12+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N12" s="290" t="n">
         <f aca="false">K12*(L12+M12)</f>
@@ -23593,7 +23852,7 @@
       </c>
       <c r="R12" s="299" t="n">
         <f aca="false">ROUND(L12/Q12,0)+IF(M12&gt;0,ROUND(M12/Q12,0),0)</f>
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="S12" s="290" t="n">
         <f aca="false">R12*D12*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23623,7 +23882,7 @@
       </c>
       <c r="D13" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F13</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E13" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G13</f>
@@ -23649,7 +23908,7 @@
       </c>
       <c r="K13" s="299" t="n">
         <f aca="false">ROUNDUP(D13/H13,0)</f>
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="L13" s="287" t="n">
         <f aca="false">IF(I13=2,2*(G13-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E13+F13-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G13-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E13+F13/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23657,7 +23916,7 @@
       </c>
       <c r="M13" s="287" t="n">
         <f aca="false">IF(I13=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E13+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N13" s="290" t="n">
         <f aca="false">K13*(L13+M13)</f>
@@ -23677,7 +23936,7 @@
       </c>
       <c r="R13" s="299" t="n">
         <f aca="false">ROUND(L13/Q13,0)+IF(M13&gt;0,ROUND(M13/Q13,0),0)</f>
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="S13" s="290" t="n">
         <f aca="false">R13*D13*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23733,7 +23992,7 @@
       </c>
       <c r="K14" s="299" t="n">
         <f aca="false">ROUNDUP(D14/H14,0)</f>
-        <v>89</v>
+        <v>89.0</v>
       </c>
       <c r="L14" s="287" t="n">
         <f aca="false">IF(I14=2,2*(G14-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E14+F14-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G14-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E14+F14/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23741,7 +24000,7 @@
       </c>
       <c r="M14" s="287" t="n">
         <f aca="false">IF(I14=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E14+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N14" s="290" t="n">
         <f aca="false">K14*(L14+M14)</f>
@@ -23761,7 +24020,7 @@
       </c>
       <c r="R14" s="299" t="n">
         <f aca="false">ROUND(L14/Q14,0)+IF(M14&gt;0,ROUND(M14/Q14,0),0)</f>
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="S14" s="290" t="n">
         <f aca="false">R14*D14*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23817,7 +24076,7 @@
       </c>
       <c r="K15" s="299" t="n">
         <f aca="false">ROUNDUP(D15/H15,0)</f>
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="L15" s="287" t="n">
         <f aca="false">IF(I15=2,2*(G15-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E15+F15-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G15-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E15+F15/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23825,7 +24084,7 @@
       </c>
       <c r="M15" s="287" t="n">
         <f aca="false">IF(I15=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E15+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N15" s="290" t="n">
         <f aca="false">K15*(L15+M15)</f>
@@ -23845,7 +24104,7 @@
       </c>
       <c r="R15" s="299" t="n">
         <f aca="false">ROUND(L15/Q15,0)+IF(M15&gt;0,ROUND(M15/Q15,0),0)</f>
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="S15" s="290" t="n">
         <f aca="false">R15*D15*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -23875,7 +24134,7 @@
       </c>
       <c r="D16" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F16</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E16" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!G16</f>
@@ -23901,7 +24160,7 @@
       </c>
       <c r="K16" s="299" t="n">
         <f aca="false">ROUNDUP(D16/H16,0)</f>
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="L16" s="287" t="n">
         <f aca="false">IF(I16=2,2*(G16-2*'COLECTOR PARAMETROS'!$C$19)+2*('COLECTOR PARAMETROS'!$C$12+E16+F16-2*'COLECTOR PARAMETROS'!$C$19)+'COLECTOR PARAMETROS'!$C$24,2*(G16-'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12/2+E16+F16/2)+'COLECTOR PARAMETROS'!$C$24)</f>
@@ -23909,7 +24168,7 @@
       </c>
       <c r="M16" s="287" t="n">
         <f aca="false">IF(I16=2,2*('COLECTOR PARAMETROS'!$C$10+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+2*(E16+2*('COLECTOR PARAMETROS'!$C$11-'COLECTOR PARAMETROS'!$C$19))+'COLECTOR PARAMETROS'!$C$24,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="N16" s="290" t="n">
         <f aca="false">K16*(L16+M16)</f>
@@ -23929,7 +24188,7 @@
       </c>
       <c r="R16" s="299" t="n">
         <f aca="false">ROUND(L16/Q16,0)+IF(M16&gt;0,ROUND(M16/Q16,0),0)</f>
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="S16" s="290" t="n">
         <f aca="false">R16*D16*(1+'COLECTOR PARAMETROS'!$C$22/'COLECTOR PARAMETROS'!$C$23)</f>
@@ -24095,7 +24354,7 @@
       </c>
       <c r="I21" s="290" t="n">
         <f aca="false">((D21/F21+1)*E21+(E21/F21+1)*D21)*G21*H21</f>
-        <v>53</v>
+        <v>53.0</v>
       </c>
       <c r="J21" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$31</f>
@@ -24150,7 +24409,7 @@
       </c>
       <c r="I22" s="290" t="n">
         <f aca="false">((D22/F22+1)*E22+(E22/F22+1)*D22)*G22*H22</f>
-        <v>53</v>
+        <v>53.0</v>
       </c>
       <c r="J22" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$31</f>
@@ -24242,7 +24501,7 @@
       </c>
       <c r="D24" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!E21</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E24" s="287" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!F21</f>
@@ -24315,7 +24574,7 @@
       </c>
       <c r="I25" s="290" t="n">
         <f aca="false">((D25/F25+1)*E25+(E25/F25+1)*D25)*G25*H25</f>
-        <v>148</v>
+        <v>148.0</v>
       </c>
       <c r="J25" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$31</f>
@@ -24370,7 +24629,7 @@
       </c>
       <c r="I26" s="290" t="n">
         <f aca="false">((D26/F26+1)*E26+(E26/F26+1)*D26)*G26*H26</f>
-        <v>148</v>
+        <v>148.0</v>
       </c>
       <c r="J26" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$31</f>
@@ -24626,14 +24885,14 @@
       </c>
       <c r="F33" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G33" s="289" t="n">
         <v>1.4</v>
       </c>
       <c r="H33" s="290" t="n">
         <f aca="false">E33*F33*G33</f>
-        <v>112</v>
+        <v>112.0</v>
       </c>
       <c r="I33" s="287" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$21</f>
@@ -24676,7 +24935,7 @@
       </c>
       <c r="F34" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G34" s="289" t="n">
         <v>0.62</v>
@@ -24726,14 +24985,14 @@
       </c>
       <c r="F35" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G35" s="289" t="n">
         <v>0.4</v>
       </c>
       <c r="H35" s="290" t="n">
         <f aca="false">E35*F35*G35</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="I35" s="287" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
@@ -24776,14 +25035,14 @@
       </c>
       <c r="F36" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="G36" s="289" t="n">
         <v>0.2</v>
       </c>
       <c r="H36" s="290" t="n">
         <f aca="false">E36*F36*G36</f>
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="I36" s="287" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
@@ -25509,7 +25768,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>907</v>
+        <v>1339</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -25565,7 +25824,7 @@
       </c>
       <c r="D11" s="299" t="n">
         <f aca="false">INT('COLECTOR PARAMETROS'!$C$64/'COLECTOR PARAMETROS'!$C$62)</f>
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="E11" s="290" t="n">
         <f aca="false">2*('COLECTOR PARAMETROS'!$C$10+2*'COLECTOR PARAMETROS'!$C$11)+2*('COLECTOR PARAMETROS'!$C$12+'COLECTOR PARAMETROS'!$C$63+'COLECTOR PARAMETROS'!$C$13)</f>
@@ -25638,14 +25897,14 @@
         <v>2</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>917</v>
+        <v>1334</v>
       </c>
       <c r="C16" s="301" t="str">
-        <f aca="false">"2 x 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$64,"000.00")</f>
-        <v>2 x 0+069.89</v>
+        <f aca="false">"1 x 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$64,"000.00")</f>
+        <v>1 x 0+069.89</v>
       </c>
       <c r="D16" s="298" t="n">
-        <v>2</v>
+        <v>1.0</v>
       </c>
       <c r="E16" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$64</f>
@@ -25653,10 +25912,10 @@
       </c>
       <c r="F16" s="290" t="n">
         <f aca="false">D16*E16</f>
-        <v>139.774</v>
+        <v>69.887</v>
       </c>
       <c r="G16" s="286" t="s">
-        <v>918</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25664,13 +25923,13 @@
         <v>3</v>
       </c>
       <c r="B17" s="149" t="s">
-        <v>919</v>
+        <v>1336</v>
       </c>
       <c r="C17" s="283" t="s">
-        <v>920</v>
+        <v>1337</v>
       </c>
       <c r="D17" s="298" t="n">
-        <v>2</v>
+        <v>1.0</v>
       </c>
       <c r="E17" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!D21+2*'COLECTOR PARAMETROS'!$C$11+0.3</f>
@@ -25678,7 +25937,7 @@
       </c>
       <c r="F17" s="290" t="n">
         <f aca="false">D17*E17</f>
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="G17" s="286" t="s">
         <v>871</v>
@@ -25689,13 +25948,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="149" t="s">
-        <v>921</v>
+        <v>1338</v>
       </c>
       <c r="C18" s="283" t="s">
-        <v>920</v>
+        <v>1337</v>
       </c>
       <c r="D18" s="298" t="n">
-        <v>2</v>
+        <v>1.0</v>
       </c>
       <c r="E18" s="290" t="n">
         <f aca="false">'COLECTOR MOV. TIERRAS'!D22+2*'COLECTOR PARAMETROS'!$C$11+0.3</f>
@@ -25703,7 +25962,7 @@
       </c>
       <c r="F18" s="290" t="n">
         <f aca="false">D18*E18</f>
-        <v>8.2</v>
+        <v>4.1</v>
       </c>
       <c r="G18" s="286" t="s">
         <v>871</v>
@@ -25719,7 +25978,7 @@
       <c r="E19" s="292"/>
       <c r="F19" s="293" t="n">
         <f aca="false">SUM(F15:F18)</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
       <c r="G19" s="292"/>
     </row>
@@ -25753,7 +26012,7 @@
       <c r="E22" s="21"/>
       <c r="F22" s="299" t="n">
         <f aca="false">D22</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="286" t="s">
         <v>926</v>
@@ -25775,7 +26034,7 @@
       <c r="E23" s="21"/>
       <c r="F23" s="299" t="n">
         <f aca="false">D23</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="286" t="s">
         <v>926</v>
@@ -25797,7 +26056,7 @@
       <c r="E24" s="21"/>
       <c r="F24" s="299" t="n">
         <f aca="false">D24</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G24" s="286" t="s">
         <v>926</v>
@@ -25819,7 +26078,7 @@
       <c r="E25" s="21"/>
       <c r="F25" s="299" t="n">
         <f aca="false">D25</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G25" s="286" t="s">
         <v>926</v>
@@ -25841,7 +26100,7 @@
       <c r="E26" s="21"/>
       <c r="F26" s="299" t="n">
         <f aca="false">D26</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="286" t="s">
         <v>926</v>
@@ -25863,7 +26122,7 @@
       <c r="E27" s="21"/>
       <c r="F27" s="299" t="n">
         <f aca="false">D27</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="G27" s="286" t="s">
         <v>926</v>
@@ -25879,7 +26138,7 @@
       <c r="E28" s="292"/>
       <c r="F28" s="300" t="n">
         <f aca="false">SUM(F22:F27)</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="G28" s="292"/>
     </row>
@@ -27369,7 +27628,7 @@
       </c>
       <c r="D73" s="290" t="n">
         <f aca="false">'PLANILLA GENERAL DE METRADOS'!K322</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
       <c r="E73" s="295" t="s">
         <v>986</v>
@@ -27379,11 +27638,11 @@
       </c>
       <c r="G73" s="306" t="n">
         <f aca="false">'ACU JUNTA CERCO'!$D$16*(1+'ACU JUNTA CERCO'!$D$17)</f>
-        <v>0.339128515160277</v>
+        <v>0.471190730362068</v>
       </c>
       <c r="H73" s="296" t="n">
         <f aca="false">G73*$D$73</f>
-        <v>71.548995</v>
+        <v>63.55986</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27402,7 +27661,7 @@
       </c>
       <c r="H74" s="296" t="n">
         <f aca="false">G74*$D$73</f>
-        <v>21.0979</v>
+        <v>13.4892</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27424,7 +27683,7 @@
       </c>
       <c r="H75" s="296" t="n">
         <f aca="false">G75*$D$73</f>
-        <v>0.27223042328</v>
+        <v>0.17405384544</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27443,7 +27702,7 @@
       </c>
       <c r="H76" s="296" t="n">
         <f aca="false">G76*$D$73</f>
-        <v>10.54895</v>
+        <v>6.7446</v>
       </c>
     </row>
   </sheetData>
@@ -27967,7 +28226,7 @@
       </c>
       <c r="G25" s="290" t="n">
         <f aca="false">F25*SUMIF($B$68:$B$93,B25,$F$68:$F$93)</f>
-        <v>30.7290672</v>
+        <v>29.597688</v>
       </c>
       <c r="H25" s="149" t="s">
         <v>1029</v>
@@ -28040,7 +28299,7 @@
       <c r="F28" s="295"/>
       <c r="G28" s="296" t="n">
         <f aca="false">SUM(G22:G27)</f>
-        <v>100.30787784</v>
+        <v>99.17649864</v>
       </c>
       <c r="H28" s="295"/>
     </row>
@@ -28248,7 +28507,7 @@
       </c>
       <c r="G36" s="290" t="n">
         <f aca="false">F36*SUMIF($B$68:$B$93,B36,$F$68:$F$93)</f>
-        <v>0.900237312</v>
+        <v>0.86709248</v>
       </c>
       <c r="H36" s="149" t="s">
         <v>1036</v>
@@ -28321,7 +28580,7 @@
       <c r="F39" s="295"/>
       <c r="G39" s="296" t="n">
         <f aca="false">SUM(G30:G38)</f>
-        <v>21.16991419136</v>
+        <v>21.13676935936</v>
       </c>
       <c r="H39" s="295"/>
     </row>
@@ -28473,7 +28732,7 @@
       </c>
       <c r="G46" s="290" t="n">
         <f aca="false">F46*SUMIF($B$68:$B$93,B46,$F$68:$F$93)</f>
-        <v>16.877113344</v>
+        <v>16.25573376</v>
       </c>
       <c r="H46" s="149" t="s">
         <v>1036</v>
@@ -28518,7 +28777,7 @@
       <c r="F48" s="295"/>
       <c r="G48" s="296" t="n">
         <f aca="false">SUM(G44:G47)</f>
-        <v>97.517758464</v>
+        <v>96.89637888</v>
       </c>
       <c r="H48" s="295"/>
     </row>
@@ -28670,7 +28929,7 @@
       </c>
       <c r="G54" s="290" t="n">
         <f aca="false">F54*SUMIF($B$68:$B$93,B54,$F$68:$F$93)</f>
-        <v>10.20943872</v>
+        <v>9.8335488</v>
       </c>
       <c r="H54" s="149" t="s">
         <v>1036</v>
@@ -28687,7 +28946,7 @@
       <c r="F55" s="295"/>
       <c r="G55" s="296" t="n">
         <f aca="false">SUM(G50:G54)</f>
-        <v>17.62990848</v>
+        <v>17.25401856</v>
       </c>
       <c r="H55" s="295"/>
     </row>
@@ -28726,7 +28985,7 @@
       </c>
       <c r="G57" s="290" t="n">
         <f aca="false">F57*SUMIF($B$68:$B$93,B57,$F$68:$F$93)</f>
-        <v>30.42</v>
+        <v>29.3</v>
       </c>
       <c r="H57" s="149" t="s">
         <v>1052</v>
@@ -28770,7 +29029,7 @@
       <c r="F59" s="295"/>
       <c r="G59" s="296" t="n">
         <f aca="false">SUM(G57:G58)</f>
-        <v>51.21</v>
+        <v>50.09</v>
       </c>
       <c r="H59" s="295"/>
     </row>
@@ -28785,7 +29044,7 @@
       <c r="F60" s="295"/>
       <c r="G60" s="296" t="n">
         <f aca="false">+G28+G39+G42+G48+G55+G59</f>
-        <v>292.90695897536</v>
+        <v>289.62516543936</v>
       </c>
       <c r="H60" s="295"/>
     </row>
@@ -28930,14 +29189,15 @@
         <v>2.9301728</v>
       </c>
       <c r="F69" s="289" t="n">
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G69" s="290" t="n">
         <f aca="false">E69*F69</f>
-        <v>89.135856576</v>
+        <v>85.85406304</v>
       </c>
       <c r="H69" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28959,6 +29219,7 @@
         <v>1.5945568</v>
       </c>
       <c r="F70" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$12</f>
         <v>22.95</v>
       </c>
       <c r="G70" s="290" t="n">
@@ -28966,7 +29227,7 @@
         <v>36.59507856</v>
       </c>
       <c r="H70" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28988,6 +29249,7 @@
         <v>1.2367488</v>
       </c>
       <c r="F71" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G71" s="290" t="n">
@@ -28995,7 +29257,7 @@
         <v>25.712007552</v>
       </c>
       <c r="H71" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29009,7 +29271,7 @@
       <c r="F72" s="295"/>
       <c r="G72" s="296" t="n">
         <f aca="false">SUM(G69:G71)</f>
-        <v>151.442942688</v>
+        <v>148.161149152</v>
       </c>
       <c r="H72" s="295"/>
     </row>
@@ -29406,11 +29668,11 @@
       </c>
       <c r="F89" s="290" t="n">
         <f aca="false">+G72</f>
-        <v>151.442942688</v>
+        <v>148.161149152</v>
       </c>
       <c r="G89" s="290" t="n">
         <f aca="false">E89*F89</f>
-        <v>4.54328828064</v>
+        <v>4.44483447456</v>
       </c>
       <c r="H89" s="149" t="s">
         <v>1073</v>
@@ -29514,7 +29776,7 @@
       <c r="F93" s="295"/>
       <c r="G93" s="296" t="n">
         <f aca="false">SUM(G89:G92)</f>
-        <v>13.32682440864</v>
+        <v>13.22837060256</v>
       </c>
       <c r="H93" s="295"/>
     </row>
@@ -29529,7 +29791,7 @@
       <c r="F94" s="294"/>
       <c r="G94" s="296" t="n">
         <f aca="false">+G72+G87+G93</f>
-        <v>297.450247256</v>
+        <v>294.06999991392</v>
       </c>
       <c r="H94" s="295"/>
     </row>
@@ -29544,7 +29806,7 @@
       <c r="F95" s="294"/>
       <c r="G95" s="296" t="n">
         <f aca="false">G94*C65</f>
-        <v>2974.50247256</v>
+        <v>2940.6999991392</v>
       </c>
       <c r="H95" s="295"/>
     </row>
@@ -30103,14 +30365,15 @@
         <v>0.32</v>
       </c>
       <c r="F31" s="289" t="n">
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G31" s="290" t="n">
         <f aca="false">E31*F31</f>
-        <v>9.7344</v>
+        <v>9.376</v>
       </c>
       <c r="H31" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30131,6 +30394,7 @@
         <v>0.32</v>
       </c>
       <c r="F32" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G32" s="290" t="n">
@@ -30138,7 +30402,7 @@
         <v>6.6528</v>
       </c>
       <c r="H32" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30152,7 +30416,7 @@
       <c r="F33" s="295"/>
       <c r="G33" s="296" t="n">
         <f aca="false">SUM(G31:G32)</f>
-        <v>16.3872</v>
+        <v>16.0288</v>
       </c>
       <c r="H33" s="295"/>
     </row>
@@ -30289,11 +30553,11 @@
       </c>
       <c r="F40" s="290" t="n">
         <f aca="false">+G33</f>
-        <v>16.3872</v>
+        <v>16.0288</v>
       </c>
       <c r="G40" s="290" t="n">
         <f aca="false">E40*F40</f>
-        <v>0.81936</v>
+        <v>0.80144</v>
       </c>
       <c r="H40" s="149" t="s">
         <v>1118</v>
@@ -30310,7 +30574,7 @@
       <c r="F41" s="295"/>
       <c r="G41" s="296" t="n">
         <f aca="false">SUM(G40:G40)</f>
-        <v>0.81936</v>
+        <v>0.80144</v>
       </c>
       <c r="H41" s="295"/>
     </row>
@@ -30325,7 +30589,7 @@
       <c r="F42" s="294"/>
       <c r="G42" s="296" t="n">
         <f aca="false">+G33+G38+G41</f>
-        <v>40.6357685040984</v>
+        <v>40.2594485040984</v>
       </c>
       <c r="H42" s="295"/>
     </row>
@@ -30340,7 +30604,7 @@
       <c r="F43" s="294"/>
       <c r="G43" s="296" t="n">
         <f aca="false">G42*C27</f>
-        <v>20885.9722957365</v>
+        <v>20692.5513421365</v>
       </c>
       <c r="H43" s="295"/>
     </row>
@@ -30377,7 +30641,7 @@
       <c r="B47" s="294"/>
       <c r="C47" s="290" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K150</f>
-        <v>884</v>
+        <v>884.0</v>
       </c>
       <c r="D47" s="295"/>
       <c r="E47" s="295"/>
@@ -30457,14 +30721,15 @@
         <v>0.2</v>
       </c>
       <c r="F51" s="289" t="n">
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G51" s="290" t="n">
         <f aca="false">E51*F51</f>
-        <v>6.084</v>
+        <v>5.86</v>
       </c>
       <c r="H51" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30485,6 +30750,7 @@
         <v>0.1</v>
       </c>
       <c r="F52" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G52" s="290" t="n">
@@ -30492,7 +30758,7 @@
         <v>2.079</v>
       </c>
       <c r="H52" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30506,7 +30772,7 @@
       <c r="F53" s="295"/>
       <c r="G53" s="296" t="n">
         <f aca="false">SUM(G51:G52)</f>
-        <v>8.163</v>
+        <v>7.939</v>
       </c>
       <c r="H53" s="295"/>
     </row>
@@ -30641,11 +30907,11 @@
       </c>
       <c r="F60" s="290" t="n">
         <f aca="false">+G53</f>
-        <v>8.163</v>
+        <v>7.939</v>
       </c>
       <c r="G60" s="290" t="n">
         <f aca="false">E60*F60</f>
-        <v>0.40815</v>
+        <v>0.39695</v>
       </c>
       <c r="H60" s="149" t="s">
         <v>1118</v>
@@ -30662,7 +30928,7 @@
       <c r="F61" s="295"/>
       <c r="G61" s="296" t="n">
         <f aca="false">SUM(G60:G60)</f>
-        <v>0.40815</v>
+        <v>0.39695</v>
       </c>
       <c r="H61" s="295"/>
     </row>
@@ -30677,7 +30943,7 @@
       <c r="F62" s="294"/>
       <c r="G62" s="296" t="n">
         <f aca="false">+G53+G58+G61</f>
-        <v>16.78745</v>
+        <v>16.55225</v>
       </c>
       <c r="H62" s="295"/>
     </row>
@@ -30692,7 +30958,7 @@
       <c r="F63" s="294"/>
       <c r="G63" s="296" t="n">
         <f aca="false">G62*C47</f>
-        <v>14840.1058</v>
+        <v>14632.189</v>
       </c>
       <c r="H63" s="295"/>
     </row>
@@ -30729,7 +30995,7 @@
       <c r="B67" s="294"/>
       <c r="C67" s="290" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K151</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="D67" s="295"/>
       <c r="E67" s="295"/>
@@ -30809,14 +31075,15 @@
         <v>0.266666666666667</v>
       </c>
       <c r="F71" s="289" t="n">
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G71" s="290" t="n">
         <f aca="false">E71*F71</f>
-        <v>8.112</v>
+        <v>7.81333333333333</v>
       </c>
       <c r="H71" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30837,6 +31104,7 @@
         <v>0.133333333333333</v>
       </c>
       <c r="F72" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G72" s="290" t="n">
@@ -30844,7 +31112,7 @@
         <v>2.772</v>
       </c>
       <c r="H72" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30858,7 +31126,7 @@
       <c r="F73" s="295"/>
       <c r="G73" s="296" t="n">
         <f aca="false">SUM(G71:G72)</f>
-        <v>10.884</v>
+        <v>10.5853333333333</v>
       </c>
       <c r="H73" s="295"/>
     </row>
@@ -30994,11 +31262,11 @@
       </c>
       <c r="F80" s="290" t="n">
         <f aca="false">+G73</f>
-        <v>10.884</v>
+        <v>10.5853333333333</v>
       </c>
       <c r="G80" s="290" t="n">
         <f aca="false">E80*F80</f>
-        <v>0.5442</v>
+        <v>0.529266666666667</v>
       </c>
       <c r="H80" s="149" t="s">
         <v>1118</v>
@@ -31015,7 +31283,7 @@
       <c r="F81" s="295"/>
       <c r="G81" s="296" t="n">
         <f aca="false">SUM(G80:G80)</f>
-        <v>0.5442</v>
+        <v>0.529266666666667</v>
       </c>
       <c r="H81" s="295"/>
     </row>
@@ -31030,7 +31298,7 @@
       <c r="F82" s="294"/>
       <c r="G82" s="296" t="n">
         <f aca="false">+G73+G78+G81</f>
-        <v>16.0325525</v>
+        <v>15.7189525</v>
       </c>
       <c r="H82" s="295"/>
     </row>
@@ -31045,7 +31313,7 @@
       <c r="F83" s="294"/>
       <c r="G83" s="296" t="n">
         <f aca="false">G82*C67</f>
-        <v>641.3021</v>
+        <v>628.7581</v>
       </c>
       <c r="H83" s="295"/>
     </row>
@@ -31082,7 +31350,7 @@
       <c r="B87" s="294"/>
       <c r="C87" s="290" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K152</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
       <c r="D87" s="295"/>
       <c r="E87" s="295"/>
@@ -31162,14 +31430,15 @@
         <v>0.5</v>
       </c>
       <c r="F91" s="289" t="n">
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G91" s="290" t="n">
         <f aca="false">E91*F91</f>
-        <v>15.21</v>
+        <v>14.65</v>
       </c>
       <c r="H91" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31190,6 +31459,7 @@
         <v>0.25</v>
       </c>
       <c r="F92" s="289" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G92" s="290" t="n">
@@ -31197,7 +31467,7 @@
         <v>5.1975</v>
       </c>
       <c r="H92" s="149" t="s">
-        <v>1067</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31211,7 +31481,7 @@
       <c r="F93" s="295"/>
       <c r="G93" s="296" t="n">
         <f aca="false">SUM(G91:G92)</f>
-        <v>20.4075</v>
+        <v>19.8475</v>
       </c>
       <c r="H93" s="295"/>
     </row>
@@ -31347,11 +31617,11 @@
       </c>
       <c r="F100" s="290" t="n">
         <f aca="false">+G93</f>
-        <v>20.4075</v>
+        <v>19.8475</v>
       </c>
       <c r="G100" s="290" t="n">
         <f aca="false">E100*F100</f>
-        <v>1.020375</v>
+        <v>0.992375</v>
       </c>
       <c r="H100" s="149" t="s">
         <v>1118</v>
@@ -31368,7 +31638,7 @@
       <c r="F101" s="295"/>
       <c r="G101" s="296" t="n">
         <f aca="false">SUM(G100:G100)</f>
-        <v>1.020375</v>
+        <v>0.992375</v>
       </c>
       <c r="H101" s="295"/>
     </row>
@@ -31383,7 +31653,7 @@
       <c r="F102" s="294"/>
       <c r="G102" s="296" t="n">
         <f aca="false">+G93+G98+G101</f>
-        <v>27.9158733730072</v>
+        <v>27.3278733730072</v>
       </c>
       <c r="H102" s="295"/>
     </row>
@@ -31398,7 +31668,7 @@
       <c r="F103" s="294"/>
       <c r="G103" s="296" t="n">
         <f aca="false">G102*C87</f>
-        <v>1451.62541539637</v>
+        <v>1421.04941539637</v>
       </c>
       <c r="H103" s="295"/>
     </row>
@@ -31450,11 +31720,11 @@
       </c>
       <c r="E107" s="290" t="n">
         <f aca="false">+G42</f>
-        <v>40.6357685040984</v>
+        <v>40.2594485040984</v>
       </c>
       <c r="F107" s="290" t="n">
         <f aca="false">+G43</f>
-        <v>20885.9722957365</v>
+        <v>20692.5513421365</v>
       </c>
       <c r="G107" s="295"/>
       <c r="H107" s="295"/>
@@ -31471,15 +31741,15 @@
       </c>
       <c r="D108" s="290" t="n">
         <f aca="false">+C47</f>
-        <v>884</v>
+        <v>884.0</v>
       </c>
       <c r="E108" s="290" t="n">
         <f aca="false">+G62</f>
-        <v>16.78745</v>
+        <v>16.55225</v>
       </c>
       <c r="F108" s="290" t="n">
         <f aca="false">+G63</f>
-        <v>14840.1058</v>
+        <v>14632.189</v>
       </c>
       <c r="G108" s="295"/>
       <c r="H108" s="295"/>
@@ -31496,15 +31766,15 @@
       </c>
       <c r="D109" s="290" t="n">
         <f aca="false">+C67</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="E109" s="290" t="n">
         <f aca="false">+G82</f>
-        <v>16.0325525</v>
+        <v>15.7189525</v>
       </c>
       <c r="F109" s="290" t="n">
         <f aca="false">+G83</f>
-        <v>641.3021</v>
+        <v>628.7581</v>
       </c>
       <c r="G109" s="295"/>
       <c r="H109" s="295"/>
@@ -31521,15 +31791,15 @@
       </c>
       <c r="D110" s="290" t="n">
         <f aca="false">+C87</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
       <c r="E110" s="290" t="n">
         <f aca="false">+G102</f>
-        <v>27.9158733730072</v>
+        <v>27.3278733730072</v>
       </c>
       <c r="F110" s="290" t="n">
         <f aca="false">+G103</f>
-        <v>1451.62541539637</v>
+        <v>1421.04941539637</v>
       </c>
       <c r="G110" s="295"/>
       <c r="H110" s="295"/>
@@ -31544,7 +31814,7 @@
       <c r="E111" s="295"/>
       <c r="F111" s="296" t="n">
         <f aca="false">SUM(F107:F110)</f>
-        <v>37819.0056111329</v>
+        <v>37374.5478575328</v>
       </c>
       <c r="G111" s="295"/>
       <c r="H111" s="295"/>
@@ -33069,15 +33339,15 @@
         <v>0.2</v>
       </c>
       <c r="F34" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F69</f>
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">E34*F34</f>
-        <v>6.084</v>
+        <v>5.86</v>
       </c>
       <c r="H34" s="149" t="s">
-        <v>1261</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33099,7 +33369,7 @@
         <v>0.2</v>
       </c>
       <c r="F35" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F71</f>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G35" s="290" t="n">
@@ -33107,7 +33377,7 @@
         <v>4.158</v>
       </c>
       <c r="H35" s="149" t="s">
-        <v>1261</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33121,7 +33391,7 @@
       <c r="F36" s="295"/>
       <c r="G36" s="296" t="n">
         <f aca="false">SUM(G34:G35)</f>
-        <v>10.242</v>
+        <v>10.018</v>
       </c>
       <c r="H36" s="295"/>
     </row>
@@ -33261,11 +33531,11 @@
       </c>
       <c r="F43" s="290" t="n">
         <f aca="false">+G36</f>
-        <v>10.242</v>
+        <v>10.018</v>
       </c>
       <c r="G43" s="290" t="n">
         <f aca="false">E43*F43</f>
-        <v>0.30726</v>
+        <v>0.30054</v>
       </c>
       <c r="H43" s="149" t="s">
         <v>1268</v>
@@ -33282,7 +33552,7 @@
       <c r="F44" s="295"/>
       <c r="G44" s="296" t="n">
         <f aca="false">SUM(G43:G43)</f>
-        <v>0.30726</v>
+        <v>0.30054</v>
       </c>
       <c r="H44" s="295"/>
     </row>
@@ -33297,7 +33567,7 @@
       <c r="F45" s="294"/>
       <c r="G45" s="296" t="n">
         <f aca="false">+G36+G41+G44</f>
-        <v>12.00996805416</v>
+        <v>11.77924805416</v>
       </c>
       <c r="H45" s="295"/>
     </row>
@@ -33312,7 +33582,7 @@
       <c r="F46" s="294"/>
       <c r="G46" s="296" t="n">
         <f aca="false">G45*C30</f>
-        <v>1208.68318497067</v>
+        <v>1185.46352417067</v>
       </c>
       <c r="H46" s="295"/>
     </row>
@@ -33445,7 +33715,7 @@
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1271</v>
+        <v>1340</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -33533,14 +33803,14 @@
         <v>3.0</v>
       </c>
       <c r="B13" s="149" t="s">
-        <v>1276</v>
+        <v>1341</v>
       </c>
       <c r="C13" s="285" t="s">
         <v>57</v>
       </c>
       <c r="D13" s="306" t="n">
         <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F16+'COLECTOR JUNTAS Y EMPALMES'!F17+'COLECTOR JUNTAS Y EMPALMES'!F18</f>
-        <v>152.174</v>
+        <v>76.087</v>
       </c>
       <c r="E13" s="295"/>
       <c r="F13" s="295"/>
@@ -33581,7 +33851,7 @@
       </c>
       <c r="D15" s="306" t="n">
         <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
       <c r="E15" s="295"/>
       <c r="F15" s="295"/>
@@ -33602,7 +33872,7 @@
       </c>
       <c r="D16" s="306" t="n">
         <f aca="false">(D11*D12+D13*D14)/D15</f>
-        <v>0.322979538247883</v>
+        <v>0.448753076535302</v>
       </c>
       <c r="E16" s="295"/>
       <c r="F16" s="295"/>
@@ -33663,7 +33933,7 @@
       </c>
       <c r="D19" s="306" t="n">
         <f aca="false">D16*(1+D17)/D18</f>
-        <v>0.117752956652874</v>
+        <v>0.163607892486829</v>
       </c>
       <c r="E19" s="295"/>
       <c r="F19" s="295"/>
@@ -33836,7 +34106,7 @@
       <c r="B30" s="294"/>
       <c r="C30" s="290" t="n">
         <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>210.979</v>
+        <v>134.892</v>
       </c>
       <c r="D30" s="290"/>
       <c r="E30" s="290"/>
@@ -33916,15 +34186,15 @@
         <v>0.05</v>
       </c>
       <c r="F34" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F69</f>
-        <v>30.42</v>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">E34*F34</f>
-        <v>1.521</v>
+        <v>1.465</v>
       </c>
       <c r="H34" s="149" t="s">
-        <v>1261</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33946,7 +34216,7 @@
         <v>0.1</v>
       </c>
       <c r="F35" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F71</f>
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
         <v>20.79</v>
       </c>
       <c r="G35" s="290" t="n">
@@ -33954,7 +34224,7 @@
         <v>2.079</v>
       </c>
       <c r="H35" s="149" t="s">
-        <v>1261</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33968,7 +34238,7 @@
       <c r="F36" s="295"/>
       <c r="G36" s="296" t="n">
         <f aca="false">SUM(G34:G35)</f>
-        <v>3.6</v>
+        <v>3.544</v>
       </c>
       <c r="H36" s="295"/>
     </row>
@@ -33997,7 +34267,7 @@
       <c r="D38" s="295"/>
       <c r="E38" s="306" t="n">
         <f aca="false">$D$19</f>
-        <v>0.117752956652874</v>
+        <v>0.163607892486829</v>
       </c>
       <c r="F38" s="290" t="n">
         <f aca="false">13.9/1.18</f>
@@ -34005,7 +34275,7 @@
       </c>
       <c r="G38" s="290" t="n">
         <f aca="false">E38*F38</f>
-        <v>1.38708991311436</v>
+        <v>1.92724551319231</v>
       </c>
       <c r="H38" s="149" t="s">
         <v>1264</v>
@@ -34076,7 +34346,7 @@
       <c r="F41" s="295"/>
       <c r="G41" s="296" t="n">
         <f aca="false">SUM(G38:G40)</f>
-        <v>2.40994464159436</v>
+        <v>2.95010024167231</v>
       </c>
       <c r="H41" s="295"/>
     </row>
@@ -34108,11 +34378,11 @@
       </c>
       <c r="F43" s="290" t="n">
         <f aca="false">+G36</f>
-        <v>3.6</v>
+        <v>3.544</v>
       </c>
       <c r="G43" s="290" t="n">
         <f aca="false">E43*F43</f>
-        <v>0.108</v>
+        <v>0.10632</v>
       </c>
       <c r="H43" s="149" t="s">
         <v>1268</v>
@@ -34129,7 +34399,7 @@
       <c r="F44" s="295"/>
       <c r="G44" s="296" t="n">
         <f aca="false">SUM(G43:G43)</f>
-        <v>0.108</v>
+        <v>0.10632</v>
       </c>
       <c r="H44" s="295"/>
     </row>
@@ -34144,7 +34414,7 @@
       <c r="F45" s="294"/>
       <c r="G45" s="296" t="n">
         <f aca="false">+G36+G41+G44</f>
-        <v>6.11794464159436</v>
+        <v>6.60042024167231</v>
       </c>
       <c r="H45" s="295"/>
     </row>
@@ -34159,7 +34429,7 @@
       <c r="F46" s="294"/>
       <c r="G46" s="296" t="n">
         <f aca="false">G45*C30</f>
-        <v>1290.75784253894</v>
+        <v>890.343887239661</v>
       </c>
       <c r="H46" s="295"/>
     </row>
@@ -36060,7 +36330,7 @@
       </c>
       <c r="F40" s="86" t="n">
         <f aca="false">E40*E41*E42</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" s="86"/>
       <c r="J40" s="92"/>
@@ -36328,7 +36598,7 @@
       </c>
       <c r="F52" s="98" t="n">
         <f aca="false">E52*E53*E54</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="G52" s="81"/>
       <c r="J52" s="92"/>
@@ -36343,7 +36613,7 @@
       </c>
       <c r="N52" s="80" t="n">
         <f aca="false">M52*M53*M54</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="O52" s="81"/>
     </row>
@@ -37104,6 +37374,1244 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="278"/>
+      <c r="C2" s="279" t="str">
+        <f aca="false">+RESUMEN!B4</f>
+        <v>GERENCIA TERRITORIAL BAJO MAYO - TARAPOTO</v>
+      </c>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+    </row>
+    <row r="3" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="278"/>
+      <c r="C3" s="279" t="str">
+        <f aca="false">+RESUMEN!B5</f>
+        <v>“CREACIÓN DEL SERVICIO DE PROTECCIÓN A MUJERES VÍCTIMAS DE VIOLENCIA EN SITUACIÓN DE RIESGO DE FEMINICIDIO O PELIGRE SU INTEGRIDAD Y/O SALUD FÍSICA Y/O MENTAL EN HOGAR DE REFUGIO TEMPORAL DISTRITO DE MORALES DE LA PROVINCIA DE SAN MARTÍN DEL DEPARTAMENTO DE SAN MARTÍN”, con CUI N.° 2675514</v>
+      </c>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="278"/>
+      <c r="C4" s="279" t="str">
+        <f aca="false">+RESUMEN!B6</f>
+        <v>SAN MARTIN - SAN MARTIN - MORALES</v>
+      </c>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="278"/>
+      <c r="C5" s="280" t="n">
+        <f aca="false">+RESUMEN!B7</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="294" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E10" s="282" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F10" s="282" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G10" s="282" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H10" s="282" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>952</v>
+      </c>
+      <c r="C11" s="289" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="D11" s="289" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="E11" s="306" t="n">
+        <f aca="false">D11/C11</f>
+        <v>0.328110599078341</v>
+      </c>
+      <c r="F11" s="289" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G11" s="290" t="n">
+        <f aca="false">ROUND(E11*F11,2)</f>
+        <v>29.3</v>
+      </c>
+      <c r="H11" s="149" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>954</v>
+      </c>
+      <c r="C12" s="289" t="n">
+        <v>68.1</v>
+      </c>
+      <c r="D12" s="289" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="E12" s="306" t="n">
+        <f aca="false">D12/C12</f>
+        <v>0.329074889867841</v>
+      </c>
+      <c r="F12" s="289" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="G12" s="290" t="n">
+        <f aca="false">ROUND(E12*F12,2)</f>
+        <v>22.95</v>
+      </c>
+      <c r="H12" s="149" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>955</v>
+      </c>
+      <c r="C13" s="289" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D13" s="289" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="E13" s="306" t="n">
+        <f aca="false">D13/C13</f>
+        <v>0.330995106035889</v>
+      </c>
+      <c r="F13" s="289" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G13" s="290" t="n">
+        <f aca="false">ROUND(E13*F13,2)</f>
+        <v>20.79</v>
+      </c>
+      <c r="H13" s="149" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="294" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B15" s="294"/>
+      <c r="C15" s="294"/>
+      <c r="D15" s="294"/>
+      <c r="E15" s="294"/>
+      <c r="F15" s="294"/>
+      <c r="G15" s="294"/>
+      <c r="H15" s="294"/>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C16" s="149"/>
+      <c r="D16" s="149"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="149"/>
+      <c r="G16" s="149"/>
+      <c r="H16" s="149"/>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="149"/>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C19" s="149"/>
+      <c r="D19" s="149"/>
+      <c r="E19" s="149"/>
+      <c r="F19" s="149"/>
+      <c r="G19" s="149"/>
+      <c r="H19" s="149"/>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C20" s="149"/>
+      <c r="D20" s="149"/>
+      <c r="E20" s="149"/>
+      <c r="F20" s="149"/>
+      <c r="G20" s="149"/>
+      <c r="H20" s="149"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:H20"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H48"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="277" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1" s="277"/>
+      <c r="C1" s="277"/>
+      <c r="D1" s="277"/>
+      <c r="E1" s="277"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
+    </row>
+    <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="278"/>
+      <c r="C2" s="279" t="str">
+        <f aca="false">+RESUMEN!B4</f>
+        <v>GERENCIA TERRITORIAL BAJO MAYO - TARAPOTO</v>
+      </c>
+      <c r="D2" s="279"/>
+      <c r="E2" s="279"/>
+      <c r="F2" s="279"/>
+      <c r="G2" s="279"/>
+      <c r="H2" s="279"/>
+    </row>
+    <row r="3" customFormat="false" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="278"/>
+      <c r="C3" s="279" t="str">
+        <f aca="false">+RESUMEN!B5</f>
+        <v>“CREACIÓN DEL SERVICIO DE PROTECCIÓN A MUJERES VÍCTIMAS DE VIOLENCIA EN SITUACIÓN DE RIESGO DE FEMINICIDIO O PELIGRE SU INTEGRIDAD Y/O SALUD FÍSICA Y/O MENTAL EN HOGAR DE REFUGIO TEMPORAL DISTRITO DE MORALES DE LA PROVINCIA DE SAN MARTÍN DEL DEPARTAMENTO DE SAN MARTÍN”, con CUI N.° 2675514</v>
+      </c>
+      <c r="D3" s="279"/>
+      <c r="E3" s="279"/>
+      <c r="F3" s="279"/>
+      <c r="G3" s="279"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="278"/>
+      <c r="C4" s="279" t="str">
+        <f aca="false">+RESUMEN!B6</f>
+        <v>SAN MARTIN - SAN MARTIN - MORALES</v>
+      </c>
+      <c r="D4" s="279"/>
+      <c r="E4" s="279"/>
+      <c r="F4" s="279"/>
+      <c r="G4" s="279"/>
+      <c r="H4" s="279"/>
+    </row>
+    <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="278"/>
+      <c r="C5" s="280" t="n">
+        <f aca="false">+RESUMEN!B7</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="280"/>
+      <c r="E5" s="280"/>
+      <c r="F5" s="280"/>
+      <c r="G5" s="280"/>
+      <c r="H5" s="280"/>
+    </row>
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="281" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B7" s="281"/>
+      <c r="C7" s="281"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="281"/>
+      <c r="F7" s="281"/>
+      <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
+    </row>
+    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="294" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B9" s="294"/>
+      <c r="C9" s="294"/>
+      <c r="D9" s="294"/>
+      <c r="E9" s="294"/>
+      <c r="F9" s="294"/>
+      <c r="G9" s="294"/>
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="282" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C10" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="282" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C11" s="285" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="306" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!F23</f>
+        <v>157.0</v>
+      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
+      <c r="H11" s="149" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C12" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="306" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!D37</f>
+        <v>0.3</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
+      <c r="H12" s="149" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C13" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D13" s="307" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
+      <c r="H13" s="149" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="149" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C14" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D14" s="306" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!D40</f>
+        <v>0.0297</v>
+      </c>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
+      <c r="H14" s="149" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="149" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C15" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D15" s="306" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!D41</f>
+        <v>0.594</v>
+      </c>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
+      <c r="H15" s="149" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="149" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C16" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="307" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="149" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="149" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D17" s="306" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!D42</f>
+        <v>0.0005</v>
+      </c>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D18" s="307" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D19" s="307" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B20" s="149" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D20" s="307" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D21" s="307" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D22" s="307" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C23" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D23" s="307" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
+      <c r="H23" s="149" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="294" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B25" s="294"/>
+      <c r="C25" s="294"/>
+      <c r="D25" s="294"/>
+      <c r="E25" s="294"/>
+      <c r="F25" s="294"/>
+      <c r="G25" s="294"/>
+      <c r="H25" s="294"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B26" s="294"/>
+      <c r="C26" s="295" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D26" s="295"/>
+      <c r="E26" s="295"/>
+      <c r="F26" s="295"/>
+      <c r="G26" s="295"/>
+      <c r="H26" s="295"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="294" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B27" s="294"/>
+      <c r="C27" s="295" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D27" s="295"/>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
+      <c r="H27" s="295"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="294" t="s">
+        <v>502</v>
+      </c>
+      <c r="B28" s="294"/>
+      <c r="C28" s="295" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="295"/>
+      <c r="E28" s="295"/>
+      <c r="F28" s="295"/>
+      <c r="G28" s="295"/>
+      <c r="H28" s="295"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="294" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B29" s="294"/>
+      <c r="C29" s="290" t="n">
+        <f aca="false">'DESAGREGADO LLORADEROS'!F23</f>
+        <v>157.0</v>
+      </c>
+      <c r="D29" s="290"/>
+      <c r="E29" s="290"/>
+      <c r="F29" s="290"/>
+      <c r="G29" s="290"/>
+      <c r="H29" s="290"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="294" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B30" s="294"/>
+      <c r="C30" s="290" t="n">
+        <f aca="false">$D$21</f>
+        <v>24.0</v>
+      </c>
+      <c r="D30" s="290"/>
+      <c r="E30" s="290"/>
+      <c r="F30" s="290"/>
+      <c r="G30" s="290"/>
+      <c r="H30" s="290"/>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B31" s="282" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C31" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="282" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E31" s="282" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F31" s="282" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G31" s="282" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H31" s="282" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="294" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C32" s="294"/>
+      <c r="D32" s="294"/>
+      <c r="E32" s="294"/>
+      <c r="F32" s="294"/>
+      <c r="G32" s="294"/>
+      <c r="H32" s="294"/>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B33" s="295" t="s">
+        <v>952</v>
+      </c>
+      <c r="C33" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D33" s="306" t="n">
+        <f aca="false">E33*$C$30/8</f>
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="306" t="n">
+        <f aca="false">$D$22*8/$D$21</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="F33" s="290" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>29.3</v>
+      </c>
+      <c r="G33" s="290" t="n">
+        <f aca="false">E33*F33</f>
+        <v>4.88333333333333</v>
+      </c>
+      <c r="H33" s="149" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B34" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="C34" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D34" s="306" t="n">
+        <f aca="false">E34*$C$30/8</f>
+        <v>1.0</v>
+      </c>
+      <c r="E34" s="306" t="n">
+        <f aca="false">$D$23*8/$D$21</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="F34" s="290" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
+        <v>20.79</v>
+      </c>
+      <c r="G34" s="290" t="n">
+        <f aca="false">E34*F34</f>
+        <v>6.93</v>
+      </c>
+      <c r="H34" s="149" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21"/>
+      <c r="B35" s="294" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C35" s="295"/>
+      <c r="D35" s="295"/>
+      <c r="E35" s="295"/>
+      <c r="F35" s="295"/>
+      <c r="G35" s="296" t="n">
+        <f aca="false">SUM(G33:G34)</f>
+        <v>11.8133333333333</v>
+      </c>
+      <c r="H35" s="295"/>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21"/>
+      <c r="B36" s="294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C36" s="294"/>
+      <c r="D36" s="294"/>
+      <c r="E36" s="294"/>
+      <c r="F36" s="294"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B37" s="295" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C37" s="285" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="295"/>
+      <c r="E37" s="306" t="n">
+        <f aca="false">$D$12*(1+$D$13)</f>
+        <v>0.315</v>
+      </c>
+      <c r="F37" s="290" t="n">
+        <f aca="false">39.9/1.18/3</f>
+        <v>11.271186440678</v>
+      </c>
+      <c r="G37" s="290" t="n">
+        <f aca="false">E37*F37</f>
+        <v>3.55042372881356</v>
+      </c>
+      <c r="H37" s="149" t="s">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B38" s="295" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C38" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" s="295"/>
+      <c r="E38" s="306" t="n">
+        <f aca="false">$D$14</f>
+        <v>0.0297</v>
+      </c>
+      <c r="F38" s="290" t="n">
+        <f aca="false">70.0/1.18</f>
+        <v>59.3220338983051</v>
+      </c>
+      <c r="G38" s="290" t="n">
+        <f aca="false">E38*F38</f>
+        <v>1.76186440677966</v>
+      </c>
+      <c r="H38" s="149" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B39" s="295" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C39" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="295"/>
+      <c r="E39" s="306" t="n">
+        <f aca="false">$D$15*(1+$D$16)</f>
+        <v>0.6237</v>
+      </c>
+      <c r="F39" s="290" t="n">
+        <f aca="false">2300.0/400/1.18</f>
+        <v>4.8728813559322</v>
+      </c>
+      <c r="G39" s="290" t="n">
+        <f aca="false">E39*F39</f>
+        <v>3.03921610169492</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B40" s="295" t="s">
+        <v>944</v>
+      </c>
+      <c r="C40" s="285" t="s">
+        <v>945</v>
+      </c>
+      <c r="D40" s="295"/>
+      <c r="E40" s="306" t="n">
+        <f aca="false">$D$17*$D$18</f>
+        <v>0.00525</v>
+      </c>
+      <c r="F40" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F76</f>
+        <v>30.93</v>
+      </c>
+      <c r="G40" s="290" t="n">
+        <f aca="false">E40*F40</f>
+        <v>0.1623825</v>
+      </c>
+      <c r="H40" s="149" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B41" s="295" t="s">
+        <v>946</v>
+      </c>
+      <c r="C41" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="295"/>
+      <c r="E41" s="306" t="n">
+        <f aca="false">$D$17*$D$19</f>
+        <v>0.000525</v>
+      </c>
+      <c r="F41" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <v>40.68</v>
+      </c>
+      <c r="G41" s="290" t="n">
+        <f aca="false">E41*F41</f>
+        <v>0.021357</v>
+      </c>
+      <c r="H41" s="149" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B42" s="295" t="s">
+        <v>948</v>
+      </c>
+      <c r="C42" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D42" s="295"/>
+      <c r="E42" s="306" t="n">
+        <f aca="false">$D$17*$D$20</f>
+        <v>0.000135</v>
+      </c>
+      <c r="F42" s="290" t="n">
+        <f aca="false">'ACU TAPA REGISTRO'!F79</f>
+        <v>8.33</v>
+      </c>
+      <c r="G42" s="290" t="n">
+        <f aca="false">E42*F42</f>
+        <v>0.00112455</v>
+      </c>
+      <c r="H42" s="149" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21"/>
+      <c r="B43" s="294" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C43" s="295"/>
+      <c r="D43" s="295"/>
+      <c r="E43" s="295"/>
+      <c r="F43" s="295"/>
+      <c r="G43" s="296" t="n">
+        <f aca="false">SUM(G37:G42)</f>
+        <v>8.53636828728814</v>
+      </c>
+      <c r="H43" s="295"/>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21"/>
+      <c r="B44" s="294" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C44" s="294"/>
+      <c r="D44" s="294"/>
+      <c r="E44" s="294"/>
+      <c r="F44" s="294"/>
+      <c r="G44" s="294"/>
+      <c r="H44" s="294"/>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B45" s="295" t="s">
+        <v>969</v>
+      </c>
+      <c r="C45" s="285" t="s">
+        <v>970</v>
+      </c>
+      <c r="D45" s="295"/>
+      <c r="E45" s="284" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F45" s="290" t="n">
+        <f aca="false">+G35</f>
+        <v>11.8133333333333</v>
+      </c>
+      <c r="G45" s="290" t="n">
+        <f aca="false">E45*F45</f>
+        <v>0.3544</v>
+      </c>
+      <c r="H45" s="149" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21"/>
+      <c r="B46" s="294" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C46" s="295"/>
+      <c r="D46" s="295"/>
+      <c r="E46" s="295"/>
+      <c r="F46" s="295"/>
+      <c r="G46" s="296" t="n">
+        <f aca="false">SUM(G45:G45)</f>
+        <v>0.3544</v>
+      </c>
+      <c r="H46" s="295"/>
+    </row>
+    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="294" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B47" s="294"/>
+      <c r="C47" s="294"/>
+      <c r="D47" s="294"/>
+      <c r="E47" s="294"/>
+      <c r="F47" s="294"/>
+      <c r="G47" s="296" t="n">
+        <f aca="false">+G35+G43+G46</f>
+        <v>20.7041016206215</v>
+      </c>
+      <c r="H47" s="295"/>
+    </row>
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="294" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B48" s="294"/>
+      <c r="C48" s="294"/>
+      <c r="D48" s="294"/>
+      <c r="E48" s="294"/>
+      <c r="F48" s="294"/>
+      <c r="G48" s="296" t="n">
+        <f aca="false">G47*C29</f>
+        <v>3250.54395443757</v>
+      </c>
+      <c r="H48" s="295"/>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A48:F48"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -37784,7 +39292,7 @@
       </c>
       <c r="G27" s="89" t="n">
         <f aca="false">F27*F28</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H27" s="118"/>
       <c r="I27" s="1"/>
@@ -37803,7 +39311,7 @@
       </c>
       <c r="O27" s="89" t="n">
         <f aca="false">N27*N28</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P27" s="118"/>
     </row>
@@ -37846,7 +39354,7 @@
       </c>
       <c r="G29" s="89" t="n">
         <f aca="false">F29*F30+F31</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="118"/>
       <c r="I29" s="1"/>
@@ -37863,7 +39371,7 @@
       </c>
       <c r="O29" s="89" t="n">
         <f aca="false">N29*N30+N31</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P29" s="118"/>
     </row>
@@ -38326,7 +39834,7 @@
       </c>
       <c r="O45" s="89" t="n">
         <f aca="false">N45*N46</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P45" s="118" t="n">
         <f aca="false">SUM(O45:O53)</f>
@@ -38389,7 +39897,7 @@
       </c>
       <c r="O47" s="89" t="n">
         <f aca="false">N47*N48</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P47" s="118"/>
     </row>
@@ -38639,7 +40147,7 @@
       </c>
       <c r="G57" s="89" t="n">
         <f aca="false">F57*F58</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" s="118" t="n">
         <f aca="false">SUM(G57:G65)</f>
@@ -38707,7 +40215,7 @@
       </c>
       <c r="G59" s="89" t="n">
         <f aca="false">F59*F60</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" s="118"/>
       <c r="J59" s="119"/>
@@ -38785,7 +40293,7 @@
       </c>
       <c r="O61" s="89" t="n">
         <f aca="false">N61*N62</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P61" s="118"/>
     </row>
@@ -38843,7 +40351,7 @@
       </c>
       <c r="O63" s="89" t="n">
         <f aca="false">N63*N64+N65</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P63" s="118"/>
     </row>
@@ -39703,7 +41211,7 @@
       </c>
       <c r="D12" s="117" t="n">
         <f aca="false">C12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E12" s="117" t="n">
         <v>5.9</v>
@@ -39717,40 +41225,40 @@
       </c>
       <c r="H12" s="117" t="n">
         <f aca="false">C12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I12" s="135" t="n">
         <f aca="false">H12*G12</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J12" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E12/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K12" s="117" t="n">
         <f aca="false">C12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L12" s="135" t="n">
         <f aca="false">K12*J12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M12" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N12" s="117" t="n">
         <f aca="false">C12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O12" s="135" t="n">
         <f aca="false">N12*M12</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P12" s="138"/>
       <c r="Q12" s="138"/>
       <c r="R12" s="139" t="n">
         <f aca="false">Q12*P12</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39762,7 +41270,7 @@
       </c>
       <c r="D13" s="117" t="n">
         <f aca="false">C13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E13" s="117" t="n">
         <v>5.9</v>
@@ -39776,40 +41284,40 @@
       </c>
       <c r="H13" s="117" t="n">
         <f aca="false">C13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I13" s="135" t="n">
         <f aca="false">H13*G13</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J13" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E13/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K13" s="117" t="n">
         <f aca="false">C13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L13" s="135" t="n">
         <f aca="false">K13*J13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M13" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N13" s="117" t="n">
         <f aca="false">C13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O13" s="135" t="n">
         <f aca="false">N13*M13</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P13" s="138"/>
       <c r="Q13" s="138"/>
       <c r="R13" s="139" t="n">
         <f aca="false">Q13*P13</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39842,7 +41350,7 @@
       </c>
       <c r="D15" s="117" t="n">
         <f aca="false">C15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E15" s="117" t="n">
         <v>6.27</v>
@@ -39856,40 +41364,40 @@
       </c>
       <c r="H15" s="117" t="n">
         <f aca="false">C15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="135" t="n">
         <f aca="false">H15*G15</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J15" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E15/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K15" s="117" t="n">
         <f aca="false">C15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L15" s="135" t="n">
         <f aca="false">K15*J15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M15" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N15" s="117" t="n">
         <f aca="false">C15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O15" s="135" t="n">
         <f aca="false">N15*M15</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P15" s="138"/>
       <c r="Q15" s="138"/>
       <c r="R15" s="139" t="n">
         <f aca="false">Q15*P15</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39901,7 +41409,7 @@
       </c>
       <c r="D16" s="117" t="n">
         <f aca="false">C16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E16" s="117" t="n">
         <v>6.27</v>
@@ -39915,40 +41423,40 @@
       </c>
       <c r="H16" s="117" t="n">
         <f aca="false">C16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="135" t="n">
         <f aca="false">H16*G16</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J16" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E16/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K16" s="117" t="n">
         <f aca="false">C16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L16" s="135" t="n">
         <f aca="false">K16*J16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M16" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N16" s="117" t="n">
         <f aca="false">C16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O16" s="135" t="n">
         <f aca="false">N16*M16</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P16" s="138"/>
       <c r="Q16" s="138"/>
       <c r="R16" s="139" t="n">
         <f aca="false">Q16*P16</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39981,7 +41489,7 @@
       </c>
       <c r="D18" s="117" t="n">
         <f aca="false">C18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E18" s="117" t="n">
         <v>6.35</v>
@@ -39995,40 +41503,40 @@
       </c>
       <c r="H18" s="117" t="n">
         <f aca="false">C18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I18" s="135" t="n">
         <f aca="false">H18*G18</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J18" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E18/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K18" s="117" t="n">
         <f aca="false">C18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L18" s="135" t="n">
         <f aca="false">K18*J18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M18" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N18" s="117" t="n">
         <f aca="false">C18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O18" s="135" t="n">
         <f aca="false">N18*M18</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P18" s="138"/>
       <c r="Q18" s="138"/>
       <c r="R18" s="139" t="n">
         <f aca="false">Q18*P18</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40040,7 +41548,7 @@
       </c>
       <c r="D19" s="117" t="n">
         <f aca="false">C19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E19" s="117" t="n">
         <v>6.35</v>
@@ -40054,40 +41562,40 @@
       </c>
       <c r="H19" s="117" t="n">
         <f aca="false">C19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I19" s="135" t="n">
         <f aca="false">H19*G19</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J19" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E19/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K19" s="117" t="n">
         <f aca="false">C19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L19" s="135" t="n">
         <f aca="false">K19*J19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M19" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N19" s="117" t="n">
         <f aca="false">C19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O19" s="135" t="n">
         <f aca="false">N19*M19</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P19" s="138"/>
       <c r="Q19" s="138"/>
       <c r="R19" s="139" t="n">
         <f aca="false">Q19*P19</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40120,7 +41628,7 @@
       </c>
       <c r="D21" s="117" t="n">
         <f aca="false">C21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E21" s="117" t="n">
         <v>6.26</v>
@@ -40134,40 +41642,40 @@
       </c>
       <c r="H21" s="117" t="n">
         <f aca="false">C21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I21" s="135" t="n">
         <f aca="false">H21*G21</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J21" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E21/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K21" s="117" t="n">
         <f aca="false">C21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L21" s="135" t="n">
         <f aca="false">K21*J21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M21" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N21" s="117" t="n">
         <f aca="false">C21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O21" s="135" t="n">
         <f aca="false">N21*M21</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P21" s="138"/>
       <c r="Q21" s="138"/>
       <c r="R21" s="139" t="n">
         <f aca="false">Q21*P21</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40179,7 +41687,7 @@
       </c>
       <c r="D22" s="117" t="n">
         <f aca="false">C22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E22" s="117" t="n">
         <v>6.26</v>
@@ -40193,40 +41701,40 @@
       </c>
       <c r="H22" s="117" t="n">
         <f aca="false">C22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I22" s="135" t="n">
         <f aca="false">H22*G22</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J22" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E22/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K22" s="117" t="n">
         <f aca="false">C22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L22" s="135" t="n">
         <f aca="false">K22*J22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M22" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N22" s="117" t="n">
         <f aca="false">C22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O22" s="135" t="n">
         <f aca="false">N22*M22</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P22" s="138"/>
       <c r="Q22" s="138"/>
       <c r="R22" s="139" t="n">
         <f aca="false">Q22*P22</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40259,7 +41767,7 @@
       </c>
       <c r="D24" s="117" t="n">
         <f aca="false">C24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E24" s="117" t="n">
         <v>7.53</v>
@@ -40273,40 +41781,40 @@
       </c>
       <c r="H24" s="117" t="n">
         <f aca="false">C24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I24" s="135" t="n">
         <f aca="false">H24*G24</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J24" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E24/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K24" s="117" t="n">
         <f aca="false">C24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L24" s="135" t="n">
         <f aca="false">K24*J24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M24" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N24" s="117" t="n">
         <f aca="false">C24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O24" s="135" t="n">
         <f aca="false">N24*M24</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P24" s="138"/>
       <c r="Q24" s="138"/>
       <c r="R24" s="139" t="n">
         <f aca="false">Q24*P24</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40318,7 +41826,7 @@
       </c>
       <c r="D25" s="117" t="n">
         <f aca="false">C25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E25" s="117" t="n">
         <v>7.53</v>
@@ -40332,40 +41840,40 @@
       </c>
       <c r="H25" s="117" t="n">
         <f aca="false">C25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I25" s="135" t="n">
         <f aca="false">H25*G25</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J25" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E25/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K25" s="117" t="n">
         <f aca="false">C25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L25" s="135" t="n">
         <f aca="false">K25*J25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M25" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N25" s="117" t="n">
         <f aca="false">C25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O25" s="135" t="n">
         <f aca="false">N25*M25</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P25" s="138"/>
       <c r="Q25" s="138"/>
       <c r="R25" s="139" t="n">
         <f aca="false">Q25*P25</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40398,7 +41906,7 @@
       </c>
       <c r="D27" s="117" t="n">
         <f aca="false">C27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E27" s="117" t="n">
         <v>6.18</v>
@@ -40412,40 +41920,40 @@
       </c>
       <c r="H27" s="117" t="n">
         <f aca="false">C27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I27" s="135" t="n">
         <f aca="false">H27*G27</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J27" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E27/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K27" s="117" t="n">
         <f aca="false">C27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L27" s="135" t="n">
         <f aca="false">K27*J27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M27" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N27" s="117" t="n">
         <f aca="false">C27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O27" s="135" t="n">
         <f aca="false">N27*M27</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P27" s="138"/>
       <c r="Q27" s="138"/>
       <c r="R27" s="139" t="n">
         <f aca="false">Q27*P27</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40457,7 +41965,7 @@
       </c>
       <c r="D28" s="117" t="n">
         <f aca="false">C28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E28" s="117" t="n">
         <v>6.18</v>
@@ -40471,40 +41979,40 @@
       </c>
       <c r="H28" s="117" t="n">
         <f aca="false">C28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I28" s="135" t="n">
         <f aca="false">H28*G28</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J28" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E28/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K28" s="117" t="n">
         <f aca="false">C28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L28" s="135" t="n">
         <f aca="false">K28*J28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M28" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="117" t="n">
         <f aca="false">C28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O28" s="135" t="n">
         <f aca="false">N28*M28</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P28" s="138"/>
       <c r="Q28" s="138"/>
       <c r="R28" s="139" t="n">
         <f aca="false">Q28*P28</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40537,7 +42045,7 @@
       </c>
       <c r="D30" s="117" t="n">
         <f aca="false">C30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E30" s="117" t="n">
         <v>6.24</v>
@@ -40551,40 +42059,40 @@
       </c>
       <c r="H30" s="117" t="n">
         <f aca="false">C30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I30" s="135" t="n">
         <f aca="false">H30*G30</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J30" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E30/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K30" s="117" t="n">
         <f aca="false">C30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L30" s="135" t="n">
         <f aca="false">K30*J30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M30" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N30" s="117" t="n">
         <f aca="false">C30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O30" s="135" t="n">
         <f aca="false">N30*M30</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P30" s="138"/>
       <c r="Q30" s="138"/>
       <c r="R30" s="139" t="n">
         <f aca="false">Q30*P30</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40596,7 +42104,7 @@
       </c>
       <c r="D31" s="117" t="n">
         <f aca="false">C31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="E31" s="117" t="n">
         <v>6.24</v>
@@ -40610,40 +42118,40 @@
       </c>
       <c r="H31" s="117" t="n">
         <f aca="false">C31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="I31" s="135" t="n">
         <f aca="false">H31*G31</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="J31" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E31/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K31" s="117" t="n">
         <f aca="false">C31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L31" s="135" t="n">
         <f aca="false">K31*J31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="M31" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N31" s="117" t="n">
         <f aca="false">C31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O31" s="135" t="n">
         <f aca="false">N31*M31</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="P31" s="138"/>
       <c r="Q31" s="138"/>
       <c r="R31" s="139" t="n">
         <f aca="false">Q31*P31</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40676,7 +42184,7 @@
       </c>
       <c r="D33" s="117" t="n">
         <f aca="false">C33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E33" s="117" t="n">
         <v>6.26</v>
@@ -40690,40 +42198,40 @@
       </c>
       <c r="H33" s="2" t="n">
         <f aca="false">C33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I33" s="135" t="n">
         <f aca="false">H33*G33</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J33" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E33/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K33" s="117" t="n">
         <f aca="false">C33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L33" s="135" t="n">
         <f aca="false">K33*J33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M33" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N33" s="117" t="n">
         <f aca="false">C33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O33" s="135" t="n">
         <f aca="false">N33*M33</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P33" s="138"/>
       <c r="Q33" s="138"/>
       <c r="R33" s="139" t="n">
         <f aca="false">Q33*P33</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40735,7 +42243,7 @@
       </c>
       <c r="D34" s="117" t="n">
         <f aca="false">C34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E34" s="117" t="n">
         <v>6.26</v>
@@ -40749,40 +42257,40 @@
       </c>
       <c r="H34" s="117" t="n">
         <f aca="false">C34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="135" t="n">
         <f aca="false">H34*G34</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J34" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E34/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K34" s="117" t="n">
         <f aca="false">C34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L34" s="135" t="n">
         <f aca="false">K34*J34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M34" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N34" s="117" t="n">
         <f aca="false">C34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O34" s="135" t="n">
         <f aca="false">N34*M34</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P34" s="138"/>
       <c r="Q34" s="138"/>
       <c r="R34" s="139" t="n">
         <f aca="false">Q34*P34</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40815,7 +42323,7 @@
       </c>
       <c r="D36" s="117" t="n">
         <f aca="false">C36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E36" s="117" t="n">
         <v>6.26</v>
@@ -40829,40 +42337,40 @@
       </c>
       <c r="H36" s="117" t="n">
         <f aca="false">C36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I36" s="135" t="n">
         <f aca="false">H36*G36</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J36" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E36/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K36" s="117" t="n">
         <f aca="false">C36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L36" s="135" t="n">
         <f aca="false">K36*J36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M36" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N36" s="117" t="n">
         <f aca="false">C36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O36" s="135" t="n">
         <f aca="false">N36*M36</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P36" s="138"/>
       <c r="Q36" s="138"/>
       <c r="R36" s="139" t="n">
         <f aca="false">Q36*P36</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40874,7 +42382,7 @@
       </c>
       <c r="D37" s="117" t="n">
         <f aca="false">C37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E37" s="117" t="n">
         <v>6.26</v>
@@ -40888,40 +42396,40 @@
       </c>
       <c r="H37" s="117" t="n">
         <f aca="false">C37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I37" s="135" t="n">
         <f aca="false">H37*G37</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="J37" s="117" t="n">
         <f aca="false">MAX(1,ROUNDDOWN(E37/4,0))</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="K37" s="117" t="n">
         <f aca="false">C37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="L37" s="135" t="n">
         <f aca="false">K37*J37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="M37" s="117" t="n">
         <v>2</v>
       </c>
       <c r="N37" s="117" t="n">
         <f aca="false">C37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="O37" s="135" t="n">
         <f aca="false">N37*M37</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P37" s="138"/>
       <c r="Q37" s="138"/>
       <c r="R37" s="139" t="n">
         <f aca="false">Q37*P37</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -40954,53 +42462,53 @@
       </c>
       <c r="D39" s="117" t="n">
         <f aca="false">C39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="E39" s="117" t="n">
         <v>11</v>
       </c>
       <c r="F39" s="135" t="n">
         <f aca="false">E39*D39</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="G39" s="117" t="n">
         <v>3</v>
       </c>
       <c r="H39" s="117" t="n">
         <f aca="false">C39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I39" s="135" t="n">
         <f aca="false">H39*G39</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="J39" s="117" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="117" t="n">
         <f aca="false">C39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L39" s="135" t="n">
         <f aca="false">K39*J39</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="M39" s="117" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="117" t="n">
         <f aca="false">C39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O39" s="135" t="n">
         <f aca="false">N39*M39</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P39" s="138"/>
       <c r="Q39" s="138"/>
       <c r="R39" s="139" t="n">
         <f aca="false">Q39*P39</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41012,53 +42520,53 @@
       </c>
       <c r="D40" s="117" t="n">
         <f aca="false">C40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="E40" s="117" t="n">
         <v>11</v>
       </c>
       <c r="F40" s="135" t="n">
         <f aca="false">E40*D40</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="G40" s="117" t="n">
         <v>3</v>
       </c>
       <c r="H40" s="117" t="n">
         <f aca="false">C40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="I40" s="135" t="n">
         <f aca="false">H40*G40</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="J40" s="117" t="n">
         <v>3</v>
       </c>
       <c r="K40" s="117" t="n">
         <f aca="false">C40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L40" s="135" t="n">
         <f aca="false">K40*J40</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="M40" s="117" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="117" t="n">
         <f aca="false">C40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O40" s="135" t="n">
         <f aca="false">N40*M40</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="P40" s="138"/>
       <c r="Q40" s="138"/>
       <c r="R40" s="139" t="n">
         <f aca="false">Q40*P40</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41070,53 +42578,53 @@
       </c>
       <c r="D41" s="117" t="n">
         <f aca="false">C41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E41" s="117" t="n">
         <v>6</v>
       </c>
       <c r="F41" s="135" t="n">
         <f aca="false">E41*D41</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="G41" s="117" t="n">
         <v>3</v>
       </c>
       <c r="H41" s="117" t="n">
         <f aca="false">C41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="I41" s="135" t="n">
         <f aca="false">H41*G41</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J41" s="117" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="117" t="n">
         <f aca="false">C41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L41" s="135" t="n">
         <f aca="false">K41*J41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="M41" s="117" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="117" t="n">
         <f aca="false">C41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="O41" s="135" t="n">
         <f aca="false">N41*M41</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P41" s="138"/>
       <c r="Q41" s="138"/>
       <c r="R41" s="139" t="n">
         <f aca="false">Q41*P41</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41128,59 +42636,59 @@
       </c>
       <c r="D42" s="117" t="n">
         <f aca="false">C42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="E42" s="117" t="n">
         <v>6</v>
       </c>
       <c r="F42" s="135" t="n">
         <f aca="false">E42*D42</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="G42" s="117" t="n">
         <v>3</v>
       </c>
       <c r="H42" s="117" t="n">
         <f aca="false">C42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="I42" s="135" t="n">
         <f aca="false">H42*G42</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="J42" s="117" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="117" t="n">
         <f aca="false">C42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L42" s="135" t="n">
         <f aca="false">K42*J42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="M42" s="117" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="117" t="n">
         <f aca="false">C42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="O42" s="135" t="n">
         <f aca="false">N42*M42</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P42" s="138"/>
       <c r="Q42" s="138"/>
       <c r="R42" s="139" t="n">
         <f aca="false">Q42*P42</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C43" s="142" t="n">
         <f aca="false">SUM(C11:C42)</f>
-        <v>54</v>
+        <v>54.0</v>
       </c>
       <c r="D43" s="117"/>
       <c r="E43" s="117"/>
@@ -41192,25 +42700,25 @@
       <c r="H43" s="117"/>
       <c r="I43" s="142" t="n">
         <f aca="false">SUM(I11:I42)</f>
-        <v>162</v>
+        <v>162.0</v>
       </c>
       <c r="J43" s="117"/>
       <c r="K43" s="117"/>
       <c r="L43" s="142" t="n">
         <f aca="false">SUM(L11:L42)</f>
-        <v>70</v>
+        <v>70.0</v>
       </c>
       <c r="M43" s="117"/>
       <c r="N43" s="117"/>
       <c r="O43" s="142" t="n">
         <f aca="false">SUM(O11:O42)</f>
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="P43" s="138"/>
       <c r="Q43" s="138"/>
       <c r="R43" s="142" t="n">
         <f aca="false">SUM(R11:R42)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41439,27 +42947,27 @@
       </c>
       <c r="F12" s="117" t="n">
         <f aca="false">IF(D12&gt;0,ROUNDUP(D12/$F$50,0)+1,0)</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="G12" s="135" t="n">
         <f aca="false">C12*F12</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="H12" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I12" s="135" t="n">
         <f aca="false">C12*H12</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J12" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K12" s="135" t="n">
         <f aca="false">C12*J12</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41479,27 +42987,27 @@
       </c>
       <c r="F13" s="117" t="n">
         <f aca="false">IF(D13&gt;0,ROUNDUP(D13/$F$50,0)+1,0)</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="G13" s="135" t="n">
         <f aca="false">C13*F13</f>
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="H13" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I13" s="135" t="n">
         <f aca="false">C13*H13</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J13" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K13" s="135" t="n">
         <f aca="false">C13*J13</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41532,27 +43040,27 @@
       </c>
       <c r="F15" s="117" t="n">
         <f aca="false">IF(D15&gt;0,ROUNDUP(D15/$F$50,0)+1,0)</f>
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="G15" s="135" t="n">
         <f aca="false">C15*F15</f>
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H15" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="135" t="n">
         <f aca="false">C15*H15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J15" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K15" s="135" t="n">
         <f aca="false">C15*J15</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41572,27 +43080,27 @@
       </c>
       <c r="F16" s="117" t="n">
         <f aca="false">IF(D16&gt;0,ROUNDUP(D16/$F$50,0)+1,0)</f>
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="G16" s="135" t="n">
         <f aca="false">C16*F16</f>
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="H16" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="135" t="n">
         <f aca="false">C16*H16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J16" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K16" s="135" t="n">
         <f aca="false">C16*J16</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41625,27 +43133,27 @@
       </c>
       <c r="F18" s="117" t="n">
         <f aca="false">IF(D18&gt;0,ROUNDUP(D18/$F$50,0)+1,0)</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="G18" s="135" t="n">
         <f aca="false">C18*F18</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="H18" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I18" s="135" t="n">
         <f aca="false">C18*H18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J18" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K18" s="135" t="n">
         <f aca="false">C18*J18</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41665,27 +43173,27 @@
       </c>
       <c r="F19" s="117" t="n">
         <f aca="false">IF(D19&gt;0,ROUNDUP(D19/$F$50,0)+1,0)</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="G19" s="135" t="n">
         <f aca="false">C19*F19</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="H19" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I19" s="135" t="n">
         <f aca="false">C19*H19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J19" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K19" s="135" t="n">
         <f aca="false">C19*J19</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41718,27 +43226,27 @@
       </c>
       <c r="F21" s="117" t="n">
         <f aca="false">IF(D21&gt;0,ROUNDUP(D21/$F$50,0)+1,0)</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="G21" s="135" t="n">
         <f aca="false">C21*F21</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="H21" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I21" s="135" t="n">
         <f aca="false">C21*H21</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J21" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K21" s="135" t="n">
         <f aca="false">C21*J21</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41758,27 +43266,27 @@
       </c>
       <c r="F22" s="117" t="n">
         <f aca="false">IF(D22&gt;0,ROUNDUP(D22/$F$50,0)+1,0)</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="G22" s="135" t="n">
         <f aca="false">C22*F22</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="H22" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I22" s="135" t="n">
         <f aca="false">C22*H22</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J22" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K22" s="135" t="n">
         <f aca="false">C22*J22</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41811,27 +43319,27 @@
       </c>
       <c r="F24" s="117" t="n">
         <f aca="false">IF(D24&gt;0,ROUNDUP(D24/$F$50,0)+1,0)</f>
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="G24" s="135" t="n">
         <f aca="false">C24*F24</f>
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="H24" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I24" s="135" t="n">
         <f aca="false">C24*H24</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J24" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K24" s="135" t="n">
         <f aca="false">C24*J24</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41851,27 +43359,27 @@
       </c>
       <c r="F25" s="117" t="n">
         <f aca="false">IF(D25&gt;0,ROUNDUP(D25/$F$50,0)+1,0)</f>
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="G25" s="135" t="n">
         <f aca="false">C25*F25</f>
-        <v>55</v>
+        <v>55.0</v>
       </c>
       <c r="H25" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I25" s="135" t="n">
         <f aca="false">C25*H25</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J25" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K25" s="135" t="n">
         <f aca="false">C25*J25</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41904,27 +43412,27 @@
       </c>
       <c r="F27" s="117" t="n">
         <f aca="false">IF(D27&gt;0,ROUNDUP(D27/$F$50,0)+1,0)</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="G27" s="135" t="n">
         <f aca="false">C27*F27</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="H27" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I27" s="135" t="n">
         <f aca="false">C27*H27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J27" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K27" s="135" t="n">
         <f aca="false">C27*J27</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41944,27 +43452,27 @@
       </c>
       <c r="F28" s="117" t="n">
         <f aca="false">IF(D28&gt;0,ROUNDUP(D28/$F$50,0)+1,0)</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="G28" s="135" t="n">
         <f aca="false">C28*F28</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="H28" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I28" s="135" t="n">
         <f aca="false">C28*H28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J28" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K28" s="135" t="n">
         <f aca="false">C28*J28</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -41997,27 +43505,27 @@
       </c>
       <c r="F30" s="117" t="n">
         <f aca="false">IF(D30&gt;0,ROUNDUP(D30/$F$50,0)+1,0)</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="G30" s="135" t="n">
         <f aca="false">C30*F30</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="H30" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I30" s="135" t="n">
         <f aca="false">C30*H30</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J30" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K30" s="135" t="n">
         <f aca="false">C30*J30</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42037,27 +43545,27 @@
       </c>
       <c r="F31" s="117" t="n">
         <f aca="false">IF(D31&gt;0,ROUNDUP(D31/$F$50,0)+1,0)</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="G31" s="135" t="n">
         <f aca="false">C31*F31</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="H31" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I31" s="135" t="n">
         <f aca="false">C31*H31</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J31" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="K31" s="135" t="n">
         <f aca="false">C31*J31</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42090,27 +43598,27 @@
       </c>
       <c r="F33" s="117" t="n">
         <f aca="false">IF(D33&gt;0,ROUNDUP(D33/$F$50,0)+1,0)</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="G33" s="135" t="n">
         <f aca="false">C33*F33</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="H33" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I33" s="135" t="n">
         <f aca="false">C33*H33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J33" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K33" s="135" t="n">
         <f aca="false">C33*J33</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42130,27 +43638,27 @@
       </c>
       <c r="F34" s="117" t="n">
         <f aca="false">IF(D34&gt;0,ROUNDUP(D34/$F$50,0)+1,0)</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="G34" s="135" t="n">
         <f aca="false">C34*F34</f>
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="H34" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I34" s="135" t="n">
         <f aca="false">C34*H34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J34" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K34" s="135" t="n">
         <f aca="false">C34*J34</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42183,27 +43691,27 @@
       </c>
       <c r="F36" s="117" t="n">
         <f aca="false">IF(D36&gt;0,ROUNDUP(D36/$F$50,0)+1,0)</f>
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="G36" s="135" t="n">
         <f aca="false">C36*F36</f>
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="H36" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I36" s="135" t="n">
         <f aca="false">C36*H36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J36" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K36" s="135" t="n">
         <f aca="false">C36*J36</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42223,27 +43731,27 @@
       </c>
       <c r="F37" s="117" t="n">
         <f aca="false">IF(D37&gt;0,ROUNDUP(D37/$F$50,0)+1,0)</f>
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="G37" s="135" t="n">
         <f aca="false">C37*F37</f>
-        <v>26</v>
+        <v>26.0</v>
       </c>
       <c r="H37" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I37" s="135" t="n">
         <f aca="false">C37*H37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J37" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="K37" s="135" t="n">
         <f aca="false">C37*J37</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42276,27 +43784,27 @@
       </c>
       <c r="F39" s="117" t="n">
         <f aca="false">IF(D39&gt;0,ROUNDUP(D39/$F$50,0)+1,0)</f>
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="G39" s="135" t="n">
         <f aca="false">C39*F39</f>
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="H39" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I39" s="135" t="n">
         <f aca="false">C39*H39</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J39" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K39" s="135" t="n">
         <f aca="false">C39*J39</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42316,27 +43824,27 @@
       </c>
       <c r="F40" s="117" t="n">
         <f aca="false">IF(D40&gt;0,ROUNDUP(D40/$F$50,0)+1,0)</f>
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="G40" s="135" t="n">
         <f aca="false">C40*F40</f>
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="H40" s="145" t="n">
         <f aca="false">$F$51</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="I40" s="135" t="n">
         <f aca="false">C40*H40</f>
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J40" s="117" t="n">
         <f aca="false">'METRADO MONTANTES'!C40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="K40" s="135" t="n">
         <f aca="false">C40*J40</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -42345,7 +43853,7 @@
       </c>
       <c r="C41" s="142" t="n">
         <f aca="false">SUM(C11:C40)</f>
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="D41" s="142"/>
       <c r="E41" s="146" t="n">
@@ -42355,17 +43863,17 @@
       <c r="F41" s="142"/>
       <c r="G41" s="142" t="n">
         <f aca="false">SUM(G11:G40)</f>
-        <v>884</v>
+        <v>884.0</v>
       </c>
       <c r="H41" s="142"/>
       <c r="I41" s="142" t="n">
         <f aca="false">SUM(I11:I40)</f>
-        <v>40</v>
+        <v>40.0</v>
       </c>
       <c r="J41" s="142"/>
       <c r="K41" s="142" t="n">
         <f aca="false">SUM(K11:K40)</f>
-        <v>52</v>
+        <v>52.0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42826,19 +44334,19 @@
       </c>
       <c r="C12" s="171" t="n">
         <f aca="false">SUM(C8:C11)</f>
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="D12" s="171" t="n">
         <f aca="false">SUM(D8:D11)</f>
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="E12" s="171" t="n">
         <f aca="false">SUM(E8:E11)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="F12" s="171" t="n">
         <f aca="false">SUM(F8:F11)</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="G12" s="172"/>
     </row>
@@ -43600,11 +45108,11 @@
       </c>
       <c r="M11" s="195" t="n">
         <f aca="false">IF(B11="","",(K11+L11)/2)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="N11" s="195" t="n">
         <f aca="false">IF(B11="","",G11*M11)</f>
-        <v>84</v>
+        <v>84.0</v>
       </c>
       <c r="O11" s="195" t="n">
         <f aca="false">IF(B11="","",N11*I11)</f>
@@ -43625,7 +45133,7 @@
       </c>
       <c r="T11" s="195" t="n">
         <f aca="false">IF(B11="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G11/P11,0)+1,G11/P11+1),0))</f>
-        <v>49</v>
+        <v>49.0</v>
       </c>
       <c r="U11" s="195" t="n">
         <f aca="false">IF(B11="","",S11*T11)</f>
@@ -43646,19 +45154,19 @@
       <c r="AB11" s="198"/>
       <c r="AC11" s="199" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",(AA11+AB11)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD11" s="199" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G11/Z11,0)+1,G11/Z11+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE11" s="199" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",AC11*AD11,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF11" s="199" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",AE11*Y11,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG11" s="200" t="n">
         <f aca="false">IF(B11="","",W11+AF11)</f>
@@ -43705,7 +45213,7 @@
       </c>
       <c r="M12" s="195" t="n">
         <f aca="false">IF(B12="","",(K12+L12)/2)</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="N12" s="195" t="n">
         <f aca="false">IF(B12="","",G12*M12)</f>
@@ -43820,7 +45328,7 @@
       </c>
       <c r="M13" s="195" t="n">
         <f aca="false">IF(B13="","",(K13+L13)/2)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="N13" s="195" t="n">
         <f aca="false">IF(B13="","",G13*M13)</f>
@@ -43845,7 +45353,7 @@
       </c>
       <c r="T13" s="195" t="n">
         <f aca="false">IF(B13="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G13/P13,0)+1,G13/P13+1),0))</f>
-        <v>71</v>
+        <v>71.0</v>
       </c>
       <c r="U13" s="195" t="n">
         <f aca="false">IF(B13="","",S13*T13)</f>
@@ -43866,19 +45374,19 @@
       <c r="AB13" s="198"/>
       <c r="AC13" s="199" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",(AA13+AB13)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD13" s="199" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G13/Z13,0)+1,G13/Z13+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE13" s="199" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",AC13*AD13,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF13" s="199" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",AE13*Y13,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG13" s="200" t="n">
         <f aca="false">IF(B13="","",W13+AF13)</f>
@@ -43925,7 +45433,7 @@
       </c>
       <c r="M14" s="195" t="n">
         <f aca="false">IF(B14="","",(K14+L14)/2)</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="N14" s="195" t="n">
         <f aca="false">IF(B14="","",G14*M14)</f>
@@ -44040,7 +45548,7 @@
       </c>
       <c r="M15" s="195" t="n">
         <f aca="false">IF(B15="","",(K15+L15)/2)</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="N15" s="195" t="n">
         <f aca="false">IF(B15="","",G15*M15)</f>
@@ -44086,19 +45594,19 @@
       <c r="AB15" s="198"/>
       <c r="AC15" s="199" t="n">
         <f aca="false">IF(B15="","",IF(D15="TAPADA",(AA15+AB15)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD15" s="199" t="n">
         <f aca="false">IF(B15="","",IF(D15="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G15/Z15,0)+1,G15/Z15+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE15" s="199" t="n">
         <f aca="false">IF(B15="","",IF(D15="TAPADA",AC15*AD15,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF15" s="199" t="n">
         <f aca="false">IF(B15="","",IF(D15="TAPADA",AE15*Y15,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG15" s="200" t="n">
         <f aca="false">IF(B15="","",W15+AF15)</f>
@@ -44145,7 +45653,7 @@
       </c>
       <c r="M16" s="195" t="n">
         <f aca="false">IF(B16="","",(K16+L16)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N16" s="195" t="n">
         <f aca="false">IF(B16="","",G16*M16)</f>
@@ -44260,7 +45768,7 @@
       </c>
       <c r="M17" s="195" t="n">
         <f aca="false">IF(B17="","",(K17+L17)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N17" s="195" t="n">
         <f aca="false">IF(B17="","",G17*M17)</f>
@@ -44306,19 +45814,19 @@
       <c r="AB17" s="198"/>
       <c r="AC17" s="199" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",(AA17+AB17)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD17" s="199" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G17/Z17,0)+1,G17/Z17+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE17" s="199" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",AC17*AD17,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF17" s="199" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",AE17*Y17,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG17" s="200" t="n">
         <f aca="false">IF(B17="","",W17+AF17)</f>
@@ -44365,11 +45873,11 @@
       </c>
       <c r="M18" s="195" t="n">
         <f aca="false">IF(B18="","",(K18+L18)/2)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N18" s="195" t="n">
         <f aca="false">IF(B18="","",G18*M18)</f>
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="O18" s="195" t="n">
         <f aca="false">IF(B18="","",N18*I18)</f>
@@ -44390,7 +45898,7 @@
       </c>
       <c r="T18" s="195" t="n">
         <f aca="false">IF(B18="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G18/P18,0)+1,G18/P18+1),0))</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="U18" s="195" t="n">
         <f aca="false">IF(B18="","",S18*T18)</f>
@@ -44425,7 +45933,7 @@
       </c>
       <c r="AD18" s="199" t="n">
         <f aca="false">IF(B18="","",IF(D18="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G18/Z18,0)+1,G18/Z18+1),0),0))</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="AE18" s="199" t="n">
         <f aca="false">IF(B18="","",IF(D18="TAPADA",AC18*AD18,0))</f>
@@ -44480,7 +45988,7 @@
       </c>
       <c r="M19" s="195" t="n">
         <f aca="false">IF(B19="","",(K19+L19)/2)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N19" s="195" t="n">
         <f aca="false">IF(B19="","",G19*M19)</f>
@@ -44595,7 +46103,7 @@
       </c>
       <c r="M20" s="195" t="n">
         <f aca="false">IF(B20="","",(K20+L20)/2)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="N20" s="195" t="n">
         <f aca="false">IF(B20="","",G20*M20)</f>
@@ -44641,19 +46149,19 @@
       <c r="AB20" s="198"/>
       <c r="AC20" s="199" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",(AA20+AB20)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD20" s="199" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G20/Z20,0)+1,G20/Z20+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE20" s="199" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",AC20*AD20,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF20" s="199" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",AE20*Y20,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG20" s="200" t="n">
         <f aca="false">IF(B20="","",W20+AF20)</f>
@@ -44700,7 +46208,7 @@
       </c>
       <c r="M21" s="195" t="n">
         <f aca="false">IF(B21="","",(K21+L21)/2)</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="N21" s="195" t="n">
         <f aca="false">IF(B21="","",G21*M21)</f>
@@ -44815,7 +46323,7 @@
       </c>
       <c r="M22" s="195" t="n">
         <f aca="false">IF(B22="","",(K22+L22)/2)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="N22" s="195" t="n">
         <f aca="false">IF(B22="","",G22*M22)</f>
@@ -44861,19 +46369,19 @@
       <c r="AB22" s="198"/>
       <c r="AC22" s="199" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",(AA22+AB22)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD22" s="199" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G22/Z22,0)+1,G22/Z22+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE22" s="199" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",AC22*AD22,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF22" s="199" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",AE22*Y22,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG22" s="200" t="n">
         <f aca="false">IF(B22="","",W22+AF22)</f>
@@ -44920,7 +46428,7 @@
       </c>
       <c r="M23" s="195" t="n">
         <f aca="false">IF(B23="","",(K23+L23)/2)</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="N23" s="195" t="n">
         <f aca="false">IF(B23="","",G23*M23)</f>
@@ -45035,7 +46543,7 @@
       </c>
       <c r="M24" s="195" t="n">
         <f aca="false">IF(B24="","",(K24+L24)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N24" s="195" t="n">
         <f aca="false">IF(B24="","",G24*M24)</f>
@@ -45081,19 +46589,19 @@
       <c r="AB24" s="198"/>
       <c r="AC24" s="199" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",(AA24+AB24)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD24" s="199" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G24/Z24,0)+1,G24/Z24+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE24" s="199" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",AC24*AD24,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF24" s="199" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",AE24*Y24,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG24" s="200" t="n">
         <f aca="false">IF(B24="","",W24+AF24)</f>
@@ -45140,11 +46648,11 @@
       </c>
       <c r="M25" s="195" t="n">
         <f aca="false">IF(B25="","",(K25+L25)/2)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N25" s="195" t="n">
         <f aca="false">IF(B25="","",G25*M25)</f>
-        <v>180</v>
+        <v>180.0</v>
       </c>
       <c r="O25" s="195" t="n">
         <f aca="false">IF(B25="","",N25*I25)</f>
@@ -45165,7 +46673,7 @@
       </c>
       <c r="T25" s="195" t="n">
         <f aca="false">IF(B25="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G25/P25,0)+1,G25/P25+1),0))</f>
-        <v>61</v>
+        <v>61.0</v>
       </c>
       <c r="U25" s="195" t="n">
         <f aca="false">IF(B25="","",S25*T25)</f>
@@ -45200,7 +46708,7 @@
       </c>
       <c r="AD25" s="199" t="n">
         <f aca="false">IF(B25="","",IF(D25="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G25/Z25,0)+1,G25/Z25+1),0),0))</f>
-        <v>61</v>
+        <v>61.0</v>
       </c>
       <c r="AE25" s="199" t="n">
         <f aca="false">IF(B25="","",IF(D25="TAPADA",AC25*AD25,0))</f>
@@ -45255,7 +46763,7 @@
       </c>
       <c r="M26" s="195" t="n">
         <f aca="false">IF(B26="","",(K26+L26)/2)</f>
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="N26" s="195" t="n">
         <f aca="false">IF(B26="","",G26*M26)</f>
@@ -45301,19 +46809,19 @@
       <c r="AB26" s="198"/>
       <c r="AC26" s="199" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",(AA26+AB26)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD26" s="199" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G26/Z26,0)+1,G26/Z26+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE26" s="199" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",AC26*AD26,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF26" s="199" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",AE26*Y26,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG26" s="200" t="n">
         <f aca="false">IF(B26="","",W26+AF26)</f>
@@ -45360,7 +46868,7 @@
       </c>
       <c r="M27" s="195" t="n">
         <f aca="false">IF(B27="","",(K27+L27)/2)</f>
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="N27" s="195" t="n">
         <f aca="false">IF(B27="","",G27*M27)</f>
@@ -45475,7 +46983,7 @@
       </c>
       <c r="M28" s="195" t="n">
         <f aca="false">IF(B28="","",(K28+L28)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N28" s="195" t="n">
         <f aca="false">IF(B28="","",G28*M28)</f>
@@ -45483,7 +46991,7 @@
       </c>
       <c r="O28" s="195" t="n">
         <f aca="false">IF(B28="","",N28*I28)</f>
-        <v>357</v>
+        <v>357.0</v>
       </c>
       <c r="P28" s="193" t="n">
         <v>0.25</v>
@@ -45500,7 +47008,7 @@
       </c>
       <c r="T28" s="195" t="n">
         <f aca="false">IF(B28="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G28/P28,0)+1,G28/P28+1),0))</f>
-        <v>256</v>
+        <v>256.0</v>
       </c>
       <c r="U28" s="195" t="n">
         <f aca="false">IF(B28="","",S28*T28)</f>
@@ -45521,19 +47029,19 @@
       <c r="AB28" s="198"/>
       <c r="AC28" s="199" t="n">
         <f aca="false">IF(B28="","",IF(D28="TAPADA",(AA28+AB28)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD28" s="199" t="n">
         <f aca="false">IF(B28="","",IF(D28="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G28/Z28,0)+1,G28/Z28+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE28" s="199" t="n">
         <f aca="false">IF(B28="","",IF(D28="TAPADA",AC28*AD28,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF28" s="199" t="n">
         <f aca="false">IF(B28="","",IF(D28="TAPADA",AE28*Y28,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG28" s="200" t="n">
         <f aca="false">IF(B28="","",W28+AF28)</f>
@@ -45580,7 +47088,7 @@
       </c>
       <c r="M29" s="195" t="n">
         <f aca="false">IF(B29="","",(K29+L29)/2)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N29" s="195" t="n">
         <f aca="false">IF(B29="","",G29*M29)</f>
@@ -45695,7 +47203,7 @@
       </c>
       <c r="M30" s="195" t="n">
         <f aca="false">IF(B30="","",(K30+L30)/2)</f>
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="N30" s="195" t="n">
         <f aca="false">IF(B30="","",G30*M30)</f>
@@ -45810,7 +47318,7 @@
       </c>
       <c r="M31" s="195" t="n">
         <f aca="false">IF(B31="","",(K31+L31)/2)</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="N31" s="195" t="n">
         <f aca="false">IF(B31="","",G31*M31)</f>
@@ -45925,11 +47433,11 @@
       </c>
       <c r="M32" s="195" t="n">
         <f aca="false">IF(B32="","",(K32+L32)/2)</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="N32" s="195" t="n">
         <f aca="false">IF(B32="","",G32*M32)</f>
-        <v>56</v>
+        <v>56.0</v>
       </c>
       <c r="O32" s="195" t="n">
         <f aca="false">IF(B32="","",N32*I32)</f>
@@ -45950,7 +47458,7 @@
       </c>
       <c r="T32" s="195" t="n">
         <f aca="false">IF(B32="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G32/P32,0)+1,G32/P32+1),0))</f>
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="U32" s="195" t="n">
         <f aca="false">IF(B32="","",S32*T32)</f>
@@ -45985,7 +47493,7 @@
       </c>
       <c r="AD32" s="199" t="n">
         <f aca="false">IF(B32="","",IF(D32="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G32/Z32,0)+1,G32/Z32+1),0),0))</f>
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="AE32" s="199" t="n">
         <f aca="false">IF(B32="","",IF(D32="TAPADA",AC32*AD32,0))</f>
@@ -46040,7 +47548,7 @@
       </c>
       <c r="M33" s="195" t="n">
         <f aca="false">IF(B33="","",(K33+L33)/2)</f>
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="N33" s="195" t="n">
         <f aca="false">IF(B33="","",G33*M33)</f>
@@ -46086,19 +47594,19 @@
       <c r="AB33" s="198"/>
       <c r="AC33" s="199" t="n">
         <f aca="false">IF(B33="","",IF(D33="TAPADA",(AA33+AB33)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD33" s="199" t="n">
         <f aca="false">IF(B33="","",IF(D33="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G33/Z33,0)+1,G33/Z33+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE33" s="199" t="n">
         <f aca="false">IF(B33="","",IF(D33="TAPADA",AC33*AD33,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF33" s="199" t="n">
         <f aca="false">IF(B33="","",IF(D33="TAPADA",AE33*Y33,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG33" s="200" t="n">
         <f aca="false">IF(B33="","",W33+AF33)</f>
@@ -46145,11 +47653,11 @@
       </c>
       <c r="M34" s="195" t="n">
         <f aca="false">IF(B34="","",(K34+L34)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N34" s="195" t="n">
         <f aca="false">IF(B34="","",G34*M34)</f>
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="O34" s="195" t="n">
         <f aca="false">IF(B34="","",N34*I34)</f>
@@ -46260,11 +47768,11 @@
       </c>
       <c r="M35" s="195" t="n">
         <f aca="false">IF(B35="","",(K35+L35)/2)</f>
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="N35" s="195" t="n">
         <f aca="false">IF(B35="","",G35*M35)</f>
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="O35" s="195" t="n">
         <f aca="false">IF(B35="","",N35*I35)</f>
@@ -46285,7 +47793,7 @@
       </c>
       <c r="T35" s="195" t="n">
         <f aca="false">IF(B35="","",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G35/P35,0)+1,G35/P35+1),0))</f>
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="U35" s="195" t="n">
         <f aca="false">IF(B35="","",S35*T35)</f>
@@ -46320,7 +47828,7 @@
       </c>
       <c r="AD35" s="199" t="n">
         <f aca="false">IF(B35="","",IF(D35="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G35/Z35,0)+1,G35/Z35+1),0),0))</f>
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="AE35" s="199" t="n">
         <f aca="false">IF(B35="","",IF(D35="TAPADA",AC35*AD35,0))</f>
@@ -46421,19 +47929,19 @@
       <c r="AB36" s="198"/>
       <c r="AC36" s="199" t="n">
         <f aca="false">IF(B36="","",IF(D36="TAPADA",(AA36+AB36)/2,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AD36" s="199" t="n">
         <f aca="false">IF(B36="","",IF(D36="TAPADA",IFERROR(IF($X$1="ENTERO (redondeo arriba)",ROUNDUP(G36/Z36,0)+1,G36/Z36+1),0),0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AE36" s="199" t="n">
         <f aca="false">IF(B36="","",IF(D36="TAPADA",AC36*AD36,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AF36" s="199" t="n">
         <f aca="false">IF(B36="","",IF(D36="TAPADA",AE36*Y36,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="AG36" s="200" t="n">
         <f aca="false">IF(B36="","",W36+AF36)</f>
@@ -46480,7 +47988,7 @@
       </c>
       <c r="M37" s="195" t="n">
         <f aca="false">IF(B37="","",(K37+L37)/2)</f>
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="N37" s="195" t="n">
         <f aca="false">IF(B37="","",G37*M37)</f>
@@ -46856,7 +48364,7 @@
       </c>
       <c r="L7" s="199" t="n">
         <f aca="false">IF(B7="","",IF(D7="TAPADA",E7*F7,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M7" s="211" t="n">
         <f aca="false">SUM(J7:L7)</f>
@@ -46864,7 +48372,7 @@
       </c>
       <c r="N7" s="212" t="n">
         <f aca="false">IF(B7="","",IF(D7="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O7" s="213" t="s">
         <v>18</v>
@@ -46917,7 +48425,7 @@
       </c>
       <c r="N8" s="212" t="n">
         <f aca="false">IF(B8="","",IF(D8="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O8" s="213" t="s">
         <v>18</v>
@@ -46958,11 +48466,11 @@
       </c>
       <c r="K9" s="199" t="n">
         <f aca="false">IF(B9="","",E9*F9)</f>
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="L9" s="199" t="n">
         <f aca="false">IF(B9="","",IF(D9="TAPADA",E9*F9,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M9" s="211" t="n">
         <f aca="false">SUM(J9:L9)</f>
@@ -46970,7 +48478,7 @@
       </c>
       <c r="N9" s="212" t="n">
         <f aca="false">IF(B9="","",IF(D9="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O9" s="213" t="s">
         <v>18</v>
@@ -47023,7 +48531,7 @@
       </c>
       <c r="N10" s="212" t="n">
         <f aca="false">IF(B10="","",IF(D10="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O10" s="213" t="s">
         <v>18</v>
@@ -47068,7 +48576,7 @@
       </c>
       <c r="L11" s="199" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",E11*F11,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M11" s="211" t="n">
         <f aca="false">SUM(J11:L11)</f>
@@ -47076,7 +48584,7 @@
       </c>
       <c r="N11" s="212" t="n">
         <f aca="false">IF(B11="","",IF(D11="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O11" s="213" t="s">
         <v>18</v>
@@ -47129,7 +48637,7 @@
       </c>
       <c r="N12" s="212" t="n">
         <f aca="false">IF(B12="","",IF(D12="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O12" s="213" t="s">
         <v>18</v>
@@ -47174,7 +48682,7 @@
       </c>
       <c r="L13" s="199" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",E13*F13,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M13" s="211" t="n">
         <f aca="false">SUM(J13:L13)</f>
@@ -47182,7 +48690,7 @@
       </c>
       <c r="N13" s="212" t="n">
         <f aca="false">IF(B13="","",IF(D13="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O13" s="213" t="s">
         <v>18</v>
@@ -47235,7 +48743,7 @@
       </c>
       <c r="N14" s="212" t="n">
         <f aca="false">IF(B14="","",IF(D14="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O14" s="213" t="s">
         <v>18</v>
@@ -47288,7 +48796,7 @@
       </c>
       <c r="N15" s="212" t="n">
         <f aca="false">IF(B15="","",IF(D15="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O15" s="213" t="s">
         <v>18</v>
@@ -47333,7 +48841,7 @@
       </c>
       <c r="L16" s="199" t="n">
         <f aca="false">IF(B16="","",IF(D16="TAPADA",E16*F16,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M16" s="211" t="n">
         <f aca="false">SUM(J16:L16)</f>
@@ -47341,7 +48849,7 @@
       </c>
       <c r="N16" s="212" t="n">
         <f aca="false">IF(B16="","",IF(D16="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O16" s="213" t="s">
         <v>18</v>
@@ -47386,7 +48894,7 @@
       </c>
       <c r="L17" s="199" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",E17*F17,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M17" s="211" t="n">
         <f aca="false">SUM(J17:L17)</f>
@@ -47394,7 +48902,7 @@
       </c>
       <c r="N17" s="212" t="n">
         <f aca="false">IF(B17="","",IF(D17="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O17" s="213" t="s">
         <v>18</v>
@@ -47439,7 +48947,7 @@
       </c>
       <c r="L18" s="199" t="n">
         <f aca="false">IF(B18="","",IF(D18="TAPADA",E18*F18,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M18" s="211" t="n">
         <f aca="false">SUM(J18:L18)</f>
@@ -47447,7 +48955,7 @@
       </c>
       <c r="N18" s="212" t="n">
         <f aca="false">IF(B18="","",IF(D18="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O18" s="213" t="s">
         <v>18</v>
@@ -47500,7 +49008,7 @@
       </c>
       <c r="N19" s="212" t="n">
         <f aca="false">IF(B19="","",IF(D19="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O19" s="213" t="s">
         <v>18</v>
@@ -47545,7 +49053,7 @@
       </c>
       <c r="L20" s="199" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",E20*F20,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M20" s="211" t="n">
         <f aca="false">SUM(J20:L20)</f>
@@ -47553,7 +49061,7 @@
       </c>
       <c r="N20" s="212" t="n">
         <f aca="false">IF(B20="","",IF(D20="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O20" s="213" t="s">
         <v>18</v>
@@ -47606,7 +49114,7 @@
       </c>
       <c r="N21" s="212" t="n">
         <f aca="false">IF(B21="","",IF(D21="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O21" s="213" t="s">
         <v>18</v>
@@ -47651,7 +49159,7 @@
       </c>
       <c r="L22" s="199" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",E22*F22,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M22" s="211" t="n">
         <f aca="false">SUM(J22:L22)</f>
@@ -47659,7 +49167,7 @@
       </c>
       <c r="N22" s="212" t="n">
         <f aca="false">IF(B22="","",IF(D22="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O22" s="213" t="s">
         <v>18</v>
@@ -47700,11 +49208,11 @@
       </c>
       <c r="K23" s="199" t="n">
         <f aca="false">IF(B23="","",E23*F23)</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="L23" s="199" t="n">
         <f aca="false">IF(B23="","",IF(D23="TAPADA",E23*F23,0))</f>
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="M23" s="211" t="n">
         <f aca="false">SUM(J23:L23)</f>
@@ -47712,7 +49220,7 @@
       </c>
       <c r="N23" s="212" t="n">
         <f aca="false">IF(B23="","",IF(D23="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O23" s="213" t="s">
         <v>18</v>
@@ -47757,7 +49265,7 @@
       </c>
       <c r="L24" s="199" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",E24*F24,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M24" s="211" t="n">
         <f aca="false">SUM(J24:L24)</f>
@@ -47765,7 +49273,7 @@
       </c>
       <c r="N24" s="212" t="n">
         <f aca="false">IF(B24="","",IF(D24="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O24" s="213" t="s">
         <v>18</v>
@@ -47818,7 +49326,7 @@
       </c>
       <c r="N25" s="212" t="n">
         <f aca="false">IF(B25="","",IF(D25="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O25" s="213" t="s">
         <v>18</v>
@@ -47863,7 +49371,7 @@
       </c>
       <c r="L26" s="199" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",E26*F26,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M26" s="211" t="n">
         <f aca="false">SUM(J26:L26)</f>
@@ -47871,7 +49379,7 @@
       </c>
       <c r="N26" s="212" t="n">
         <f aca="false">IF(B26="","",IF(D26="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O26" s="213" t="s">
         <v>18</v>
@@ -47924,7 +49432,7 @@
       </c>
       <c r="N27" s="212" t="n">
         <f aca="false">IF(B27="","",IF(D27="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O27" s="213" t="s">
         <v>18</v>
@@ -47977,7 +49485,7 @@
       </c>
       <c r="N28" s="212" t="n">
         <f aca="false">IF(B28="","",IF(D28="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O28" s="213" t="s">
         <v>18</v>
@@ -48030,7 +49538,7 @@
       </c>
       <c r="N29" s="212" t="n">
         <f aca="false">IF(B29="","",IF(D29="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O29" s="213" t="s">
         <v>18</v>
@@ -48083,7 +49591,7 @@
       </c>
       <c r="N30" s="212" t="n">
         <f aca="false">IF(B30="","",IF(D30="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O30" s="213" t="s">
         <v>18</v>
@@ -48128,7 +49636,7 @@
       </c>
       <c r="L31" s="199" t="n">
         <f aca="false">IF(B31="","",IF(D31="TAPADA",E31*F31,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M31" s="211" t="n">
         <f aca="false">SUM(J31:L31)</f>
@@ -48136,7 +49644,7 @@
       </c>
       <c r="N31" s="212" t="n">
         <f aca="false">IF(B31="","",IF(D31="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O31" s="213" t="s">
         <v>18</v>
@@ -48181,7 +49689,7 @@
       </c>
       <c r="L32" s="199" t="n">
         <f aca="false">IF(B32="","",IF(D32="TAPADA",E32*F32,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M32" s="211" t="n">
         <f aca="false">SUM(J32:L32)</f>
@@ -48189,7 +49697,7 @@
       </c>
       <c r="N32" s="212" t="n">
         <f aca="false">IF(B32="","",IF(D32="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O32" s="213" t="s">
         <v>18</v>
@@ -48242,7 +49750,7 @@
       </c>
       <c r="N33" s="212" t="n">
         <f aca="false">IF(B33="","",IF(D33="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O33" s="213" t="s">
         <v>18</v>
@@ -48295,7 +49803,7 @@
       </c>
       <c r="N34" s="212" t="n">
         <f aca="false">IF(B34="","",IF(D34="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O34" s="213" t="s">
         <v>18</v>
@@ -48340,7 +49848,7 @@
       </c>
       <c r="L35" s="199" t="n">
         <f aca="false">IF(B35="","",IF(D35="TAPADA",E35*F35,0))</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="M35" s="211" t="n">
         <f aca="false">SUM(J35:L35)</f>
@@ -48348,7 +49856,7 @@
       </c>
       <c r="N35" s="212" t="n">
         <f aca="false">IF(B35="","",IF(D35="TAPADA",4,3))</f>
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="O35" s="213" t="s">
         <v>18</v>
@@ -48401,7 +49909,7 @@
       </c>
       <c r="N36" s="212" t="n">
         <f aca="false">IF(B36="","",IF(D36="TAPADA",4,3))</f>
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="O36" s="213" t="s">
         <v>18</v>

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1480">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4762,6 +4762,213 @@
   </si>
   <si>
     <t xml:space="preserve">Jornal 2026: R.M. 197-2025-TR (FTCCP). Costo HH: tabla CAPECO 2024-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSTO DE LA HORA-HOMBRE 2026 - REGIMEN DE CONSTRUCCION CIVIL (TABLA OFICIAL CAPECO - FTCCP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo de la hora-hombre en edificacion del 01.01.2026 al 31.12.2026, segun la tabla oficial elaborada entre CAPECO y la FTCCP (Remuneracion y condiciones de trabajo en construccion civil 2026, Acta final de negociacion colectiva, Exp. N° 339-2025-MTPE/2.14-NC). El resumen de la parte 1 es el que usan todas las ACU de la planilla. Celda amarilla = dato de la tabla oficial; verde = formula.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. COSTO HORA-HOMBRE 2026 POR CATEGORIA (lo usan todas las ACU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORNAL BASICO (S/ dia)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL POR DIA DE 8 h (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabla oficial CAPECO - FTCCP 2026 (Exp. N° 339-2025-MTPE/2.14-NC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. COSTO HORA-HOMBRE EN EDIFICACION DEL 01.01.2026 AL 31.12.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERARIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFICIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remuneracion basica del 01/01/2026 al 31/12/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jornal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.M. 197-2025-TR; tabla oficial CAPECO - FTCCP 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneficios y leyes sociales sobre el jornal basico (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parte 3: 112.20 % sobre el jornal basico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonificacion unificada de construccion (BUC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32/30/30 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 % operario; 30 % oficial y peon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beneficios y leyes sociales sobre el BUC (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parte 3: 12.25 % sobre el BUC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro de vida ESSALUD + Vida (S/ 5.00 por mes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tabla oficial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fondo de capacitacion (Exp. N° 339-2025-MTPE/2.14-NC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonificacion por movilidad (R.M. N° 139-2024-TR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S/ 8.60 por dia laborado en todo el pais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overol (R.D. N° 777-87-DR-LIM): (2 x S/ 132.80) / 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total por dia de 8 horas (S/)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costo de la hora-hombre (S/ hh)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total por dia / 8 horas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. PORCENTAJES DE BENEFICIOS Y LEYES SOCIALES EN EDIFICACION (tabla oficial CAPECO - FTCCP 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOBRE JORNAL BASICO (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOBRE BUC (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01 Indemnizacion por tiempo de servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01 Indemnizacion por participacion de utilidades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02 SCTR: prestaciones asistenciales (Ley 26790)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.02 SCTR: prestaciones economicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.04 Regimen de prestaciones de salud (ESSALUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05 Seguro de vida ley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01 Salario dominical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02 Vacaciones record (30 dias)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03 Gratificacion por Fiestas Patrias y Navidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04 Jornales por dias feriados no laborables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05 Asignacion escolar (promedio 3 hijos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01 ESSALUD sobre salario dominical (9 % de 17.58 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02 ESSALUD sobre vacaciones (9 % de 10.00 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03 ESSALUD sobre feriados (9 % de 4.33 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01 SCTR sobre salario dominical (2.35 % de 17.58 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02 SCTR sobre vacaciones (2.35 % de 10.00 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03 SCTR sobre feriados (2.35 % de 4.33 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01 Seguro de vida ley sobre salario dominical (0.90 % de 17.58 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02 Seguro de vida ley sobre feriados (0.90 % de 4.33 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01 Bonificacion extraordinaria Ley 30334 (9 % de 22.22 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCENTAJE TOTAL DE LEYES Y BENEFICIOS SOCIALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.20 % y 12.25 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoja COSTO HORA HOMBRE 2026 (tabla oficial CAPECO - FTCCP 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (nota 5), DP-03, DP-06C y DD-03. Junta de dilatacion de 1" cada 4.00 m en todo el perimetro de la seccion (tecnopor de 1" en todo el perimetro + sellador asfaltico RC-250 con arena de 1" x 2" en la cara expuesta, EG-2013 MTC). Junta longitudinal de tecnopor de 1" con sellador asfaltico entre el muro del colector y el cimiento del cerco, en todo el tramo pegado al cerco; al otro lado hay terreno natural (sin vereda ni piso) y no lleva junta. Empalme de cada cuneta por ventana en el muro lado predio con caida libre al fondo (sin dintel adicional).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junta longitudinal contra el cimiento del cerco (tramo pegado al cerco, 0+000 al primer quiebre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-01, DP-04 y DD-03 C: junta entre el muro lado predio y el cimiento del cerco (h = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado opuesto al cerco (colector y cajas CL y CC): terreno natural, sin vereda ni piso: no lleva junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-04 y DD-03 D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL JUNTA LONGITUDINAL CON EL CERCO (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.02 JUNTA E=1" CON TECNOPOR Y SELLADOR ASFALTICO ENTRE COLECTOR Y CERCO PERIMETRICO (metrado 01.04.04.06.02, hoja COLECTOR JUNTAS Y EMPALMES). Cantidades de la lamina DD-03: junta longitudinal con plancha de tecnopor de 1" de 0.90 m de altura contra el cimiento del cerco, en todo el tramo pegado al cerco, con sellador asfaltico 1" x 2" (RC-250 + arena) en la cara superior. Al otro lado hay terreno natural: no lleva junta. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado opuesto al cerco: terreno natural, sin junta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altura de plancha en el lado opuesto (no aplica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR JUNTAS Y EMPALMES fila 16 (0 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 B; EG-2013 MTC, Seccion 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD-03 C; EG-2013 MTC, Seccion 510</t>
   </si>
 </sst>
 </file>
@@ -8174,7 +8381,7 @@
       </c>
       <c r="D75" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K322</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
     </row>
   </sheetData>
@@ -23332,7 +23539,7 @@
       <c r="J322" s="25"/>
       <c r="K322" s="25" t="n">
         <f aca="false">+'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
       <c r="L322" s="24" t="s">
         <v>57</v>
@@ -25768,7 +25975,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1339</v>
+        <v>1468</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -25871,7 +26078,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>915</v>
+        <v>1469</v>
       </c>
       <c r="C15" s="301" t="str">
         <f aca="false">"0+000.00 a 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$65,"000.00")</f>
@@ -25889,7 +26096,7 @@
         <v>58.805</v>
       </c>
       <c r="G15" s="286" t="s">
-        <v>916</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25897,14 +26104,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>1334</v>
-      </c>
-      <c r="C16" s="301" t="str">
-        <f aca="false">"1 x 0+"&amp;TEXT('COLECTOR PARAMETROS'!$C$64,"000.00")</f>
-        <v>1 x 0+069.89</v>
+        <v>1471</v>
+      </c>
+      <c r="C16" s="301" t="s">
+        <v>523</v>
       </c>
       <c r="D16" s="298" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$64</f>
@@ -25912,65 +26118,33 @@
       </c>
       <c r="F16" s="290" t="n">
         <f aca="false">D16*E16</f>
-        <v>69.887</v>
+        <v>0.0</v>
       </c>
       <c r="G16" s="286" t="s">
-        <v>1335</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="283" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="149" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C17" s="283" t="s">
-        <v>1337</v>
-      </c>
-      <c r="D17" s="298" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E17" s="290" t="n">
-        <f aca="false">'COLECTOR MOV. TIERRAS'!D21+2*'COLECTOR PARAMETROS'!$C$11+0.3</f>
-        <v>2.1</v>
-      </c>
-      <c r="F17" s="290" t="n">
-        <f aca="false">D17*E17</f>
-        <v>2.1</v>
-      </c>
-      <c r="G17" s="286" t="s">
-        <v>871</v>
-      </c>
+      <c r="A17" s="283"/>
+      <c r="B17" s="149"/>
+      <c r="C17" s="283"/>
+      <c r="D17" s="298"/>
+      <c r="E17" s="290"/>
+      <c r="F17" s="290"/>
+      <c r="G17" s="286"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="283" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="149" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C18" s="283" t="s">
-        <v>1337</v>
-      </c>
-      <c r="D18" s="298" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="E18" s="290" t="n">
-        <f aca="false">'COLECTOR MOV. TIERRAS'!D22+2*'COLECTOR PARAMETROS'!$C$11+0.3</f>
-        <v>4.1</v>
-      </c>
-      <c r="F18" s="290" t="n">
-        <f aca="false">D18*E18</f>
-        <v>4.1</v>
-      </c>
-      <c r="G18" s="286" t="s">
-        <v>871</v>
-      </c>
+      <c r="A18" s="283"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="283"/>
+      <c r="D18" s="298"/>
+      <c r="E18" s="290"/>
+      <c r="F18" s="290"/>
+      <c r="G18" s="286"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="291" t="s">
-        <v>922</v>
+        <v>1473</v>
       </c>
       <c r="B19" s="302"/>
       <c r="C19" s="292"/>
@@ -25978,7 +26152,7 @@
       <c r="E19" s="292"/>
       <c r="F19" s="293" t="n">
         <f aca="false">SUM(F15:F18)</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
       <c r="G19" s="292"/>
     </row>
@@ -27628,7 +27802,7 @@
       </c>
       <c r="D73" s="290" t="n">
         <f aca="false">'PLANILLA GENERAL DE METRADOS'!K322</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
       <c r="E73" s="295" t="s">
         <v>986</v>
@@ -27638,11 +27812,11 @@
       </c>
       <c r="G73" s="306" t="n">
         <f aca="false">'ACU JUNTA CERCO'!$D$16*(1+'ACU JUNTA CERCO'!$D$17)</f>
-        <v>0.471190730362068</v>
+        <v>0.945</v>
       </c>
       <c r="H73" s="296" t="n">
         <f aca="false">G73*$D$73</f>
-        <v>63.55986</v>
+        <v>55.570725</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27661,7 +27835,7 @@
       </c>
       <c r="H74" s="296" t="n">
         <f aca="false">G74*$D$73</f>
-        <v>13.4892</v>
+        <v>5.8805</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27683,7 +27857,7 @@
       </c>
       <c r="H75" s="296" t="n">
         <f aca="false">G75*$D$73</f>
-        <v>0.17405384544</v>
+        <v>0.0758772676</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27702,7 +27876,7 @@
       </c>
       <c r="H76" s="296" t="n">
         <f aca="false">G76*$D$73</f>
-        <v>6.7446</v>
+        <v>2.94025</v>
       </c>
     </row>
   </sheetData>
@@ -28226,7 +28400,7 @@
       </c>
       <c r="G25" s="290" t="n">
         <f aca="false">F25*SUMIF($B$68:$B$93,B25,$F$68:$F$93)</f>
-        <v>29.597688</v>
+        <v>29.244132</v>
       </c>
       <c r="H25" s="149" t="s">
         <v>1029</v>
@@ -28254,7 +28428,7 @@
       </c>
       <c r="G26" s="290" t="n">
         <f aca="false">F26*SUMIF($B$68:$B$93,B26,$F$68:$F$93)</f>
-        <v>23.183172</v>
+        <v>22.9104288</v>
       </c>
       <c r="H26" s="149" t="s">
         <v>1029</v>
@@ -28299,7 +28473,7 @@
       <c r="F28" s="295"/>
       <c r="G28" s="296" t="n">
         <f aca="false">SUM(G22:G27)</f>
-        <v>99.17649864</v>
+        <v>98.55019944</v>
       </c>
       <c r="H28" s="295"/>
     </row>
@@ -28507,7 +28681,7 @@
       </c>
       <c r="G36" s="290" t="n">
         <f aca="false">F36*SUMIF($B$68:$B$93,B36,$F$68:$F$93)</f>
-        <v>0.86709248</v>
+        <v>0.85673472</v>
       </c>
       <c r="H36" s="149" t="s">
         <v>1036</v>
@@ -28535,7 +28709,7 @@
       </c>
       <c r="G37" s="290" t="n">
         <f aca="false">F37*SUMIF($B$68:$B$93,B37,$F$68:$F$93)</f>
-        <v>0.67917312</v>
+        <v>0.671182848</v>
       </c>
       <c r="H37" s="149" t="s">
         <v>1036</v>
@@ -28563,7 +28737,7 @@
       </c>
       <c r="G38" s="290" t="n">
         <f aca="false">F38*SUMIF($B$68:$B$93,B38,$F$68:$F$93)</f>
-        <v>4.922007552</v>
+        <v>4.862820352</v>
       </c>
       <c r="H38" s="149" t="s">
         <v>1036</v>
@@ -28580,7 +28754,7 @@
       <c r="F39" s="295"/>
       <c r="G39" s="296" t="n">
         <f aca="false">SUM(G30:G38)</f>
-        <v>21.13676935936</v>
+        <v>21.05923412736</v>
       </c>
       <c r="H39" s="295"/>
     </row>
@@ -28732,7 +28906,7 @@
       </c>
       <c r="G46" s="290" t="n">
         <f aca="false">F46*SUMIF($B$68:$B$93,B46,$F$68:$F$93)</f>
-        <v>16.25573376</v>
+        <v>16.06155264</v>
       </c>
       <c r="H46" s="149" t="s">
         <v>1036</v>
@@ -28760,7 +28934,7 @@
       </c>
       <c r="G47" s="290" t="n">
         <f aca="false">F47*SUMIF($B$68:$B$93,B47,$F$68:$F$93)</f>
-        <v>12.73273344</v>
+        <v>12.582936576</v>
       </c>
       <c r="H47" s="149" t="s">
         <v>1036</v>
@@ -28777,7 +28951,7 @@
       <c r="F48" s="295"/>
       <c r="G48" s="296" t="n">
         <f aca="false">SUM(G44:G47)</f>
-        <v>96.89637888</v>
+        <v>96.552400896</v>
       </c>
       <c r="H48" s="295"/>
     </row>
@@ -28929,7 +29103,7 @@
       </c>
       <c r="G54" s="290" t="n">
         <f aca="false">F54*SUMIF($B$68:$B$93,B54,$F$68:$F$93)</f>
-        <v>9.8335488</v>
+        <v>9.7160832</v>
       </c>
       <c r="H54" s="149" t="s">
         <v>1036</v>
@@ -28946,7 +29120,7 @@
       <c r="F55" s="295"/>
       <c r="G55" s="296" t="n">
         <f aca="false">SUM(G50:G54)</f>
-        <v>17.25401856</v>
+        <v>17.13655296</v>
       </c>
       <c r="H55" s="295"/>
     </row>
@@ -28985,7 +29159,7 @@
       </c>
       <c r="G57" s="290" t="n">
         <f aca="false">F57*SUMIF($B$68:$B$93,B57,$F$68:$F$93)</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="H57" s="149" t="s">
         <v>1052</v>
@@ -29012,7 +29186,7 @@
       </c>
       <c r="G58" s="290" t="n">
         <f aca="false">F58*SUMIF($B$68:$B$93,B58,$F$68:$F$93)</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="H58" s="149" t="s">
         <v>1052</v>
@@ -29029,7 +29203,7 @@
       <c r="F59" s="295"/>
       <c r="G59" s="296" t="n">
         <f aca="false">SUM(G57:G58)</f>
-        <v>50.09</v>
+        <v>49.49</v>
       </c>
       <c r="H59" s="295"/>
     </row>
@@ -29044,7 +29218,7 @@
       <c r="F60" s="295"/>
       <c r="G60" s="296" t="n">
         <f aca="false">+G28+G39+G42+G48+G55+G59</f>
-        <v>289.62516543936</v>
+        <v>287.85988742336</v>
       </c>
       <c r="H60" s="295"/>
     </row>
@@ -29190,14 +29364,14 @@
       </c>
       <c r="F69" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G69" s="290" t="n">
         <f aca="false">E69*F69</f>
-        <v>85.85406304</v>
+        <v>84.82850256</v>
       </c>
       <c r="H69" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29220,14 +29394,14 @@
       </c>
       <c r="F70" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$12</f>
-        <v>22.95</v>
+        <v>22.68</v>
       </c>
       <c r="G70" s="290" t="n">
         <f aca="false">E70*F70</f>
-        <v>36.59507856</v>
+        <v>36.164548224</v>
       </c>
       <c r="H70" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29250,14 +29424,14 @@
       </c>
       <c r="F71" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G71" s="290" t="n">
         <f aca="false">E71*F71</f>
-        <v>25.712007552</v>
+        <v>25.402820352</v>
       </c>
       <c r="H71" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29271,7 +29445,7 @@
       <c r="F72" s="295"/>
       <c r="G72" s="296" t="n">
         <f aca="false">SUM(G69:G71)</f>
-        <v>148.161149152</v>
+        <v>146.395871136</v>
       </c>
       <c r="H72" s="295"/>
     </row>
@@ -29668,11 +29842,11 @@
       </c>
       <c r="F89" s="290" t="n">
         <f aca="false">+G72</f>
-        <v>148.161149152</v>
+        <v>146.395871136</v>
       </c>
       <c r="G89" s="290" t="n">
         <f aca="false">E89*F89</f>
-        <v>4.44483447456</v>
+        <v>4.39187613408</v>
       </c>
       <c r="H89" s="149" t="s">
         <v>1073</v>
@@ -29776,7 +29950,7 @@
       <c r="F93" s="295"/>
       <c r="G93" s="296" t="n">
         <f aca="false">SUM(G89:G92)</f>
-        <v>13.22837060256</v>
+        <v>13.17541226208</v>
       </c>
       <c r="H93" s="295"/>
     </row>
@@ -29791,7 +29965,7 @@
       <c r="F94" s="294"/>
       <c r="G94" s="296" t="n">
         <f aca="false">+G72+G87+G93</f>
-        <v>294.06999991392</v>
+        <v>292.25176355744</v>
       </c>
       <c r="H94" s="295"/>
     </row>
@@ -29806,7 +29980,7 @@
       <c r="F95" s="294"/>
       <c r="G95" s="296" t="n">
         <f aca="false">G94*C65</f>
-        <v>2940.6999991392</v>
+        <v>2922.5176355744</v>
       </c>
       <c r="H95" s="295"/>
     </row>
@@ -30366,14 +30540,14 @@
       </c>
       <c r="F31" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G31" s="290" t="n">
         <f aca="false">E31*F31</f>
-        <v>9.376</v>
+        <v>9.264</v>
       </c>
       <c r="H31" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30395,14 +30569,14 @@
       </c>
       <c r="F32" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G32" s="290" t="n">
         <f aca="false">E32*F32</f>
-        <v>6.6528</v>
+        <v>6.5728</v>
       </c>
       <c r="H32" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30416,7 +30590,7 @@
       <c r="F33" s="295"/>
       <c r="G33" s="296" t="n">
         <f aca="false">SUM(G31:G32)</f>
-        <v>16.0288</v>
+        <v>15.8368</v>
       </c>
       <c r="H33" s="295"/>
     </row>
@@ -30553,11 +30727,11 @@
       </c>
       <c r="F40" s="290" t="n">
         <f aca="false">+G33</f>
-        <v>16.0288</v>
+        <v>15.8368</v>
       </c>
       <c r="G40" s="290" t="n">
         <f aca="false">E40*F40</f>
-        <v>0.80144</v>
+        <v>0.79184</v>
       </c>
       <c r="H40" s="149" t="s">
         <v>1118</v>
@@ -30574,7 +30748,7 @@
       <c r="F41" s="295"/>
       <c r="G41" s="296" t="n">
         <f aca="false">SUM(G40:G40)</f>
-        <v>0.80144</v>
+        <v>0.79184</v>
       </c>
       <c r="H41" s="295"/>
     </row>
@@ -30589,7 +30763,7 @@
       <c r="F42" s="294"/>
       <c r="G42" s="296" t="n">
         <f aca="false">+G33+G38+G41</f>
-        <v>40.2594485040984</v>
+        <v>40.0578485040984</v>
       </c>
       <c r="H42" s="295"/>
     </row>
@@ -30604,7 +30778,7 @@
       <c r="F43" s="294"/>
       <c r="G43" s="296" t="n">
         <f aca="false">G42*C27</f>
-        <v>20692.5513421365</v>
+        <v>20588.9329741365</v>
       </c>
       <c r="H43" s="295"/>
     </row>
@@ -30722,14 +30896,14 @@
       </c>
       <c r="F51" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G51" s="290" t="n">
         <f aca="false">E51*F51</f>
-        <v>5.86</v>
+        <v>5.79</v>
       </c>
       <c r="H51" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30751,14 +30925,14 @@
       </c>
       <c r="F52" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G52" s="290" t="n">
         <f aca="false">E52*F52</f>
-        <v>2.079</v>
+        <v>2.054</v>
       </c>
       <c r="H52" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30772,7 +30946,7 @@
       <c r="F53" s="295"/>
       <c r="G53" s="296" t="n">
         <f aca="false">SUM(G51:G52)</f>
-        <v>7.939</v>
+        <v>7.844</v>
       </c>
       <c r="H53" s="295"/>
     </row>
@@ -30907,11 +31081,11 @@
       </c>
       <c r="F60" s="290" t="n">
         <f aca="false">+G53</f>
-        <v>7.939</v>
+        <v>7.844</v>
       </c>
       <c r="G60" s="290" t="n">
         <f aca="false">E60*F60</f>
-        <v>0.39695</v>
+        <v>0.3922</v>
       </c>
       <c r="H60" s="149" t="s">
         <v>1118</v>
@@ -30928,7 +31102,7 @@
       <c r="F61" s="295"/>
       <c r="G61" s="296" t="n">
         <f aca="false">SUM(G60:G60)</f>
-        <v>0.39695</v>
+        <v>0.3922</v>
       </c>
       <c r="H61" s="295"/>
     </row>
@@ -30943,7 +31117,7 @@
       <c r="F62" s="294"/>
       <c r="G62" s="296" t="n">
         <f aca="false">+G53+G58+G61</f>
-        <v>16.55225</v>
+        <v>16.4525</v>
       </c>
       <c r="H62" s="295"/>
     </row>
@@ -30958,7 +31132,7 @@
       <c r="F63" s="294"/>
       <c r="G63" s="296" t="n">
         <f aca="false">G62*C47</f>
-        <v>14632.189</v>
+        <v>14544.01</v>
       </c>
       <c r="H63" s="295"/>
     </row>
@@ -31076,14 +31250,14 @@
       </c>
       <c r="F71" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G71" s="290" t="n">
         <f aca="false">E71*F71</f>
-        <v>7.81333333333333</v>
+        <v>7.72</v>
       </c>
       <c r="H71" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31105,14 +31279,14 @@
       </c>
       <c r="F72" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G72" s="290" t="n">
         <f aca="false">E72*F72</f>
-        <v>2.772</v>
+        <v>2.73866666666667</v>
       </c>
       <c r="H72" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31126,7 +31300,7 @@
       <c r="F73" s="295"/>
       <c r="G73" s="296" t="n">
         <f aca="false">SUM(G71:G72)</f>
-        <v>10.5853333333333</v>
+        <v>10.4586666666667</v>
       </c>
       <c r="H73" s="295"/>
     </row>
@@ -31262,11 +31436,11 @@
       </c>
       <c r="F80" s="290" t="n">
         <f aca="false">+G73</f>
-        <v>10.5853333333333</v>
+        <v>10.4586666666667</v>
       </c>
       <c r="G80" s="290" t="n">
         <f aca="false">E80*F80</f>
-        <v>0.529266666666667</v>
+        <v>0.522933333333333</v>
       </c>
       <c r="H80" s="149" t="s">
         <v>1118</v>
@@ -31283,7 +31457,7 @@
       <c r="F81" s="295"/>
       <c r="G81" s="296" t="n">
         <f aca="false">SUM(G80:G80)</f>
-        <v>0.529266666666667</v>
+        <v>0.522933333333333</v>
       </c>
       <c r="H81" s="295"/>
     </row>
@@ -31298,7 +31472,7 @@
       <c r="F82" s="294"/>
       <c r="G82" s="296" t="n">
         <f aca="false">+G73+G78+G81</f>
-        <v>15.7189525</v>
+        <v>15.5859525</v>
       </c>
       <c r="H82" s="295"/>
     </row>
@@ -31313,7 +31487,7 @@
       <c r="F83" s="294"/>
       <c r="G83" s="296" t="n">
         <f aca="false">G82*C67</f>
-        <v>628.7581</v>
+        <v>623.4381</v>
       </c>
       <c r="H83" s="295"/>
     </row>
@@ -31431,14 +31605,14 @@
       </c>
       <c r="F91" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G91" s="290" t="n">
         <f aca="false">E91*F91</f>
-        <v>14.65</v>
+        <v>14.475</v>
       </c>
       <c r="H91" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31460,14 +31634,14 @@
       </c>
       <c r="F92" s="289" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G92" s="290" t="n">
         <f aca="false">E92*F92</f>
-        <v>5.1975</v>
+        <v>5.135</v>
       </c>
       <c r="H92" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31481,7 +31655,7 @@
       <c r="F93" s="295"/>
       <c r="G93" s="296" t="n">
         <f aca="false">SUM(G91:G92)</f>
-        <v>19.8475</v>
+        <v>19.61</v>
       </c>
       <c r="H93" s="295"/>
     </row>
@@ -31617,11 +31791,11 @@
       </c>
       <c r="F100" s="290" t="n">
         <f aca="false">+G93</f>
-        <v>19.8475</v>
+        <v>19.61</v>
       </c>
       <c r="G100" s="290" t="n">
         <f aca="false">E100*F100</f>
-        <v>0.992375</v>
+        <v>0.9805</v>
       </c>
       <c r="H100" s="149" t="s">
         <v>1118</v>
@@ -31638,7 +31812,7 @@
       <c r="F101" s="295"/>
       <c r="G101" s="296" t="n">
         <f aca="false">SUM(G100:G100)</f>
-        <v>0.992375</v>
+        <v>0.9805</v>
       </c>
       <c r="H101" s="295"/>
     </row>
@@ -31653,7 +31827,7 @@
       <c r="F102" s="294"/>
       <c r="G102" s="296" t="n">
         <f aca="false">+G93+G98+G101</f>
-        <v>27.3278733730072</v>
+        <v>27.0784983730072</v>
       </c>
       <c r="H102" s="295"/>
     </row>
@@ -31668,7 +31842,7 @@
       <c r="F103" s="294"/>
       <c r="G103" s="296" t="n">
         <f aca="false">G102*C87</f>
-        <v>1421.04941539637</v>
+        <v>1408.08191539637</v>
       </c>
       <c r="H103" s="295"/>
     </row>
@@ -31720,11 +31894,11 @@
       </c>
       <c r="E107" s="290" t="n">
         <f aca="false">+G42</f>
-        <v>40.2594485040984</v>
+        <v>40.0578485040984</v>
       </c>
       <c r="F107" s="290" t="n">
         <f aca="false">+G43</f>
-        <v>20692.5513421365</v>
+        <v>20588.9329741365</v>
       </c>
       <c r="G107" s="295"/>
       <c r="H107" s="295"/>
@@ -31745,11 +31919,11 @@
       </c>
       <c r="E108" s="290" t="n">
         <f aca="false">+G62</f>
-        <v>16.55225</v>
+        <v>16.4525</v>
       </c>
       <c r="F108" s="290" t="n">
         <f aca="false">+G63</f>
-        <v>14632.189</v>
+        <v>14544.01</v>
       </c>
       <c r="G108" s="295"/>
       <c r="H108" s="295"/>
@@ -31770,11 +31944,11 @@
       </c>
       <c r="E109" s="290" t="n">
         <f aca="false">+G82</f>
-        <v>15.7189525</v>
+        <v>15.5859525</v>
       </c>
       <c r="F109" s="290" t="n">
         <f aca="false">+G83</f>
-        <v>628.7581</v>
+        <v>623.4381</v>
       </c>
       <c r="G109" s="295"/>
       <c r="H109" s="295"/>
@@ -31795,11 +31969,11 @@
       </c>
       <c r="E110" s="290" t="n">
         <f aca="false">+G102</f>
-        <v>27.3278733730072</v>
+        <v>27.0784983730072</v>
       </c>
       <c r="F110" s="290" t="n">
         <f aca="false">+G103</f>
-        <v>1421.04941539637</v>
+        <v>1408.08191539637</v>
       </c>
       <c r="G110" s="295"/>
       <c r="H110" s="295"/>
@@ -31814,7 +31988,7 @@
       <c r="E111" s="295"/>
       <c r="F111" s="296" t="n">
         <f aca="false">SUM(F107:F110)</f>
-        <v>37374.5478575328</v>
+        <v>37164.4629895329</v>
       </c>
       <c r="G111" s="295"/>
       <c r="H111" s="295"/>
@@ -33092,7 +33266,7 @@
       <c r="F19" s="295"/>
       <c r="G19" s="295"/>
       <c r="H19" s="149" t="s">
-        <v>1242</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33340,14 +33514,14 @@
       </c>
       <c r="F34" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">E34*F34</f>
-        <v>5.86</v>
+        <v>5.79</v>
       </c>
       <c r="H34" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33370,14 +33544,14 @@
       </c>
       <c r="F35" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G35" s="290" t="n">
         <f aca="false">E35*F35</f>
-        <v>4.158</v>
+        <v>4.108</v>
       </c>
       <c r="H35" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33391,7 +33565,7 @@
       <c r="F36" s="295"/>
       <c r="G36" s="296" t="n">
         <f aca="false">SUM(G34:G35)</f>
-        <v>10.018</v>
+        <v>9.898</v>
       </c>
       <c r="H36" s="295"/>
     </row>
@@ -33531,11 +33705,11 @@
       </c>
       <c r="F43" s="290" t="n">
         <f aca="false">+G36</f>
-        <v>10.018</v>
+        <v>9.898</v>
       </c>
       <c r="G43" s="290" t="n">
         <f aca="false">E43*F43</f>
-        <v>0.30054</v>
+        <v>0.29694</v>
       </c>
       <c r="H43" s="149" t="s">
         <v>1268</v>
@@ -33552,7 +33726,7 @@
       <c r="F44" s="295"/>
       <c r="G44" s="296" t="n">
         <f aca="false">SUM(G43:G43)</f>
-        <v>0.30054</v>
+        <v>0.29694</v>
       </c>
       <c r="H44" s="295"/>
     </row>
@@ -33567,7 +33741,7 @@
       <c r="F45" s="294"/>
       <c r="G45" s="296" t="n">
         <f aca="false">+G36+G41+G44</f>
-        <v>11.77924805416</v>
+        <v>11.65564805416</v>
       </c>
       <c r="H45" s="295"/>
     </row>
@@ -33582,7 +33756,7 @@
       <c r="F46" s="294"/>
       <c r="G46" s="296" t="n">
         <f aca="false">G45*C30</f>
-        <v>1185.46352417067</v>
+        <v>1173.02442017067</v>
       </c>
       <c r="H46" s="295"/>
     </row>
@@ -33715,7 +33889,7 @@
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1340</v>
+        <v>1474</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -33803,20 +33977,20 @@
         <v>3.0</v>
       </c>
       <c r="B13" s="149" t="s">
-        <v>1341</v>
+        <v>1475</v>
       </c>
       <c r="C13" s="285" t="s">
         <v>57</v>
       </c>
       <c r="D13" s="306" t="n">
-        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F16+'COLECTOR JUNTAS Y EMPALMES'!F17+'COLECTOR JUNTAS Y EMPALMES'!F18</f>
-        <v>76.087</v>
+        <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F16</f>
+        <v>0.0</v>
       </c>
       <c r="E13" s="295"/>
       <c r="F13" s="295"/>
       <c r="G13" s="295"/>
       <c r="H13" s="149" t="s">
-        <v>1277</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33824,13 +33998,13 @@
         <v>4.0</v>
       </c>
       <c r="B14" s="149" t="s">
-        <v>1278</v>
+        <v>1476</v>
       </c>
       <c r="C14" s="285" t="s">
         <v>57</v>
       </c>
       <c r="D14" s="309" t="n">
-        <v>0.1</v>
+        <v>0.0</v>
       </c>
       <c r="E14" s="295"/>
       <c r="F14" s="295"/>
@@ -33851,7 +34025,7 @@
       </c>
       <c r="D15" s="306" t="n">
         <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
       <c r="E15" s="295"/>
       <c r="F15" s="295"/>
@@ -33872,7 +34046,7 @@
       </c>
       <c r="D16" s="306" t="n">
         <f aca="false">(D11*D12+D13*D14)/D15</f>
-        <v>0.448753076535302</v>
+        <v>0.9</v>
       </c>
       <c r="E16" s="295"/>
       <c r="F16" s="295"/>
@@ -33933,7 +34107,7 @@
       </c>
       <c r="D19" s="306" t="n">
         <f aca="false">D16*(1+D17)/D18</f>
-        <v>0.163607892486829</v>
+        <v>0.328125</v>
       </c>
       <c r="E19" s="295"/>
       <c r="F19" s="295"/>
@@ -33960,7 +34134,7 @@
       <c r="F20" s="295"/>
       <c r="G20" s="295"/>
       <c r="H20" s="149" t="s">
-        <v>1286</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34106,7 +34280,7 @@
       <c r="B30" s="294"/>
       <c r="C30" s="290" t="n">
         <f aca="false">'COLECTOR JUNTAS Y EMPALMES'!F19</f>
-        <v>134.892</v>
+        <v>58.805</v>
       </c>
       <c r="D30" s="290"/>
       <c r="E30" s="290"/>
@@ -34187,14 +34361,14 @@
       </c>
       <c r="F34" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">E34*F34</f>
-        <v>1.465</v>
+        <v>1.4475</v>
       </c>
       <c r="H34" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34217,14 +34391,14 @@
       </c>
       <c r="F35" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G35" s="290" t="n">
         <f aca="false">E35*F35</f>
-        <v>2.079</v>
+        <v>2.054</v>
       </c>
       <c r="H35" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34238,7 +34412,7 @@
       <c r="F36" s="295"/>
       <c r="G36" s="296" t="n">
         <f aca="false">SUM(G34:G35)</f>
-        <v>3.544</v>
+        <v>3.5015</v>
       </c>
       <c r="H36" s="295"/>
     </row>
@@ -34267,7 +34441,7 @@
       <c r="D38" s="295"/>
       <c r="E38" s="306" t="n">
         <f aca="false">$D$19</f>
-        <v>0.163607892486829</v>
+        <v>0.328125</v>
       </c>
       <c r="F38" s="290" t="n">
         <f aca="false">13.9/1.18</f>
@@ -34275,7 +34449,7 @@
       </c>
       <c r="G38" s="290" t="n">
         <f aca="false">E38*F38</f>
-        <v>1.92724551319231</v>
+        <v>3.86520127118644</v>
       </c>
       <c r="H38" s="149" t="s">
         <v>1264</v>
@@ -34346,7 +34520,7 @@
       <c r="F41" s="295"/>
       <c r="G41" s="296" t="n">
         <f aca="false">SUM(G38:G40)</f>
-        <v>2.95010024167231</v>
+        <v>4.88805599966644</v>
       </c>
       <c r="H41" s="295"/>
     </row>
@@ -34378,11 +34552,11 @@
       </c>
       <c r="F43" s="290" t="n">
         <f aca="false">+G36</f>
-        <v>3.544</v>
+        <v>3.5015</v>
       </c>
       <c r="G43" s="290" t="n">
         <f aca="false">E43*F43</f>
-        <v>0.10632</v>
+        <v>0.105045</v>
       </c>
       <c r="H43" s="149" t="s">
         <v>1268</v>
@@ -34399,7 +34573,7 @@
       <c r="F44" s="295"/>
       <c r="G44" s="296" t="n">
         <f aca="false">SUM(G43:G43)</f>
-        <v>0.10632</v>
+        <v>0.105045</v>
       </c>
       <c r="H44" s="295"/>
     </row>
@@ -34414,7 +34588,7 @@
       <c r="F45" s="294"/>
       <c r="G45" s="296" t="n">
         <f aca="false">+G36+G41+G44</f>
-        <v>6.60042024167231</v>
+        <v>8.49460099966644</v>
       </c>
       <c r="H45" s="295"/>
     </row>
@@ -34429,7 +34603,7 @@
       <c r="F46" s="294"/>
       <c r="G46" s="296" t="n">
         <f aca="false">G45*C30</f>
-        <v>890.343887239661</v>
+        <v>499.525011785385</v>
       </c>
       <c r="H46" s="295"/>
     </row>
@@ -37379,7 +37553,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -37391,7 +37565,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="277" t="s">
-        <v>1349</v>
+        <v>1411</v>
       </c>
       <c r="B1" s="277"/>
       <c r="C1" s="277"/>
@@ -37463,7 +37637,7 @@
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1350</v>
+        <v>1412</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -37475,7 +37649,7 @@
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="294" t="s">
-        <v>1351</v>
+        <v>1413</v>
       </c>
       <c r="B9" s="294"/>
       <c r="C9" s="294"/>
@@ -37485,7 +37659,7 @@
       <c r="G9" s="294"/>
       <c r="H9" s="294"/>
     </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="282" t="s">
         <v>331</v>
       </c>
@@ -37493,17 +37667,13 @@
         <v>1352</v>
       </c>
       <c r="C10" s="282" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="D10" s="282" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E10" s="282" t="s">
-        <v>1355</v>
-      </c>
-      <c r="F10" s="282" t="s">
-        <v>1356</v>
-      </c>
+        <v>1415</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
       <c r="G10" s="282" t="s">
         <v>1357</v>
       </c>
@@ -37511,93 +37681,84 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="283" t="n">
         <v>1.0</v>
       </c>
       <c r="B11" s="149" t="s">
         <v>952</v>
       </c>
-      <c r="C11" s="289" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="D11" s="289" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="E11" s="306" t="n">
-        <f aca="false">D11/C11</f>
-        <v>0.328110599078341</v>
-      </c>
-      <c r="F11" s="289" t="n">
+      <c r="C11" s="290" t="n">
+        <f aca="false">D17</f>
         <v>89.3</v>
       </c>
-      <c r="G11" s="290" t="n">
-        <f aca="false">ROUND(E11*F11,2)</f>
-        <v>29.3</v>
+      <c r="D11" s="290" t="n">
+        <f aca="false">D25</f>
+        <v>231.62</v>
+      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="296" t="n">
+        <f aca="false">D26</f>
+        <v>28.95</v>
       </c>
       <c r="H11" s="149" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="283" t="n">
         <v>2.0</v>
       </c>
       <c r="B12" s="149" t="s">
         <v>954</v>
       </c>
-      <c r="C12" s="289" t="n">
-        <v>68.1</v>
-      </c>
-      <c r="D12" s="289" t="n">
-        <v>22.41</v>
-      </c>
-      <c r="E12" s="306" t="n">
-        <f aca="false">D12/C12</f>
-        <v>0.329074889867841</v>
-      </c>
-      <c r="F12" s="289" t="n">
+      <c r="C12" s="290" t="n">
+        <f aca="false">E17</f>
         <v>69.75</v>
       </c>
-      <c r="G12" s="290" t="n">
-        <f aca="false">ROUND(E12*F12,2)</f>
-        <v>22.95</v>
+      <c r="D12" s="290" t="n">
+        <f aca="false">E25</f>
+        <v>181.46</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="296" t="n">
+        <f aca="false">E26</f>
+        <v>22.68</v>
       </c>
       <c r="H12" s="149" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="283" t="n">
         <v>3.0</v>
       </c>
       <c r="B13" s="149" t="s">
         <v>955</v>
       </c>
-      <c r="C13" s="289" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="D13" s="289" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="E13" s="306" t="n">
-        <f aca="false">D13/C13</f>
-        <v>0.330995106035889</v>
-      </c>
-      <c r="F13" s="289" t="n">
+      <c r="C13" s="290" t="n">
+        <f aca="false">F17</f>
         <v>62.8</v>
       </c>
-      <c r="G13" s="290" t="n">
-        <f aca="false">ROUND(E13*F13,2)</f>
-        <v>20.79</v>
+      <c r="D13" s="290" t="n">
+        <f aca="false">F25</f>
+        <v>164.34</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="296" t="n">
+        <f aca="false">F26</f>
+        <v>20.54</v>
       </c>
       <c r="H13" s="149" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="294" t="s">
-        <v>1360</v>
+        <v>1417</v>
       </c>
       <c r="B15" s="294"/>
       <c r="C15" s="294"/>
@@ -37607,78 +37768,702 @@
       <c r="G15" s="294"/>
       <c r="H15" s="294"/>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="283" t="n">
+    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B16" s="282" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C16" s="282" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D16" s="282" t="s">
+        <v>1419</v>
+      </c>
+      <c r="E16" s="282" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F16" s="282" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G16" s="282"/>
+      <c r="H16" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="283" t="n">
         <v>1.0</v>
       </c>
-      <c r="B16" s="149" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C16" s="149"/>
-      <c r="D16" s="149"/>
-      <c r="E16" s="149"/>
-      <c r="F16" s="149"/>
-      <c r="G16" s="149"/>
-      <c r="H16" s="149"/>
-    </row>
-    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="283" t="n">
+      <c r="B17" s="149" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C17" s="285" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D17" s="289" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E17" s="289" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="F17" s="289" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
         <v>2.0</v>
       </c>
-      <c r="B17" s="149" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="149"/>
-      <c r="G17" s="149"/>
-      <c r="H17" s="149"/>
-    </row>
-    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="283" t="n">
+      <c r="B18" s="149" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C18" s="290" t="n">
+        <f aca="false">$D$50</f>
+        <v>112.2</v>
+      </c>
+      <c r="D18" s="290" t="n">
+        <f aca="false">ROUND(D17*$C$18/100,2)</f>
+        <v>100.19</v>
+      </c>
+      <c r="E18" s="290" t="n">
+        <f aca="false">ROUND(E17*$C$18/100,2)</f>
+        <v>78.26</v>
+      </c>
+      <c r="F18" s="290" t="n">
+        <f aca="false">ROUND(F17*$C$18/100,2)</f>
+        <v>70.46</v>
+      </c>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
         <v>3.0</v>
       </c>
-      <c r="B18" s="149" t="s">
-        <v>1363</v>
-      </c>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-    </row>
-    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="283" t="n">
+      <c r="B19" s="149" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D19" s="290" t="n">
+        <f aca="false">ROUND(D17*0.32,2)</f>
+        <v>28.58</v>
+      </c>
+      <c r="E19" s="290" t="n">
+        <f aca="false">ROUND(E17*0.30,2)</f>
+        <v>20.93</v>
+      </c>
+      <c r="F19" s="290" t="n">
+        <f aca="false">ROUND(F17*0.30,2)</f>
+        <v>18.84</v>
+      </c>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
         <v>4.0</v>
       </c>
-      <c r="B19" s="149" t="s">
-        <v>1364</v>
-      </c>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-    </row>
-    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="283" t="n">
+      <c r="B20" s="149" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C20" s="290" t="n">
+        <f aca="false">$E$50</f>
+        <v>12.25</v>
+      </c>
+      <c r="D20" s="290" t="n">
+        <f aca="false">ROUND(D19*$C$20/100,2)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E20" s="290" t="n">
+        <f aca="false">ROUND(E19*$C$20/100,2)</f>
+        <v>2.56</v>
+      </c>
+      <c r="F20" s="290" t="n">
+        <f aca="false">ROUND(F19*$C$20/100,2)</f>
+        <v>2.31</v>
+      </c>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="283" t="n">
         <v>5.0</v>
       </c>
-      <c r="B20" s="149" t="s">
-        <v>1365</v>
-      </c>
-      <c r="C20" s="149"/>
-      <c r="D20" s="149"/>
-      <c r="E20" s="149"/>
-      <c r="F20" s="149"/>
-      <c r="G20" s="149"/>
-      <c r="H20" s="149"/>
+      <c r="B21" s="149" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D21" s="289" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E21" s="289" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F21" s="289" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C22" s="285" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D22" s="289" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="289" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F22" s="289" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G22" s="295"/>
+      <c r="H22" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C23" s="285" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D23" s="289" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E23" s="289" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F23" s="289" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G23" s="295"/>
+      <c r="H23" s="149" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C24" s="285" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D24" s="290" t="n">
+        <f aca="false">ROUND(2*132.8/300,2)</f>
+        <v>0.89</v>
+      </c>
+      <c r="E24" s="290" t="n">
+        <f aca="false">ROUND(2*132.8/300,2)</f>
+        <v>0.89</v>
+      </c>
+      <c r="F24" s="290" t="n">
+        <f aca="false">ROUND(2*132.8/300,2)</f>
+        <v>0.89</v>
+      </c>
+      <c r="G24" s="295"/>
+      <c r="H24" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21"/>
+      <c r="B25" s="294" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C25" s="295"/>
+      <c r="D25" s="296" t="n">
+        <f aca="false">SUM(D17:D24)</f>
+        <v>231.62</v>
+      </c>
+      <c r="E25" s="296" t="n">
+        <f aca="false">SUM(E17:E24)</f>
+        <v>181.46</v>
+      </c>
+      <c r="F25" s="296" t="n">
+        <f aca="false">SUM(F17:F24)</f>
+        <v>164.34</v>
+      </c>
+      <c r="G25" s="295"/>
+      <c r="H25" s="295"/>
+    </row>
+    <row r="26" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21"/>
+      <c r="B26" s="294" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C26" s="295"/>
+      <c r="D26" s="296" t="n">
+        <f aca="false">ROUND(D25/8,2)</f>
+        <v>28.95</v>
+      </c>
+      <c r="E26" s="296" t="n">
+        <f aca="false">ROUND(E25/8,2)</f>
+        <v>22.68</v>
+      </c>
+      <c r="F26" s="296" t="n">
+        <f aca="false">ROUND(F25/8,2)</f>
+        <v>20.54</v>
+      </c>
+      <c r="G26" s="295"/>
+      <c r="H26" s="149" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="294" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B28" s="294"/>
+      <c r="C28" s="294"/>
+      <c r="D28" s="294"/>
+      <c r="E28" s="294"/>
+      <c r="F28" s="294"/>
+      <c r="G28" s="294"/>
+      <c r="H28" s="294"/>
+    </row>
+    <row r="29" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="282" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C29" s="282"/>
+      <c r="D29" s="282" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E29" s="282" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F29" s="282"/>
+      <c r="G29" s="282"/>
+      <c r="H29" s="282" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B30" s="149" t="s">
+        <v>1445</v>
+      </c>
+      <c r="C30" s="295"/>
+      <c r="D30" s="289" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B31" s="149" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C31" s="295"/>
+      <c r="D31" s="289" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="E31" s="295"/>
+      <c r="F31" s="295"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B32" s="149" t="s">
+        <v>1447</v>
+      </c>
+      <c r="C32" s="295"/>
+      <c r="D32" s="289" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E32" s="289" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F32" s="295"/>
+      <c r="G32" s="295"/>
+      <c r="H32" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B33" s="149" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C33" s="295"/>
+      <c r="D33" s="289" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E33" s="289" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F33" s="295"/>
+      <c r="G33" s="295"/>
+      <c r="H33" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B34" s="149" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C34" s="295"/>
+      <c r="D34" s="289" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="E34" s="289" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="F34" s="295"/>
+      <c r="G34" s="295"/>
+      <c r="H34" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B35" s="149" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C35" s="295"/>
+      <c r="D35" s="289" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E35" s="289" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F35" s="295"/>
+      <c r="G35" s="295"/>
+      <c r="H35" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B36" s="149" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C36" s="295"/>
+      <c r="D36" s="289" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="E36" s="295"/>
+      <c r="F36" s="295"/>
+      <c r="G36" s="295"/>
+      <c r="H36" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B37" s="149" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C37" s="295"/>
+      <c r="D37" s="289" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="E37" s="295"/>
+      <c r="F37" s="295"/>
+      <c r="G37" s="295"/>
+      <c r="H37" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B38" s="149" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C38" s="295"/>
+      <c r="D38" s="289" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="E38" s="295"/>
+      <c r="F38" s="295"/>
+      <c r="G38" s="295"/>
+      <c r="H38" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B39" s="149" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C39" s="295"/>
+      <c r="D39" s="289" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E39" s="295"/>
+      <c r="F39" s="295"/>
+      <c r="G39" s="295"/>
+      <c r="H39" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B40" s="149" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C40" s="295"/>
+      <c r="D40" s="289" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="E40" s="295"/>
+      <c r="F40" s="295"/>
+      <c r="G40" s="295"/>
+      <c r="H40" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B41" s="149" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C41" s="295"/>
+      <c r="D41" s="289" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E41" s="295"/>
+      <c r="F41" s="295"/>
+      <c r="G41" s="295"/>
+      <c r="H41" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B42" s="149" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C42" s="295"/>
+      <c r="D42" s="289" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E42" s="295"/>
+      <c r="F42" s="295"/>
+      <c r="G42" s="295"/>
+      <c r="H42" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="283" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B43" s="149" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C43" s="295"/>
+      <c r="D43" s="289" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E43" s="295"/>
+      <c r="F43" s="295"/>
+      <c r="G43" s="295"/>
+      <c r="H43" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="283" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B44" s="149" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C44" s="295"/>
+      <c r="D44" s="289" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E44" s="295"/>
+      <c r="F44" s="295"/>
+      <c r="G44" s="295"/>
+      <c r="H44" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="283" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B45" s="149" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C45" s="295"/>
+      <c r="D45" s="289" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E45" s="295"/>
+      <c r="F45" s="295"/>
+      <c r="G45" s="295"/>
+      <c r="H45" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="283" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B46" s="149" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C46" s="295"/>
+      <c r="D46" s="289" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="295"/>
+      <c r="F46" s="295"/>
+      <c r="G46" s="295"/>
+      <c r="H46" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="283" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B47" s="149" t="s">
+        <v>1462</v>
+      </c>
+      <c r="C47" s="295"/>
+      <c r="D47" s="289" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E47" s="295"/>
+      <c r="F47" s="295"/>
+      <c r="G47" s="295"/>
+      <c r="H47" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="283" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B48" s="149" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C48" s="295"/>
+      <c r="D48" s="289" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E48" s="295"/>
+      <c r="F48" s="295"/>
+      <c r="G48" s="295"/>
+      <c r="H48" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="283" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B49" s="149" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C49" s="295"/>
+      <c r="D49" s="289" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E49" s="295"/>
+      <c r="F49" s="295"/>
+      <c r="G49" s="295"/>
+      <c r="H49" s="149" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21"/>
+      <c r="B50" s="294" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C50" s="295"/>
+      <c r="D50" s="296" t="n">
+        <f aca="false">SUM(D30:D49)</f>
+        <v>112.2</v>
+      </c>
+      <c r="E50" s="296" t="n">
+        <f aca="false">SUM(E30:E49)</f>
+        <v>12.25</v>
+      </c>
+      <c r="F50" s="295"/>
+      <c r="G50" s="295"/>
+      <c r="H50" s="149" t="s">
+        <v>1466</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="13">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
@@ -37691,11 +38476,7 @@
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A28:H28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -38245,14 +39026,14 @@
       </c>
       <c r="F33" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G33" s="290" t="n">
         <f aca="false">E33*F33</f>
-        <v>4.88333333333333</v>
+        <v>4.825</v>
       </c>
       <c r="H33" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38275,14 +39056,14 @@
       </c>
       <c r="F34" s="290" t="n">
         <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G34" s="290" t="n">
         <f aca="false">E34*F34</f>
-        <v>6.93</v>
+        <v>6.84666666666667</v>
       </c>
       <c r="H34" s="149" t="s">
-        <v>1366</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38296,7 +39077,7 @@
       <c r="F35" s="295"/>
       <c r="G35" s="296" t="n">
         <f aca="false">SUM(G33:G34)</f>
-        <v>11.8133333333333</v>
+        <v>11.6716666666667</v>
       </c>
       <c r="H35" s="295"/>
     </row>
@@ -38517,11 +39298,11 @@
       </c>
       <c r="F45" s="290" t="n">
         <f aca="false">+G35</f>
-        <v>11.8133333333333</v>
+        <v>11.6716666666667</v>
       </c>
       <c r="G45" s="290" t="n">
         <f aca="false">E45*F45</f>
-        <v>0.3544</v>
+        <v>0.35015</v>
       </c>
       <c r="H45" s="149" t="s">
         <v>1406</v>
@@ -38538,7 +39319,7 @@
       <c r="F46" s="295"/>
       <c r="G46" s="296" t="n">
         <f aca="false">SUM(G45:G45)</f>
-        <v>0.3544</v>
+        <v>0.35015</v>
       </c>
       <c r="H46" s="295"/>
     </row>
@@ -38553,7 +39334,7 @@
       <c r="F47" s="294"/>
       <c r="G47" s="296" t="n">
         <f aca="false">+G35+G43+G46</f>
-        <v>20.7041016206215</v>
+        <v>20.5581849539548</v>
       </c>
       <c r="H47" s="295"/>
     </row>
@@ -38568,7 +39349,7 @@
       <c r="F48" s="294"/>
       <c r="G48" s="296" t="n">
         <f aca="false">G47*C29</f>
-        <v>3250.54395443757</v>
+        <v>3227.6350377709</v>
       </c>
       <c r="H48" s="295"/>
     </row>

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1481">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4969,6 +4969,9 @@
   </si>
   <si>
     <t xml:space="preserve">DD-03 C; EG-2013 MTC, Seccion 510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caja de caida CC: descuento ventana de salida (alto = interior del R-01 del CAR Mujeres: losa 259.25 - 0.10 - fondo)</t>
   </si>
 </sst>
 </file>
@@ -8256,7 +8259,7 @@
       </c>
       <c r="D66" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K240</f>
-        <v>58.3136159999999</v>
+        <v>58.4063159999999</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15045,7 +15048,7 @@
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="21"/>
       <c r="B38" s="149" t="s">
-        <v>757</v>
+        <v>1480</v>
       </c>
       <c r="C38" s="283" t="s">
         <v>729</v>
@@ -15059,8 +15062,8 @@
         <v>0.15</v>
       </c>
       <c r="F38" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$57+0.5-'COLECTOR PARAMETROS'!$C$56</f>
-        <v>0.841999999999985</v>
+        <f aca="false">259.25-0.1-'COLECTOR PARAMETROS'!$C$56</f>
+        <v>0.42999999999995</v>
       </c>
       <c r="G38" s="298" t="n">
         <v>-1</v>
@@ -15069,7 +15072,7 @@
       <c r="I38" s="21"/>
       <c r="J38" s="290" t="n">
         <f aca="false">D38*E38*F38*G38</f>
-        <v>-0.189449999999997</v>
+        <v>-0.0967499999999887</v>
       </c>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
@@ -15367,7 +15370,7 @@
       </c>
       <c r="J47" s="293" t="n">
         <f aca="false">SUM(J21:J46)</f>
-        <v>4.53719999999988</v>
+        <v>4.62989999999989</v>
       </c>
       <c r="K47" s="293" t="n">
         <f aca="false">SUM(K21:K46)</f>
@@ -15472,11 +15475,11 @@
       </c>
       <c r="H52" s="290" t="n">
         <f aca="false">J47</f>
-        <v>4.53719999999988</v>
+        <v>4.62989999999989</v>
       </c>
       <c r="I52" s="296" t="n">
         <f aca="false">G52+H52</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21833,7 +21836,7 @@
       <c r="J240" s="25"/>
       <c r="K240" s="25" t="n">
         <f aca="false">SUM(J241:J271)</f>
-        <v>58.3136159999999</v>
+        <v>58.4063159999999</v>
       </c>
       <c r="L240" s="24" t="s">
         <v>25</v>
@@ -22228,7 +22231,7 @@
       <c r="I259" s="27"/>
       <c r="J259" s="27" t="n">
         <f aca="false">SUM('COLECTOR CONCRETO'!J33:J43)</f>
-        <v>2.91449999999992</v>
+        <v>3.00719999999993</v>
       </c>
       <c r="K259" s="27"/>
       <c r="L259" s="26"/>
@@ -26673,7 +26676,7 @@
       </c>
       <c r="D19" s="290" t="n">
         <f aca="false">SUM('PLANILLA GENERAL DE METRADOS'!J251:J259)</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
       <c r="E19" s="295" t="s">
         <v>944</v>
@@ -26686,7 +26689,7 @@
       </c>
       <c r="H19" s="296" t="n">
         <f aca="false">G19*$D$19</f>
-        <v>348.939361679999</v>
+        <v>349.841332679999</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26705,7 +26708,7 @@
       </c>
       <c r="H20" s="296" t="n">
         <f aca="false">G20*$D$19</f>
-        <v>18.6483523199999</v>
+        <v>18.6965563199999</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26724,7 +26727,7 @@
       </c>
       <c r="H21" s="296" t="n">
         <f aca="false">G21*$D$19</f>
-        <v>19.0069744799999</v>
+        <v>19.0561054799999</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26743,7 +26746,7 @@
       </c>
       <c r="H22" s="296" t="n">
         <f aca="false">G22*$D$19</f>
-        <v>6.67037217599998</v>
+        <v>6.68761437599998</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26762,7 +26765,7 @@
       </c>
       <c r="H23" s="296" t="n">
         <f aca="false">G23*$D$19</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26781,7 +26784,7 @@
       </c>
       <c r="H24" s="296" t="n">
         <f aca="false">G24*$D$19</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26800,7 +26803,7 @@
       </c>
       <c r="H25" s="296" t="n">
         <f aca="false">G25*$D$19</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26819,7 +26822,7 @@
       </c>
       <c r="H26" s="296" t="n">
         <f aca="false">G26*$D$19</f>
-        <v>35.8622159999999</v>
+        <v>35.9549159999999</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26838,7 +26841,7 @@
       </c>
       <c r="H27" s="296" t="n">
         <f aca="false">G27*$D$19</f>
-        <v>286.897727999999</v>
+        <v>287.639327999999</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1566">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -4972,6 +4972,261 @@
   </si>
   <si>
     <t xml:space="preserve">Caja de caida CC: descuento ventana de salida (alto = interior del R-01 del CAR Mujeres: losa 259.25 - 0.10 - fondo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lado del rebaje de asiento de la tapa en la losa (0.70 x 0.70 x 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (tapa ciega)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luz libre del registro bajo el rebaje (0.60 x 0.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perimetro del encofrado lateral de la tapa (4 x 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje por tapa (fierro liso 1/2" en cajuelas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desarrollo de cada asa de fierro liso 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02: agarre 0.15 + 2 patas de 0.11 con gancho de 0.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holgura entre la tapa y el rebaje (cada lado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bisel de los cantos superiores de la tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (tapa ciega de concreto armado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02 (= profundidad del rebaje)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje de la tapa (en cajuelas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/2" liso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02: 2 asas de fierro liso 1/2" por tapa, desarrollo 0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02: 7 + 7 barras de 3/8" @0.10, L = 0.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO DE REFUERZO EN TAPAS, BORDES Y ASAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caja de llegada CL: descuento de rebajes y aberturas de registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rebaje 0.70 x 0.70 x 0.08 + luz 0.60 x 0.60 en el resto (e equivalente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caja de caida CC: descuento de rebajes y aberturas de registro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registros RS-01 a RS-07: descuento del rebaje y de la abertura en la losa superior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08 (vaciada aparte en obra)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCOFRADO LATERAL DE LA TAPA (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registros x 4 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO EN TAPAS: PARRILLA 3/8" Y ASAS 1/2" LISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hoja COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02; COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASIENTO DE LA TAPA: REBAJE DE CONCRETO 0.70 x 0.70 x 0.08 EN LA LOSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 por registro (concreto incluido en la losa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP-06B rev. 02; COLECTOR CONCRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOCACION DE LA TAPA EN EL REBAJE (izaje con las asas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-01 (ubicacion) y DP-06B rev. 02 (detalle): tapa ciega de concreto armado 0.68 x 0.68 x 0.08, vaciada aparte en obra, con 2 asas de fierro liso 1/2", apoyada en un rebaje de concreto de 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60). Sin marco ni contramarco metalico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 TAPA DE REGISTRO: encofrado lateral de la tapa (molde de madera, 6 usos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 TAPA DE REGISTRO: colocacion de la tapa en el rebaje y curado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada tapa: concreto armado f'c=210 de 0.68 x 0.68 x 0.08 vaciado aparte en obra, parrilla 3/8" @0.10, 2 asas de fierro liso 1/2", asiento en rebaje de concreto 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60) y refuerzo de borde 4 x 2 barras de 1/2". Sin marco ni contramarco metalico.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANALISIS DE COSTO UNITARIO - TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partida de Delphin 01.04.04.06.05.01 TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08 (metrado 01.04.04.05.01, hojas COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO). Tapa ciega de concreto armado vaciada aparte en obra sobre tablero, con parrilla 3/8" @0.10, 2 asas de fierro liso 1/2" en cajuelas y cantos biselados; se coloca en el rebaje de concreto de 0.70 x 0.70 x 0.08 de la losa (el rebaje y el borde engrosado se metran con el concreto del colector). Incluye el refuerzo de borde de la abertura (2 barras de 1/2" por lado). Sin marco ni contramarco metalico. Celda amarilla = dato; verde = formula. Precios sin IGV.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. CANTIDADES POR TAPA (hojas COLECTOR PARAMETROS, COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numero de tapas (registros)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR REGISTROS Y TAPAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concreto f'c=210 por tapa: 0.68 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral por tapa: 4 x 0.68 x 0.08 (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablero de vaciado: 0.80 x 0.80 x 1" = 6.89 p2 en 6 usos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero 3/8" de la parrilla por tapa (7 + 7 barras, L = 0.62)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR ACERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero 1/2" de borde de la abertura por registro (8 barras, L = 1.40)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fierro liso 1/2" de las 2 asas por tapa (desarrollo 0.50 c/u)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperdicio de acero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cemento por m3 de concreto f'c=210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (diseno de mezcla)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arena gruesa por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piedra chancada 1/2" por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua por m3 (mezcla) + curado de la tapa (0.01 m3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del concreto: operario / oficial / peon por m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (0.8 / 0.8 / 6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peon por m3 de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del acero: operario / oficial por kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mano de obra del encofrado: operario / oficial por m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/m2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLECTOR INSUMOS (encofrado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocacion de la tapa en el rebaje: operario + peon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hh/und</t>
+  </si>
+  <si>
+    <t xml:space="preserve">criterio de obra: 1 hh por tapa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.06.05.01 TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.04.04.05.01 (hoja COLECTOR REGISTROS Y TAPAS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fierro liso 1/2" (asas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mismo precio por kg del acero corrugado (referencial): Sodimac Peru, Aceros Arequipa: 1/2" x 9 m S/ 36.50 y 3/8" x 9 m S/ 20.35 con IGV (ponderado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 % del costo de mano de obra (incluye mezcla y vibrado manual del concreto de la tapa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESAGREGADO DE LA PARTIDA 01.04.04.05.01 - TAPA DE REGISTRO CIEGA DE CONCRETO ARMADO 0.68x0.68x0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La partida se mide por unidad de registro. Cada tapa ciega de concreto armado se vacia aparte en obra y se coloca en el rebaje de 0.70 x 0.70 x 0.08 de la losa (luz libre 0.60 x 0.60). Sin marco ni contramarco metalico. Componentes tomados de las hojas COLECTOR REGISTROS Y TAPAS y COLECTOR ACERO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapa ciega de concreto f'c=210: 0.68 x 0.68 x 0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lamina DP-06B rev. 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENCOFRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral de la tapa: 4 x 0.68 x 0.08 (molde de madera)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal encofrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACERO DE REFUERZO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asas de izaje: 2 barras de fierro liso 1/2", desarrollo 0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal acero de refuerzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encofrado lateral de tapas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acero en tapas, asas y bordes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hay angulos, soldadura ni pintura: la tapa es ciega de concreto armado (lamina DP-06B rev. 02). El rebaje de asiento y el borde engrosado de la abertura se metran con el concreto de la losa del colector (hoja COLECTOR CONCRETO).</t>
   </si>
 </sst>
 </file>
@@ -5765,7 +6020,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="311">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7006,6 +7261,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="24" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8259,7 +8518,7 @@
       </c>
       <c r="D66" s="16" t="n">
         <f aca="false">+'PLANILLA GENERAL DE METRADOS'!K240</f>
-        <v>58.4063159999999</v>
+        <v>58.4323159999999</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8337,7 +8596,7 @@
         <v>132</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>133</v>
+        <v>1516</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>60</v>
@@ -12052,7 +12311,7 @@
         <v>57</v>
       </c>
       <c r="E33" s="286" t="s">
-        <v>593</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12069,7 +12328,7 @@
         <v>57</v>
       </c>
       <c r="E34" s="286" t="s">
-        <v>593</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12077,7 +12336,7 @@
         <v>26</v>
       </c>
       <c r="B35" s="149" t="s">
-        <v>595</v>
+        <v>1481</v>
       </c>
       <c r="C35" s="284" t="n">
         <v>0.7</v>
@@ -12086,7 +12345,7 @@
         <v>57</v>
       </c>
       <c r="E35" s="286" t="s">
-        <v>593</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12094,16 +12353,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="149" t="s">
-        <v>1184</v>
+        <v>1483</v>
       </c>
       <c r="C36" s="284" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="D36" s="285" t="s">
         <v>57</v>
       </c>
       <c r="E36" s="286" t="s">
-        <v>593</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12111,7 +12370,7 @@
         <v>28</v>
       </c>
       <c r="B37" s="149" t="s">
-        <v>597</v>
+        <v>1485</v>
       </c>
       <c r="C37" s="284" t="n">
         <v>2.72</v>
@@ -12120,7 +12379,7 @@
         <v>57</v>
       </c>
       <c r="E37" s="286" t="s">
-        <v>593</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12128,16 +12387,16 @@
         <v>29</v>
       </c>
       <c r="B38" s="149" t="s">
-        <v>1185</v>
+        <v>1486</v>
       </c>
       <c r="C38" s="284" t="n">
-        <v>1.83</v>
+        <v>2.0</v>
       </c>
       <c r="D38" s="285" t="s">
-        <v>515</v>
+        <v>60</v>
       </c>
       <c r="E38" s="286" t="s">
-        <v>599</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12145,16 +12404,16 @@
         <v>30</v>
       </c>
       <c r="B39" s="149" t="s">
-        <v>1186</v>
+        <v>1487</v>
       </c>
       <c r="C39" s="284" t="n">
-        <v>1.83</v>
+        <v>0.5</v>
       </c>
       <c r="D39" s="285" t="s">
-        <v>515</v>
+        <v>57</v>
       </c>
       <c r="E39" s="286" t="s">
-        <v>599</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12162,16 +12421,16 @@
         <v>31</v>
       </c>
       <c r="B40" s="149" t="s">
-        <v>1187</v>
+        <v>1489</v>
       </c>
       <c r="C40" s="284" t="n">
-        <v>0.152</v>
+        <v>0.01</v>
       </c>
       <c r="D40" s="285" t="s">
-        <v>602</v>
+        <v>57</v>
       </c>
       <c r="E40" s="286" t="s">
-        <v>605</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12179,16 +12438,16 @@
         <v>32</v>
       </c>
       <c r="B41" s="149" t="s">
-        <v>1188</v>
+        <v>1490</v>
       </c>
       <c r="C41" s="284" t="n">
-        <v>0.152</v>
+        <v>0.01</v>
       </c>
       <c r="D41" s="285" t="s">
-        <v>602</v>
+        <v>57</v>
       </c>
       <c r="E41" s="286" t="s">
-        <v>605</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14763,10 +15022,10 @@
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21"/>
       <c r="B30" s="149" t="s">
-        <v>740</v>
+        <v>1498</v>
       </c>
       <c r="C30" s="283" t="s">
-        <v>741</v>
+        <v>1499</v>
       </c>
       <c r="D30" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$35</f>
@@ -14777,8 +15036,8 @@
         <v>0.7</v>
       </c>
       <c r="F30" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$13</f>
-        <v>0.1</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$34+('COLECTOR PARAMETROS'!$C$13-'COLECTOR PARAMETROS'!$C$34)*('COLECTOR PARAMETROS'!$C$36/'COLECTOR PARAMETROS'!$C$35)^2</f>
+        <v>0.0946938775510204</v>
       </c>
       <c r="G30" s="298" t="n">
         <v>-1</v>
@@ -14788,7 +15047,7 @@
       <c r="J30" s="21"/>
       <c r="K30" s="290" t="n">
         <f aca="false">D30*E30*F30*G30</f>
-        <v>-0.049</v>
+        <v>-0.0464</v>
       </c>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
@@ -15156,10 +15415,10 @@
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21"/>
       <c r="B41" s="149" t="s">
-        <v>761</v>
+        <v>1500</v>
       </c>
       <c r="C41" s="283" t="s">
-        <v>741</v>
+        <v>1499</v>
       </c>
       <c r="D41" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$35</f>
@@ -15170,8 +15429,8 @@
         <v>0.7</v>
       </c>
       <c r="F41" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$13</f>
-        <v>0.1</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$34+('COLECTOR PARAMETROS'!$C$13-'COLECTOR PARAMETROS'!$C$34)*('COLECTOR PARAMETROS'!$C$36/'COLECTOR PARAMETROS'!$C$35)^2</f>
+        <v>0.0946938775510204</v>
       </c>
       <c r="G41" s="298" t="n">
         <v>-2</v>
@@ -15181,7 +15440,7 @@
       <c r="J41" s="21"/>
       <c r="K41" s="290" t="n">
         <f aca="false">D41*E41*F41*G41</f>
-        <v>-0.098</v>
+        <v>-0.0928</v>
       </c>
       <c r="L41" s="21"/>
       <c r="M41" s="21"/>
@@ -15316,10 +15575,10 @@
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="21"/>
       <c r="B46" s="283" t="s">
-        <v>769</v>
+        <v>1501</v>
       </c>
       <c r="C46" s="283" t="s">
-        <v>741</v>
+        <v>1499</v>
       </c>
       <c r="D46" s="290" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$35</f>
@@ -15330,8 +15589,8 @@
         <v>0.7</v>
       </c>
       <c r="F46" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$13</f>
-        <v>0.1</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$34+('COLECTOR PARAMETROS'!$C$13-'COLECTOR PARAMETROS'!$C$34)*('COLECTOR PARAMETROS'!$C$36/'COLECTOR PARAMETROS'!$C$35)^2</f>
+        <v>0.0946938775510204</v>
       </c>
       <c r="G46" s="299" t="n">
         <f aca="false">-('COLECTOR PARAMETROS'!$C$32-3)</f>
@@ -15342,7 +15601,7 @@
       <c r="J46" s="21"/>
       <c r="K46" s="290" t="n">
         <f aca="false">D46*E46*F46*G46</f>
-        <v>-0.343</v>
+        <v>-0.3248</v>
       </c>
       <c r="L46" s="21"/>
       <c r="M46" s="21"/>
@@ -15374,7 +15633,7 @@
       </c>
       <c r="K47" s="293" t="n">
         <f aca="false">SUM(K21:K46)</f>
-        <v>0.878</v>
+        <v>0.904</v>
       </c>
       <c r="L47" s="293" t="n">
         <f aca="false">SUM(L21:L46)</f>
@@ -15501,11 +15760,11 @@
       </c>
       <c r="H53" s="290" t="n">
         <f aca="false">K47</f>
-        <v>0.878</v>
+        <v>0.904</v>
       </c>
       <c r="I53" s="296" t="n">
         <f aca="false">G53+H53</f>
-        <v>9.39255</v>
+        <v>9.41855</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21836,7 +22095,7 @@
       <c r="J240" s="25"/>
       <c r="K240" s="25" t="n">
         <f aca="false">SUM(J241:J271)</f>
-        <v>58.4063159999999</v>
+        <v>58.4323159999999</v>
       </c>
       <c r="L240" s="24" t="s">
         <v>25</v>
@@ -22415,7 +22674,7 @@
       <c r="I268" s="27"/>
       <c r="J268" s="27" t="n">
         <f aca="false">SUM('COLECTOR CONCRETO'!K21:K32)</f>
-        <v>0.185</v>
+        <v>0.1876</v>
       </c>
       <c r="K268" s="27"/>
       <c r="L268" s="26"/>
@@ -22436,7 +22695,7 @@
       <c r="I269" s="27"/>
       <c r="J269" s="27" t="n">
         <f aca="false">SUM('COLECTOR CONCRETO'!K33:K43)</f>
-        <v>0.586</v>
+        <v>0.5912</v>
       </c>
       <c r="K269" s="27"/>
       <c r="L269" s="26"/>
@@ -22478,7 +22737,7 @@
       <c r="I271" s="27"/>
       <c r="J271" s="27" t="n">
         <f aca="false">'COLECTOR CONCRETO'!K46</f>
-        <v>-0.343</v>
+        <v>-0.3248</v>
       </c>
       <c r="K271" s="27"/>
       <c r="L271" s="26"/>
@@ -23354,7 +23613,7 @@
         <v>132</v>
       </c>
       <c r="B313" s="24" t="s">
-        <v>133</v>
+        <v>1516</v>
       </c>
       <c r="C313" s="25"/>
       <c r="D313" s="25"/>
@@ -23438,7 +23697,7 @@
     <row r="317" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="26"/>
       <c r="B317" s="26" t="s">
-        <v>1195</v>
+        <v>1517</v>
       </c>
       <c r="C317" s="27"/>
       <c r="D317" s="27"/>
@@ -23454,8 +23713,8 @@
     <row r="318" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="26"/>
       <c r="B318" s="26" t="str">
-        <f aca="false">"Totales para "&amp;K313&amp;" tapas: angulos "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E25,"0.00")&amp;" kg; concreto "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E27,"0.00")&amp;" m3; acero "&amp;TEXT('COLECTOR ACERO'!I41,"0.00")&amp;" kg; pintura "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E28,"0.00")&amp;" m2"</f>
-        <v>Totales para 10 tapas: angulos 101.02 kg; concreto 0.37 m3; acero 173.38 kg; pintura 8.39 m2</v>
+        <f aca="false">"Totales para "&amp;K313&amp;" tapas: concreto "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E26,"0.000")&amp;" m3; acero de tapas y asas "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E25,"0.00")&amp;" kg; encofrado "&amp;TEXT('COLECTOR REGISTROS Y TAPAS'!E24,"0.00")&amp;" m2"</f>
+        <v>Totales para 10 tapas: concreto 0.370 m3; acero de tapas y asas 58.55 kg; encofrado 2.18 m2</v>
       </c>
       <c r="C318" s="27"/>
       <c r="D318" s="27"/>
@@ -25174,7 +25433,7 @@
         <v>48.608</v>
       </c>
       <c r="V34" s="286" t="s">
-        <v>851</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25182,31 +25441,33 @@
         <v>3</v>
       </c>
       <c r="B35" s="149" t="s">
-        <v>852</v>
+        <v>1493</v>
       </c>
       <c r="C35" s="288" t="s">
-        <v>853</v>
+        <v>1494</v>
       </c>
       <c r="D35" s="283" t="s">
         <v>854</v>
       </c>
       <c r="E35" s="298" t="n">
-        <v>2</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$38</f>
+        <v>2.0</v>
       </c>
       <c r="F35" s="299" t="n">
         <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
         <v>10.0</v>
       </c>
       <c r="G35" s="289" t="n">
-        <v>0.4</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$39</f>
+        <v>0.5</v>
       </c>
       <c r="H35" s="290" t="n">
         <f aca="false">E35*F35*G35</f>
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="I35" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
-        <v>0.56</v>
+        <f aca="false">'COLECTOR PARAMETROS'!$C$21</f>
+        <v>0.994</v>
       </c>
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
@@ -25221,43 +25482,22 @@
       <c r="T35" s="21"/>
       <c r="U35" s="296" t="n">
         <f aca="false">H35*I35</f>
-        <v>4.48</v>
+        <v>9.94</v>
       </c>
       <c r="V35" s="286" t="s">
-        <v>855</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="283" t="n">
-        <v>4</v>
-      </c>
-      <c r="B36" s="149" t="s">
-        <v>856</v>
-      </c>
-      <c r="C36" s="288" t="s">
-        <v>368</v>
-      </c>
-      <c r="D36" s="283" t="s">
-        <v>857</v>
-      </c>
-      <c r="E36" s="298" t="n">
-        <v>8</v>
-      </c>
-      <c r="F36" s="299" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$32</f>
-        <v>10.0</v>
-      </c>
-      <c r="G36" s="289" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H36" s="290" t="n">
-        <f aca="false">E36*F36*G36</f>
-        <v>16.0</v>
-      </c>
-      <c r="I36" s="287" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!$C$20</f>
-        <v>0.56</v>
-      </c>
+      <c r="A36" s="283"/>
+      <c r="B36" s="149"/>
+      <c r="C36" s="288"/>
+      <c r="D36" s="283"/>
+      <c r="E36" s="298"/>
+      <c r="F36" s="299"/>
+      <c r="G36" s="289"/>
+      <c r="H36" s="290"/>
+      <c r="I36" s="287"/>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
@@ -25269,13 +25509,8 @@
       <c r="R36" s="21"/>
       <c r="S36" s="21"/>
       <c r="T36" s="21"/>
-      <c r="U36" s="296" t="n">
-        <f aca="false">H36*I36</f>
-        <v>8.96</v>
-      </c>
-      <c r="V36" s="286" t="s">
-        <v>858</v>
-      </c>
+      <c r="U36" s="296"/>
+      <c r="V36" s="286"/>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="291" t="s">
@@ -25302,7 +25537,7 @@
       <c r="T37" s="292"/>
       <c r="U37" s="293" t="n">
         <f aca="false">SUM(U33:U36)</f>
-        <v>173.376</v>
+        <v>169.876</v>
       </c>
       <c r="V37" s="292"/>
     </row>
@@ -25363,7 +25598,7 @@
         <v>2</v>
       </c>
       <c r="B41" s="295" t="s">
-        <v>862</v>
+        <v>1497</v>
       </c>
       <c r="C41" s="295"/>
       <c r="D41" s="295"/>
@@ -25373,15 +25608,15 @@
       </c>
       <c r="G41" s="290" t="n">
         <f aca="false">SUMIF(C33:C36,"3/8*",U33:U36)</f>
-        <v>62.048</v>
+        <v>48.608</v>
       </c>
       <c r="H41" s="290" t="n">
         <f aca="false">SUMIF(C33:C36,"1/2*",U33:U36)</f>
-        <v>111.328</v>
+        <v>121.268</v>
       </c>
       <c r="I41" s="296" t="n">
         <f aca="false">U37</f>
-        <v>173.376</v>
+        <v>169.876</v>
       </c>
     </row>
   </sheetData>
@@ -25492,7 +25727,7 @@
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1189</v>
+        <v>1513</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -25748,7 +25983,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="149" t="s">
-        <v>1190</v>
+        <v>1502</v>
       </c>
       <c r="C23" s="285" t="s">
         <v>60</v>
@@ -25761,7 +25996,7 @@
         <v>10.0</v>
       </c>
       <c r="F23" s="286" t="s">
-        <v>770</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25769,20 +26004,20 @@
         <v>2</v>
       </c>
       <c r="B24" s="149" t="s">
-        <v>895</v>
+        <v>1504</v>
       </c>
       <c r="C24" s="285" t="s">
-        <v>60</v>
+        <v>168</v>
       </c>
       <c r="D24" s="283" t="s">
-        <v>896</v>
+        <v>1505</v>
       </c>
       <c r="E24" s="296" t="n">
-        <f aca="false">E19</f>
-        <v>10.0</v>
+        <f aca="false">E19*'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>2.176</v>
       </c>
       <c r="F24" s="286" t="s">
-        <v>770</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25790,20 +26025,20 @@
         <v>3</v>
       </c>
       <c r="B25" s="149" t="s">
-        <v>897</v>
+        <v>1506</v>
       </c>
       <c r="C25" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="283" t="s">
-        <v>1191</v>
+        <v>1507</v>
       </c>
       <c r="E25" s="296" t="n">
-        <f aca="false">E19*('COLECTOR PARAMETROS'!$C$36*'COLECTOR PARAMETROS'!$C$38+'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$39)</f>
-        <v>101.016</v>
+        <f aca="false">'COLECTOR ACERO'!U34+'COLECTOR ACERO'!U35</f>
+        <v>58.548</v>
       </c>
       <c r="F25" s="286" t="s">
-        <v>899</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25811,20 +26046,20 @@
         <v>4</v>
       </c>
       <c r="B26" s="149" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C26" s="285" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="D26" s="283" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="E26" s="296" t="n">
-        <f aca="false">E19</f>
-        <v>10.0</v>
+        <f aca="false">E19*'COLECTOR PARAMETROS'!$C$33*'COLECTOR PARAMETROS'!$C$33*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>0.36992</v>
       </c>
       <c r="F26" s="286" t="s">
-        <v>770</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25832,20 +26067,20 @@
         <v>5</v>
       </c>
       <c r="B27" s="149" t="s">
-        <v>901</v>
+        <v>1509</v>
       </c>
       <c r="C27" s="285" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="D27" s="283" t="s">
-        <v>902</v>
+        <v>1510</v>
       </c>
       <c r="E27" s="296" t="n">
-        <f aca="false">E19*'COLECTOR PARAMETROS'!$C$33*'COLECTOR PARAMETROS'!$C$33*'COLECTOR PARAMETROS'!$C$34</f>
-        <v>0.36992</v>
+        <f aca="false">E19</f>
+        <v>10.0</v>
       </c>
       <c r="F27" s="286" t="s">
-        <v>770</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25853,20 +26088,20 @@
         <v>6</v>
       </c>
       <c r="B28" s="149" t="s">
-        <v>903</v>
+        <v>1512</v>
       </c>
       <c r="C28" s="285" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="D28" s="283" t="s">
-        <v>1192</v>
+        <v>894</v>
       </c>
       <c r="E28" s="296" t="n">
-        <f aca="false">E19*('COLECTOR PARAMETROS'!$C$36*'COLECTOR PARAMETROS'!$C$40+'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$41)</f>
-        <v>8.3904</v>
+        <f aca="false">E19</f>
+        <v>10.0</v>
       </c>
       <c r="F28" s="286" t="s">
-        <v>905</v>
+        <v>1503</v>
       </c>
     </row>
   </sheetData>
@@ -26856,7 +27091,7 @@
       </c>
       <c r="D28" s="290" t="n">
         <f aca="false">SUM('PLANILLA GENERAL DE METRADOS'!J261:J271)</f>
-        <v>9.39255</v>
+        <v>9.41855</v>
       </c>
       <c r="E28" s="295" t="s">
         <v>944</v>
@@ -26869,7 +27104,7 @@
       </c>
       <c r="H28" s="296" t="n">
         <f aca="false">G28*$D$28</f>
-        <v>91.3895115</v>
+        <v>91.6424915</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26888,7 +27123,7 @@
       </c>
       <c r="H29" s="296" t="n">
         <f aca="false">G29*$D$28</f>
-        <v>4.884126</v>
+        <v>4.897646</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26907,7 +27142,7 @@
       </c>
       <c r="H30" s="296" t="n">
         <f aca="false">G30*$D$28</f>
-        <v>4.9780515</v>
+        <v>4.9918315</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26926,7 +27161,7 @@
       </c>
       <c r="H31" s="296" t="n">
         <f aca="false">G31*$D$28</f>
-        <v>1.7470143</v>
+        <v>1.7518503</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26945,7 +27180,7 @@
       </c>
       <c r="H32" s="296" t="n">
         <f aca="false">G32*$D$28</f>
-        <v>7.51404</v>
+        <v>7.53484</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26964,7 +27199,7 @@
       </c>
       <c r="H33" s="296" t="n">
         <f aca="false">G33*$D$28</f>
-        <v>7.51404</v>
+        <v>7.53484</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26983,7 +27218,7 @@
       </c>
       <c r="H34" s="296" t="n">
         <f aca="false">G34*$D$28</f>
-        <v>7.51404</v>
+        <v>7.53484</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27002,7 +27237,7 @@
       </c>
       <c r="H35" s="296" t="n">
         <f aca="false">G35*$D$28</f>
-        <v>7.51404</v>
+        <v>7.53484</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27021,7 +27256,7 @@
       </c>
       <c r="H36" s="296" t="n">
         <f aca="false">G36*$D$28</f>
-        <v>60.11232</v>
+        <v>60.27872</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27520,27 +27755,27 @@
         <v>10</v>
       </c>
       <c r="B60" s="295" t="s">
-        <v>976</v>
+        <v>1514</v>
       </c>
       <c r="C60" s="285" t="s">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="D60" s="290" t="n">
-        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>101.016</v>
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E24</f>
+        <v>2.176</v>
       </c>
       <c r="E60" s="295" t="s">
-        <v>1196</v>
+        <v>959</v>
       </c>
       <c r="F60" s="285" t="s">
-        <v>50</v>
+        <v>960</v>
       </c>
       <c r="G60" s="284" t="n">
-        <v>1.05</v>
+        <v>0.7067</v>
       </c>
       <c r="H60" s="296" t="n">
         <f aca="false">G60*$D$60</f>
-        <v>106.0668</v>
+        <v>1.5377792</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27549,17 +27784,17 @@
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
       <c r="E61" s="295" t="s">
-        <v>978</v>
+        <v>961</v>
       </c>
       <c r="F61" s="285" t="s">
         <v>50</v>
       </c>
       <c r="G61" s="284" t="n">
-        <v>0.03</v>
+        <v>0.0333</v>
       </c>
       <c r="H61" s="296" t="n">
         <f aca="false">G61*$D$60</f>
-        <v>3.03048</v>
+        <v>0.0724608</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27574,11 +27809,11 @@
         <v>953</v>
       </c>
       <c r="G62" s="284" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H62" s="296" t="n">
         <f aca="false">G62*$D$60</f>
-        <v>10.1016</v>
+        <v>1.7408</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27593,11 +27828,11 @@
         <v>953</v>
       </c>
       <c r="G63" s="284" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="H63" s="296" t="n">
         <f aca="false">G63*$D$60</f>
-        <v>10.1016</v>
+        <v>1.7408</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27605,27 +27840,27 @@
         <v>11</v>
       </c>
       <c r="B64" s="295" t="s">
-        <v>979</v>
+        <v>1515</v>
       </c>
       <c r="C64" s="285" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="D64" s="290" t="n">
         <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>8.3904</v>
+        <v>10.0</v>
       </c>
       <c r="E64" s="295" t="s">
-        <v>980</v>
+        <v>952</v>
       </c>
       <c r="F64" s="285" t="s">
-        <v>981</v>
+        <v>953</v>
       </c>
       <c r="G64" s="284" t="n">
-        <v>0.08</v>
+        <v>1.0</v>
       </c>
       <c r="H64" s="296" t="n">
         <f aca="false">G64*$D$64</f>
-        <v>0.671232</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27634,17 +27869,17 @@
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
       <c r="E65" s="295" t="s">
-        <v>982</v>
+        <v>955</v>
       </c>
       <c r="F65" s="285" t="s">
-        <v>981</v>
+        <v>953</v>
       </c>
       <c r="G65" s="284" t="n">
-        <v>0.08</v>
+        <v>1.0</v>
       </c>
       <c r="H65" s="296" t="n">
         <f aca="false">G65*$D$64</f>
-        <v>0.671232</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27653,17 +27888,17 @@
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
       <c r="E66" s="295" t="s">
-        <v>1197</v>
+        <v>948</v>
       </c>
       <c r="F66" s="285" t="s">
-        <v>60</v>
+        <v>167</v>
       </c>
       <c r="G66" s="284" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="H66" s="296" t="n">
         <f aca="false">G66*$D$64</f>
-        <v>2.0976</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27671,38 +27906,20 @@
       <c r="B67" s="304"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
-      <c r="E67" s="295" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F67" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="G67" s="284" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="H67" s="296" t="n">
-        <f aca="false">G67*$D$64</f>
-        <v>0.2013696</v>
-      </c>
+      <c r="E67" s="295"/>
+      <c r="F67" s="285"/>
+      <c r="G67" s="284"/>
+      <c r="H67" s="296"/>
     </row>
     <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21"/>
       <c r="B68" s="304"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
-      <c r="E68" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="F68" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="G68" s="284" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H68" s="296" t="n">
-        <f aca="false">G68*$D$64</f>
-        <v>3.35616</v>
-      </c>
+      <c r="E68" s="295"/>
+      <c r="F68" s="285"/>
+      <c r="G68" s="284"/>
+      <c r="H68" s="296"/>
     </row>
     <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="283" t="n">
@@ -27910,7 +28127,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -27922,7 +28139,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="277" t="s">
-        <v>989</v>
+        <v>1518</v>
       </c>
       <c r="B1" s="277"/>
       <c r="C1" s="277"/>
@@ -27994,7 +28211,7 @@
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1221</v>
+        <v>1519</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -28006,7 +28223,7 @@
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="294" t="s">
-        <v>991</v>
+        <v>1520</v>
       </c>
       <c r="B9" s="294"/>
       <c r="C9" s="294"/>
@@ -28021,472 +28238,379 @@
         <v>331</v>
       </c>
       <c r="B10" s="282" t="s">
-        <v>992</v>
+        <v>1225</v>
       </c>
       <c r="C10" s="282" t="s">
         <v>151</v>
       </c>
       <c r="D10" s="282" t="s">
-        <v>993</v>
-      </c>
-      <c r="E10" s="282" t="s">
-        <v>994</v>
-      </c>
-      <c r="F10" s="282" t="s">
-        <v>995</v>
-      </c>
-      <c r="G10" s="282" t="s">
-        <v>992</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
       <c r="H10" s="282" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="283" t="n">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B11" s="149" t="s">
-        <v>1199</v>
+        <v>1521</v>
       </c>
       <c r="C11" s="285" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="290" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E23</f>
+      <c r="D11" s="306" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E19</f>
         <v>10.0</v>
       </c>
-      <c r="E11" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F11" s="306" t="n">
-        <f aca="false">D11/E11</f>
-        <v>1.0</v>
-      </c>
-      <c r="G11" s="283" t="s">
-        <v>997</v>
-      </c>
+      <c r="E11" s="295"/>
+      <c r="F11" s="295"/>
+      <c r="G11" s="295"/>
       <c r="H11" s="149" t="s">
-        <v>998</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="283" t="n">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B12" s="149" t="s">
-        <v>999</v>
+        <v>1523</v>
       </c>
       <c r="C12" s="285" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="290" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E24</f>
-        <v>10.0</v>
-      </c>
-      <c r="E12" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F12" s="306" t="n">
-        <f aca="false">D12/E12</f>
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="283" t="s">
-        <v>1000</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D12" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$33^2*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E12" s="295"/>
+      <c r="F12" s="295"/>
+      <c r="G12" s="295"/>
       <c r="H12" s="149" t="s">
-        <v>1001</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="283" t="n">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B13" s="149" t="s">
-        <v>1002</v>
+        <v>1524</v>
       </c>
       <c r="C13" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="290" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>101.016</v>
-      </c>
-      <c r="E13" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F13" s="306" t="n">
-        <f aca="false">D13/E13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="G13" s="283" t="s">
-        <v>1003</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="D13" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E13" s="295"/>
+      <c r="F13" s="295"/>
+      <c r="G13" s="295"/>
       <c r="H13" s="149" t="s">
-        <v>1200</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="283" t="n">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B14" s="149" t="s">
-        <v>1005</v>
+        <v>1525</v>
       </c>
       <c r="C14" s="285" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="290" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E26</f>
-        <v>10.0</v>
-      </c>
-      <c r="E14" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F14" s="306" t="n">
-        <f aca="false">D14/E14</f>
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="283" t="s">
-        <v>1006</v>
-      </c>
+        <v>960</v>
+      </c>
+      <c r="D14" s="310" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E14" s="295"/>
+      <c r="F14" s="295"/>
+      <c r="G14" s="295"/>
       <c r="H14" s="149" t="s">
-        <v>770</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="283" t="n">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>1007</v>
+        <v>1526</v>
       </c>
       <c r="C15" s="285" t="s">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="D15" s="306" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E27</f>
-        <v>0.36992</v>
-      </c>
-      <c r="E15" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F15" s="306" t="n">
-        <f aca="false">D15/E15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="G15" s="283" t="s">
-        <v>1008</v>
-      </c>
+        <f aca="false">'COLECTOR ACERO'!U34/'COLECTOR ACERO'!F34</f>
+        <v>4.8608</v>
+      </c>
+      <c r="E15" s="295"/>
+      <c r="F15" s="295"/>
+      <c r="G15" s="295"/>
       <c r="H15" s="149" t="s">
-        <v>1009</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="283" t="n">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>1010</v>
+        <v>1528</v>
       </c>
       <c r="C16" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="290" t="n">
-        <f aca="false">+'COLECTOR ACERO'!I41</f>
-        <v>173.376</v>
-      </c>
-      <c r="E16" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
-        <v>10.0</v>
-      </c>
-      <c r="F16" s="306" t="n">
-        <f aca="false">D16/E16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="G16" s="283" t="s">
-        <v>1011</v>
-      </c>
+      <c r="D16" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U33/'COLECTOR ACERO'!F33</f>
+        <v>11.1328</v>
+      </c>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295"/>
+      <c r="G16" s="295"/>
       <c r="H16" s="149" t="s">
-        <v>1012</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="283" t="n">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B17" s="149" t="s">
-        <v>1013</v>
+        <v>1529</v>
       </c>
       <c r="C17" s="285" t="s">
-        <v>168</v>
-      </c>
-      <c r="D17" s="290" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>8.3904</v>
-      </c>
-      <c r="E17" s="305" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E19</f>
+        <v>50</v>
+      </c>
+      <c r="D17" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U35/'COLECTOR ACERO'!F35</f>
+        <v>0.994</v>
+      </c>
+      <c r="E17" s="295"/>
+      <c r="F17" s="295"/>
+      <c r="G17" s="295"/>
+      <c r="H17" s="149" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="149" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C18" s="285" t="s">
+        <v>523</v>
+      </c>
+      <c r="D18" s="310" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E18" s="295"/>
+      <c r="F18" s="295"/>
+      <c r="G18" s="295"/>
+      <c r="H18" s="149" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="149" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C19" s="285" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D19" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G10</f>
+        <v>9.73</v>
+      </c>
+      <c r="E19" s="295"/>
+      <c r="F19" s="295"/>
+      <c r="G19" s="295"/>
+      <c r="H19" s="149" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="283" t="n">
         <v>10.0</v>
       </c>
-      <c r="F17" s="306" t="n">
-        <f aca="false">D17/E17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="G17" s="283" t="s">
-        <v>1014</v>
-      </c>
-      <c r="H17" s="149" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="294" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B19" s="294"/>
-      <c r="C19" s="294"/>
-      <c r="D19" s="294"/>
-      <c r="E19" s="294"/>
-      <c r="F19" s="294"/>
-      <c r="G19" s="294"/>
-      <c r="H19" s="294"/>
-    </row>
-    <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="282" t="s">
-        <v>331</v>
-      </c>
-      <c r="B20" s="282" t="s">
-        <v>939</v>
-      </c>
-      <c r="C20" s="282" t="s">
-        <v>151</v>
-      </c>
-      <c r="D20" s="282" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E20" s="282" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F20" s="282" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G20" s="282" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H20" s="282" t="s">
-        <v>1021</v>
+      <c r="B20" s="149" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C20" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D20" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G11</f>
+        <v>0.52</v>
+      </c>
+      <c r="E20" s="295"/>
+      <c r="F20" s="295"/>
+      <c r="G20" s="295"/>
+      <c r="H20" s="149" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="283" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B21" s="294" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C21" s="294"/>
-      <c r="D21" s="294"/>
-      <c r="E21" s="294"/>
-      <c r="F21" s="294"/>
-      <c r="G21" s="294"/>
-      <c r="H21" s="294"/>
+      <c r="A21" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B21" s="149" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C21" s="285" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D21" s="306" t="n">
+        <f aca="false">'COLECTOR INSUMOS'!G12</f>
+        <v>0.53</v>
+      </c>
+      <c r="E21" s="295"/>
+      <c r="F21" s="295"/>
+      <c r="G21" s="295"/>
+      <c r="H21" s="149" t="s">
+        <v>1036</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21"/>
-      <c r="B22" s="295" t="s">
-        <v>1026</v>
+      <c r="A22" s="283" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B22" s="149" t="s">
+        <v>1535</v>
       </c>
       <c r="C22" s="285" t="s">
-        <v>50</v>
+        <v>1249</v>
       </c>
       <c r="D22" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C38</f>
-        <v>5.124</v>
-      </c>
-      <c r="E22" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G60</f>
-        <v>1.05</v>
-      </c>
-      <c r="F22" s="306" t="n">
-        <f aca="false">D22*E22</f>
-        <v>5.3802</v>
-      </c>
-      <c r="G22" s="290" t="n">
-        <f aca="false">F22*SUMIF($B$68:$B$93,B22,$F$68:$F$93)</f>
-        <v>16.571016</v>
-      </c>
+        <f aca="false">'COLECTOR INSUMOS'!G13</f>
+        <v>0.186</v>
+      </c>
+      <c r="E22" s="295"/>
+      <c r="F22" s="295"/>
+      <c r="G22" s="295"/>
       <c r="H22" s="149" t="s">
-        <v>1202</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21"/>
-      <c r="B23" s="295" t="s">
-        <v>1026</v>
+      <c r="A23" s="283" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>1536</v>
       </c>
       <c r="C23" s="285" t="s">
-        <v>50</v>
+        <v>1537</v>
       </c>
       <c r="D23" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C37*'COLECTOR PARAMETROS'!C39</f>
-        <v>4.9776</v>
-      </c>
-      <c r="E23" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G60</f>
-        <v>1.05</v>
-      </c>
-      <c r="F23" s="306" t="n">
-        <f aca="false">D23*E23</f>
-        <v>5.22648</v>
-      </c>
-      <c r="G23" s="290" t="n">
-        <f aca="false">F23*SUMIF($B$68:$B$93,B23,$F$68:$F$93)</f>
-        <v>16.0975584</v>
-      </c>
+        <f aca="false">'COLECTOR INSUMOS'!G16</f>
+        <v>0.8</v>
+      </c>
+      <c r="E23" s="295"/>
+      <c r="F23" s="295"/>
+      <c r="G23" s="295"/>
       <c r="H23" s="149" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
-      <c r="B24" s="295" t="s">
-        <v>1028</v>
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="283" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>1539</v>
       </c>
       <c r="C24" s="285" t="s">
-        <v>50</v>
+        <v>1537</v>
       </c>
       <c r="D24" s="306" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E24" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G61</f>
-        <v>0.03</v>
-      </c>
-      <c r="F24" s="306" t="n">
-        <f aca="false">D24*E24</f>
-        <v>0.303048</v>
-      </c>
-      <c r="G24" s="290" t="n">
-        <f aca="false">F24*SUMIF($B$68:$B$93,B24,$F$68:$F$93)</f>
-        <v>5.64578424</v>
-      </c>
+        <f aca="false">'COLECTOR INSUMOS'!G18</f>
+        <v>6.4</v>
+      </c>
+      <c r="E24" s="295"/>
+      <c r="F24" s="295"/>
+      <c r="G24" s="295"/>
       <c r="H24" s="149" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
-      <c r="B25" s="295" t="s">
-        <v>952</v>
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="283" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B25" s="149" t="s">
+        <v>1540</v>
       </c>
       <c r="C25" s="285" t="s">
-        <v>953</v>
+        <v>1541</v>
       </c>
       <c r="D25" s="306" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E25" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G62</f>
-        <v>0.1</v>
-      </c>
-      <c r="F25" s="306" t="n">
-        <f aca="false">D25*E25</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G25" s="290" t="n">
-        <f aca="false">F25*SUMIF($B$68:$B$93,B25,$F$68:$F$93)</f>
-        <v>29.244132</v>
-      </c>
+        <f aca="false">'COLECTOR INSUMOS'!G44</f>
+        <v>0.032</v>
+      </c>
+      <c r="E25" s="295"/>
+      <c r="F25" s="295"/>
+      <c r="G25" s="295"/>
       <c r="H25" s="149" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21"/>
-      <c r="B26" s="295" t="s">
-        <v>954</v>
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="283" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B26" s="149" t="s">
+        <v>1542</v>
       </c>
       <c r="C26" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D26" s="306" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E26" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G63</f>
-        <v>0.1</v>
-      </c>
-      <c r="F26" s="306" t="n">
-        <f aca="false">D26*E26</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G26" s="290" t="n">
-        <f aca="false">F26*SUMIF($B$68:$B$93,B26,$F$68:$F$93)</f>
-        <v>22.9104288</v>
-      </c>
+        <v>1543</v>
+      </c>
+      <c r="D26" s="310" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E26" s="295"/>
+      <c r="F26" s="295"/>
+      <c r="G26" s="295"/>
       <c r="H26" s="149" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21"/>
-      <c r="B27" s="295" t="s">
-        <v>1030</v>
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="283" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>1545</v>
       </c>
       <c r="C27" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D27" s="306" t="n">
-        <f aca="false">F13</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E27" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G62</f>
-        <v>0.1</v>
-      </c>
-      <c r="F27" s="306" t="n">
-        <f aca="false">D27*E27</f>
-        <v>1.01016</v>
-      </c>
-      <c r="G27" s="290" t="n">
-        <f aca="false">F27*SUMIF($B$68:$B$93,B27,$F$68:$F$93)</f>
-        <v>8.08128</v>
-      </c>
+        <v>1546</v>
+      </c>
+      <c r="D27" s="310" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="295"/>
+      <c r="F27" s="295"/>
+      <c r="G27" s="295"/>
       <c r="H27" s="149" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="294" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C28" s="295"/>
-      <c r="D28" s="295"/>
-      <c r="E28" s="295"/>
-      <c r="F28" s="295"/>
-      <c r="G28" s="296" t="n">
-        <f aca="false">SUM(G22:G27)</f>
-        <v>98.55019944</v>
-      </c>
-      <c r="H28" s="295"/>
-    </row>
-    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="283" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B29" s="294" t="s">
-        <v>1034</v>
-      </c>
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="294" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B29" s="294"/>
       <c r="C29" s="294"/>
       <c r="D29" s="294"/>
       <c r="E29" s="294"/>
@@ -28494,1516 +28618,541 @@
       <c r="G29" s="294"/>
       <c r="H29" s="294"/>
     </row>
-    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21"/>
-      <c r="B30" s="295" t="s">
-        <v>944</v>
-      </c>
-      <c r="C30" s="285" t="s">
-        <v>945</v>
-      </c>
-      <c r="D30" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E30" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G28</f>
-        <v>9.73</v>
-      </c>
-      <c r="F30" s="306" t="n">
-        <f aca="false">D30*E30</f>
-        <v>0.35993216</v>
-      </c>
-      <c r="G30" s="290" t="n">
-        <f aca="false">F30*SUMIF($B$68:$B$93,B30,$F$68:$F$93)</f>
-        <v>11.1327017088</v>
-      </c>
-      <c r="H30" s="149" t="s">
-        <v>1035</v>
-      </c>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="294" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B30" s="294"/>
+      <c r="C30" s="295" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D30" s="295"/>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="295"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21"/>
-      <c r="B31" s="295" t="s">
-        <v>946</v>
-      </c>
-      <c r="C31" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E31" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G29</f>
-        <v>0.52</v>
-      </c>
-      <c r="F31" s="306" t="n">
-        <f aca="false">D31*E31</f>
-        <v>0.01923584</v>
-      </c>
-      <c r="G31" s="290" t="n">
-        <f aca="false">F31*SUMIF($B$68:$B$93,B31,$F$68:$F$93)</f>
-        <v>0.7825139712</v>
-      </c>
-      <c r="H31" s="149" t="s">
-        <v>1036</v>
-      </c>
+      <c r="A31" s="294" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B31" s="294"/>
+      <c r="C31" s="295" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D31" s="295"/>
+      <c r="E31" s="295"/>
+      <c r="F31" s="295"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="295"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21"/>
-      <c r="B32" s="295" t="s">
-        <v>947</v>
-      </c>
-      <c r="C32" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D32" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E32" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G30</f>
-        <v>0.53</v>
-      </c>
-      <c r="F32" s="306" t="n">
-        <f aca="false">D32*E32</f>
-        <v>0.01960576</v>
-      </c>
-      <c r="G32" s="290" t="n">
-        <f aca="false">F32*SUMIF($B$68:$B$93,B32,$F$68:$F$93)</f>
-        <v>1.9937097344</v>
-      </c>
-      <c r="H32" s="149" t="s">
-        <v>1036</v>
-      </c>
+      <c r="A32" s="294" t="s">
+        <v>502</v>
+      </c>
+      <c r="B32" s="294"/>
+      <c r="C32" s="295" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="295"/>
+      <c r="E32" s="295"/>
+      <c r="F32" s="295"/>
+      <c r="G32" s="295"/>
+      <c r="H32" s="295"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
-      <c r="B33" s="295" t="s">
-        <v>948</v>
-      </c>
-      <c r="C33" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E33" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G31</f>
-        <v>0.186</v>
-      </c>
-      <c r="F33" s="306" t="n">
-        <f aca="false">D33*E33</f>
-        <v>0.006880512</v>
-      </c>
-      <c r="G33" s="290" t="n">
-        <f aca="false">F33*SUMIF($B$68:$B$93,B33,$F$68:$F$93)</f>
-        <v>0.05731466496</v>
-      </c>
-      <c r="H33" s="149" t="s">
-        <v>1036</v>
-      </c>
+      <c r="A33" s="294" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B33" s="294"/>
+      <c r="C33" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E23</f>
+        <v>10.0</v>
+      </c>
+      <c r="D33" s="290"/>
+      <c r="E33" s="290"/>
+      <c r="F33" s="290"/>
+      <c r="G33" s="290"/>
+      <c r="H33" s="290"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21"/>
-      <c r="B34" s="295" t="s">
-        <v>949</v>
-      </c>
-      <c r="C34" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D34" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E34" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G32</f>
-        <v>0.8</v>
-      </c>
-      <c r="F34" s="306" t="n">
-        <f aca="false">D34*E34</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G34" s="290" t="n">
-        <f aca="false">F34*SUMIF($B$68:$B$93,B34,$F$68:$F$93)</f>
-        <v>0.376134656</v>
-      </c>
-      <c r="H34" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21"/>
-      <c r="B35" s="295" t="s">
-        <v>951</v>
-      </c>
-      <c r="C35" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D35" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E35" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G33</f>
-        <v>0.8</v>
-      </c>
-      <c r="F35" s="306" t="n">
-        <f aca="false">D35*E35</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G35" s="290" t="n">
-        <f aca="false">F35*SUMIF($B$68:$B$93,B35,$F$68:$F$93)</f>
-        <v>0.326121472</v>
-      </c>
-      <c r="H35" s="149" t="s">
-        <v>1036</v>
+      <c r="A34" s="294" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B34" s="294"/>
+      <c r="C34" s="290" t="n">
+        <f aca="false">8/E37</f>
+        <v>4.57855332366343</v>
+      </c>
+      <c r="D34" s="290"/>
+      <c r="E34" s="290"/>
+      <c r="F34" s="290"/>
+      <c r="G34" s="290"/>
+      <c r="H34" s="290"/>
+    </row>
+    <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="282" t="s">
+        <v>331</v>
+      </c>
+      <c r="B35" s="282" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C35" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="282" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E35" s="282" t="s">
+        <v>995</v>
+      </c>
+      <c r="F35" s="282" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G35" s="282" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H35" s="282" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21"/>
-      <c r="B36" s="295" t="s">
+      <c r="B36" s="294" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C36" s="294"/>
+      <c r="D36" s="294"/>
+      <c r="E36" s="294"/>
+      <c r="F36" s="294"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="283" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B37" s="295" t="s">
         <v>952</v>
-      </c>
-      <c r="C36" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D36" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E36" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G34</f>
-        <v>0.8</v>
-      </c>
-      <c r="F36" s="306" t="n">
-        <f aca="false">D36*E36</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="G36" s="290" t="n">
-        <f aca="false">F36*SUMIF($B$68:$B$93,B36,$F$68:$F$93)</f>
-        <v>0.85673472</v>
-      </c>
-      <c r="H36" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21"/>
-      <c r="B37" s="295" t="s">
-        <v>954</v>
       </c>
       <c r="C37" s="285" t="s">
         <v>953</v>
       </c>
       <c r="D37" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
+        <f aca="false">E37*$C$34/8</f>
+        <v>1.0</v>
       </c>
       <c r="E37" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G35</f>
-        <v>0.8</v>
-      </c>
-      <c r="F37" s="306" t="n">
-        <f aca="false">D37*E37</f>
-        <v>0.0295936</v>
+        <f aca="false">$D$12*$D$23+($D$15+$D$16+$D$17)*$D$25+$D$13*$D$26+$D$27</f>
+        <v>1.7472768</v>
+      </c>
+      <c r="F37" s="290" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
+        <v>28.95</v>
       </c>
       <c r="G37" s="290" t="n">
-        <f aca="false">F37*SUMIF($B$68:$B$93,B37,$F$68:$F$93)</f>
-        <v>0.671182848</v>
+        <f aca="false">E37*F37</f>
+        <v>50.58366336</v>
       </c>
       <c r="H37" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21"/>
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="283" t="n">
+        <v>2.0</v>
+      </c>
       <c r="B38" s="295" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C38" s="285" t="s">
         <v>953</v>
       </c>
       <c r="D38" s="306" t="n">
-        <f aca="false">F15</f>
-        <v>0.036992</v>
+        <f aca="false">E38*$C$34/8</f>
+        <v>0.427680834542071</v>
       </c>
       <c r="E38" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G36</f>
-        <v>6.4</v>
-      </c>
-      <c r="F38" s="306" t="n">
-        <f aca="false">D38*E38</f>
-        <v>0.2367488</v>
+        <f aca="false">$D$12*$D$23+($D$15+$D$16+$D$17)*$D$25+$D$13*$D$26</f>
+        <v>0.7472768</v>
+      </c>
+      <c r="F38" s="290" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$12</f>
+        <v>22.68</v>
       </c>
       <c r="G38" s="290" t="n">
-        <f aca="false">F38*SUMIF($B$68:$B$93,B38,$F$68:$F$93)</f>
-        <v>4.862820352</v>
+        <f aca="false">E38*F38</f>
+        <v>16.948237824</v>
       </c>
       <c r="H38" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21"/>
-      <c r="B39" s="294" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C39" s="295"/>
-      <c r="D39" s="295"/>
-      <c r="E39" s="295"/>
-      <c r="F39" s="295"/>
-      <c r="G39" s="296" t="n">
-        <f aca="false">SUM(G30:G38)</f>
-        <v>21.05923412736</v>
-      </c>
-      <c r="H39" s="295"/>
-    </row>
-    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="283" t="s">
-        <v>1038</v>
-      </c>
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B39" s="295" t="s">
+        <v>955</v>
+      </c>
+      <c r="C39" s="285" t="s">
+        <v>953</v>
+      </c>
+      <c r="D39" s="306" t="n">
+        <f aca="false">E39*$C$34/8</f>
+        <v>0.707815041097095</v>
+      </c>
+      <c r="E39" s="306" t="n">
+        <f aca="false">$D$12*$D$24+$D$27</f>
+        <v>1.2367488</v>
+      </c>
+      <c r="F39" s="290" t="n">
+        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
+        <v>20.54</v>
+      </c>
+      <c r="G39" s="290" t="n">
+        <f aca="false">E39*F39</f>
+        <v>25.402820352</v>
+      </c>
+      <c r="H39" s="149" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21"/>
       <c r="B40" s="294" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C40" s="294"/>
-      <c r="D40" s="294"/>
-      <c r="E40" s="294"/>
-      <c r="F40" s="294"/>
-      <c r="G40" s="294"/>
-      <c r="H40" s="294"/>
-    </row>
-    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1068</v>
+      </c>
+      <c r="C40" s="295"/>
+      <c r="D40" s="295"/>
+      <c r="E40" s="295"/>
+      <c r="F40" s="295"/>
+      <c r="G40" s="296" t="n">
+        <f aca="false">SUM(G37:G39)</f>
+        <v>92.934721536</v>
+      </c>
+      <c r="H40" s="295"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="21"/>
-      <c r="B41" s="295" t="s">
+      <c r="B41" s="294" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C41" s="294"/>
+      <c r="D41" s="294"/>
+      <c r="E41" s="294"/>
+      <c r="F41" s="294"/>
+      <c r="G41" s="294"/>
+      <c r="H41" s="294"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="283" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B42" s="295" t="s">
+        <v>944</v>
+      </c>
+      <c r="C42" s="285" t="s">
+        <v>945</v>
+      </c>
+      <c r="D42" s="295"/>
+      <c r="E42" s="306" t="n">
+        <f aca="false">$D$12*$D$19</f>
+        <v>0.35993216</v>
+      </c>
+      <c r="F42" s="289" t="n">
+        <v>30.93</v>
+      </c>
+      <c r="G42" s="290" t="n">
+        <f aca="false">E42*F42</f>
+        <v>11.1327017088</v>
+      </c>
+      <c r="H42" s="149" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="283" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B43" s="295" t="s">
+        <v>946</v>
+      </c>
+      <c r="C43" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="295"/>
+      <c r="E43" s="306" t="n">
+        <f aca="false">$D$12*$D$20</f>
+        <v>0.01923584</v>
+      </c>
+      <c r="F43" s="289" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="G43" s="290" t="n">
+        <f aca="false">E43*F43</f>
+        <v>0.7825139712</v>
+      </c>
+      <c r="H43" s="149" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="283" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B44" s="295" t="s">
+        <v>947</v>
+      </c>
+      <c r="C44" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" s="295"/>
+      <c r="E44" s="306" t="n">
+        <f aca="false">$D$12*$D$21</f>
+        <v>0.01960576</v>
+      </c>
+      <c r="F44" s="289" t="n">
+        <v>101.69</v>
+      </c>
+      <c r="G44" s="290" t="n">
+        <f aca="false">E44*F44</f>
+        <v>1.9937097344</v>
+      </c>
+      <c r="H44" s="149" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="283" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B45" s="295" t="s">
+        <v>948</v>
+      </c>
+      <c r="C45" s="285" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="295"/>
+      <c r="E45" s="306" t="n">
+        <f aca="false">$D$12*$D$22+0.01</f>
+        <v>0.016880512</v>
+      </c>
+      <c r="F45" s="289" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G45" s="290" t="n">
+        <f aca="false">E45*F45</f>
+        <v>0.14061466496</v>
+      </c>
+      <c r="H45" s="149" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="283" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B46" s="295" t="s">
         <v>959</v>
       </c>
-      <c r="C41" s="285" t="s">
+      <c r="C46" s="285" t="s">
         <v>960</v>
       </c>
-      <c r="D41" s="306" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E41" s="307" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F41" s="306" t="n">
-        <f aca="false">D41*E41</f>
-        <v>1.15</v>
-      </c>
-      <c r="G41" s="290" t="n">
-        <f aca="false">F41*SUMIF($B$68:$B$93,B41,$F$68:$F$93)</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H41" s="149" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21"/>
-      <c r="B42" s="294" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C42" s="295"/>
-      <c r="D42" s="295"/>
-      <c r="E42" s="295"/>
-      <c r="F42" s="295"/>
-      <c r="G42" s="296" t="n">
-        <f aca="false">SUM(G41:G41)</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H42" s="295"/>
-    </row>
-    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="283" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B43" s="294" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C43" s="294"/>
-      <c r="D43" s="294"/>
-      <c r="E43" s="294"/>
-      <c r="F43" s="294"/>
-      <c r="G43" s="294"/>
-      <c r="H43" s="294"/>
-    </row>
-    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21"/>
-      <c r="B44" s="295" t="s">
+      <c r="D46" s="295"/>
+      <c r="E46" s="306" t="n">
+        <f aca="false">$D$13*4.24/6+$D$14</f>
+        <v>1.30377066666667</v>
+      </c>
+      <c r="F46" s="289" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="G46" s="290" t="n">
+        <f aca="false">E46*F46</f>
+        <v>5.74962864</v>
+      </c>
+      <c r="H46" s="149" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="283" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B47" s="295" t="s">
         <v>1044</v>
       </c>
-      <c r="C44" s="285" t="s">
+      <c r="C47" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D44" s="306" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E44" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G42</f>
-        <v>1.05</v>
-      </c>
-      <c r="F44" s="306" t="n">
-        <f aca="false">D44*E44</f>
-        <v>18.20448</v>
-      </c>
-      <c r="G44" s="290" t="n">
-        <f aca="false">F44*SUMIF($B$68:$B$93,B44,$F$68:$F$93)</f>
-        <v>62.6234112</v>
-      </c>
-      <c r="H44" s="149" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21"/>
-      <c r="B45" s="295" t="s">
+      <c r="D47" s="295"/>
+      <c r="E47" s="306" t="n">
+        <f aca="false">($D$15+$D$16)*(1+$D$18)</f>
+        <v>16.79328</v>
+      </c>
+      <c r="F47" s="289" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G47" s="290" t="n">
+        <f aca="false">E47*F47</f>
+        <v>57.7688832</v>
+      </c>
+      <c r="H47" s="149" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="283" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B48" s="295" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C48" s="285" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="295"/>
+      <c r="E48" s="306" t="n">
+        <f aca="false">$D$17*(1+$D$18)</f>
+        <v>1.0437</v>
+      </c>
+      <c r="F48" s="289" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="G48" s="290" t="n">
+        <f aca="false">E48*F48</f>
+        <v>3.590328</v>
+      </c>
+      <c r="H48" s="149" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="283" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B49" s="295" t="s">
         <v>965</v>
       </c>
-      <c r="C45" s="285" t="s">
+      <c r="C49" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="306" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E45" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G43</f>
-        <v>0.06</v>
-      </c>
-      <c r="F45" s="306" t="n">
-        <f aca="false">D45*E45</f>
-        <v>1.040256</v>
-      </c>
-      <c r="G45" s="290" t="n">
-        <f aca="false">F45*SUMIF($B$68:$B$93,B45,$F$68:$F$93)</f>
-        <v>5.28450048</v>
-      </c>
-      <c r="H45" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21"/>
-      <c r="B46" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="C46" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D46" s="306" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E46" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G44</f>
-        <v>0.032</v>
-      </c>
-      <c r="F46" s="306" t="n">
-        <f aca="false">D46*E46</f>
-        <v>0.5548032</v>
-      </c>
-      <c r="G46" s="290" t="n">
-        <f aca="false">F46*SUMIF($B$68:$B$93,B46,$F$68:$F$93)</f>
-        <v>16.06155264</v>
-      </c>
-      <c r="H46" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21"/>
-      <c r="B47" s="295" t="s">
-        <v>954</v>
-      </c>
-      <c r="C47" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D47" s="306" t="n">
-        <f aca="false">F16</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E47" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G45</f>
-        <v>0.032</v>
-      </c>
-      <c r="F47" s="306" t="n">
-        <f aca="false">D47*E47</f>
-        <v>0.5548032</v>
-      </c>
-      <c r="G47" s="290" t="n">
-        <f aca="false">F47*SUMIF($B$68:$B$93,B47,$F$68:$F$93)</f>
-        <v>12.582936576</v>
-      </c>
-      <c r="H47" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21"/>
-      <c r="B48" s="294" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C48" s="295"/>
-      <c r="D48" s="295"/>
-      <c r="E48" s="295"/>
-      <c r="F48" s="295"/>
-      <c r="G48" s="296" t="n">
-        <f aca="false">SUM(G44:G47)</f>
-        <v>96.552400896</v>
-      </c>
-      <c r="H48" s="295"/>
-    </row>
-    <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="283" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B49" s="294" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C49" s="294"/>
-      <c r="D49" s="294"/>
-      <c r="E49" s="294"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="306" t="n">
+        <f aca="false">($D$15+$D$16+$D$17)*0.06</f>
+        <v>1.019256</v>
+      </c>
+      <c r="F49" s="289" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="G49" s="290" t="n">
+        <f aca="false">E49*F49</f>
+        <v>5.17782048</v>
+      </c>
+      <c r="H49" s="149" t="s">
+        <v>1213</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21"/>
-      <c r="B50" s="295" t="s">
-        <v>980</v>
-      </c>
-      <c r="C50" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D50" s="306" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E50" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G64</f>
-        <v>0.08</v>
-      </c>
-      <c r="F50" s="306" t="n">
-        <f aca="false">D50*E50</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="G50" s="290" t="n">
-        <f aca="false">F50*SUMIF($B$68:$B$93,B50,$F$68:$F$93)</f>
-        <v>3.015174144</v>
-      </c>
-      <c r="H50" s="149" t="s">
-        <v>1036</v>
-      </c>
+      <c r="B50" s="294" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C50" s="295"/>
+      <c r="D50" s="295"/>
+      <c r="E50" s="295"/>
+      <c r="F50" s="295"/>
+      <c r="G50" s="296" t="n">
+        <f aca="false">SUM(G42:G49)</f>
+        <v>86.33620039936</v>
+      </c>
+      <c r="H50" s="295"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21"/>
-      <c r="B51" s="295" t="s">
-        <v>982</v>
-      </c>
-      <c r="C51" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D51" s="306" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E51" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G65</f>
-        <v>0.08</v>
-      </c>
-      <c r="F51" s="306" t="n">
-        <f aca="false">D51*E51</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="G51" s="290" t="n">
-        <f aca="false">F51*SUMIF($B$68:$B$93,B51,$F$68:$F$93)</f>
-        <v>3.242721792</v>
-      </c>
-      <c r="H51" s="149" t="s">
-        <v>1036</v>
-      </c>
+      <c r="B51" s="294" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C51" s="294"/>
+      <c r="D51" s="294"/>
+      <c r="E51" s="294"/>
+      <c r="F51" s="294"/>
+      <c r="G51" s="294"/>
+      <c r="H51" s="294"/>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21"/>
+      <c r="A52" s="283" t="n">
+        <v>12.0</v>
+      </c>
       <c r="B52" s="295" t="s">
-        <v>1197</v>
+        <v>969</v>
       </c>
       <c r="C52" s="285" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" s="306" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E52" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G66</f>
-        <v>0.25</v>
-      </c>
-      <c r="F52" s="306" t="n">
-        <f aca="false">D52*E52</f>
-        <v>0.20976</v>
+        <v>970</v>
+      </c>
+      <c r="D52" s="295"/>
+      <c r="E52" s="284" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F52" s="290" t="n">
+        <f aca="false">+G40</f>
+        <v>92.934721536</v>
       </c>
       <c r="G52" s="290" t="n">
-        <f aca="false">F52*SUMIF($B$68:$B$93,B52,$F$68:$F$93)</f>
-        <v>0.4446912</v>
+        <f aca="false">E52*F52</f>
+        <v>2.78804164608</v>
       </c>
       <c r="H52" s="149" t="s">
-        <v>1203</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="21"/>
-      <c r="B53" s="295" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C53" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D53" s="306" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E53" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G67</f>
-        <v>0.024</v>
-      </c>
-      <c r="F53" s="306" t="n">
-        <f aca="false">D53*E53</f>
-        <v>0.02013696</v>
-      </c>
-      <c r="G53" s="290" t="n">
-        <f aca="false">F53*SUMIF($B$68:$B$93,B53,$F$68:$F$93)</f>
-        <v>0.717882624</v>
-      </c>
-      <c r="H53" s="149" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="21"/>
-      <c r="B54" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="C54" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D54" s="306" t="n">
-        <f aca="false">F17</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E54" s="306" t="n">
-        <f aca="false">+'COLECTOR INSUMOS'!G68</f>
-        <v>0.4</v>
-      </c>
-      <c r="F54" s="306" t="n">
-        <f aca="false">D54*E54</f>
-        <v>0.335616</v>
-      </c>
-      <c r="G54" s="290" t="n">
-        <f aca="false">F54*SUMIF($B$68:$B$93,B54,$F$68:$F$93)</f>
-        <v>9.7160832</v>
-      </c>
-      <c r="H54" s="149" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21"/>
-      <c r="B55" s="294" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C55" s="295"/>
-      <c r="D55" s="295"/>
-      <c r="E55" s="295"/>
-      <c r="F55" s="295"/>
+      <c r="B53" s="294" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C53" s="295"/>
+      <c r="D53" s="295"/>
+      <c r="E53" s="295"/>
+      <c r="F53" s="295"/>
+      <c r="G53" s="296" t="n">
+        <f aca="false">SUM(G52:G52)</f>
+        <v>2.78804164608</v>
+      </c>
+      <c r="H53" s="295"/>
+    </row>
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="294" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B54" s="294"/>
+      <c r="C54" s="294"/>
+      <c r="D54" s="294"/>
+      <c r="E54" s="294"/>
+      <c r="F54" s="294"/>
+      <c r="G54" s="296" t="n">
+        <f aca="false">+G40+G50+G53</f>
+        <v>182.05896358144</v>
+      </c>
+      <c r="H54" s="295"/>
+    </row>
+    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="294" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B55" s="294"/>
+      <c r="C55" s="294"/>
+      <c r="D55" s="294"/>
+      <c r="E55" s="294"/>
+      <c r="F55" s="294"/>
       <c r="G55" s="296" t="n">
-        <f aca="false">SUM(G50:G54)</f>
-        <v>17.13655296</v>
+        <f aca="false">G54*C33</f>
+        <v>1820.5896358144</v>
       </c>
       <c r="H55" s="295"/>
     </row>
-    <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="283" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B56" s="294" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C56" s="294"/>
-      <c r="D56" s="294"/>
-      <c r="E56" s="294"/>
-      <c r="F56" s="294"/>
-      <c r="G56" s="294"/>
-      <c r="H56" s="294"/>
-    </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="21"/>
-      <c r="B57" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="C57" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D57" s="306" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E57" s="307" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" s="306" t="n">
-        <f aca="false">D57*E57</f>
-        <v>1.0</v>
-      </c>
-      <c r="G57" s="290" t="n">
-        <f aca="false">F57*SUMIF($B$68:$B$93,B57,$F$68:$F$93)</f>
-        <v>28.95</v>
-      </c>
-      <c r="H57" s="149" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21"/>
-      <c r="B58" s="295" t="s">
-        <v>955</v>
-      </c>
-      <c r="C58" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D58" s="306" t="n">
-        <f aca="false">F14</f>
-        <v>1.0</v>
-      </c>
-      <c r="E58" s="307" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="306" t="n">
-        <f aca="false">D58*E58</f>
-        <v>1.0</v>
-      </c>
-      <c r="G58" s="290" t="n">
-        <f aca="false">F58*SUMIF($B$68:$B$93,B58,$F$68:$F$93)</f>
-        <v>20.54</v>
-      </c>
-      <c r="H58" s="149" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="21"/>
-      <c r="B59" s="294" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C59" s="295"/>
-      <c r="D59" s="295"/>
-      <c r="E59" s="295"/>
-      <c r="F59" s="295"/>
-      <c r="G59" s="296" t="n">
-        <f aca="false">SUM(G57:G58)</f>
-        <v>49.49</v>
-      </c>
-      <c r="H59" s="295"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="295"/>
-      <c r="B60" s="294" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C60" s="295"/>
-      <c r="D60" s="295"/>
-      <c r="E60" s="295"/>
-      <c r="F60" s="295"/>
-      <c r="G60" s="296" t="n">
-        <f aca="false">+G28+G39+G42+G48+G55+G59</f>
-        <v>287.85988742336</v>
-      </c>
-      <c r="H60" s="295"/>
-    </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="294" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B61" s="294"/>
-      <c r="C61" s="294"/>
-      <c r="D61" s="294"/>
-      <c r="E61" s="294"/>
-      <c r="F61" s="294"/>
-      <c r="G61" s="294"/>
-      <c r="H61" s="294"/>
-    </row>
-    <row r="62" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="294" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B62" s="294"/>
-      <c r="C62" s="295" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D62" s="295"/>
-      <c r="E62" s="295"/>
-      <c r="F62" s="295"/>
-      <c r="G62" s="295"/>
-      <c r="H62" s="295"/>
-    </row>
-    <row r="63" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="294" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B63" s="294"/>
-      <c r="C63" s="295" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D63" s="295"/>
-      <c r="E63" s="295"/>
-      <c r="F63" s="295"/>
-      <c r="G63" s="295"/>
-      <c r="H63" s="295"/>
-    </row>
-    <row r="64" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="294" t="s">
-        <v>502</v>
-      </c>
-      <c r="B64" s="294"/>
-      <c r="C64" s="295" t="s">
-        <v>60</v>
-      </c>
-      <c r="D64" s="295"/>
-      <c r="E64" s="295"/>
-      <c r="F64" s="295"/>
-      <c r="G64" s="295"/>
-      <c r="H64" s="295"/>
-    </row>
-    <row r="65" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="294" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B65" s="294"/>
-      <c r="C65" s="290" t="n">
-        <f aca="false">+E11</f>
-        <v>10.0</v>
-      </c>
-      <c r="D65" s="290"/>
-      <c r="E65" s="290"/>
-      <c r="F65" s="290"/>
-      <c r="G65" s="290"/>
-      <c r="H65" s="290"/>
-    </row>
-    <row r="66" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="294" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B66" s="294"/>
-      <c r="C66" s="290" t="n">
-        <f aca="false">8/E69</f>
-        <v>2.73021440919798</v>
-      </c>
-      <c r="D66" s="290"/>
-      <c r="E66" s="290"/>
-      <c r="F66" s="290"/>
-      <c r="G66" s="290"/>
-      <c r="H66" s="290"/>
-    </row>
-    <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="282" t="s">
-        <v>331</v>
-      </c>
-      <c r="B67" s="282" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C67" s="282" t="s">
-        <v>151</v>
-      </c>
-      <c r="D67" s="282" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E67" s="282" t="s">
-        <v>995</v>
-      </c>
-      <c r="F67" s="282" t="s">
-        <v>1064</v>
-      </c>
-      <c r="G67" s="282" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H67" s="282" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21"/>
-      <c r="B68" s="294" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C68" s="294"/>
-      <c r="D68" s="294"/>
-      <c r="E68" s="294"/>
-      <c r="F68" s="294"/>
-      <c r="G68" s="294"/>
-      <c r="H68" s="294"/>
-    </row>
-    <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="283" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="295" t="s">
-        <v>952</v>
-      </c>
-      <c r="C69" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D69" s="306" t="n">
-        <f aca="false">E69*$C$66/8</f>
-        <v>1.0</v>
-      </c>
-      <c r="E69" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B69,$F$21:$F$59)</f>
-        <v>2.9301728</v>
-      </c>
-      <c r="F69" s="289" t="n">
-        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$11</f>
-        <v>28.95</v>
-      </c>
-      <c r="G69" s="290" t="n">
-        <f aca="false">E69*F69</f>
-        <v>84.82850256</v>
-      </c>
-      <c r="H69" s="149" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="283" t="n">
-        <v>2</v>
-      </c>
-      <c r="B70" s="295" t="s">
-        <v>954</v>
-      </c>
-      <c r="C70" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D70" s="306" t="n">
-        <f aca="false">E70*$C$66/8</f>
-        <v>0.544185243955578</v>
-      </c>
-      <c r="E70" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B70,$F$21:$F$59)</f>
-        <v>1.5945568</v>
-      </c>
-      <c r="F70" s="289" t="n">
-        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$12</f>
-        <v>22.68</v>
-      </c>
-      <c r="G70" s="290" t="n">
-        <f aca="false">E70*F70</f>
-        <v>36.164548224</v>
-      </c>
-      <c r="H70" s="149" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="283" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="295" t="s">
-        <v>955</v>
-      </c>
-      <c r="C71" s="285" t="s">
-        <v>953</v>
-      </c>
-      <c r="D71" s="306" t="n">
-        <f aca="false">E71*$C$66/8</f>
-        <v>0.422073674289789</v>
-      </c>
-      <c r="E71" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B71,$F$21:$F$59)</f>
-        <v>1.2367488</v>
-      </c>
-      <c r="F71" s="289" t="n">
-        <f aca="false">'COSTO HORA HOMBRE 2026'!$G$13</f>
-        <v>20.54</v>
-      </c>
-      <c r="G71" s="290" t="n">
-        <f aca="false">E71*F71</f>
-        <v>25.402820352</v>
-      </c>
-      <c r="H71" s="149" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21"/>
-      <c r="B72" s="294" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C72" s="295"/>
-      <c r="D72" s="295"/>
-      <c r="E72" s="295"/>
-      <c r="F72" s="295"/>
-      <c r="G72" s="296" t="n">
-        <f aca="false">SUM(G69:G71)</f>
-        <v>146.395871136</v>
-      </c>
-      <c r="H72" s="295"/>
-    </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21"/>
-      <c r="B73" s="294" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C73" s="294"/>
-      <c r="D73" s="294"/>
-      <c r="E73" s="294"/>
-      <c r="F73" s="294"/>
-      <c r="G73" s="294"/>
-      <c r="H73" s="294"/>
-    </row>
-    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="283" t="n">
-        <v>4</v>
-      </c>
-      <c r="B74" s="295" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C74" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" s="295"/>
-      <c r="E74" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B74,$F$21:$F$59)</f>
-        <v>10.60668</v>
-      </c>
-      <c r="F74" s="289" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="G74" s="290" t="n">
-        <f aca="false">E74*F74</f>
-        <v>32.6685744</v>
-      </c>
-      <c r="H74" s="149" t="s">
-        <v>1205</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="283" t="n">
-        <v>5</v>
-      </c>
-      <c r="B75" s="295" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C75" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="295"/>
-      <c r="E75" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B75,$F$21:$F$59)</f>
-        <v>0.303048</v>
-      </c>
-      <c r="F75" s="289" t="n">
-        <v>18.63</v>
-      </c>
-      <c r="G75" s="290" t="n">
-        <f aca="false">E75*F75</f>
-        <v>5.64578424</v>
-      </c>
-      <c r="H75" s="149" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="283" t="n">
-        <v>6</v>
-      </c>
-      <c r="B76" s="295" t="s">
-        <v>944</v>
-      </c>
-      <c r="C76" s="285" t="s">
-        <v>945</v>
-      </c>
-      <c r="D76" s="295"/>
-      <c r="E76" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B76,$F$21:$F$59)</f>
-        <v>0.35993216</v>
-      </c>
-      <c r="F76" s="289" t="n">
-        <v>30.93</v>
-      </c>
-      <c r="G76" s="290" t="n">
-        <f aca="false">E76*F76</f>
-        <v>11.1327017088</v>
-      </c>
-      <c r="H76" s="149" t="s">
-        <v>1207</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="283" t="n">
-        <v>7</v>
-      </c>
-      <c r="B77" s="295" t="s">
-        <v>946</v>
-      </c>
-      <c r="C77" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D77" s="295"/>
-      <c r="E77" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B77,$F$21:$F$59)</f>
-        <v>0.01923584</v>
-      </c>
-      <c r="F77" s="289" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="G77" s="290" t="n">
-        <f aca="false">E77*F77</f>
-        <v>0.7825139712</v>
-      </c>
-      <c r="H77" s="149" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="283" t="n">
-        <v>8</v>
-      </c>
-      <c r="B78" s="295" t="s">
-        <v>947</v>
-      </c>
-      <c r="C78" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D78" s="295"/>
-      <c r="E78" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B78,$F$21:$F$59)</f>
-        <v>0.01960576</v>
-      </c>
-      <c r="F78" s="289" t="n">
-        <v>101.69</v>
-      </c>
-      <c r="G78" s="290" t="n">
-        <f aca="false">E78*F78</f>
-        <v>1.9937097344</v>
-      </c>
-      <c r="H78" s="149" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="283" t="n">
-        <v>9</v>
-      </c>
-      <c r="B79" s="295" t="s">
-        <v>948</v>
-      </c>
-      <c r="C79" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D79" s="295"/>
-      <c r="E79" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B79,$F$21:$F$59)</f>
-        <v>0.006880512</v>
-      </c>
-      <c r="F79" s="289" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="G79" s="290" t="n">
-        <f aca="false">E79*F79</f>
-        <v>0.05731466496</v>
-      </c>
-      <c r="H79" s="149" t="s">
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="283" t="n">
-        <v>10</v>
-      </c>
-      <c r="B80" s="295" t="s">
-        <v>959</v>
-      </c>
-      <c r="C80" s="285" t="s">
-        <v>960</v>
-      </c>
-      <c r="D80" s="295"/>
-      <c r="E80" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B80,$F$21:$F$59)</f>
-        <v>1.15</v>
-      </c>
-      <c r="F80" s="289" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="G80" s="290" t="n">
-        <f aca="false">E80*F80</f>
-        <v>5.0715</v>
-      </c>
-      <c r="H80" s="149" t="s">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="283" t="n">
-        <v>11</v>
-      </c>
-      <c r="B81" s="295" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C81" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="295"/>
-      <c r="E81" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B81,$F$21:$F$59)</f>
-        <v>18.20448</v>
-      </c>
-      <c r="F81" s="289" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="G81" s="290" t="n">
-        <f aca="false">E81*F81</f>
-        <v>62.6234112</v>
-      </c>
-      <c r="H81" s="149" t="s">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="283" t="n">
-        <v>12</v>
-      </c>
-      <c r="B82" s="295" t="s">
-        <v>965</v>
-      </c>
-      <c r="C82" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="295"/>
-      <c r="E82" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B82,$F$21:$F$59)</f>
-        <v>1.040256</v>
-      </c>
-      <c r="F82" s="289" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="G82" s="290" t="n">
-        <f aca="false">E82*F82</f>
-        <v>5.28450048</v>
-      </c>
-      <c r="H82" s="149" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="283" t="n">
-        <v>13</v>
-      </c>
-      <c r="B83" s="295" t="s">
-        <v>980</v>
-      </c>
-      <c r="C83" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D83" s="295"/>
-      <c r="E83" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B83,$F$21:$F$59)</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="F83" s="289" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="G83" s="290" t="n">
-        <f aca="false">E83*F83</f>
-        <v>3.015174144</v>
-      </c>
-      <c r="H83" s="149" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="283" t="n">
-        <v>14</v>
-      </c>
-      <c r="B84" s="295" t="s">
-        <v>982</v>
-      </c>
-      <c r="C84" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D84" s="295"/>
-      <c r="E84" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B84,$F$21:$F$59)</f>
-        <v>0.0671232</v>
-      </c>
-      <c r="F84" s="289" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="G84" s="290" t="n">
-        <f aca="false">E84*F84</f>
-        <v>3.242721792</v>
-      </c>
-      <c r="H84" s="149" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="283" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="295" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C85" s="285" t="s">
-        <v>60</v>
-      </c>
-      <c r="D85" s="295"/>
-      <c r="E85" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B85,$F$21:$F$59)</f>
-        <v>0.20976</v>
-      </c>
-      <c r="F85" s="289" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="G85" s="290" t="n">
-        <f aca="false">E85*F85</f>
-        <v>0.4446912</v>
-      </c>
-      <c r="H85" s="149" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="283" t="n">
-        <v>16</v>
-      </c>
-      <c r="B86" s="295" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C86" s="285" t="s">
-        <v>981</v>
-      </c>
-      <c r="D86" s="295"/>
-      <c r="E86" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B86,$F$21:$F$59)</f>
-        <v>0.02013696</v>
-      </c>
-      <c r="F86" s="289" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="G86" s="290" t="n">
-        <f aca="false">E86*F86</f>
-        <v>0.717882624</v>
-      </c>
-      <c r="H86" s="149" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21"/>
-      <c r="B87" s="294" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C87" s="295"/>
-      <c r="D87" s="295"/>
-      <c r="E87" s="295"/>
-      <c r="F87" s="295"/>
-      <c r="G87" s="296" t="n">
-        <f aca="false">SUM(G74:G86)</f>
-        <v>132.68048015936</v>
-      </c>
-      <c r="H87" s="295"/>
-    </row>
-    <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="21"/>
-      <c r="B88" s="294" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C88" s="294"/>
-      <c r="D88" s="294"/>
-      <c r="E88" s="294"/>
-      <c r="F88" s="294"/>
-      <c r="G88" s="294"/>
-      <c r="H88" s="294"/>
-    </row>
-    <row r="89" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="283" t="n">
-        <v>17</v>
-      </c>
-      <c r="B89" s="295" t="s">
-        <v>969</v>
-      </c>
-      <c r="C89" s="285" t="s">
-        <v>970</v>
-      </c>
-      <c r="D89" s="295"/>
-      <c r="E89" s="284" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F89" s="290" t="n">
-        <f aca="false">+G72</f>
-        <v>146.395871136</v>
-      </c>
-      <c r="G89" s="290" t="n">
-        <f aca="false">E89*F89</f>
-        <v>4.39187613408</v>
-      </c>
-      <c r="H89" s="149" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="283" t="n">
-        <v>18</v>
-      </c>
-      <c r="B90" s="295" t="s">
-        <v>949</v>
-      </c>
-      <c r="C90" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D90" s="306" t="n">
-        <f aca="false">E90*$C$66/8</f>
-        <v>0.0100996091425052</v>
-      </c>
-      <c r="E90" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B90,$F$21:$F$59)</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="F90" s="289" t="n">
-        <v>12.71</v>
-      </c>
-      <c r="G90" s="290" t="n">
-        <f aca="false">E90*F90</f>
-        <v>0.376134656</v>
-      </c>
-      <c r="H90" s="149" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="283" t="n">
-        <v>19</v>
-      </c>
-      <c r="B91" s="295" t="s">
-        <v>951</v>
-      </c>
-      <c r="C91" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D91" s="306" t="n">
-        <f aca="false">E91*$C$66/8</f>
-        <v>0.0100996091425052</v>
-      </c>
-      <c r="E91" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B91,$F$21:$F$59)</f>
-        <v>0.0295936</v>
-      </c>
-      <c r="F91" s="289" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="G91" s="290" t="n">
-        <f aca="false">E91*F91</f>
-        <v>0.326121472</v>
-      </c>
-      <c r="H91" s="149" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="283" t="n">
-        <v>20</v>
-      </c>
-      <c r="B92" s="295" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C92" s="285" t="s">
-        <v>950</v>
-      </c>
-      <c r="D92" s="306" t="n">
-        <f aca="false">E92*$C$66/8</f>
-        <v>0.344744173449429</v>
-      </c>
-      <c r="E92" s="306" t="n">
-        <f aca="false">SUMIF($B$21:$B$59,B92,$F$21:$F$59)</f>
-        <v>1.01016</v>
-      </c>
-      <c r="F92" s="289" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="G92" s="290" t="n">
-        <f aca="false">E92*F92</f>
-        <v>8.08128</v>
-      </c>
-      <c r="H92" s="149" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="21"/>
-      <c r="B93" s="294" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C93" s="295"/>
-      <c r="D93" s="295"/>
-      <c r="E93" s="295"/>
-      <c r="F93" s="295"/>
-      <c r="G93" s="296" t="n">
-        <f aca="false">SUM(G89:G92)</f>
-        <v>13.17541226208</v>
-      </c>
-      <c r="H93" s="295"/>
-    </row>
-    <row r="94" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="294" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B94" s="294"/>
-      <c r="C94" s="294"/>
-      <c r="D94" s="294"/>
-      <c r="E94" s="294"/>
-      <c r="F94" s="294"/>
-      <c r="G94" s="296" t="n">
-        <f aca="false">+G72+G87+G93</f>
-        <v>292.25176355744</v>
-      </c>
-      <c r="H94" s="295"/>
-    </row>
-    <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="294" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B95" s="294"/>
-      <c r="C95" s="294"/>
-      <c r="D95" s="294"/>
-      <c r="E95" s="294"/>
-      <c r="F95" s="294"/>
-      <c r="G95" s="296" t="n">
-        <f aca="false">G94*C65</f>
-        <v>2922.5176355744</v>
-      </c>
-      <c r="H95" s="295"/>
-    </row>
-    <row r="96" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="295" t="s">
-        <v>1078</v>
-      </c>
-      <c r="B96" s="295"/>
-      <c r="C96" s="295"/>
-      <c r="D96" s="295"/>
-      <c r="E96" s="295"/>
-      <c r="F96" s="295"/>
-      <c r="G96" s="283" t="str">
-        <f aca="false">IF(ABS(G60+G89-G94)&lt;0.005,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-      <c r="H96" s="295"/>
-    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="27">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
@@ -30015,30 +29164,22 @@
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B43:H43"/>
-    <mergeCell ref="B49:H49"/>
-    <mergeCell ref="B56:H56"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:H62"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:H63"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:H64"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:H65"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:H66"/>
-    <mergeCell ref="B68:H68"/>
-    <mergeCell ref="B73:H73"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A55:F55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -32066,7 +31207,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -32076,9 +31217,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="277" t="s">
-        <v>1145</v>
+        <v>1553</v>
       </c>
       <c r="B1" s="277"/>
       <c r="C1" s="277"/>
@@ -32086,6 +31227,7 @@
       <c r="E1" s="277"/>
       <c r="F1" s="277"/>
       <c r="G1" s="277"/>
+      <c r="H1" s="277"/>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="278" t="s">
@@ -32143,9 +31285,9 @@
       <c r="F5" s="280"/>
       <c r="G5" s="280"/>
     </row>
-    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="281" t="s">
-        <v>1146</v>
+        <v>1554</v>
       </c>
       <c r="B7" s="281"/>
       <c r="C7" s="281"/>
@@ -32153,6 +31295,7 @@
       <c r="E7" s="281"/>
       <c r="F7" s="281"/>
       <c r="G7" s="281"/>
+      <c r="H7" s="281"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="294" t="s">
@@ -32164,8 +31307,9 @@
       <c r="E9" s="294"/>
       <c r="F9" s="294"/>
       <c r="G9" s="294"/>
-    </row>
-    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H9" s="294"/>
+    </row>
+    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="282" t="s">
         <v>331</v>
       </c>
@@ -32185,16 +31329,17 @@
       <c r="G10" s="282" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H10" s="282"/>
+    </row>
+    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="283" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="283" t="str">
+        <v>1.0</v>
+      </c>
+      <c r="B11" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B10</f>
         <v>CL</v>
       </c>
-      <c r="C11" s="283" t="str">
+      <c r="C11" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C10</f>
         <v>0+000.00</v>
       </c>
@@ -32202,25 +31347,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D10</f>
         <v>Caja de llegada (empalme con CAR Varones y cuneta Eje 01)</v>
       </c>
-      <c r="E11" s="149"/>
+      <c r="E11" s="295"/>
       <c r="F11" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E10</f>
         <v>1.0</v>
       </c>
-      <c r="G11" s="283" t="str">
+      <c r="G11" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F10</f>
         <v>DP-07</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H11" s="295"/>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="283" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="283" t="str">
+        <v>2.0</v>
+      </c>
+      <c r="B12" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B11</f>
         <v>RS-01</v>
       </c>
-      <c r="C12" s="283" t="str">
+      <c r="C12" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C11</f>
         <v>0+011.27</v>
       </c>
@@ -32228,25 +31374,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D11</f>
         <v>Registro en la losa del colector; empalme cuneta</v>
       </c>
-      <c r="E12" s="149"/>
+      <c r="E12" s="295"/>
       <c r="F12" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E11</f>
         <v>1.0</v>
       </c>
-      <c r="G12" s="283" t="str">
+      <c r="G12" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F11</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H12" s="295"/>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="283" t="n">
-        <v>3</v>
-      </c>
-      <c r="B13" s="283" t="str">
+        <v>3.0</v>
+      </c>
+      <c r="B13" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B12</f>
         <v>RS-02</v>
       </c>
-      <c r="C13" s="283" t="str">
+      <c r="C13" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C12</f>
         <v>0+022.00</v>
       </c>
@@ -32254,25 +31401,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D12</f>
         <v>Registro en la losa del colector; limpieza / quiebre</v>
       </c>
-      <c r="E13" s="149"/>
+      <c r="E13" s="295"/>
       <c r="F13" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E12</f>
         <v>1.0</v>
       </c>
-      <c r="G13" s="283" t="str">
+      <c r="G13" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F12</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H13" s="295"/>
+    </row>
+    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="283" t="n">
-        <v>4</v>
-      </c>
-      <c r="B14" s="283" t="str">
+        <v>4.0</v>
+      </c>
+      <c r="B14" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B13</f>
         <v>RS-03</v>
       </c>
-      <c r="C14" s="283" t="str">
+      <c r="C14" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C13</f>
         <v>0+032.50</v>
       </c>
@@ -32280,25 +31428,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D13</f>
         <v>Registro en la losa del colector; empalme cuneta</v>
       </c>
-      <c r="E14" s="149"/>
+      <c r="E14" s="295"/>
       <c r="F14" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E13</f>
         <v>1.0</v>
       </c>
-      <c r="G14" s="283" t="str">
+      <c r="G14" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F13</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H14" s="295"/>
+    </row>
+    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="283" t="n">
-        <v>5</v>
-      </c>
-      <c r="B15" s="283" t="str">
+        <v>5.0</v>
+      </c>
+      <c r="B15" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B14</f>
         <v>RS-04</v>
       </c>
-      <c r="C15" s="283" t="str">
+      <c r="C15" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C14</f>
         <v>0+042.68</v>
       </c>
@@ -32306,25 +31455,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D14</f>
         <v>Registro en la losa del colector; empalme cuneta</v>
       </c>
-      <c r="E15" s="149"/>
+      <c r="E15" s="295"/>
       <c r="F15" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E14</f>
         <v>1.0</v>
       </c>
-      <c r="G15" s="283" t="str">
+      <c r="G15" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F14</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H15" s="295"/>
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="283" t="n">
-        <v>6</v>
-      </c>
-      <c r="B16" s="283" t="str">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B15</f>
         <v>RS-05</v>
       </c>
-      <c r="C16" s="283" t="str">
+      <c r="C16" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C15</f>
         <v>0+052.00</v>
       </c>
@@ -32332,25 +31482,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D15</f>
         <v>Registro en la losa del colector; limpieza / quiebre</v>
       </c>
-      <c r="E16" s="149"/>
+      <c r="E16" s="295"/>
       <c r="F16" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E15</f>
         <v>1.0</v>
       </c>
-      <c r="G16" s="283" t="str">
+      <c r="G16" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F15</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H16" s="295"/>
+    </row>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="283" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="283" t="str">
+        <v>7.0</v>
+      </c>
+      <c r="B17" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B16</f>
         <v>RS-06</v>
       </c>
-      <c r="C17" s="283" t="str">
+      <c r="C17" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C16</f>
         <v>0+058.81</v>
       </c>
@@ -32358,25 +31509,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D16</f>
         <v>Registro en la losa del colector; limpieza / quiebre</v>
       </c>
-      <c r="E17" s="149"/>
+      <c r="E17" s="295"/>
       <c r="F17" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E16</f>
         <v>1.0</v>
       </c>
-      <c r="G17" s="283" t="str">
+      <c r="G17" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F16</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H17" s="295"/>
+    </row>
+    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="283" t="n">
-        <v>8</v>
-      </c>
-      <c r="B18" s="283" t="str">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B17</f>
         <v>RS-07</v>
       </c>
-      <c r="C18" s="283" t="str">
+      <c r="C18" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C17</f>
         <v>0+066.89</v>
       </c>
@@ -32384,25 +31536,26 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D17</f>
         <v>Registro en la losa del colector; limpieza / quiebre</v>
       </c>
-      <c r="E18" s="149"/>
+      <c r="E18" s="295"/>
       <c r="F18" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E17</f>
         <v>1.0</v>
       </c>
-      <c r="G18" s="283" t="str">
+      <c r="G18" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F17</f>
         <v>DP-01, DP-06B</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="295"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="283" t="n">
-        <v>9</v>
-      </c>
-      <c r="B19" s="283" t="str">
+        <v>9.0</v>
+      </c>
+      <c r="B19" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!B18</f>
         <v>CC (2)</v>
       </c>
-      <c r="C19" s="283" t="str">
+      <c r="C19" s="295" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!C18</f>
         <v>0+069.89</v>
       </c>
@@ -32410,18 +31563,19 @@
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!D18</f>
         <v>Caja de caida: dos registros sobre la poza</v>
       </c>
-      <c r="E19" s="149"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="290" t="n">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E18</f>
         <v>2.0</v>
       </c>
-      <c r="G19" s="283" t="str">
+      <c r="G19" s="149" t="str">
         <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!F18</f>
         <v>DP-07</v>
       </c>
+      <c r="H19" s="295"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="295"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="294" t="s">
         <v>1149</v>
       </c>
@@ -32433,6 +31587,7 @@
         <v>10.0</v>
       </c>
       <c r="G20" s="295"/>
+      <c r="H20" s="295"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="294" t="s">
@@ -32444,8 +31599,9 @@
       <c r="E22" s="294"/>
       <c r="F22" s="294"/>
       <c r="G22" s="294"/>
-    </row>
-    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H22" s="294"/>
+    </row>
+    <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="282" t="s">
         <v>331</v>
       </c>
@@ -32467,482 +31623,371 @@
       <c r="G23" s="282" t="s">
         <v>657</v>
       </c>
+      <c r="H23" s="282"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21"/>
       <c r="B24" s="294" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="C24" s="294"/>
       <c r="D24" s="294"/>
       <c r="E24" s="294"/>
       <c r="F24" s="294"/>
       <c r="G24" s="294"/>
-    </row>
-    <row r="25" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H24" s="294"/>
+    </row>
+    <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="283" t="n">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="B25" s="149" t="s">
-        <v>1193</v>
+        <v>1555</v>
       </c>
       <c r="C25" s="285" t="s">
-        <v>50</v>
+        <v>167</v>
       </c>
       <c r="D25" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C38</f>
-        <v>5.124</v>
-      </c>
-      <c r="E25" s="301" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$33^2*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E25" s="290" t="n">
         <f aca="false">+$F$20</f>
         <v>10.0</v>
       </c>
-      <c r="F25" s="306" t="n">
+      <c r="F25" s="290" t="n">
         <f aca="false">D25*E25</f>
-        <v>51.24</v>
+        <v>0.36992</v>
       </c>
       <c r="G25" s="149" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="283" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="149" t="s">
-        <v>1156</v>
+        <v>1556</v>
+      </c>
+      <c r="H25" s="295"/>
+    </row>
+    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21"/>
+      <c r="B26" s="294" t="s">
+        <v>1162</v>
       </c>
       <c r="C26" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C37*'COLECTOR PARAMETROS'!C39</f>
-        <v>4.9776</v>
-      </c>
-      <c r="E26" s="301" t="n">
-        <f aca="false">+$F$20</f>
-        <v>10.0</v>
-      </c>
-      <c r="F26" s="306" t="n">
-        <f aca="false">D26*E26</f>
-        <v>49.776</v>
-      </c>
-      <c r="G26" s="149" t="s">
-        <v>1157</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D26" s="290" t="n">
+        <f aca="false">SUM(D25:D25)</f>
+        <v>0.036992</v>
+      </c>
+      <c r="E26" s="295"/>
+      <c r="F26" s="296" t="n">
+        <f aca="false">SUM(F25:F25)</f>
+        <v>0.36992</v>
+      </c>
+      <c r="G26" s="295"/>
+      <c r="H26" s="295"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21"/>
       <c r="B27" s="294" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C27" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="308" t="n">
-        <f aca="false">SUM(D25:D26)</f>
-        <v>10.1016</v>
-      </c>
-      <c r="E27" s="295"/>
-      <c r="F27" s="296" t="n">
-        <f aca="false">SUM(F25:F26)</f>
-        <v>101.016</v>
-      </c>
-      <c r="G27" s="295"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="294" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C28" s="294"/>
-      <c r="D28" s="294"/>
-      <c r="E28" s="294"/>
-      <c r="F28" s="294"/>
-      <c r="G28" s="294"/>
-    </row>
-    <row r="29" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="283" t="n">
-        <v>3</v>
-      </c>
-      <c r="B29" s="149" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C29" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D29" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C33*'COLECTOR PARAMETROS'!C33*'COLECTOR PARAMETROS'!C34</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E29" s="301" t="n">
+        <v>1557</v>
+      </c>
+      <c r="C27" s="294"/>
+      <c r="D27" s="294"/>
+      <c r="E27" s="294"/>
+      <c r="F27" s="294"/>
+      <c r="G27" s="294"/>
+      <c r="H27" s="294"/>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="283" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C28" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="306" t="n">
+        <f aca="false">'COLECTOR PARAMETROS'!$C$37*'COLECTOR PARAMETROS'!$C$34</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E28" s="290" t="n">
         <f aca="false">+$F$20</f>
         <v>10.0</v>
       </c>
-      <c r="F29" s="306" t="n">
-        <f aca="false">D29*E29</f>
-        <v>0.36992</v>
-      </c>
-      <c r="G29" s="149" t="s">
-        <v>1161</v>
-      </c>
+      <c r="F28" s="290" t="n">
+        <f aca="false">D28*E28</f>
+        <v>2.176</v>
+      </c>
+      <c r="G28" s="149" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H28" s="295"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="294" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C29" s="285" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="290" t="n">
+        <f aca="false">SUM(D28:D28)</f>
+        <v>0.2176</v>
+      </c>
+      <c r="E29" s="295"/>
+      <c r="F29" s="296" t="n">
+        <f aca="false">SUM(F28:F28)</f>
+        <v>2.176</v>
+      </c>
+      <c r="G29" s="295"/>
+      <c r="H29" s="295"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21"/>
       <c r="B30" s="294" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C30" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="308" t="n">
-        <f aca="false">SUM(D29:D29)</f>
-        <v>0.036992</v>
-      </c>
-      <c r="E30" s="295"/>
-      <c r="F30" s="296" t="n">
-        <f aca="false">SUM(F29:F29)</f>
-        <v>0.36992</v>
-      </c>
-      <c r="G30" s="295"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21"/>
-      <c r="B31" s="294" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C31" s="294"/>
-      <c r="D31" s="294"/>
-      <c r="E31" s="294"/>
-      <c r="F31" s="294"/>
-      <c r="G31" s="294"/>
-    </row>
-    <row r="32" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1560</v>
+      </c>
+      <c r="C30" s="294"/>
+      <c r="D30" s="294"/>
+      <c r="E30" s="294"/>
+      <c r="F30" s="294"/>
+      <c r="G30" s="294"/>
+      <c r="H30" s="294"/>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="283" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B31" s="149" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C31" s="285" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="306" t="n">
+        <f aca="false">'COLECTOR ACERO'!U34/'COLECTOR ACERO'!F34</f>
+        <v>4.8608</v>
+      </c>
+      <c r="E31" s="290" t="n">
+        <f aca="false">+$F$20</f>
+        <v>10.0</v>
+      </c>
+      <c r="F31" s="290" t="n">
+        <f aca="false">D31*E31</f>
+        <v>48.608</v>
+      </c>
+      <c r="G31" s="149" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H31" s="295"/>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="283" t="n">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B32" s="149" t="s">
-        <v>1164</v>
+        <v>1561</v>
       </c>
       <c r="C32" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D32" s="306" t="n">
-        <f aca="false">'COLECTOR ACERO'!U34/'COLECTOR ACERO'!F34</f>
-        <v>4.8608</v>
-      </c>
-      <c r="E32" s="301" t="n">
+        <f aca="false">'COLECTOR ACERO'!U35/'COLECTOR ACERO'!F35</f>
+        <v>0.994</v>
+      </c>
+      <c r="E32" s="290" t="n">
         <f aca="false">+$F$20</f>
         <v>10.0</v>
       </c>
-      <c r="F32" s="306" t="n">
+      <c r="F32" s="290" t="n">
         <f aca="false">D32*E32</f>
-        <v>48.608</v>
+        <v>9.94</v>
       </c>
       <c r="G32" s="149" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1167</v>
+      </c>
+      <c r="H32" s="295"/>
+    </row>
+    <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="283" t="n">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B33" s="149" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="C33" s="285" t="s">
         <v>50</v>
       </c>
       <c r="D33" s="306" t="n">
-        <f aca="false">'COLECTOR ACERO'!U35/'COLECTOR ACERO'!F35</f>
-        <v>0.448</v>
-      </c>
-      <c r="E33" s="301" t="n">
+        <f aca="false">'COLECTOR ACERO'!U33/'COLECTOR ACERO'!F33</f>
+        <v>11.1328</v>
+      </c>
+      <c r="E33" s="290" t="n">
         <f aca="false">+$F$20</f>
         <v>10.0</v>
       </c>
-      <c r="F33" s="306" t="n">
+      <c r="F33" s="290" t="n">
         <f aca="false">D33*E33</f>
-        <v>4.48</v>
+        <v>111.328</v>
       </c>
       <c r="G33" s="149" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="283" t="n">
-        <v>6</v>
-      </c>
-      <c r="B34" s="149" t="s">
-        <v>1168</v>
+        <v>1171</v>
+      </c>
+      <c r="H33" s="295"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21"/>
+      <c r="B34" s="294" t="s">
+        <v>1562</v>
       </c>
       <c r="C34" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D34" s="306" t="n">
-        <f aca="false">'COLECTOR ACERO'!U36/'COLECTOR ACERO'!F36</f>
-        <v>0.896</v>
-      </c>
-      <c r="E34" s="301" t="n">
-        <f aca="false">+$F$20</f>
-        <v>10.0</v>
-      </c>
-      <c r="F34" s="306" t="n">
-        <f aca="false">D34*E34</f>
-        <v>8.96</v>
-      </c>
-      <c r="G34" s="149" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="283" t="n">
-        <v>7</v>
-      </c>
-      <c r="B35" s="149" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C35" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="306" t="n">
-        <f aca="false">'COLECTOR ACERO'!U33/'COLECTOR ACERO'!F33</f>
-        <v>11.1328</v>
-      </c>
-      <c r="E35" s="301" t="n">
-        <f aca="false">+$F$20</f>
-        <v>10.0</v>
-      </c>
-      <c r="F35" s="306" t="n">
-        <f aca="false">D35*E35</f>
-        <v>111.328</v>
-      </c>
-      <c r="G35" s="149" t="s">
-        <v>1171</v>
-      </c>
+      <c r="D34" s="290" t="n">
+        <f aca="false">SUM(D31:D33)</f>
+        <v>16.9876</v>
+      </c>
+      <c r="E34" s="295"/>
+      <c r="F34" s="296" t="n">
+        <f aca="false">SUM(F31:F33)</f>
+        <v>169.876</v>
+      </c>
+      <c r="G34" s="295"/>
+      <c r="H34" s="295"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21"/>
-      <c r="B36" s="294" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C36" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="308" t="n">
-        <f aca="false">SUM(D32:D35)</f>
-        <v>17.3376</v>
-      </c>
-      <c r="E36" s="295"/>
-      <c r="F36" s="296" t="n">
-        <f aca="false">SUM(F32:F35)</f>
-        <v>173.376</v>
-      </c>
-      <c r="G36" s="295"/>
-    </row>
-    <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21"/>
-      <c r="B37" s="294" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C37" s="294"/>
-      <c r="D37" s="294"/>
-      <c r="E37" s="294"/>
-      <c r="F37" s="294"/>
-      <c r="G37" s="294"/>
-    </row>
-    <row r="38" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="283" t="n">
-        <v>8</v>
-      </c>
+      <c r="A36" s="294" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B36" s="294"/>
+      <c r="C36" s="294"/>
+      <c r="D36" s="294"/>
+      <c r="E36" s="294"/>
+      <c r="F36" s="294"/>
+      <c r="G36" s="294"/>
+      <c r="H36" s="294"/>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="282"/>
+      <c r="B37" s="282" t="s">
+        <v>992</v>
+      </c>
+      <c r="C37" s="282" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" s="282"/>
+      <c r="E37" s="282" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F37" s="282" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G37" s="282" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H37" s="282"/>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21"/>
       <c r="B38" s="149" t="s">
-        <v>1194</v>
+        <v>1181</v>
       </c>
       <c r="C38" s="285" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" s="306" t="n">
-        <f aca="false">'COLECTOR PARAMETROS'!C36*'COLECTOR PARAMETROS'!C40+'COLECTOR PARAMETROS'!C37*'COLECTOR PARAMETROS'!C41</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E38" s="301" t="n">
-        <f aca="false">+$F$20</f>
-        <v>10.0</v>
-      </c>
-      <c r="F38" s="306" t="n">
-        <f aca="false">D38*E38</f>
-        <v>8.3904</v>
-      </c>
-      <c r="G38" s="149" t="s">
-        <v>905</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="D38" s="295"/>
+      <c r="E38" s="290" t="n">
+        <f aca="false">+F26</f>
+        <v>0.36992</v>
+      </c>
+      <c r="F38" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E26</f>
+        <v>0.36992</v>
+      </c>
+      <c r="G38" s="295" t="str">
+        <f aca="false">IF(ABS(E38-F38)&lt;0.0005,"CONFORME","REVISAR")</f>
+        <v>CONFORME</v>
+      </c>
+      <c r="H38" s="295"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="21"/>
-      <c r="B39" s="294" t="s">
-        <v>1175</v>
+      <c r="B39" s="149" t="s">
+        <v>1563</v>
       </c>
       <c r="C39" s="285" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="308" t="n">
-        <f aca="false">SUM(D38:D38)</f>
-        <v>0.83904</v>
-      </c>
-      <c r="E39" s="295"/>
-      <c r="F39" s="296" t="n">
-        <f aca="false">SUM(F38:F38)</f>
-        <v>8.3904</v>
-      </c>
-      <c r="G39" s="295"/>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="294" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B41" s="294"/>
-      <c r="C41" s="294"/>
-      <c r="D41" s="294"/>
-      <c r="E41" s="294"/>
-      <c r="F41" s="294"/>
-      <c r="G41" s="294"/>
-    </row>
-    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="282"/>
-      <c r="B42" s="282" t="s">
-        <v>992</v>
-      </c>
-      <c r="C42" s="282" t="s">
-        <v>151</v>
-      </c>
-      <c r="D42" s="282"/>
-      <c r="E42" s="282" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F42" s="282" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G42" s="282" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21"/>
-      <c r="B43" s="149" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C43" s="285" t="s">
+      <c r="D39" s="295"/>
+      <c r="E39" s="290" t="n">
+        <f aca="false">+F29</f>
+        <v>2.176</v>
+      </c>
+      <c r="F39" s="290" t="n">
+        <f aca="false">'COLECTOR REGISTROS Y TAPAS'!E24</f>
+        <v>2.176</v>
+      </c>
+      <c r="G39" s="295" t="str">
+        <f aca="false">IF(ABS(E39-F39)&lt;0.0005,"CONFORME","REVISAR")</f>
+        <v>CONFORME</v>
+      </c>
+      <c r="H39" s="295"/>
+    </row>
+    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21"/>
+      <c r="B40" s="149" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C40" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="295"/>
-      <c r="E43" s="306" t="n">
-        <f aca="false">+F27</f>
-        <v>101.016</v>
-      </c>
-      <c r="F43" s="306" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E25</f>
-        <v>101.016</v>
-      </c>
-      <c r="G43" s="283" t="str">
-        <f aca="false">IF(ABS(E43-F43)&lt;0.001,"CONFORME","REVISAR")</f>
+      <c r="D40" s="295"/>
+      <c r="E40" s="290" t="n">
+        <f aca="false">+F34</f>
+        <v>169.876</v>
+      </c>
+      <c r="F40" s="290" t="n">
+        <f aca="false">'COLECTOR ACERO'!U33+'COLECTOR REGISTROS Y TAPAS'!E25</f>
+        <v>169.876</v>
+      </c>
+      <c r="G40" s="295" t="str">
+        <f aca="false">IF(ABS(E40-F40)&lt;0.0005,"CONFORME","REVISAR")</f>
         <v>CONFORME</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21"/>
-      <c r="B44" s="149" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C44" s="285" t="s">
-        <v>167</v>
-      </c>
-      <c r="D44" s="295"/>
-      <c r="E44" s="306" t="n">
-        <f aca="false">+F30</f>
-        <v>0.36992</v>
-      </c>
-      <c r="F44" s="306" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E27</f>
-        <v>0.36992</v>
-      </c>
-      <c r="G44" s="283" t="str">
-        <f aca="false">IF(ABS(E44-F44)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21"/>
-      <c r="B45" s="149" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C45" s="285" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="295"/>
-      <c r="E45" s="306" t="n">
-        <f aca="false">+F36</f>
-        <v>173.376</v>
-      </c>
-      <c r="F45" s="306" t="n">
-        <f aca="false">+'COLECTOR ACERO'!I41</f>
-        <v>173.376</v>
-      </c>
-      <c r="G45" s="283" t="str">
-        <f aca="false">IF(ABS(E45-F45)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21"/>
-      <c r="B46" s="149" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C46" s="285" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="295"/>
-      <c r="E46" s="306" t="n">
-        <f aca="false">+F39</f>
-        <v>8.3904</v>
-      </c>
-      <c r="F46" s="306" t="n">
-        <f aca="false">+'COLECTOR REGISTROS Y TAPAS'!E28</f>
-        <v>8.3904</v>
-      </c>
-      <c r="G46" s="283" t="str">
-        <f aca="false">IF(ABS(E46-F46)&lt;0.001,"CONFORME","REVISAR")</f>
-        <v>CONFORME</v>
-      </c>
+      <c r="H40" s="295"/>
+    </row>
+    <row r="42" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="281" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B42" s="281"/>
+      <c r="C42" s="281"/>
+      <c r="D42" s="281"/>
+      <c r="E42" s="281"/>
+      <c r="F42" s="281"/>
+      <c r="G42" s="281"/>
+      <c r="H42" s="281"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C3:H3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C4:H4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A42:H42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -33654,7 +32699,7 @@
         <v>0.00117175005405405</v>
       </c>
       <c r="F40" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G40" s="290" t="n">
@@ -34501,7 +33546,7 @@
         <v>0.001354836</v>
       </c>
       <c r="F40" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G40" s="290" t="n">
@@ -39193,7 +38238,7 @@
         <v>0.00525</v>
       </c>
       <c r="F40" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F76</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F42</f>
         <v>30.93</v>
       </c>
       <c r="G40" s="290" t="n">
@@ -39220,7 +38265,7 @@
         <v>0.000525</v>
       </c>
       <c r="F41" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F77</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F43</f>
         <v>40.68</v>
       </c>
       <c r="G41" s="290" t="n">
@@ -39247,7 +38292,7 @@
         <v>0.000135</v>
       </c>
       <c r="F42" s="290" t="n">
-        <f aca="false">'ACU TAPA REGISTRO'!F79</f>
+        <f aca="false">'ACU TAPA REGISTRO'!F45</f>
         <v>8.33</v>
       </c>
       <c r="G42" s="290" t="n">

--- a/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
+++ b/insumos/metrados_vigentes/METRADO_DRENAJE_MUJERES_VIOLENTADAS.xlsx
@@ -515,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3401" uniqueCount="1568">
   <si>
     <t xml:space="preserve">RESUMEN METRADOS DE DRENAJE PLUVIAL</t>
   </si>
@@ -5227,6 +5227,12 @@
   </si>
   <si>
     <t xml:space="preserve">No hay angulos, soldadura ni pintura: la tapa es ciega de concreto armado (lamina DP-06B rev. 02). El rebaje de asiento y el borde engrosado de la abertura se metran con el concreto de la losa del colector (hoja COLECTOR CONCRETO).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamina DP-06B rev. 02: agarre 0.15 + 2 patas de 0.02 + 2 ganchos de 0.15 (0.49, se toma 0.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGISTROS DE LIMPIEZA Y TAPAS - lamina DP-06B: refuerzo de borde de la abertura, parrilla de la tapa, asas de la tapa ciega (cantidad de registros de la hoja COLECTOR REGISTROS Y TAPAS)</t>
   </si>
 </sst>
 </file>
@@ -12413,7 +12419,7 @@
         <v>57</v>
       </c>
       <c r="E39" s="286" t="s">
-        <v>1488</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25266,7 +25272,7 @@
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="294" t="s">
-        <v>839</v>
+        <v>1567</v>
       </c>
       <c r="B31" s="294"/>
       <c r="C31" s="294"/>
